--- a/docs/SLR_Korpus.xlsx
+++ b/docs/SLR_Korpus.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sintesis &amp; Gap Final" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Peta Teori ke Dimensi" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Konsep Kunci Model" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Paper Inti &amp; Skor" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -484,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L110"/>
+  <dimension ref="A1:J107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -494,11 +495,9 @@
     <col width="7" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="26" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="9" customWidth="1" min="9" max="9"/>
-    <col width="34" customWidth="1" min="10" max="10"/>
-    <col width="60" customWidth="1" min="11" max="11"/>
-    <col width="55" customWidth="1" min="12" max="12"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="60" customWidth="1" min="9" max="9"/>
+    <col width="55" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -539,25 +538,15 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Relevansi</t>
+          <t>Link/DOI</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Kualitas</t>
+          <t>Ringkasan Temuan</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Link/DOI</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Ringkasan Temuan</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Kontribusi terhadap Research Gap</t>
         </is>
@@ -597,23 +586,15 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>6</v>
+          <t>https://doi.org/10.1038/s41598-026-63408-z</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan kerangka condition monitoring dan prognostik untuk blade small-scale wind turbine (SSWT) dengan menggabungkan fitur signal-based (time/frequency domain) dan properti dinamika struktur (natural frequency, mode shape curvature, transmissibility). Tiga Health Index (PCA-based, Mahalanobis, autoencoder) difusi menjadi Combined Health Index (CHI) berbobot entropy. RUL diestimasi dengan pemodelan degradasi berbasis Weibull dan prediksi sekuensial LSTM/GRU, divalidasi pada tiga kondisi blade: healthy (C), degradasi global (L), dan degradasi lokal (R).</t>
+        </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1038/s41598-026-63408-z</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan kerangka condition monitoring dan prognostik untuk blade small-scale wind turbine (SSWT) dengan menggabungkan fitur signal-based (time/frequency domain) dan properti dinamika struktur (natural frequency, mode shape curvature, transmissibility). Tiga Health Index (PCA-based, Mahalanobis, autoencoder) difusi menjadi Combined Health Index (CHI) berbobot entropy. RUL diestimasi dengan pemodelan degradasi berbasis Weibull dan prediksi sekuensial LSTM/GRU, divalidasi pada tiga kondisi blade: healthy (C), degradasi global (L), dan degradasi lokal (R).</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>Menunjukkan pola fusi HI multi-indikator + estimasi RUL ganda (Weibull statistis + LSTM data-driven) dengan pelaporan interval bootstrap - berguna sebagai contoh strateji prognostik hybrid; namun pemodelan Weibull dangkal (tanpa pencensoringan) dan domainnya blade turbin angin, bukan membran/RO.</t>
         </is>
@@ -653,23 +634,15 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.1016/j.ress.2026.113080</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Artikel ini mengusulkan kerangka berbasis kausalitas untuk memodelkan data degradasi dependen pada sistem dengan beberapa indikator performa. Setiap indikator dimodelkan sebagai proses Wiener univariat dengan multi-sumber ketidakpastian, hubungan sebab-akibat antar jalur degradasi ditemukan via algoritma Stable-PC, dan efek kausal dikuantifikasi dengan neural network sadar-ketidakpastian lalu digabung dalam kerangka Bayes. Reliabilitas sistem dan RUL diturunkan melalui simulasi Monte Carlo dan divalidasi pada dataset C-MAPSS.</t>
+        </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.ress.2026.113080</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>Artikel ini mengusulkan kerangka berbasis kausalitas untuk memodelkan data degradasi dependen pada sistem dengan beberapa indikator performa. Setiap indikator dimodelkan sebagai proses Wiener univariat dengan multi-sumber ketidakpastian, hubungan sebab-akibat antar jalur degradasi ditemukan via algoritma Stable-PC, dan efek kausal dikuantifikasi dengan neural network sadar-ketidakpastian lalu digabung dalam kerangka Bayes. Reliabilitas sistem dan RUL diturunkan melalui simulasi Monte Carlo dan divalidasi pada dataset C-MAPSS.</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>Memberikan contoh bagaimana struktur kausalitas eksplisit dapat memperbaiki model degradasi dependen dan akurasi RUL dibanding pendekatan korelasi (kopula/kovarians). Bagi tesis, ini menawarkan alternatif/model acuan pemodelan dependensi multi-indikator yang dapat diadaptasi ke jalur fouling membran, sekaligus memperlihatkan teknik penggabungan prior proses stokastik dengan model pembelajaran.</t>
         </is>
@@ -709,23 +682,15 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.3390/s26061915</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Tinjauan sistematis tentang model survival (time-to-event) untuk predictive maintenance dan estimasi RUL pada jaringan energi pintar berbasis sensor (distribusi listrik + district heating). Artikel menyusun taksonomi model non-parametrik, semi-parametrik, parametrik, dan learning-based; memetakannya ke tipe data (kovariat statis vs time-varying), asumsi (proportional hazards vs distribusi parametrik), dan keluaran berorientasi keputusan (risk ranking, horizon failure probability, distribusi RUL). Evaluasi juga disintesiskan via metrik diskriminasi (C-index, AUC), kalibrasi, akurasi RUL sadar-censoring, dan proper scoring rules (Brier/IBS).</t>
+        </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/s26061915</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Tinjauan sistematis tentang model survival (time-to-event) untuk predictive maintenance dan estimasi RUL pada jaringan energi pintar berbasis sensor (distribusi listrik + district heating). Artikel menyusun taksonomi model non-parametrik, semi-parametrik, parametrik, dan learning-based; memetakannya ke tipe data (kovariat statis vs time-varying), asumsi (proportional hazards vs distribusi parametrik), dan keluaran berorientasi keputusan (risk ranking, horizon failure probability, distribusi RUL). Evaluasi juga disintesiskan via metrik diskriminasi (C-index, AUC), kalibrasi, akurasi RUL sadar-censoring, dan proper scoring rules (Brier/IBS).</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>Menjadi peta metodologis komprehensif untuk pemilihan model survival berbasis censoring dan kuantifikasi ketidakpastian - persis kerangka metode yang akan dipakai tesis - serta menegaskan bahwa censoring/truncation adalah karakteristik inti, bukan detail pinggiran; namun tidak membahas domain membran/RO.</t>
         </is>
@@ -765,23 +730,15 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.1038/s41598-026-65271-4</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Studi menyajikan kerangka predictive maintenance yang dapat diinterpretasi di mana Cox proportional hazards (Cox-PH) dipakai untuk mengidentifikasi variabel operasional paling terkait risiko kegagalan dan memandu pembangunan model data-driven. Divvalidasi pada dataset riil MetroPT-3 (kompresor udara kereta) dengan tanggal kegagalan dari operator untuk membentuk label event biner dan target proxy RUL. Empat keluarga model (ANN, RF, XGBoost, LSTM) dievaluasi untuk dua tugas: klasifikasi event kegagalan dan regresi proxy RUL. Model sekuensial (LSTM) unggul untuk deteksi event, sedangkan model pohon nonlinier lebih robust untuk proxy RUL.</t>
+        </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1038/s41598-026-65271-4</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>Studi menyajikan kerangka predictive maintenance yang dapat diinterpretasi di mana Cox proportional hazards (Cox-PH) dipakai untuk mengidentifikasi variabel operasional paling terkait risiko kegagalan dan memandu pembangunan model data-driven. Divvalidasi pada dataset riil MetroPT-3 (kompresor udara kereta) dengan tanggal kegagalan dari operator untuk membentuk label event biner dan target proxy RUL. Empat keluarga model (ANN, RF, XGBoost, LSTM) dievaluasi untuk dua tugas: klasifikasi event kegagalan dan regresi proxy RUL. Model sekuensial (LSTM) unggul untuk deteksi event, sedangkan model pohon nonlinier lebih robust untuk proxy RUL.</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>Sangat relevan ke tesis: menggabungkan Cox-PH survival analysis (hazard/censoring) sebagai lapisan seleksi fitur terarah dengan machine learning (ANN/RF/XGBoost/LSTM) untuk kegagalan dan RUL, ditambah implikasi keputusan pemeliharaan (kebijakan alarm). Namun domainnya kompresor kereta, bukan membran/RO, dan tanpa komponen Weibull eksplisit.</t>
         </is>
@@ -821,23 +778,15 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>7</v>
+          <t>https://doi.org/10.3390/s26092592</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan Bayesian convolutional neural network (BCNN) dengan unit dual-output untuk prediksi interval RUL. Parameter CNN diubah menjadi variabel acak dan dilatih dengan Bayes-by-backprop untuk menangkap epistemic uncertainty, sementara struktur dual-output memodelkan aleatoric uncertainty heteroskedastik melalui likelihood Gaussian dan loss negative log-likelihood. Validasi pada dataset IEEE PHM 2012 menunjukkan akurasi titik dan kuantifikasi ketidakpastian yang lebih baik daripada metode uncertainty-aware lain (PCIP 0,9628).</t>
+        </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/s26092592</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan Bayesian convolutional neural network (BCNN) dengan unit dual-output untuk prediksi interval RUL. Parameter CNN diubah menjadi variabel acak dan dilatih dengan Bayes-by-backprop untuk menangkap epistemic uncertainty, sementara struktur dual-output memodelkan aleatoric uncertainty heteroskedastik melalui likelihood Gaussian dan loss negative log-likelihood. Validasi pada dataset IEEE PHM 2012 menunjukkan akurasi titik dan kuantifikasi ketidakpastian yang lebih baik daripada metode uncertainty-aware lain (PCIP 0,9628).</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>Memberikan kerangka probabilistik terpadu untuk memisahkan aleatoric dan epistemic uncertainty pada prediksi RUL - berguna bagi komponen deep learning + kuantifikasi ketidakpastian tesis. Namun tidak menangani data tersensor dan domainnya bearing, bukan membran.</t>
         </is>
@@ -877,23 +826,15 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode+Domain</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>7</v>
+          <t>https://doi.org/10.1109/tim.2026.3684677</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan kerangka multisensor forecasting-based augmentation (MSFA) untuk RUL aero engine pada kondisi data tak seimbang (long-tail). Model multiscale-and-multicomponent transformer (MSMCT) meramalkan segmen degradasi lanjut untuk melengkapi data tersensor (censored), selektor berbasis Wasserstein distance menyaring sampel hasil augmentasi yang konsisten distribusinya, dan dynamic graph spatio-temporal network (DGSTN) dilatih pada dataset teraugmentasi untuk prediksi RUL. Pada C-MAPSS, metode unggul di semua rasio data (10-30%) dengan RMSE FD002 ~12,12 dan improvement 20,3% (RMSE) / 60,3% (Score) dibanding terbaik kedua.</t>
+        </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/tim.2026.3684677</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan kerangka multisensor forecasting-based augmentation (MSFA) untuk RUL aero engine pada kondisi data tak seimbang (long-tail). Model multiscale-and-multicomponent transformer (MSMCT) meramalkan segmen degradasi lanjut untuk melengkapi data tersensor (censored), selektor berbasis Wasserstein distance menyaring sampel hasil augmentasi yang konsisten distribusinya, dan dynamic graph spatio-temporal network (DGSTN) dilatih pada dataset teraugmentasi untuk prediksi RUL. Pada C-MAPSS, metode unggul di semua rasio data (10-30%) dengan RMSE FD002 ~12,12 dan improvement 20,3% (RMSE) / 60,3% (Score) dibanding terbaik kedua.</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>Sangat relevan bagi tesis: secara eksplisit menangani data tersensor/terpotong (censored data) dan ketidakseimbangan data dengan melengkapi segmen degradasi lanjut via forecasting, lalu memvalidasi distribusi (Wasserstein/KL). Menyediakan pola alternatif penanganan penyensoran (forecasting-completion) selain survival analysis, plus arsitektur graph spatio-temporal.</t>
         </is>
@@ -933,23 +874,15 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>Inti-Domain</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.1016/j.ceja.2026.101217</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan model prediktif berbasis AI untuk mengestimasi RUL membran reverse osmosis (RO), didefinisikan sebagai volume air (m3) yang dapat diproduksi hingga membran mencapai ambang kinerja yang memicu clean-in-place (CIP). Model memakai 20 parameter operasional mentah (SDI, suhu, kecepatan pompa, tekanan, konduktivitas, turbiditas) ditambah 14 fitur turunan dari 2999 catatan harian (Jan 2021 - Agu 2025) sebuah pabrik desalinasi RO di UAE. Random Forest terbaik (R2=0,984; RMSE=0,136; MAE=0,0997) mengalahkan XGBoost (0,977), CART (0,936), dan LR (0,655); SHAP mengidentifikasi SDI maksimum, suhu maksimum, usia membran, dan kecepatan pompa PX sebagai prediktor utama.</t>
+        </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.ceja.2026.101217</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan model prediktif berbasis AI untuk mengestimasi RUL membran reverse osmosis (RO), didefinisikan sebagai volume air (m3) yang dapat diproduksi hingga membran mencapai ambang kinerja yang memicu clean-in-place (CIP). Model memakai 20 parameter operasional mentah (SDI, suhu, kecepatan pompa, tekanan, konduktivitas, turbiditas) ditambah 14 fitur turunan dari 2999 catatan harian (Jan 2021 - Agu 2025) sebuah pabrik desalinasi RO di UAE. Random Forest terbaik (R2=0,984; RMSE=0,136; MAE=0,0997) mengalahkan XGBoost (0,977), CART (0,936), dan LR (0,655); SHAP mengidentifikasi SDI maksimum, suhu maksimum, usia membran, dan kecepatan pompa PX sebagai prediktor utama.</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>Menjadi salah satu dari sangat sedikit studi yang memprediksi langsung RUL membran RO/desalinasi dengan data operasional pabrik nyata dan mengaitkannya dengan penjadwalan CIP - inti domain tesis; namun tidak memakai survival analysis maupun penanganan data tersensor.</t>
         </is>
@@ -989,23 +922,15 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>Konteks</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.1016/j.advmem.2026.100219</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Tinjauan kritis yang membedakan dan mengintegrasikan tiga tingkat digitalisasi untuk membran: model hibrida (fisika + ML), digital shadow (DS, aliran data satu arah), dan digital twin (DT, loop tertutup dua arah). Review menyintesis aplikasi pada desalinasi/pengolahan air, MBR, separasi gas (CO2/H2/O2/N2), catalytic membrane reactor, dan PEMFC; menyoroti peran CFD untuk menghasilkan data sintetis, kuantifikasi ketidakpastian (mis. Stochastic Greybox Modeling and Control), serta DSS pemeliharaan prediktif membran (mis. optimasi strategi restorasi elemen RO dengan pengurangan penggantian 50-80 %).</t>
+        </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.advmem.2026.100219</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>Tinjauan kritis yang membedakan dan mengintegrasikan tiga tingkat digitalisasi untuk membran: model hibrida (fisika + ML), digital shadow (DS, aliran data satu arah), dan digital twin (DT, loop tertutup dua arah). Review menyintesis aplikasi pada desalinasi/pengolahan air, MBR, separasi gas (CO2/H2/O2/N2), catalytic membrane reactor, dan PEMFC; menyoroti peran CFD untuk menghasilkan data sintetis, kuantifikasi ketidakpastian (mis. Stochastic Greybox Modeling and Control), serta DSS pemeliharaan prediktif membran (mis. optimasi strategi restorasi elemen RO dengan pengurangan penggantian 50-80 %).</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>Memberikan kerangka konseptual domain untuk keputusan pemeliharaan/penggantian membran berbasis digital twin dan DSS, serta menempatkan kuantifikasi ketidakpastian sebagai prioritas; tidak memakai survival/pencensoringan maupun membangun model RUL survivals.</t>
         </is>
@@ -1045,23 +970,15 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>Konteks</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.1016/j.jwpe.2026.110543</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Tinjauan kritis yang mengembangkan kerangka machine learning selaras-mekanisme (mechanism-aligned) untuk prediksi fouling dan kontrol proses pada membran UF, NF, dan RO. Kerangka menghubungkan mekanisme fouling dominan dengan struktur data, arsitektur model, dan aksi kontrol: GRU untuk sinyal hidraulik frekuensi tinggi UF (regulasi fluks, backwash), XGBoost terregularisasi untuk variabel kualitas air multikolinear NF (dosis koagulan, pH), dan CNN-GRU-SHAP untuk biofouling/scaling RO yang heterogen spasial (antiscalant, pH, pembersihan tertarget, biocide). Tinjauan juga membahas benchmarking, noise SCADA, kelangkaan data, fallback control, edge deployment, dan interpretabilitas operator.</t>
+        </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.jwpe.2026.110543</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>Tinjauan kritis yang mengembangkan kerangka machine learning selaras-mekanisme (mechanism-aligned) untuk prediksi fouling dan kontrol proses pada membran UF, NF, dan RO. Kerangka menghubungkan mekanisme fouling dominan dengan struktur data, arsitektur model, dan aksi kontrol: GRU untuk sinyal hidraulik frekuensi tinggi UF (regulasi fluks, backwash), XGBoost terregularisasi untuk variabel kualitas air multikolinear NF (dosis koagulan, pH), dan CNN-GRU-SHAP untuk biofouling/scaling RO yang heterogen spasial (antiscalant, pH, pembersihan tertarget, biocide). Tinjauan juga membahas benchmarking, noise SCADA, kelangkaan data, fallback control, edge deployment, dan interpretabilitas operator.</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>Menghubungkan prediksi fouling (termasuk target seperti 'probability of crossing a cleaning threshold' dan 'expected time to CIP') dengan aksi kontrol/pemeliharaan pada membran RO - sangat relevan untuk konteks domain tesis; namun tidak memakai survival analysis/censoring dan tidak memprediksi RUL secara eksplisit.</t>
         </is>
@@ -1101,23 +1018,15 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>Inti-Domain</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.1038/s41598-026-54120-z</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Studi menggabungkan model finite-element reduced-order (ROM) transport dan resistansi fouling dengan kerangka data-driven yang memetakan metadata eksperimen ke perilaku penurunan fluks lintas data. Dari 112 dataset (berbagai membran, minyak, kondisi operasi), ROM mereproduksi trajektori fluks dengan R2 rata-rata ~0,95; prediksi tersegmentasi (early/mid/late) memberi MAE 0,079-0,14 pada grouped cross-validation. Validasi publikasi-level (holdout studi tak terlihat) menunjukkan MAE meningkat ~2x, mengungkap 'cross-study generalization penalty': keterbatasan prediksi lebih disebabkan kelengkapan metadata dan variabilitas antar-studi, bukan kapasitas model. Diusulkan checklist metadata minimal untuk model fouling yang reproducible.</t>
+        </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1038/s41598-026-54120-z</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>Studi menggabungkan model finite-element reduced-order (ROM) transport dan resistansi fouling dengan kerangka data-driven yang memetakan metadata eksperimen ke perilaku penurunan fluks lintas data. Dari 112 dataset (berbagai membran, minyak, kondisi operasi), ROM mereproduksi trajektori fluks dengan R2 rata-rata ~0,95; prediksi tersegmentasi (early/mid/late) memberi MAE 0,079-0,14 pada grouped cross-validation. Validasi publikasi-level (holdout studi tak terlihat) menunjukkan MAE meningkat ~2x, mengungkap 'cross-study generalization penalty': keterbatasan prediksi lebih disebabkan kelengkapan metadata dan variabilitas antar-studi, bukan kapasitas model. Diusulkan checklist metadata minimal untuk model fouling yang reproducible.</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>Sangat relevan pada sumbu domain (fouling membran) dan sumbu transfer lintas-studi (small-data/domain shift) tesis, serta menegaskan pentingnya keterwakilan data; tidak memakai survival/pencensoringan dan berfokus pada MF/UF oil-water, bukan RO.</t>
         </is>
@@ -1157,23 +1066,15 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>Inti-Domain</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.1038/s41598-026-42910-4</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan kerangka predictive maintenance dua tahap yang berorientasi keputusan biaya, menghubungkan prediksi RUL per komponen dengan optimasi jadwal perawatan. Tahap pertama memakai LSTM untuk memprediksi RUL tiap komponen dan WGAN-GP untuk membangkitkan data run-to-failure sintetis guna mengatasi kelangkaan data kegagalan; tahap kedua mengelompokkan komponen dengan degradasi mirip memakai DBSCAN, lalu memilih ambang waktu perawatan optimal per klaster lewat grid search atas fungsi biaya (preventif, korektif, downtime) dengan proxy risiko berbasis CDF. Validasi pada sistem pabrik air minum kemasan (16 komponen, 3.319 jam operasi) menunjukkan jadwal berbasis klaster menurunkan kegagalan korektif dan biaya dibanding strategi random dan fixed-percentile.</t>
+        </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1038/s41598-026-42910-4</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan kerangka predictive maintenance dua tahap yang berorientasi keputusan biaya, menghubungkan prediksi RUL per komponen dengan optimasi jadwal perawatan. Tahap pertama memakai LSTM untuk memprediksi RUL tiap komponen dan WGAN-GP untuk membangkitkan data run-to-failure sintetis guna mengatasi kelangkaan data kegagalan; tahap kedua mengelompokkan komponen dengan degradasi mirip memakai DBSCAN, lalu memilih ambang waktu perawatan optimal per klaster lewat grid search atas fungsi biaya (preventif, korektif, downtime) dengan proxy risiko berbasis CDF. Validasi pada sistem pabrik air minum kemasan (16 komponen, 3.319 jam operasi) menunjukkan jadwal berbasis klaster menurunkan kegagalan korektif dan biaya dibanding strategi random dan fixed-percentile.</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>Menunjukkan jalur lengkap dari prediksi RUL sampai keputusan perawatan yang sadar-biaya dan sadar-risiko, plus penanganan data kecil via GAN; sangat relevan sebagai cetak biru DSS, tetapi tidak memakai survival/pencensoringan nyata (penulis sendiri menyebutnya sebagai future work) dan domainnya bukan membran.</t>
         </is>
@@ -1213,23 +1114,15 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.1109/tase.2025.3640217</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan Bayesian LSTM-SURV, metode yang mengintegrasikan survival analysis (SA) dengan jaringan saraf untuk memodelkan hubungan non-linear antara sinyal degradasi multi-sensor dan RUL dengan adanya data tersensor. Alih-alih memprediksi nilai RUL langsung, model mengasumsikan masa pakai mengikuti distribusi Weibull dan memakai fungsi loss yang diturunkan dari likelihood SA agar memanfaatkan data lengkap dan tersensor; prosedur Bayesian mentransfer informasi dari unit latih ke unit uji. Diuji pada data simulasi dan dataset gas turbine C-MAPSS, model mengungguli TSNN dan DeepSurv (RMSE terbaik 4,420) serta mengkuantifikasi ketidakpastian via interval 90%.</t>
+        </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/tase.2025.3640217</t>
-        </is>
-      </c>
-      <c r="K13" s="3" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan Bayesian LSTM-SURV, metode yang mengintegrasikan survival analysis (SA) dengan jaringan saraf untuk memodelkan hubungan non-linear antara sinyal degradasi multi-sensor dan RUL dengan adanya data tersensor. Alih-alih memprediksi nilai RUL langsung, model mengasumsikan masa pakai mengikuti distribusi Weibull dan memakai fungsi loss yang diturunkan dari likelihood SA agar memanfaatkan data lengkap dan tersensor; prosedur Bayesian mentransfer informasi dari unit latih ke unit uji. Diuji pada data simulasi dan dataset gas turbine C-MAPSS, model mengungguli TSNN dan DeepSurv (RMSE terbaik 4,420) serta mengkuantifikasi ketidakpastian via interval 90%.</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr">
         <is>
           <t>Menyediakan kerangka inti-metode tesis: analisis survival + jaringan saraf (LSTM) yang menangani data tersensor sekaligus mengkuantifikasi ketidakpastian prediksi RUL - kombinasi yang persis dibutuhkan tesis untuk membran RO dengan data lapangan tersensor.</t>
         </is>
@@ -1269,23 +1162,15 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.1038/s41598-025-22866-7</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Studi membangun kerangka prediksi RUL untuk electric drive system (EDS) dengan banyak mode kegagalan. Composite health indicator dibentuk dari fusi kontribusi kerusakan tiap komponen memakai entropy weight method, lalu lintasan degradasi dimodelkan secara nonlinier eksponensial dan dikoreksi dengan acceleration factor antara spektrum uji dipercepat dan spektrum pengguna. Parameter diestimasi dengan EM dan diperbarui secara Bayesian untuk memprediksi RUL beserta kuantifikasi ketidakpastian (distribusi RUL, interval 95%).</t>
+        </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1038/s41598-025-22866-7</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>Studi membangun kerangka prediksi RUL untuk electric drive system (EDS) dengan banyak mode kegagalan. Composite health indicator dibentuk dari fusi kontribusi kerusakan tiap komponen memakai entropy weight method, lalu lintasan degradasi dimodelkan secara nonlinier eksponensial dan dikoreksi dengan acceleration factor antara spektrum uji dipercepat dan spektrum pengguna. Parameter diestimasi dengan EM dan diperbarui secara Bayesian untuk memprediksi RUL beserta kuantifikasi ketidakpastian (distribusi RUL, interval 95%).</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>Contoh mutakhir pemodelan degradasi nonlinier + estimasi EM + pembaruan Bayesian yang menghasilkan distribusi RUL dan interval kepercayaan (CIC) per pengguna - pola kuantifikasi ketidakpastian yang berguna bagi tesis; namun tidak memodelkan data tersensor/survival (Weibull/hazard) dan domainnya sistem penggerak listrik, bukan membran.</t>
         </is>
@@ -1325,23 +1210,15 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Inti-Domain</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.1016/j.geits.2025.100291</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengembangkan Physics-Informed Neural Network (PINN) berbasis LSTM untuk memprediksi trajektori degradasi dan RUL supercapacitor, dengan menyisipkan persamaan penuaan empiris (SOH = A·ln(cycle) + B) ke dalam fungsi loss. Bobot penyeimbang antara loss data dan loss fisika (lambda) dioptimasi secara adaptif menggunakan Bayesian optimization.</t>
+        </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.geits.2025.100291</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengembangkan Physics-Informed Neural Network (PINN) berbasis LSTM untuk memprediksi trajektori degradasi dan RUL supercapacitor, dengan menyisipkan persamaan penuaan empiris (SOH = A·ln(cycle) + B) ke dalam fungsi loss. Bobot penyeimbang antara loss data dan loss fisika (lambda) dioptimasi secara adaptif menggunakan Bayesian optimization.</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>Menunjukkan integrasi pengetahuan fisika dan deep learning dapat memangkas kebutuhan data training secara drastis (hanya 1-5% siklus hidup) sehingga relevan untuk tesis RUL membran yang berhadapan dengan kelangkaan data degradasi; namun belum menangani kelayakan/handling data tersensor maupun ketidakpastian prediksi RUL.</t>
         </is>
@@ -1381,23 +1258,15 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>7</v>
+          <t>https://doi.org/10.3390/s25020554</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Studi ini mengusulkan metode prediksi RUL bantalan gelinding berbasis CBAM-CNN-LSTM: sinyal vibrasi diproses FFT ke domain frekuensi, fitur diekstraksi CNN, dibobot oleh CBAM (channel attention lalu spatial attention secara seri), dan dependensi temporalnya dipelajari LSTM secara end-to-end dengan label RUL dinormalisasi ke rentang (0,1). Model diuji pada dataset publik PHM2012 dengan enam bantalan uji (1-3, 1-4, 1-5, 1-7, 2-3, 2-6) dan mengungguli CNN-LSTM, ECA-CNN-LSTM, serta dua metode literatur. Klaim utama: penurunan MSE 53%, MAE 16,87% (abstrak) / 9,75% (kesimpulan), dan RMSE 31,68% dibanding metode pembanding.</t>
+        </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/s25020554</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>Studi ini mengusulkan metode prediksi RUL bantalan gelinding berbasis CBAM-CNN-LSTM: sinyal vibrasi diproses FFT ke domain frekuensi, fitur diekstraksi CNN, dibobot oleh CBAM (channel attention lalu spatial attention secara seri), dan dependensi temporalnya dipelajari LSTM secara end-to-end dengan label RUL dinormalisasi ke rentang (0,1). Model diuji pada dataset publik PHM2012 dengan enam bantalan uji (1-3, 1-4, 1-5, 1-7, 2-3, 2-6) dan mengungguli CNN-LSTM, ECA-CNN-LSTM, serta dua metode literatur. Klaim utama: penurunan MSE 53%, MAE 16,87% (abstrak) / 9,75% (kesimpulan), dan RMSE 31,68% dibanding metode pembanding.</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
         <is>
           <t>Bagi tesis, paper ini menjadi bukti bahwa arsitektur CNN + atensi hibrida (channel+spatial) + LSTM adalah baseline kuat untuk point-prediction RUL di domain mekanikal, namun sama sekali tidak menangani data tersensor maupun survival analysis. Ini memperkuat gap tesis: integrasi survival analysis (censoring/Weibull/hazard) dengan deep learning masih terbuka, terlebih untuk objek membran/RO.</t>
         </is>
@@ -1437,23 +1306,15 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.1016/j.inffus.2025.102972</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Studi menggabungkan Bayesian LSTM (B-LSTM) dengan counterfactual explanations (CFE) dari DiCE untuk (1) meningkatkan interpretabilitas estimasi RUL dan (2) meningkatkan akurasi melalui augmentasi data. Dua jenis CFE dihasilkan: RUL CFE (skenario yang menaikkan/menurunkan RUL) dan Uncertainty CFE (skenario yang menurunkan ketidakpastian prediksi). Pada dataset C-MAPSS FD001, model yang diaugmentasi dengan Uncertainty CFE terbaik (RMSE 8,47 vs baseline 9,56; akurasi alpha=0,2 79% vs 74%).</t>
+        </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.inffus.2025.102972</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>Studi menggabungkan Bayesian LSTM (B-LSTM) dengan counterfactual explanations (CFE) dari DiCE untuk (1) meningkatkan interpretabilitas estimasi RUL dan (2) meningkatkan akurasi melalui augmentasi data. Dua jenis CFE dihasilkan: RUL CFE (skenario yang menaikkan/menurunkan RUL) dan Uncertainty CFE (skenario yang menurunkan ketidakpastian prediksi). Pada dataset C-MAPSS FD001, model yang diaugmentasi dengan Uncertainty CFE terbaik (RMSE 8,47 vs baseline 9,56; akurasi alpha=0,2 79% vs 74%).</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
         <is>
           <t>Menyediakan kerangka kuantifikasi ketidakpastian (posterior Bayesian) sekaligus menjelaskan keterkaitan aksi pemeliharaan dengan perubahan RUL secara kausal-kontrafaktual, inti bagi DSS tesis. Namun tidak memakai survival/penyensoran eksplisit dan tidak menyentuh domain membran.</t>
         </is>
@@ -1493,23 +1354,15 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Konteks</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>7</v>
+          <t>https://doi.org/10.3390/w17081169</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Artikel ini adalah tinjauan komprehensif penerapan kecerdasan buatan (AI) pada pengolahan air dan desalinasi, mencakup machine learning, neural network, dan genetic algorithm untuk prediksi, optimasi proses, serta deteksi kesalahan dan pemeliharaan prediktif. Studi melaporkan AI menurunkan konsumsi energi hingga ~50% (klaim abstrak) dan mendukung pemeliharaan prediktif untuk meminimalkan downtime, dengan studi kasus pada sistem RO, MSF, dan ADD yang ditenagai energi terbarukan. Penulis mengidentifikasi tantangan data, daya komputasi, dan interpretabilitas model.</t>
+        </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/w17081169</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>Artikel ini adalah tinjauan komprehensif penerapan kecerdasan buatan (AI) pada pengolahan air dan desalinasi, mencakup machine learning, neural network, dan genetic algorithm untuk prediksi, optimasi proses, serta deteksi kesalahan dan pemeliharaan prediktif. Studi melaporkan AI menurunkan konsumsi energi hingga ~50% (klaim abstrak) dan mendukung pemeliharaan prediktif untuk meminimalkan downtime, dengan studi kasus pada sistem RO, MSF, dan ADD yang ditenagai energi terbarukan. Penulis mengidentifikasi tantangan data, daya komputasi, dan interpretabilitas model.</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>Memberi peta lanskap penerapan AI di desalinasi/RO dan menegaskan bahwa pemeliharaan prediktif serta prediksi umur/penyumbatan membran adalah area kunci, sekaligus menyoroti kelangkaan data, transparansi pelaporan, dan ketiadaan studi jangka panjang. Relevan ke tesis sebagai justifikasi domain dan celah: prediksi RUL membran berbasis survival dengan data tersensor belum tercakup dalam tinjauan ini.</t>
         </is>
@@ -1549,23 +1402,15 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>7</v>
+          <t>https://doi.org/10.1109/jsen.2024.3402660</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Studi memprediksi RUL bantalan utama (main bearing) turbin angin lepas pantai menggunakan data getaran historis nyata. Indeks kondisi diekstraksi dari prinsip sideband energy ratio (SER) di sekitar frekuensi meshing gearbox, lalu LSTM yang dioptimalkan tree-seed algorithm (TSA-LSTM) memodelkan tren degradasi; RUL diperoleh dari pencocokan eksponensial indeks OM/IM terhadap first prognostic time (FPT). Model mencapai MAPE &lt; 0,228 dan RMSE &lt; 0,014 dan mengungguli LSTM dasar, PSO-LSTM, dan Random Forest.</t>
+        </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/jsen.2024.3402660</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>Studi memprediksi RUL bantalan utama (main bearing) turbin angin lepas pantai menggunakan data getaran historis nyata. Indeks kondisi diekstraksi dari prinsip sideband energy ratio (SER) di sekitar frekuensi meshing gearbox, lalu LSTM yang dioptimalkan tree-seed algorithm (TSA-LSTM) memodelkan tren degradasi; RUL diperoleh dari pencocokan eksponensial indeks OM/IM terhadap first prognostic time (FPT). Model mencapai MAPE &lt; 0,228 dan RMSE &lt; 0,014 dan mengungguli LSTM dasar, PSO-LSTM, dan Random Forest.</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>Memberi contoh konkret pipeline RUL berbasis deep learning pada data getaran nyata dengan ekstraksi fitur fisik (SER) dan optimasi metaheuristik, serta ambang alarm berjenjang. Relevan bagi tesis sebagai pembanding metode RUL DL, namun tanpa sumbu survival/penyensoran maupun domain membran.</t>
         </is>
@@ -1605,23 +1450,15 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Konteks</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.1016/j.jwpe.2024.106532</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Tinjauan bibliometrik (PRISMA, Scopus/Web of Science, 2013-2023) atas penerapan AI pada proses separasi membran, mencakup MF, UF, NF, RO, FO, MBR, dan MD. Review memetakan algoritma (ANN dominan &gt;150 penggunaan; RF dan SVM paling banyak di ML), rata-rata akurasi R2 per algoritma (mis. CNN ~0,98; ANN ~0,94; LR/MLR ~0,58), serta membahas fouling, optimasi proses, kendali real-time, dan tantangan keterbatasan data serta interpretabilitas.</t>
+        </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.jwpe.2024.106532</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>Tinjauan bibliometrik (PRISMA, Scopus/Web of Science, 2013-2023) atas penerapan AI pada proses separasi membran, mencakup MF, UF, NF, RO, FO, MBR, dan MD. Review memetakan algoritma (ANN dominan &gt;150 penggunaan; RF dan SVM paling banyak di ML), rata-rata akurasi R2 per algoritma (mis. CNN ~0,98; ANN ~0,94; LR/MLR ~0,58), serta membahas fouling, optimasi proses, kendali real-time, dan tantangan keterbatasan data serta interpretabilitas.</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>Memetakan lanskap AI untuk membran (termasuk RO dan prediksi fouling), berguna sebagai konteks pemilihan metode; tidak memakai survival/pencensoringan, tidak membangun model RUL, dan tidak membangun keputusan pemeliharaan.</t>
         </is>
@@ -1661,23 +1498,15 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Konteks</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="n">
-        <v>6</v>
+          <t>https://doi.org/10.1016/j.jwpe.2024.106479</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>Studi memprediksi Silt Density Index (SDI) - indikator potensi fouling partikulat pada pra-perlakuan air laut untuk reverse osmosis (RO) - memakai Gradient Boosting (GB) yang hyperparameternya dioptimasi dengan Salp Swarm Algorithm (GBSSA). Fitur input tunggal adalah tekanan harian (bar) tahap pra-perlakuan; targetnya SDI harian. Data diambil dari dua plant desalinasi di Aljazair barat (Benisaf dan El Mactaa) selama satu bulan (30 hari, Tabel 3). Tiga varian dibandingkan: GB standar, GB+PSO (GBPSO), dan GB+SSA (GBSSA). Preprocessing: interpolasi linear untuk data hilang, robust Z-score (buang &gt;3 SD), normalisasi [0,1], split acak 70/30 latih-uji. GBSSA terbaik pada kedua plant; tidak ada pemodelan RUL, survival analysis, censoring, maupun kuantifikasi ketidakpastian.</t>
+        </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.jwpe.2024.106479</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>Studi memprediksi Silt Density Index (SDI) - indikator potensi fouling partikulat pada pra-perlakuan air laut untuk reverse osmosis (RO) - memakai Gradient Boosting (GB) yang hyperparameternya dioptimasi dengan Salp Swarm Algorithm (GBSSA). Fitur input tunggal adalah tekanan harian (bar) tahap pra-perlakuan; targetnya SDI harian. Data diambil dari dua plant desalinasi di Aljazair barat (Benisaf dan El Mactaa) selama satu bulan (30 hari, Tabel 3). Tiga varian dibandingkan: GB standar, GB+PSO (GBPSO), dan GB+SSA (GBSSA). Preprocessing: interpolasi linear untuk data hilang, robust Z-score (buang &gt;3 SD), normalisasi [0,1], split acak 70/30 latih-uji. GBSSA terbaik pada kedua plant; tidak ada pemodelan RUL, survival analysis, censoring, maupun kuantifikasi ketidakpastian.</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>Mengusulkan hibrida baru GBSSA (Gradient Boosting + Salp Swarm Algorithm) untuk prediksi SDI pada sistem desalinasi; melakukan tuning hyperparameter GB (learning rate, jumlah pohon, kedalaman) dengan SSA berobjektif MAE; membandingkan secara sistematis GB vs GBPSO vs GBSSA pada dua plant desalinasi nyata; menunjukkan bahwa sensor tekanan yang murah/sederhana (tanpa sensor kompleks dan intervensi manual berlebih) cukup untuk memprediksi SDI; menghubungkan akurasi prediksi SDI dengan keputusan operasional dan jadwal pembersihan membran (manajemen fouling).</t>
         </is>
@@ -1717,23 +1546,15 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Konteks</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>7</v>
+          <t>https://doi.org/10.1109/jiot.2024.3376715</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>Artikel ini membangun kerangka penjadwalan pemeliharaan prediktif berbasis prediksi RUL untuk mesin pesawat. Prediksi RUL dilakukan oleh model ensemble 1-D CNN dan Bi-LSTM dengan attention (BO-CNN-Bi-LSTM-AM) yang hyperparameter-nya dioptimasi Bayesian optimization; ketika RUL melampaui ambang alarm, tugas penjadwalan dipicu. Penjadwalan banyak mesin ke beberapa pusat perawatan diformulasikan sebagai MILP untuk meminimalkan waktu penyelesaian pemeliharaan maksimum.</t>
+        </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/jiot.2024.3376715</t>
-        </is>
-      </c>
-      <c r="K22" s="2" t="inlineStr">
-        <is>
-          <t>Artikel ini membangun kerangka penjadwalan pemeliharaan prediktif berbasis prediksi RUL untuk mesin pesawat. Prediksi RUL dilakukan oleh model ensemble 1-D CNN dan Bi-LSTM dengan attention (BO-CNN-Bi-LSTM-AM) yang hyperparameter-nya dioptimasi Bayesian optimization; ketika RUL melampaui ambang alarm, tugas penjadwalan dipicu. Penjadwalan banyak mesin ke beberapa pusat perawatan diformulasikan sebagai MILP untuk meminimalkan waktu penyelesaian pemeliharaan maksimum.</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
         <is>
           <t>Menghubungkan prediksi RUL dengan keputusan operasional konkret (penjadwalan pemeliharaan banyak-unit) melalui MILP, memberi contoh operasionalisasi keputusan dari RUL. Relevan ke tesis sebagai rujukan lapisan keputusan (d6), namun tidak memodelkan penyensoran/survival maupun domain membran, sehingga menegaskan celah integrasi survival + keputusan pada membran RO.</t>
         </is>
@@ -1773,23 +1594,15 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.3390/en16093707</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>Paper mengintegrasikan analisis survival dengan Bayesian network untuk memperkirakan RUL pompa sentrifugal secara probabilistik dan terkondisi pada tipe kegagalan (operasi normal, kavitasi, poros bengkok). Data getaran diubah menjadi fitur (crest factor, skewness, kurtosis) yang menjadi evidence Bayesian network; fungsi survival Kaplan-Meier dan model Weibull per-tipe-fault dipakai untuk memprediksi RUL. Studi kasus menunjukkan diagnosis 95,8% kavitasi dan RUL yang mengikuti kurva kavitasi dengan deviasi akibat ketidakpastian.</t>
+        </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/en16093707</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>Paper mengintegrasikan analisis survival dengan Bayesian network untuk memperkirakan RUL pompa sentrifugal secara probabilistik dan terkondisi pada tipe kegagalan (operasi normal, kavitasi, poros bengkok). Data getaran diubah menjadi fitur (crest factor, skewness, kurtosis) yang menjadi evidence Bayesian network; fungsi survival Kaplan-Meier dan model Weibull per-tipe-fault dipakai untuk memprediksi RUL. Studi kasus menunjukkan diagnosis 95,8% kavitasi dan RUL yang mengikuti kurva kavitasi dengan deviasi akibat ketidakpastian.</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
         <is>
           <t>Menunjukkan cara mengondisikan RUL pada tipe fault via Bayesian network + survival analysis, sehingga RUL menjadi probabilistik dan dapat dipakai dalam kerangka keputusan maintenance. Ini pola yang dapat diadopsi tesis untuk mengondisikan RUL membran pada mode fouling yang berbeda.</t>
         </is>
@@ -1829,23 +1642,15 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.3390/s23125669</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan informed machine learning (IML) multiform untuk prediksi RUL aero-engine dengan mengintegrasikan dua bentuk pengetahuan domain dari rekayasa keandalan: (1) Piecewise RUL yang dipakai untuk menetapkan label data latih, dan (2) fungsi distribusi kumulatif Weibull yang diintegrasikan ke loss function (Weibull-combined loss). Model LSTM sederhana dilatih pada C-MAPSS; integrasi kedua pengetahuan menurunkan RMSE paling besar (ablation) dan model Weibull-RMSLE-Comb paling stabil, mengalahkan metode SOTA (MSTformer) pada kondisi operasi kompleks FD002/FD004.</t>
+        </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/s23125669</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan informed machine learning (IML) multiform untuk prediksi RUL aero-engine dengan mengintegrasikan dua bentuk pengetahuan domain dari rekayasa keandalan: (1) Piecewise RUL yang dipakai untuk menetapkan label data latih, dan (2) fungsi distribusi kumulatif Weibull yang diintegrasikan ke loss function (Weibull-combined loss). Model LSTM sederhana dilatih pada C-MAPSS; integrasi kedua pengetahuan menurunkan RMSE paling besar (ablation) dan model Weibull-RMSLE-Comb paling stabil, mengalahkan metode SOTA (MSTformer) pada kondisi operasi kompleks FD002/FD004.</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
         <is>
           <t>Menunjukkan cara menyuntikkan pengetahuan keandalan (Weibull CDF sebagai loss, label Piecewise) ke dalam pipeline DL untuk RUL - relevan bagi tesis karena memakai distribusi Weibull/reliability sebagai pengetahuan domain dan mengklaim membantu keterbatasan data; tetapi tidak memodelkan data tersensor dan domainnya bukan membran.</t>
         </is>
@@ -1885,23 +1690,15 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.1109/jsen.2023.3261874</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>Paper mengusulkan algoritma fusi deep learning CNN-LSTM dengan self-attention mechanism (SAM/CLS) untuk memprediksi RUL turbofan engine, khususnya pada mode multi-operating point (MOP) yang sangat non-linear. CNN mengekstrak fitur spasial, LSTM mengekstrak fitur temporal, dan SAM memberi bobot adaptif pada unit hidden untuk mengatasi kehilangan informasi LSTM. Dievaluasi pada C-MAPSS FD001-FD004, model mencapai RMSE 12,56/15,25/13,77/18,63 dan mengalahkan metode pembanding pada mode MOP.</t>
+        </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/jsen.2023.3261874</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>Paper mengusulkan algoritma fusi deep learning CNN-LSTM dengan self-attention mechanism (SAM/CLS) untuk memprediksi RUL turbofan engine, khususnya pada mode multi-operating point (MOP) yang sangat non-linear. CNN mengekstrak fitur spasial, LSTM mengekstrak fitur temporal, dan SAM memberi bobot adaptif pada unit hidden untuk mengatasi kehilangan informasi LSTM. Dievaluasi pada C-MAPSS FD001-FD004, model mencapai RMSE 12,56/15,25/13,77/18,63 dan mengalahkan metode pembanding pada mode MOP.</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>Menjadi contoh state-of-the-art arsitektur deep learning (CNN+LSTM+attention) untuk regresi RUL point-estimate pada data multi-sensor non-stasioner. Relevan ke tesis sebagai baseline model deep learning, tetapi tidak menangani data tersensor maupun kuantifikasi ketidakpastian — justru menunjukkan celah yang coba diisi tesis.</t>
         </is>
@@ -1941,23 +1738,15 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>Konteks</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.1016/j.mlwa.2023.100475</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengembangkan kerangka inteligent berbasis Artificial Neural Network (ANN) untuk mengoptimalkan dosis koagulan (FeCl3) pada plant SWRO skala industri (216.000 m3/hari, Arab Saudi). Model memprediksi Silt Density Index (SDI) air terfiltrasi setelah dosing kimia dari parameter operasional (pH, turbidity, SDI, laju dosing FeCl3/polimer) yang diperkaya via feature engineering (lag/diff). ANN (10-256-128-64-64-1) mencapai akurasi 95% dan mengalahkan decision tree, random forest, dan linear regression. Setelah diterapkan selama satu tahun, konsumsi koagulan turun 11,7% (penghematan 325.000 SAR), terutama pada musim dingin.</t>
+        </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.mlwa.2023.100475</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengembangkan kerangka inteligent berbasis Artificial Neural Network (ANN) untuk mengoptimalkan dosis koagulan (FeCl3) pada plant SWRO skala industri (216.000 m3/hari, Arab Saudi). Model memprediksi Silt Density Index (SDI) air terfiltrasi setelah dosing kimia dari parameter operasional (pH, turbidity, SDI, laju dosing FeCl3/polimer) yang diperkaya via feature engineering (lag/diff). ANN (10-256-128-64-64-1) mencapai akurasi 95% dan mengalahkan decision tree, random forest, dan linear regression. Setelah diterapkan selama satu tahun, konsumsi koagulan turun 11,7% (penghematan 325.000 SAR), terutama pada musim dingin.</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
         <is>
           <t>Memberi contoh pengendalian fouling/pra-perlakuan membran RO yang terhubung langsung ke penghematan biaya operasional nyata - konteks kuat domain desalinasi untuk tesis; namun bukan prediksi RUL, tanpa survival analysis, dan tanpa data tersensor.</t>
         </is>
@@ -1997,23 +1786,15 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.1038/s41598-022-12572-z</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>Studi menyusun kerangka survival analysis untuk prognostik pemeliharaan prediktif komponen alat kerja bergerak (mobile work equipment). Dari catatan pemeliharaan nyata (7.896 event, 658 mesin, 12 komponen), penulis mengidentifikasi campuran jenis pencensoringan (kiri, interval, kanan) dan menyaring hanya data tersensor-kanan; lalu mengestimasi fungsi survival Kaplan-Meier, hazard non-parametrik (kernel/Nelson-Aalen), serta lima model parametrik (Exponential, Weibull, Log-logistic, Log-normal, Generalized-gamma). Hazard bersifat kompleks; non-parametrik umumnya terbaik, dengan Generalized-gamma sebagai parametrik unggulan.</t>
+        </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1038/s41598-022-12572-z</t>
-        </is>
-      </c>
-      <c r="K27" s="2" t="inlineStr">
-        <is>
-          <t>Studi menyusun kerangka survival analysis untuk prognostik pemeliharaan prediktif komponen alat kerja bergerak (mobile work equipment). Dari catatan pemeliharaan nyata (7.896 event, 658 mesin, 12 komponen), penulis mengidentifikasi campuran jenis pencensoringan (kiri, interval, kanan) dan menyaring hanya data tersensor-kanan; lalu mengestimasi fungsi survival Kaplan-Meier, hazard non-parametrik (kernel/Nelson-Aalen), serta lima model parametrik (Exponential, Weibull, Log-logistic, Log-normal, Generalized-gamma). Hazard bersifat kompleks; non-parametrik umumnya terbaik, dengan Generalized-gamma sebagai parametrik unggulan.</t>
-        </is>
-      </c>
-      <c r="L27" s="2" t="inlineStr">
         <is>
           <t>Preseden metodologis kuat untuk pemodelan data tersensor (survival/hazard/Weibull) yang menjadi inti metode tesis, termasuk penanganan tiga jenis pencensoringan dan pemilihan parametrik vs non-parametrik; namun domainnya alat berat (bukan membran) dan tanpa kovariat/sensor.</t>
         </is>
@@ -2053,23 +1834,15 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.1007/s00521-022-07667-7</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>Studi menyajikan use case industri pertama WTTE-RNN (Weibull time-to-event recurrent neural network) untuk prognosis kegagalan turbocharger pada armada truk Scania. WTTE-RNN mengoptimalkan parameter distribusi Weibull waktu-ke-kegagalan via RNN menggunakan loss log-likelihood yang memanfaatkan data tersensor (truk yang tidak gagal). Data kondisi berupa histogram yang jarang ter-sampling (10-30 snapshot/truk); dimensi direduksi via relative entropy antar-histogram. Hasil: WTTE-RNN memberi rentang galat yang memadai untuk perencanaan pemeliharaan; menggabungkan data tersensor memperbaiki prediksi, tetapi rasio tersensor:tak-tersensor yang terlalu timpang merusak performa; clustering sub-armada hanya bermanfaat bila dataset cukup besar.</t>
+        </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1007/s00521-022-07667-7</t>
-        </is>
-      </c>
-      <c r="K28" s="2" t="inlineStr">
-        <is>
-          <t>Studi menyajikan use case industri pertama WTTE-RNN (Weibull time-to-event recurrent neural network) untuk prognosis kegagalan turbocharger pada armada truk Scania. WTTE-RNN mengoptimalkan parameter distribusi Weibull waktu-ke-kegagalan via RNN menggunakan loss log-likelihood yang memanfaatkan data tersensor (truk yang tidak gagal). Data kondisi berupa histogram yang jarang ter-sampling (10-30 snapshot/truk); dimensi direduksi via relative entropy antar-histogram. Hasil: WTTE-RNN memberi rentang galat yang memadai untuk perencanaan pemeliharaan; menggabungkan data tersensor memperbaiki prediksi, tetapi rasio tersensor:tak-tersensor yang terlalu timpang merusak performa; clustering sub-armada hanya bermanfaat bila dataset cukup besar.</t>
-        </is>
-      </c>
-      <c r="L28" s="2" t="inlineStr">
         <is>
           <t>Mendemonstrasikan secara industri bahwa WTTE-RNN (survival Weibull + RNN) yang memanfaatkan data tersensor dapat langsung mendukung keputusan pemeliharaan berbasis risiko - inti metode tesis, meski domainnya armada truk (bukan membran).</t>
         </is>
@@ -2109,23 +1882,15 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.1109/tim.2022.3167778</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan handcrafted feature flows (HFFs) untuk menekan noise pada sinyal mentah dan jaringan dua-stream berbasis Bi-LSTM yang menggabungkan stream sinyal mentah dengan stream HFF. Tiga metode fusi diuji (late, concatenation, addition); fusi addition terbaik. Pada dataset C-MAPSS (FD001-FD004), model mencapai RMSE 11,96/14,48/13,41/15,11 dan mengungguli 8 metode SOTA termasuk CNN-BiLSTM.</t>
+        </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/tim.2022.3167778</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan handcrafted feature flows (HFFs) untuk menekan noise pada sinyal mentah dan jaringan dua-stream berbasis Bi-LSTM yang menggabungkan stream sinyal mentah dengan stream HFF. Tiga metode fusi diuji (late, concatenation, addition); fusi addition terbaik. Pada dataset C-MAPSS (FD001-FD004), model mencapai RMSE 11,96/14,48/13,41/15,11 dan mengungguli 8 metode SOTA termasuk CNN-BiLSTM.</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="inlineStr">
         <is>
           <t>Preseden metode RUL deep learning dengan rekayasa fitur (HFF) dan arsitektur multi-stream/fusi, berguna sebagai pembanding metode bagi tesis; namun tanpa survival/penyensoran dan bukan domain membran, sehingga Pendukung.</t>
         </is>
@@ -2165,23 +1930,15 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>6</v>
+          <t>https://doi.org/10.3390/en15238918</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan model hibrida WOA-VMD-LSTM untuk prediksi RUL baterai lithium-ion. Whale Optimization Algorithm (WOA) mengoptimalkan parameter VMD (K dan alpha) agar sinyal kapasitas terdekomposisi menjadi komponen ganda tren atenuasi global dan komponen fluaktuasi pemulihan kapasitas; masing-masing komponen diprediksi LSTM lalu direkonstruksi menjadi RUL. Hasil pada dataset NASA menunjukkan AE maksimum 2 siklus, RMSE rata-rata &lt; 0,69%, dan MAPE rata-rata &lt; 0,43%, mengungguli LSTM, EMD-LSTM, VMD-LSTM, dan ELM.</t>
+        </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/en15238918</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan model hibrida WOA-VMD-LSTM untuk prediksi RUL baterai lithium-ion. Whale Optimization Algorithm (WOA) mengoptimalkan parameter VMD (K dan alpha) agar sinyal kapasitas terdekomposisi menjadi komponen ganda tren atenuasi global dan komponen fluaktuasi pemulihan kapasitas; masing-masing komponen diprediksi LSTM lalu direkonstruksi menjadi RUL. Hasil pada dataset NASA menunjukkan AE maksimum 2 siklus, RMSE rata-rata &lt; 0,69%, dan MAPE rata-rata &lt; 0,43%, mengungguli LSTM, EMD-LSTM, VMD-LSTM, dan ELM.</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
         <is>
           <t>Menunjukkan pipeline deep learning RUL dengan pra-pemrosesan dekomposisi sinyal (mengatasi fenomena pemulihan kapasitas), relevan sebagai pembanding arsitektur DL RUL. Namun tidak memakai survival/penyensoran dan bukan domain membran.</t>
         </is>
@@ -2221,23 +1978,15 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="n">
-        <v>6</v>
+          <t>https://doi.org/10.3390/s22124549</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>Makalah mengusulkan metode prediksi RUL bearing berbasis LSTM dengan kuantifikasi ketidakpastian. Fitur degradasi disaring memakai indeks evaluasi komprehensif (korelasi, monotonisitas, robustness), lalu dropout diterapkan pada LSTM untuk memperoleh aproksimasi Bayesian (epistemic uncertainty), dan estimasi kernel density nonparametrik menghasilkan distribusi RUL. Hasil pada PHM2012 menunjukkan RMSE 0,0567 dan MAE 0,0385, lebih baik daripada LSTM fitur acak, CNN, dan adaptive Kalman filter.</t>
+        </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/s22124549</t>
-        </is>
-      </c>
-      <c r="K31" s="2" t="inlineStr">
-        <is>
-          <t>Makalah mengusulkan metode prediksi RUL bearing berbasis LSTM dengan kuantifikasi ketidakpastian. Fitur degradasi disaring memakai indeks evaluasi komprehensif (korelasi, monotonisitas, robustness), lalu dropout diterapkan pada LSTM untuk memperoleh aproksimasi Bayesian (epistemic uncertainty), dan estimasi kernel density nonparametrik menghasilkan distribusi RUL. Hasil pada PHM2012 menunjukkan RMSE 0,0567 dan MAE 0,0385, lebih baik daripada LSTM fitur acak, CNN, dan adaptive Kalman filter.</t>
-        </is>
-      </c>
-      <c r="L31" s="2" t="inlineStr">
         <is>
           <t>Menunjukkan kuantifikasi ketidakpastian (dropout + kernel density) dalam prediksi RUL berbasis LSTM - relevan bagi komponen deep learning + ketidakpastian tesis, tetapi tidak memodelkan data tersensor dan domainnya bearing, bukan membran.</t>
         </is>
@@ -2277,23 +2026,15 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.1109/tte.2022.3161140</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>Artikel ini mengusulkan Bayesian Mixture Neural Network (BMNN) probabilistik untuk prediksi RUL baterai lithium-ion: Bayesian CNN mengekstraksi fitur dari citra temporal hasil transformasi quasi-Gramian Angular Field (Q-GAF), Bayesian LSTM mempelajari korelasi antara kapasitas retensi dan inducemen degradasi, dan variational Bayesian neural network mengeluarkan distribusi hasil prediksi. Metode divalidasi pada empat dataset baterai (NASA, CALCE, MIT, Cavendish) dan memberi estimasi ketidakpastian berupa confidence interval.</t>
+        </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/tte.2022.3161140</t>
-        </is>
-      </c>
-      <c r="K32" s="2" t="inlineStr">
-        <is>
-          <t>Artikel ini mengusulkan Bayesian Mixture Neural Network (BMNN) probabilistik untuk prediksi RUL baterai lithium-ion: Bayesian CNN mengekstraksi fitur dari citra temporal hasil transformasi quasi-Gramian Angular Field (Q-GAF), Bayesian LSTM mempelajari korelasi antara kapasitas retensi dan inducemen degradasi, dan variational Bayesian neural network mengeluarkan distribusi hasil prediksi. Metode divalidasi pada empat dataset baterai (NASA, CALCE, MIT, Cavendish) dan memberi estimasi ketidakpastian berupa confidence interval.</t>
-        </is>
-      </c>
-      <c r="L32" s="2" t="inlineStr">
         <is>
           <t>Memberi contoh kuantifikasi ketidakpastian prediktif penuh melalui Bayesian deep learning (posterior predictive distribution + CI), serta teknik representasi ulang time-series menjadi citra (Q-GAF). Relevan ke tesis pada sumbu ketidakpastian (d5) dan model probabilistik, tetapi tanpa pemodelan penyensoran/survival dan bukan domain membran—memperjelas celah integrasi model hazard tersensor dengan deep learning probabilistik pada membran RO.</t>
         </is>
@@ -2333,23 +2074,15 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode+Domain</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>6</v>
+          <t>https://doi.org/10.1109/tia.2022.3170525</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>Artikel mengusulkan karakterisasi probabilistik RUL baterai Li-ion dengan distribusi inverse Burr (IB) dan dua campurannya: IB-inverse Gaussian (M-IB-IG) dan IB-inverse Weibull (M-IB-IW). Sampel RUL dibangkitkan secara sintetis melalui prosedur elektrokimia dua tahap: solusi analitik PDE difusi (model Rakhmatov) yang memetakan profil arus ke RUL, dan proses Poisson-Monte Carlo yang membangkitkan M profil arus acak. Parameter distribusi diestimasi dengan MLE, dan algoritma EM dikembangkan khusus untuk distribusi campuran, lalu dievaluasi dengan empat uji GOF (ADC, Anderson-Darling, chi-square, Q-Q plot) pada 13 skenario, termasuk skenario data kecil (M=50) dan suhu operasi 25/40/55 derajat C. Distribusi berbasis IB mengungguli benchmark IG, IW, dan Gumbel; fokus paper adalah kecocokan distribusi untuk karakterisasi ketidakpastian RUL, bukan prediksi real-time.</t>
+        </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/tia.2022.3170525</t>
-        </is>
-      </c>
-      <c r="K33" s="2" t="inlineStr">
-        <is>
-          <t>Artikel mengusulkan karakterisasi probabilistik RUL baterai Li-ion dengan distribusi inverse Burr (IB) dan dua campurannya: IB-inverse Gaussian (M-IB-IG) dan IB-inverse Weibull (M-IB-IW). Sampel RUL dibangkitkan secara sintetis melalui prosedur elektrokimia dua tahap: solusi analitik PDE difusi (model Rakhmatov) yang memetakan profil arus ke RUL, dan proses Poisson-Monte Carlo yang membangkitkan M profil arus acak. Parameter distribusi diestimasi dengan MLE, dan algoritma EM dikembangkan khusus untuk distribusi campuran, lalu dievaluasi dengan empat uji GOF (ADC, Anderson-Darling, chi-square, Q-Q plot) pada 13 skenario, termasuk skenario data kecil (M=50) dan suhu operasi 25/40/55 derajat C. Distribusi berbasis IB mengungguli benchmark IG, IW, dan Gumbel; fokus paper adalah kecocokan distribusi untuk karakterisasi ketidakpastian RUL, bukan prediksi real-time.</t>
-        </is>
-      </c>
-      <c r="L33" s="2" t="inlineStr">
         <is>
           <t>1) Perumusan distribusi campuran berbasis IB (M-IB-IG dan M-IB-IW) untuk karakterisasi probabilistik RUL baterai, memperluas hasil konferensi [32]. 2) Pengembangan algoritma EM khusus untuk estimasi parameter campuran (langkah ekspektasi dengan solusi analitik untuk bobot omega, langkah maksimisasi numerik untuk parameter lain). 3) Evaluasi GOF komprehensif dengan uji baru atas 13 skenario operasi (arus pengisian/pengosongan variabel, C-rate tinggi, profil simetris/asimetris, suhu 25/40/55 derajat C) dibandingkan distribusi IG, IW, dan Gumbel sebagai benchmark.</t>
         </is>
@@ -2389,23 +2122,15 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.3390/s22103803</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan framework prognostik dua tahap: pelatihan adaptive Bayesian (particle filter) untuk mengestimasi parameter (bobot dan bias) MLP, lalu prognosis RUL memakai MLP terkonfigurasi. Kontribusi utamanya adalah weight regularization lewat particle roughening (menambahkan Gaussian jitter kecil pada partikel yang terdegradasi) untuk mengatasi particle degeneracy/impoverishment. Diuji pada data degradasi kapasitas baterai lithium-ion CALCE dan NASA; particle roughening memberi RMSE 0,04 (CALCE) dan 0,24 (NASA) dengan tingkat iterasi sukses 98%.</t>
+        </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/s22103803</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan framework prognostik dua tahap: pelatihan adaptive Bayesian (particle filter) untuk mengestimasi parameter (bobot dan bias) MLP, lalu prognosis RUL memakai MLP terkonfigurasi. Kontribusi utamanya adalah weight regularization lewat particle roughening (menambahkan Gaussian jitter kecil pada partikel yang terdegradasi) untuk mengatasi particle degeneracy/impoverishment. Diuji pada data degradasi kapasitas baterai lithium-ion CALCE dan NASA; particle roughening memberi RMSE 0,04 (CALCE) dan 0,24 (NASA) dengan tingkat iterasi sukses 98%.</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
         <is>
           <t>Menunjukkan estimasi RUL probabilistik (distribusi posterior parameter dan RUL) dengan Bayesian/particle filter pada data deret waktu degradasi, relevan sebagai preseden kuantifikasi ketidakpastian (d5) bagi tesis; namun tidak memodelkan penyensoran/survival dan domainnya baterai, sehingga bersifat Pendukung.</t>
         </is>
@@ -2445,23 +2170,15 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>Inti-Domain</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.1109/access.2022.3226780</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>Studi ini mengusulkan metodologi prediksi RUL yang hemat data: terlebih dahulu memodelkan deviasi kondisi mesin dari keadaan sehat dan rusak memakai Mahalanobis Distance (MD) atau LSTM Autoencoder (AE), lalu menghitung Health Index (HI) dan mendeteksi awal degradasi, sebelum memprediksi RUL dengan SVR, LSTM, atau regresi polinomial kuadratik. Tujuannya mengatasi kelangkaan runtun run-to-failure. Validasi pada dua dataset terbuka (C-MAPSS turbofan dan FEMTO bearing) menunjukkan perbaikan generalisasi pada data latih terbatas.</t>
+        </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/access.2022.3226780</t>
-        </is>
-      </c>
-      <c r="K35" s="2" t="inlineStr">
-        <is>
-          <t>Studi ini mengusulkan metodologi prediksi RUL yang hemat data: terlebih dahulu memodelkan deviasi kondisi mesin dari keadaan sehat dan rusak memakai Mahalanobis Distance (MD) atau LSTM Autoencoder (AE), lalu menghitung Health Index (HI) dan mendeteksi awal degradasi, sebelum memprediksi RUL dengan SVR, LSTM, atau regresi polinomial kuadratik. Tujuannya mengatasi kelangkaan runtun run-to-failure. Validasi pada dua dataset terbuka (C-MAPSS turbofan dan FEMTO bearing) menunjukkan perbaikan generalisasi pada data latih terbatas.</t>
-        </is>
-      </c>
-      <c r="L35" s="2" t="inlineStr">
         <is>
           <t>Mendemonstrasikan strategi RUL yang efisien data lewat representasi ulang fitur menjadi HI dan deteksi awal degradasi (unit-specific), bukan sekadar mengandalkan banyak runtun lengkap. Relevan ke tesis sebagai analogi 'reduksi dimensi + deteksi onset' pada rezim data kecil, tetapi tetap tanpa pemodelan penyensoran, sehingga memperjelas celah bahwa data tersensor + survival belum dieksplorasi untuk HI/RUL membran.</t>
         </is>
@@ -2501,23 +2218,15 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>Inti-Domain</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.1109/tim.2022.3200667</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>Artikel ini mengusulkan metode domain adaptation untuk prediksi RUL dengan menyelaraskan distribusi pada level fitur dan level semantik sekaligus, menggunakan Transformer sebagai tulang punggung. Dua diskriminator domain (D_f untuk fitur, D_y untuk keluaran) dilatih secara adversarial dengan Gradient Reversal Layer. Metode diuji pada C-MAPSS dan N-CMAPSS, mencapai hasil state-of-the-art pada tugas RUL source-only dan cross-domain, dilengkapi kuantifikasi ketidakpastian (95% CI) dan uji online.</t>
+        </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/tim.2022.3200667</t>
-        </is>
-      </c>
-      <c r="K36" s="2" t="inlineStr">
-        <is>
-          <t>Artikel ini mengusulkan metode domain adaptation untuk prediksi RUL dengan menyelaraskan distribusi pada level fitur dan level semantik sekaligus, menggunakan Transformer sebagai tulang punggung. Dua diskriminator domain (D_f untuk fitur, D_y untuk keluaran) dilatih secara adversarial dengan Gradient Reversal Layer. Metode diuji pada C-MAPSS dan N-CMAPSS, mencapai hasil state-of-the-art pada tugas RUL source-only dan cross-domain, dilengkapi kuantifikasi ketidakpastian (95% CI) dan uji online.</t>
-        </is>
-      </c>
-      <c r="L36" s="2" t="inlineStr">
         <is>
           <t>Mencontohkan transfer learning/domain adaptation untuk RUL lintas kondisi operasi tanpa label target, termasuk kuantifikasi ketidakpastian via Monte Carlo dropout. Relevan ke tesis pada sumbu transfer/small-data (d8) dan ketidakpastian (d5); namun tanpa pemodelan penyensoran/survival dan bukan domain membran—memperjelas celah integrasi survival tersensor dengan backbone Transformer pada membran RO.</t>
         </is>
@@ -2557,23 +2266,15 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>Inti-Domain</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.1016/j.asoc.2022.109630</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan metode prediksi RUL bantalan gelinding pada kondisi data terbatas. Tiga komponen utama: identifikasi first prediction time (FPT) berbasis kurtosis dan RMS, jendela fitur deret waktu adaptif yang dikompresi memakai degradation factor, dan jaringan stacked bidirectional LSTM (SBiLSTM) dengan strategi prediksi multi-step ahead bergulir. Pada dataset XJTU-SY, metode mencapai MAPE 6,77%, 18,92%, dan 8,95% untuk tiga bantalan representatif, mengalahkan delapan metode pembanding.</t>
+        </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.asoc.2022.109630</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan metode prediksi RUL bantalan gelinding pada kondisi data terbatas. Tiga komponen utama: identifikasi first prediction time (FPT) berbasis kurtosis dan RMS, jendela fitur deret waktu adaptif yang dikompresi memakai degradation factor, dan jaringan stacked bidirectional LSTM (SBiLSTM) dengan strategi prediksi multi-step ahead bergulir. Pada dataset XJTU-SY, metode mencapai MAPE 6,77%, 18,92%, dan 8,95% untuk tiga bantalan representatif, mengalahkan delapan metode pembanding.</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="inlineStr">
         <is>
           <t>Menunjukkan strategi RUL yang dirancang khusus untuk data terbatas (small-data) tanpa memerlukan dataset run-to-failure masif, relevan dengan tantangan kelangkaan data kegagalan membran; namun tidak memakai survival/pencensoringan dan domainnya bukan membran.</t>
         </is>
@@ -2613,23 +2314,15 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.1109/jsen.2021.3109623</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan model hybrid dua kanal Cap-LSTM untuk prediksi RUL, menggabungkan Capsule Neural Network (kanal spasial, menggantikan pooling CNN dengan routing-by-agreement) dan LSTM (kanal temporal untuk dependensi jangka panjang). Data multisensor deret waktu C-MAPSS (14 sensor terseleksi) diproses dengan sliding time window dan label RUL piece-wise linear (knee point 125). Cap-LSTM mencapai RMSE terbaik pada FD001-FD004 (12,27/17,79/12,55/22,05) dibanding CNN, LSTM, BiLSTM, dan CNN+FNN.</t>
+        </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/jsen.2021.3109623</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan model hybrid dua kanal Cap-LSTM untuk prediksi RUL, menggabungkan Capsule Neural Network (kanal spasial, menggantikan pooling CNN dengan routing-by-agreement) dan LSTM (kanal temporal untuk dependensi jangka panjang). Data multisensor deret waktu C-MAPSS (14 sensor terseleksi) diproses dengan sliding time window dan label RUL piece-wise linear (knee point 125). Cap-LSTM mencapai RMSE terbaik pada FD001-FD004 (12,27/17,79/12,55/22,05) dibanding CNN, LSTM, BiLSTM, dan CNN+FNN.</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
         <is>
           <t>Preseden arsitektur deep learning RUL (capsule + LSTM) dengan evaluasi ablation dan metrik RMSE/Score pada benchmark publik, relevan sebagai pembanding metode bagi tesis; namun tidak menangani survival/penyensoran dan bukan domain membran, sehingga Pendukung.</t>
         </is>
@@ -2669,23 +2362,15 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I39" s="2" t="n">
-        <v>7</v>
+          <t>https://doi.org/10.1109/tim.2021.3055788</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan DELTA (degradation-aware LSTM autoencoder) untuk prediksi RUL yang sadar tahap degradasi. Tiga modul: (1) identifikasi tahap sehat via Hilbert-Huang transform (HHT) + klasifikasi SVM, (2) estimasi degradation factor dengan LSTM autoencoder (latent variable), dan (3) estimasi RUL via degradation similarity matching berbobot. Diuji pada dataset FEMTO/PRONOSTIA (bearing), DELTA mengalahkan MLP, XGBoost, RFR, CNN, LSTM, SVR, RNN, dan two-stage pada metrik RMSE dan Score.</t>
+        </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/tim.2021.3055788</t>
-        </is>
-      </c>
-      <c r="K39" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan DELTA (degradation-aware LSTM autoencoder) untuk prediksi RUL yang sadar tahap degradasi. Tiga modul: (1) identifikasi tahap sehat via Hilbert-Huang transform (HHT) + klasifikasi SVM, (2) estimasi degradation factor dengan LSTM autoencoder (latent variable), dan (3) estimasi RUL via degradation similarity matching berbobot. Diuji pada dataset FEMTO/PRONOSTIA (bearing), DELTA mengalahkan MLP, XGBoost, RFR, CNN, LSTM, SVR, RNN, dan two-stage pada metrik RMSE dan Score.</t>
-        </is>
-      </c>
-      <c r="L39" s="2" t="inlineStr">
         <is>
           <t>Memberi contoh pipeline DL (LSTM autoencoder + similarity matching) untuk RUL bearing dengan data multisensor - relevan sebagai pembanding metode DL RUL pada tesis, tetapi tidak memodelkan data tersensor, tidak mengkuantifikasi ketidakpastian, dan domainnya bearing.</t>
         </is>
@@ -2725,23 +2410,15 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.1109/access.2021.3073945</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan kerangka prediksi kurva RUL bantalan gelinding pada kondisi defek yang terus berkembang, dengan menekankan perbedaan individual antar-bantalan dan fluktuasi fitur vibrasi di tahap defek lanjut. Kerangka ini menggabungkan Feature Fusion Network (FFN) berbasis CNN (memakai spektrogram vibrasi saat ini dan masa lalu serta Degradation Index Vector) dengan Hierarchical Bayesian Regression (HBR) yang menghasilkan kurva RUL monoton beserta distribusi posterior. Dievaluasi lewat leave-one-bearing-out CV pada 33 sampel bantalan, akurasi R2 median meningkat dan variasi antar-sampel menyusut.</t>
+        </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/access.2021.3073945</t>
-        </is>
-      </c>
-      <c r="K40" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan kerangka prediksi kurva RUL bantalan gelinding pada kondisi defek yang terus berkembang, dengan menekankan perbedaan individual antar-bantalan dan fluktuasi fitur vibrasi di tahap defek lanjut. Kerangka ini menggabungkan Feature Fusion Network (FFN) berbasis CNN (memakai spektrogram vibrasi saat ini dan masa lalu serta Degradation Index Vector) dengan Hierarchical Bayesian Regression (HBR) yang menghasilkan kurva RUL monoton beserta distribusi posterior. Dievaluasi lewat leave-one-bearing-out CV pada 33 sampel bantalan, akurasi R2 median meningkat dan variasi antar-sampel menyusut.</t>
-        </is>
-      </c>
-      <c r="L40" s="2" t="inlineStr">
         <is>
           <t>Menunjukkan bagaimana regresi Bayesian hierarkis dapat menghasilkan kurva RUL monoton beserta interval kredibel per-unit sekaligus menyerap perbedaan individual antar-unit - sebuah pola probabilistic RUL yang relevan bila tesis ingin melaporkan ketidakpastian prediksi; namun tidak memakai survival/Weibull/hazard dan tidak menangani data tersensor.</t>
         </is>
@@ -2781,23 +2458,15 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.1109/tii.2021.3078193</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>Studi menggunakan Bayesian Convolutional Neural Networks (BCNN) untuk memprediksi RUL solenoid valve (SV) langsung dari representasi citra sinyal arus, diperkaya dua fitur fisik (shading ring force dan Coulomb friction) dari model elektromekanis. Dua arsitektur Bayesian dibandingkan: MC dropout dan mean-field variational inference (MFVI) yang memprediksi mean dan standar deviasi distribusi Gaussian terpangkas secara eksplisit. Hasil pada 48 valve uji dipercepat menunjukkan model BCNN MFVI memberi estimasi ketidakpastian (credible interval 90%) yang terkalibrasi baik, dan menurunkan MAE RUL ~40% dibanding metode deep/feature-based sebelumnya.</t>
+        </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/tii.2021.3078193</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>Studi menggunakan Bayesian Convolutional Neural Networks (BCNN) untuk memprediksi RUL solenoid valve (SV) langsung dari representasi citra sinyal arus, diperkaya dua fitur fisik (shading ring force dan Coulomb friction) dari model elektromekanis. Dua arsitektur Bayesian dibandingkan: MC dropout dan mean-field variational inference (MFVI) yang memprediksi mean dan standar deviasi distribusi Gaussian terpangkas secara eksplisit. Hasil pada 48 valve uji dipercepat menunjukkan model BCNN MFVI memberi estimasi ketidakpastian (credible interval 90%) yang terkalibrasi baik, dan menurunkan MAE RUL ~40% dibanding metode deep/feature-based sebelumnya.</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="inlineStr">
         <is>
           <t>Menunjukkan pembangunan kuantifikasi ketidakpastian yang terkalibrasi (credible interval, calibration curve) dalam RUL berbasis DL - relevan bagi pilar C (Bayesian &amp; Uncertainty) pada tesis; namun tidak memodelkan data tersensor dan domainnya solenoid valve, bukan membran.</t>
         </is>
@@ -2837,23 +2506,15 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>Inti-Domain</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="n">
-        <v>6</v>
+          <t>https://doi.org/10.1109/tec.2021.3116423</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan algoritma deep transfer learning semi-supervised berbasis LSTM untuk memprediksi RUL bantalan gelinding dari data kecil dan tak berlabel. Health index (HI) direkonstruksi sebagai fungsi eksponensial kumulatif dan health stage (HS) dipisahkan dengan Gaussian mixture model (GMM) secara unsupervised; pengetahuan dari siklus hidup bantalan lain ditransfer ke domain target. Transfer learning menurunkan RMSE test rata-rata menjadi 0,1888 (vs 0,3125 DL biasa) dan menaikkan akurasi klasifikasi HS menjadi 0,9044 (vs 0,7558).</t>
+        </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/tec.2021.3116423</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan algoritma deep transfer learning semi-supervised berbasis LSTM untuk memprediksi RUL bantalan gelinding dari data kecil dan tak berlabel. Health index (HI) direkonstruksi sebagai fungsi eksponensial kumulatif dan health stage (HS) dipisahkan dengan Gaussian mixture model (GMM) secara unsupervised; pengetahuan dari siklus hidup bantalan lain ditransfer ke domain target. Transfer learning menurunkan RMSE test rata-rata menjadi 0,1888 (vs 0,3125 DL biasa) dan menaikkan akurasi klasifikasi HS menjadi 0,9044 (vs 0,7558).</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="inlineStr">
         <is>
           <t>Memberikan contoh penanganan data kecil + tak berlabel melalui transfer learning dan pemisahan tahap degradasi (GMM), relevan untuk skenario tesis dengan histori kegagalan membran terbatas. Namun tidak memakai survival/penyensoran eksplisit dan bukan domain membran.</t>
         </is>
@@ -2893,23 +2554,15 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.1049/cim2.12021</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan sistem dukungan pemeliharaan komprehensif yang menggabungkan modul prognostik berbasis survival theory (Weibull time-to-event recurrent neural network, WTTE-RNN) dengan model perencanaan predictive maintenance (PdM) berbasis trade-off biaya corrective maintenance dan waktu/umur yang hilang. Model WTTE-RNN memprediksi parameter distribusi kegagalan Weibull, lalu waktu optimal penggantian prediktif (OPdR) dioptimasi dari parameter biaya operasional dan pemeliharaan. Divalidasi pada studi kasus perencanaan pemeliharaan cutting tool di lingkungan manufaktur dengan analisis sensitivitas sistematis.</t>
+        </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1049/cim2.12021</t>
-        </is>
-      </c>
-      <c r="K43" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan sistem dukungan pemeliharaan komprehensif yang menggabungkan modul prognostik berbasis survival theory (Weibull time-to-event recurrent neural network, WTTE-RNN) dengan model perencanaan predictive maintenance (PdM) berbasis trade-off biaya corrective maintenance dan waktu/umur yang hilang. Model WTTE-RNN memprediksi parameter distribusi kegagalan Weibull, lalu waktu optimal penggantian prediktif (OPdR) dioptimasi dari parameter biaya operasional dan pemeliharaan. Divalidasi pada studi kasus perencanaan pemeliharaan cutting tool di lingkungan manufaktur dengan analisis sensitivitas sistematis.</t>
-        </is>
-      </c>
-      <c r="L43" s="2" t="inlineStr">
         <is>
           <t>Sangat relevan ke tesis: menggabungkan survival theory (Weibull/hazard/censoring) dengan deep learning (RNN) untuk RUL, DAN menutup celah sampai keputusan pemeliharaan biaya-optimal. Namun domainnya cutting tool, bukan membran/RO.</t>
         </is>
@@ -2949,23 +2602,15 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>7</v>
+          <t>https://doi.org/10.1371/journal.pone.0236128</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>Studi memprediksi RUL excavator Komatsu PC-1250 di tambang tembaga Sungun memakai analisis keandalan dalam model Weibull-frailty. Data time between failures (TBF) dari 80 jam operasional dimodelkan dengan dua pendekatan: model klasik-eksponensial dan model Weibull-frailty yang menyertakan frailty (faktor risiko tak teramati/heterogenitas). Model dipilih lewat uji GOF (AIC/BIC) dan uji heterogenitas likelihood ratio, lalu RUL dihitung dari mean residual life (MRL).</t>
+        </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1371/journal.pone.0236128</t>
-        </is>
-      </c>
-      <c r="K44" s="2" t="inlineStr">
-        <is>
-          <t>Studi memprediksi RUL excavator Komatsu PC-1250 di tambang tembaga Sungun memakai analisis keandalan dalam model Weibull-frailty. Data time between failures (TBF) dari 80 jam operasional dimodelkan dengan dua pendekatan: model klasik-eksponensial dan model Weibull-frailty yang menyertakan frailty (faktor risiko tak teramati/heterogenitas). Model dipilih lewat uji GOF (AIC/BIC) dan uji heterogenitas likelihood ratio, lalu RUL dihitung dari mean residual life (MRL).</t>
-        </is>
-      </c>
-      <c r="L44" s="2" t="inlineStr">
         <is>
           <t>Preseden langsung penggunaan model survival frailty (Weibull + random effect untuk heterogenitas tak teramati) dalam menghitung RUL, lengkap dengan penanganan data tersensor (suspended data) dan uji GOF/heterogenitas - klop dengan kerangka survival tesis; tetapi tidak memakai deep learning dan domainnya excavator tambang, bukan membran.</t>
         </is>
@@ -3005,23 +2650,15 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>Inti-Domain</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="n">
-        <v>6</v>
+          <t>https://doi.org/10.1109/tii.2020.3008223</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan model Auto-CNN-LSTM untuk memprediksi RUL baterai Li-ion: autoencoder memperbesar dimensi fitur untuk mengatasi keterbatasan data, CNN menambang informasi kedalaman, LSTM mengekstrak informasi temporal, dan DNN 7-lapis menghasilkan prediksi RUL yang dihaluskan dengan filter orde pertama.</t>
+        </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/tii.2020.3008223</t>
-        </is>
-      </c>
-      <c r="K45" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan model Auto-CNN-LSTM untuk memprediksi RUL baterai Li-ion: autoencoder memperbesar dimensi fitur untuk mengatasi keterbatasan data, CNN menambang informasi kedalaman, LSTM mengekstrak informasi temporal, dan DNN 7-lapis menghasilkan prediksi RUL yang dihaluskan dengan filter orde pertama.</t>
-        </is>
-      </c>
-      <c r="L45" s="2" t="inlineStr">
         <is>
           <t>Memberi contoh strategi augmentasi dimensi berbasis autoencoder untuk data degradasi terbatas dan pipeline hibrida CNN+LSTM — relevan untuk tesis pada sumbu data langka; namun tanpa penanganan censoring/survival, tanpa kuantifikasi ketidakpastian, dan bukan domain membran.</t>
         </is>
@@ -3061,23 +2698,15 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>6</v>
+          <t>https://doi.org/10.1109/tmech.2020.2971503</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>Artikel ini mengusulkan kerangka data-driven untuk prediksi RUL rolling element bearing (REB) dengan deep CNN. Getaran mentah diproses memakai Hilbert-Huang Transform untuk menyusun degradation energy indicator (DEI) nonlinier baru sebagai label latih; CNN 6 lapis dilatih untuk memetakan getaran mentah ke DEI, lalu ε-SVR memforecast evolusi DEI hingga melewati failure threshold. Metode divalidasi pada platform PRONOSTIA dan mengungguli delapan metode publikasi.</t>
+        </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/tmech.2020.2971503</t>
-        </is>
-      </c>
-      <c r="K46" s="2" t="inlineStr">
-        <is>
-          <t>Artikel ini mengusulkan kerangka data-driven untuk prediksi RUL rolling element bearing (REB) dengan deep CNN. Getaran mentah diproses memakai Hilbert-Huang Transform untuk menyusun degradation energy indicator (DEI) nonlinier baru sebagai label latih; CNN 6 lapis dilatih untuk memetakan getaran mentah ke DEI, lalu ε-SVR memforecast evolusi DEI hingga melewati failure threshold. Metode divalidasi pada platform PRONOSTIA dan mengungguli delapan metode publikasi.</t>
-        </is>
-      </c>
-      <c r="L46" s="2" t="inlineStr">
         <is>
           <t>Memperkenalkan indikator degradasi nonlinier (DEI) berbasis frekuensi alami komponen bearing dan framework HHT+CNN+ε-SVR yang menetapkan failure threshold konsisten antar-bearing. Relevan ke tesis sebagai pembanding rekayasa indikator/fitur untuk RUL, namun tanpa survival/penyensoran dan bukan domain membran.</t>
         </is>
@@ -3117,23 +2746,15 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.1109/tnnls.2020.2977132</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>Artikel ini mengusulkan Joint Prognostic Model (JPM) yang menggabungkan model linear Bayesian untuk setiap sinyal sensor (mixed-effects) dengan Artificial Neural Network untuk memetakan hubungan nonlinier antara parameter degradasi multi-sensor dan life percentage. Skema Bayesian updating menghitung distribusi posterior parameter setiap sensor untuk in-service unit, lalu menghasilkan posterior predictive distribution RUL. Metode divalidasi pada C-MAPSS FD001/FD003.</t>
+        </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/tnnls.2020.2977132</t>
-        </is>
-      </c>
-      <c r="K47" s="2" t="inlineStr">
-        <is>
-          <t>Artikel ini mengusulkan Joint Prognostic Model (JPM) yang menggabungkan model linear Bayesian untuk setiap sinyal sensor (mixed-effects) dengan Artificial Neural Network untuk memetakan hubungan nonlinier antara parameter degradasi multi-sensor dan life percentage. Skema Bayesian updating menghitung distribusi posterior parameter setiap sensor untuk in-service unit, lalu menghasilkan posterior predictive distribution RUL. Metode divalidasi pada C-MAPSS FD001/FD003.</t>
-        </is>
-      </c>
-      <c r="L47" s="2" t="inlineStr">
         <is>
           <t>Menyediakan kerangka Bayesian + NN yang menghasilkan distribusi prediktif RUL (bukan hanya titik) dan menangani heterogenitas antar-unit via mixed-effects. Relevan ke tesis pada sumbu ketidakpastian (d5) dan struktur hierarkis (d8), namun tanpa pemodelan penyensoran/survival—menegaskan celah penggabungan survival tersensor dengan prediksi nonlinier.</t>
         </is>
@@ -3173,23 +2794,15 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I48" s="2" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.1109/access.2020.3010066</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>Paper mengusulkan kerangka deep learning TLSTM-A (two-layer LSTM dengan attention) yang didahului 1-D CNN untuk memprediksi RUL komponen rotasi (bearing). CNN mengekstrak fitur lokal dari sinyal getaran, dua lapisan LSTM mengekstrak fitur temporal berlapis, dan attention mechanism menyorot informasi kunci serta mengatasi kehilangan informasi pada transmisi jarak jauh LSTM. Dievaluasi pada dataset bearing XJTU-SY, model mencapai RMSE/MAE/Score terbaik di antara pembanding.</t>
+        </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/access.2020.3010066</t>
-        </is>
-      </c>
-      <c r="K48" s="2" t="inlineStr">
-        <is>
-          <t>Paper mengusulkan kerangka deep learning TLSTM-A (two-layer LSTM dengan attention) yang didahului 1-D CNN untuk memprediksi RUL komponen rotasi (bearing). CNN mengekstrak fitur lokal dari sinyal getaran, dua lapisan LSTM mengekstrak fitur temporal berlapis, dan attention mechanism menyorot informasi kunci serta mengatasi kehilangan informasi pada transmisi jarak jauh LSTM. Dievaluasi pada dataset bearing XJTU-SY, model mencapai RMSE/MAE/Score terbaik di antara pembanding.</t>
-        </is>
-      </c>
-      <c r="L48" s="2" t="inlineStr">
         <is>
           <t>Contoh kuat arsitektur deep learning (CNN+LSTM berlapis+attention) point-estimate untuk RUL sinyal getaran, berguna sebagai baseline arsitektur di tesis. Menegaskan celah: tidak ada penanganan data tersensor maupun kuantifikasi ketidakpastian, sehingga tidak menutup gap utama tesis.</t>
         </is>
@@ -3229,23 +2842,15 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="n">
-        <v>7</v>
+          <t>https://doi.org/10.1109/tii.2020.2991796</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan jaringan CLSTM (convolution-based LSTM) untuk prediksi RUL bantalan (bearing), dengan operasi konvolusi pada transisi input-to-state dan state-to-state LSTM sehingga menangkap informasi time-frequency dan temporal sekaligus. Input berupa fitur time-frequency (STFT) dari sinyal vibrasi run-to-failure, diproses arsitektur encoding-forecasting berlapis dua CLSTM. Pada dua uji run-to-failure, CLSTM mengalahkan deep CNN dan deep LSTM (RMSE 29,7/10,8 menit vs 47,9/18,2 dan 40,7/15,6).</t>
+        </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/tii.2020.2991796</t>
-        </is>
-      </c>
-      <c r="K49" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan jaringan CLSTM (convolution-based LSTM) untuk prediksi RUL bantalan (bearing), dengan operasi konvolusi pada transisi input-to-state dan state-to-state LSTM sehingga menangkap informasi time-frequency dan temporal sekaligus. Input berupa fitur time-frequency (STFT) dari sinyal vibrasi run-to-failure, diproses arsitektur encoding-forecasting berlapis dua CLSTM. Pada dua uji run-to-failure, CLSTM mengalahkan deep CNN dan deep LSTM (RMSE 29,7/10,8 menit vs 47,9/18,2 dan 40,7/15,6).</t>
-        </is>
-      </c>
-      <c r="L49" s="2" t="inlineStr">
         <is>
           <t>Preseden arsitektur deep learning RUL (convolutional LSTM) dengan data vibrasi run-to-failure nyata dan pembanding deep CNN/LSTM, berguna bagi tesis sebagai rujukan metode prediksi RUL; namun tidak menangani penyensoran/survival dan bukan domain membran, sehingga Pendukung.</t>
         </is>
@@ -3285,23 +2890,15 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.1109/tim.2020.3031113</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan ELSTMNN (Ensemble Long Short-Term Memory Neural Network) untuk prognosis RUL: sejumlah LSTMNN dilatih paralel, masing-masing pada data satu unit peralatan, lalu digabung memakai Bayesian Inference Algorithm (BIA) yang memfit distribusi normal prediksi dan memilih RUL dengan probabilitas tertinggi. Diuji pada C-MAPSS FD001 dan FD003; ELSTMNN mencapai MScore 5,71 (deviasi 0,19) dan RMSE 18,22 (deviasi 1,38) pada FD001, terbaik dibanding ANN, SVR, RVR, DCNN, ELM, EKF, ESKF, DLSTMNN, dan mengalahkan bagging secara signifikan (p=0,0029).</t>
+        </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/tim.2020.3031113</t>
-        </is>
-      </c>
-      <c r="K50" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan ELSTMNN (Ensemble Long Short-Term Memory Neural Network) untuk prognosis RUL: sejumlah LSTMNN dilatih paralel, masing-masing pada data satu unit peralatan, lalu digabung memakai Bayesian Inference Algorithm (BIA) yang memfit distribusi normal prediksi dan memilih RUL dengan probabilitas tertinggi. Diuji pada C-MAPSS FD001 dan FD003; ELSTMNN mencapai MScore 5,71 (deviasi 0,19) dan RMSE 18,22 (deviasi 1,38) pada FD001, terbaik dibanding ANN, SVR, RVR, DCNN, ELM, EKF, ESKF, DLSTMNN, dan mengalahkan bagging secara signifikan (p=0,0029).</t>
-        </is>
-      </c>
-      <c r="L50" s="2" t="inlineStr">
         <is>
           <t>Menunjukkan ensemble LSTM + inferensi Bayesian yang memfit distribusi prediksi (prior/posterior) sebagai cara mengkuantifikasi ketidakpastian RUL dan meningkatkan generalisasi lintas-unit, relevan bagi dimensi ketidakpastian tesis; namun tidak memodelkan penyensoran/survival dan bukan domain membran, sehingga Pendukung.</t>
         </is>
@@ -3341,23 +2938,15 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="n">
-        <v>5</v>
+          <t>https://doi.org/10.1109/access.2020.3001013</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan prediksi RUL pompa roda gigi eksternal memakai Bayesian regularized RBF neural network (Trainbr-RBFNN). Sinyal vibrasi dari accelerated life test didenoise dengan VMD-Hilbert (dibandingkan EEMD/MEEMD), lalu fitur time/frequency/time-frequency domain difusikan dengan factor analysis menjadi degradation fusion index; indeks ini diprediksi dengan Holt two-parameter smoothing dan dilatih ke Trainbr-RBFNN untuk menaksir waktu kegagalan. Distribusi Weibull dua parameter dipakai untuk menaksir parameter keandalan dan RUL di bawah tegangan normal.</t>
+        </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/access.2020.3001013</t>
-        </is>
-      </c>
-      <c r="K51" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan prediksi RUL pompa roda gigi eksternal memakai Bayesian regularized RBF neural network (Trainbr-RBFNN). Sinyal vibrasi dari accelerated life test didenoise dengan VMD-Hilbert (dibandingkan EEMD/MEEMD), lalu fitur time/frequency/time-frequency domain difusikan dengan factor analysis menjadi degradation fusion index; indeks ini diprediksi dengan Holt two-parameter smoothing dan dilatih ke Trainbr-RBFNN untuk menaksir waktu kegagalan. Distribusi Weibull dua parameter dipakai untuk menaksir parameter keandalan dan RUL di bawah tegangan normal.</t>
-        </is>
-      </c>
-      <c r="L51" s="2" t="inlineStr">
         <is>
           <t>Menunjukkan pemanfaatan Bayesian-regularized neural network untuk RUL plus pemodelan distribusi waktu-kegagalan Weibull dua parameter dengan MLE dan acceleration model - kombinasi jaringan + Weibull yang dekat dengan kerangka tesis, tetapi tanpa pencensoringan eksplisit dan domainnya pompa, bukan membran.</t>
         </is>
@@ -3397,23 +2986,15 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.1016/j.jmsy.2020.11.005</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>Studi menerapkan Bayesian deep learning untuk estimasi RUL mesin turbofan, dengan inference via Hamiltonian Monte Carlo (HMC) dan variational inference (VI), lalu membandingkannya terhadap deep learning non-probabilistik. Kontribusi utamanya adalah memanfaatkan informasi ketidakpastian (varians prediksi) dalam pengambilan keputusan: distribusi RUL digeser sebesar b*sigma untuk meminimalkan fungsi biaya asimetris (score function), sehingga menurunkan total biaya. Model Bayesian mengungguli model non-probabilistik pada semua eksperimen untuk Score1, dan pendekatan pemanfaatan ketidakpastian memperbaiki Score2.</t>
+        </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.jmsy.2020.11.005</t>
-        </is>
-      </c>
-      <c r="K52" s="2" t="inlineStr">
-        <is>
-          <t>Studi menerapkan Bayesian deep learning untuk estimasi RUL mesin turbofan, dengan inference via Hamiltonian Monte Carlo (HMC) dan variational inference (VI), lalu membandingkannya terhadap deep learning non-probabilistik. Kontribusi utamanya adalah memanfaatkan informasi ketidakpastian (varians prediksi) dalam pengambilan keputusan: distribusi RUL digeser sebesar b*sigma untuk meminimalkan fungsi biaya asimetris (score function), sehingga menurunkan total biaya. Model Bayesian mengungguli model non-probabilistik pada semua eksperimen untuk Score1, dan pendekatan pemanfaatan ketidakpastian memperbaiki Score2.</t>
-        </is>
-      </c>
-      <c r="L52" s="2" t="inlineStr">
         <is>
           <t>Menunjukkan secara eksplisit bagaimana ketidakpastian RUL diterjemahkan menjadi keputusan biaya (cost-aware decision), pola yang sangat relevan untuk DSS tesis. Tetapi tidak memakai survival/penyensoran dan bukan domain membran.</t>
         </is>
@@ -3453,23 +3034,15 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>Inti-Domain</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.1109/access.2020.2976595</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>Makalah ini mengusulkan metode prediksi RUL berbasis Deep Convolutional Neural Network (DCNN) yang digabung dengan Bayesian optimization dan Adaptive Batch Normalization (AdaBN). Bayesian optimization dipakai untuk memilih struktur jaringan dan hyperparameter secara otomatis, sedangkan AdaBN dipakai untuk adaptasi domain lintas kondisi operasi. Metode divalidasi pada dataset simulasi degradasi mesin turbofan C-MAPSS dan mengalahkan grid search serta random search.</t>
+        </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/access.2020.2976595</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>Makalah ini mengusulkan metode prediksi RUL berbasis Deep Convolutional Neural Network (DCNN) yang digabung dengan Bayesian optimization dan Adaptive Batch Normalization (AdaBN). Bayesian optimization dipakai untuk memilih struktur jaringan dan hyperparameter secara otomatis, sedangkan AdaBN dipakai untuk adaptasi domain lintas kondisi operasi. Metode divalidasi pada dataset simulasi degradasi mesin turbofan C-MAPSS dan mengalahkan grid search serta random search.</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
         <is>
           <t>Memberi contoh strategi transfer/adaptasi domain berbiaya rendah (hanya fine-tuning parameter BN) untuk RUL lintas domain (FD001-FD004). Relevan ke tesis sebagai pembanding bagaimana 'pergeseran domain' ditangani tanpa memodelkan penyensoran, sehingga menegaskan celah bahwa adaptasi domain pada membran RO dengan data tersensor masih terbuka.</t>
         </is>
@@ -3509,23 +3082,15 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="n">
-        <v>7</v>
+          <t>https://doi.org/10.1109/access.2019.2919566</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>Artikel ini mengusulkan jaringan Directed Acyclic Graph (DAG) yang menggabungkan CNN dan LSTM secara paralel (bukan serial) untuk prediksi RUL. Dua jalur — jalur LSTM dan jalur CNN — tidak saling terkait tetapi keluarannya dijumlahkan secara element-wise lalu diteruskan ke LSTM kedua dan layer fully connected. Data diproses dengan sliding time window dan target RUL memakai fungsi piecewise-linear; divalidasi pada dataset C-MAPSS.</t>
+        </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/access.2019.2919566</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>Artikel ini mengusulkan jaringan Directed Acyclic Graph (DAG) yang menggabungkan CNN dan LSTM secara paralel (bukan serial) untuk prediksi RUL. Dua jalur — jalur LSTM dan jalur CNN — tidak saling terkait tetapi keluarannya dijumlahkan secara element-wise lalu diteruskan ke LSTM kedua dan layer fully connected. Data diproses dengan sliding time window dan target RUL memakai fungsi piecewise-linear; divalidasi pada dataset C-MAPSS.</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
         <is>
           <t>Menunjukkan arsitektur hibrida CNN+LSTM paralel berbasis DAG yang mengoreksi parameter kedua jalur dari galat prediksi secara holistik, dengan penanganan input timestamp lewat sliding time window. Relevan ke tesis sebagai pembanding arsitektur DL RUL, namun tanpa survival/penyensoran dan bukan domain membran.</t>
         </is>
@@ -3565,23 +3130,15 @@
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.1108/imds-03-2019-0195</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan model fusi untuk RUL baterai lithium-ion: particle filter (PF) sebagai inti dengan model double-exponential sebagai persamaan keadaan dan artificial neural network (ANN) sebagai persamaan observasi. PF memperbarui distribusi posterior parameter secara online sehingga RUL beserta PDF-nya dapat diestimasi; akurasi meningkat seiring bertambahnya siklus (error 17 siklus pada siklus ke-70 turun menjadi 2 siklus pada siklus ke-90).</t>
+        </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1108/imds-03-2019-0195</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan model fusi untuk RUL baterai lithium-ion: particle filter (PF) sebagai inti dengan model double-exponential sebagai persamaan keadaan dan artificial neural network (ANN) sebagai persamaan observasi. PF memperbarui distribusi posterior parameter secara online sehingga RUL beserta PDF-nya dapat diestimasi; akurasi meningkat seiring bertambahnya siklus (error 17 siklus pada siklus ke-70 turun menjadi 2 siklus pada siklus ke-90).</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
         <is>
           <t>Menunjukkan estimasi RUL berbasis Bayesian state estimation (particle filter) yang memberi ekspresi ketidakpastian (PDF), sekaligus mengatasi data kecil lewat koreksi posterior. Relevan bagi tesis sebagai contoh estimasi RUL probabilistik dengan data terbatas, meski tanpa penyensoran eksplisit dan bukan domain membran.</t>
         </is>
@@ -3621,23 +3178,15 @@
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>Inti-Domain</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.1109/tim.2019.2917735</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan kerangka prediksi RUL bearing yang menggabungkan representasi fitur dalam (Contractive Denoising Autoencoder, CDAE) dengan transfer learning (Transfer Component Analysis, TCA). CDAE mengekstrak fitur dari marginal spectrum Hilbert-Huang; korelasi Pearson menilai status kesehatan; TCA menyelaraskan distribusi fitur antar-bearing; LSSVM membangun model regresi RUL.</t>
+        </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/tim.2019.2917735</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan kerangka prediksi RUL bearing yang menggabungkan representasi fitur dalam (Contractive Denoising Autoencoder, CDAE) dengan transfer learning (Transfer Component Analysis, TCA). CDAE mengekstrak fitur dari marginal spectrum Hilbert-Huang; korelasi Pearson menilai status kesehatan; TCA menyelaraskan distribusi fitur antar-bearing; LSSVM membangun model regresi RUL.</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
         <is>
           <t>Menunjukkan transfer learning dapat mengatasi perbedaan distribusi data antar-unit dan data skala kecil — relevan untuk tesis pada sumbu small-data/transfer (mis. antar-modul membran); namun tanpa survival/censoring, tanpa kuantifikasi ketidakpastian penuh, dan bukan domain membran.</t>
         </is>
@@ -3677,23 +3226,15 @@
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.1016/j.dss.2019.113100</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan structured-effect neural network (SENN) untuk memprediksi RUL secara akurat sekaligus interpretable. SENN mendekomposisi prediksi menjadi tiga komponen: (1) baseline non-parametrik berupa probabilitas lifetime (conditional expectation Weibull atau log-normal, E[Z|Z&gt;t] - t), (2) kombinasi linear sensor, dan (3) komponen rekuren (LSTM) untuk menangkap non-linearitas. Parameter diestimasi via variational Bayesian inference (maximisasi ELBO), sehingga diperoleh distribusi posterior dan kuantifikasi ketidakpastian. Pada C-MAPSS, SENN mengalahkan model machine learning tradisional dan mendekati performa LSTM murni dengan interpretabilitas jauh lebih tinggi.</t>
+        </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.dss.2019.113100</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan structured-effect neural network (SENN) untuk memprediksi RUL secara akurat sekaligus interpretable. SENN mendekomposisi prediksi menjadi tiga komponen: (1) baseline non-parametrik berupa probabilitas lifetime (conditional expectation Weibull atau log-normal, E[Z|Z&gt;t] - t), (2) kombinasi linear sensor, dan (3) komponen rekuren (LSTM) untuk menangkap non-linearitas. Parameter diestimasi via variational Bayesian inference (maximisasi ELBO), sehingga diperoleh distribusi posterior dan kuantifikasi ketidakpastian. Pada C-MAPSS, SENN mengalahkan model machine learning tradisional dan mendekati performa LSTM murni dengan interpretabilitas jauh lebih tinggi.</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
         <is>
           <t>Sangat relevan bagi tesis: menggabungkan model kelangsungan hidup (Weibull/log-normal conditional residual life) dengan deep learning (LSTM) dalam satu kerangka interpretable dan Bayesian - tepat pada sumbu survival analysis + DL. Namun tidak memodelkan data tersensor (C-MAPSS run-to-failure) dan domainnya aero-engine, bukan membran.</t>
         </is>
@@ -3733,23 +3274,15 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>Konteks</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.1007/s13201-018-0821-8</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>Penelitian merancang dan membangun unit pemantauan status plant reverse osmosis (RO) berbasis embedded system untuk deteksi dini kerusakan dan pemeliharaan prediktif. Unit memantau parameter real-time (pH, TDS, laju alir feed/produk, tekanan, level tangki, daya) via sensor, menyimpan data ke smartphone/cloud, dan memakai Jaringan Saraf Tiruan (ANN) untuk memprediksi efisiensi membran serta peristiwa fouling/scaling. Sistem menghasilkan peringatan dini dan merekomendasikan tindakan pemeliharaan (chemical wash, water wash, penggantian membran); diuji pada plant 2000 LPH dan 10 desa di Rajasthan.</t>
+        </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1007/s13201-018-0821-8</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>Penelitian merancang dan membangun unit pemantauan status plant reverse osmosis (RO) berbasis embedded system untuk deteksi dini kerusakan dan pemeliharaan prediktif. Unit memantau parameter real-time (pH, TDS, laju alir feed/produk, tekanan, level tangki, daya) via sensor, menyimpan data ke smartphone/cloud, dan memakai Jaringan Saraf Tiruan (ANN) untuk memprediksi efisiensi membran serta peristiwa fouling/scaling. Sistem menghasilkan peringatan dini dan merekomendasikan tindakan pemeliharaan (chemical wash, water wash, penggantian membran); diuji pada plant 2000 LPH dan 10 desa di Rajasthan.</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
         <is>
           <t>Menunjukkan implementasi nyata sistem pemantauan prediktif pada plant RO/desalinasi (domain tesis) dan mengaitkannya ke tindakan pemeliharaan membran; namun tidak memprediksi RUL dan tidak memakai survival analysis/censoring, sehingga berperan sebagai konteks domain dan DSS.</t>
         </is>
@@ -3789,23 +3322,15 @@
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.1016/j.ress.2016.07.019</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan pendekatan prognostik data-driven untuk estimasi RUL peralatan dalam fleet heterogen yang bekerja pada kondisi operasi bervariasi. Tiga fase: (1) identifikasi level degradasi (state) via unsupervised ensemble clustering; (2) estimasi parameter distribusi Weibull diskrit transisi antar-state dengan MLE dan kuantifikasi ketidakpastiannya via Fisher Information Matrix (FIM); (3) estimasi RUL peralatan baru via simulasi Monte Carlo langsung. Dianalisis pada dua studi kasus (kapasitor elektrolit aluminium dan mesin turbofan) dan terbukti lebih baik daripada pendekatan fuzzy similarity.</t>
+        </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.ress.2016.07.019</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan pendekatan prognostik data-driven untuk estimasi RUL peralatan dalam fleet heterogen yang bekerja pada kondisi operasi bervariasi. Tiga fase: (1) identifikasi level degradasi (state) via unsupervised ensemble clustering; (2) estimasi parameter distribusi Weibull diskrit transisi antar-state dengan MLE dan kuantifikasi ketidakpastiannya via Fisher Information Matrix (FIM); (3) estimasi RUL peralatan baru via simulasi Monte Carlo langsung. Dianalisis pada dua studi kasus (kapasitor elektrolit aluminium dan mesin turbofan) dan terbukti lebih baik daripada pendekatan fuzzy similarity.</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
         <is>
           <t>Sangat relevan ke poros survival/Weibull tesis: pemodelan transisi state dengan distribusi Weibull diskrit dan penanganan eksplisit data right-censored (trajektori run-to-failure tak lengkap) di dalam likelihood, plus kuantifikasi ketidakpastian dan strategi fleet/hierarchical. Namun tanpa deep learning dan domainnya bukan membran.</t>
         </is>
@@ -3845,23 +3370,15 @@
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="n">
-        <v>6</v>
+          <t>https://doi.org/10.1016/j.ymssp.2012.02.015</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan metode tiga tahap untuk menilai degradasi kinerja mesin dan memprediksi RUL hanya dari data kondisi operasi normal. Tahap pertama membangun model identifikasi ARMA dan indeks degradasi dari RMS residual; tahap kedua membangun Cox proportional hazard model (PHM) untuk mengestimasi fungsi survival; tahap ketiga memakai support vector regression dengan prediksi multi-langkah untuk meramalkan RUL. Metode divalidasi pada data pemantauan kompresor low methane dan mencapai akurasi RUL 87,5% (RMSE survival 0,33674).</t>
+        </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.ymssp.2012.02.015</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan metode tiga tahap untuk menilai degradasi kinerja mesin dan memprediksi RUL hanya dari data kondisi operasi normal. Tahap pertama membangun model identifikasi ARMA dan indeks degradasi dari RMS residual; tahap kedua membangun Cox proportional hazard model (PHM) untuk mengestimasi fungsi survival; tahap ketiga memakai support vector regression dengan prediksi multi-langkah untuk meramalkan RUL. Metode divalidasi pada data pemantauan kompresor low methane dan mencapai akurasi RUL 87,5% (RMSE survival 0,33674).</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
         <is>
           <t>Preseden metodologis paling langsung untuk kombinasi survival analysis + machine learning pada RUL: Cox PHM yang secara eksplisit memodelkan data tersensor (seri biner 0/1 dari ambang batas) dipadukan dengan SVM. Relevan bagi poros 'survival analysis' tesis, tetapi domainnya mesin kompresor (bukan membran/RO) sehingga tidak menyentuh poros domain.</t>
         </is>
@@ -3901,23 +3418,15 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.1109/lsens.2026.3673123</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan CMA-WFT (cross-modal attention-Weibull fusion transformer), arsitektur untuk estimasi RUL pada liner press industri dengan menggabungkan encoder temporal per-modalitas, cross-modal attention, dan head survival Weibull parametrik. Setiap modalitas (vibrasi, temperatur, gap/displacement) dikodekan terpisah lalu digabung via cross-modal attention; head Weibull memprediksi parameter shape (k) dan scale (lambda) sehingga menghasilkan estimasi RUL titik sekaligus kurva reliabilitas, dan menangani pengamatan tersensor kanan secara alami. Validasi pada data sintetis, data industri nyata (gear-press), dan benchmark ATE (turbofan); CMA-WFT mengalahkan RF, SVM, RNN-Weibull, dan LSTM-Weibull (akurasi RT 84% vs 72%).</t>
+        </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/lsens.2026.3673123</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan CMA-WFT (cross-modal attention-Weibull fusion transformer), arsitektur untuk estimasi RUL pada liner press industri dengan menggabungkan encoder temporal per-modalitas, cross-modal attention, dan head survival Weibull parametrik. Setiap modalitas (vibrasi, temperatur, gap/displacement) dikodekan terpisah lalu digabung via cross-modal attention; head Weibull memprediksi parameter shape (k) dan scale (lambda) sehingga menghasilkan estimasi RUL titik sekaligus kurva reliabilitas, dan menangani pengamatan tersensor kanan secara alami. Validasi pada data sintetis, data industri nyata (gear-press), dan benchmark ATE (turbofan); CMA-WFT mengalahkan RF, SVM, RNN-Weibull, dan LSTM-Weibull (akurasi RT 84% vs 72%).</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
         <is>
           <t>Memberi contoh integrasi multisensor + transformer + survival Weibull yang menangani data tersensor kanan sekaligus mengkuantifikasi ketidakpastian (kurva reliabilitas) - sangat dekat dengan kebutuhan metode tesis, meski domainnya liner press/turbofan (bukan membran).</t>
         </is>
@@ -3957,23 +3466,15 @@
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="n">
-        <v>6</v>
+          <t>https://doi.org/10.1007/s42452-026-08390-x</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>Paper mengusulkan pipeline deep learning berbasis graph untuk prediksi RUL/keausan pahat milling CNC memakai sinyal getaran, beban spindel, dan gaya potong. Fitur time-domain dan frequency-domain diubah menjadi graph dengan sisi korelasi dan temporal, lalu tiga arsitektur GNN (GCN, GRN, GAT) dilatih dengan Random Forest Regressor dan hyperparameter tuning Optuna/Bayesian Optimization pada 120 run pemesinan.</t>
+        </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1007/s42452-026-08390-x</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>Paper mengusulkan pipeline deep learning berbasis graph untuk prediksi RUL/keausan pahat milling CNC memakai sinyal getaran, beban spindel, dan gaya potong. Fitur time-domain dan frequency-domain diubah menjadi graph dengan sisi korelasi dan temporal, lalu tiga arsitektur GNN (GCN, GRN, GAT) dilatih dengan Random Forest Regressor dan hyperparameter tuning Optuna/Bayesian Optimization pada 120 run pemesinan.</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
         <is>
           <t>Menyediakan kerangka evaluasi terpadu GNN (GCN/GRN/GAT) untuk RUL pahat milling dengan konstruksi graph korelasi-temporal yang lebih sparse dan interpretable; relevan bagi tesis sebagai contoh model representasi struktur/temporal dan sebagai pembanding non-survival.</t>
         </is>
@@ -4013,23 +3514,15 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.1002/qre.70386</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan Weibull Variational Autoencoder (WVAE) untuk prediksi RUL, yaitu VAE yang latent space-nya mengikuti distribusi Weibull sehingga bisa mempelajari bentuk dan skala distribusi kegagalan langsung dari riwayat kegagalan. Fungsi loss gabungan MSE ditambah negative log-likelihood Weibull menjaga akurasi titik sekaligus kesetiaan distribusi, sementara Monte Carlo Dropout memberi interval kepercayaan 95%. Validasi pada data simulasi (tiga tipe kegagalan: infant mortality, random, wear-out, dengan tiga tingkat noise) dan dataset lapangan Backblaze hard drive menunjukkan WVAE konsisten dengan distribusi kegagalan historis dan mengalahkan baseline pada CRPS.</t>
+        </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1002/qre.70386</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan Weibull Variational Autoencoder (WVAE) untuk prediksi RUL, yaitu VAE yang latent space-nya mengikuti distribusi Weibull sehingga bisa mempelajari bentuk dan skala distribusi kegagalan langsung dari riwayat kegagalan. Fungsi loss gabungan MSE ditambah negative log-likelihood Weibull menjaga akurasi titik sekaligus kesetiaan distribusi, sementara Monte Carlo Dropout memberi interval kepercayaan 95%. Validasi pada data simulasi (tiga tipe kegagalan: infant mortality, random, wear-out, dengan tiga tingkat noise) dan dataset lapangan Backblaze hard drive menunjukkan WVAE konsisten dengan distribusi kegagalan historis dan mengalahkan baseline pada CRPS.</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
         <is>
           <t>Menyatukan model berbasis distribusi Weibull dengan arsitektur deep generative untuk RUL, tepat pada sumbu metode tesis (survival/Weibull + kuantifikasi ketidakpastian), namun sengaja mengabaikan observasi tersensor (right-censored) dan domainnya bukan membran.</t>
         </is>
@@ -4069,23 +3562,15 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>Konteks</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.2166/wst.2026.234</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>Review penerapan machine learning (ML)/AI pada membran nanofiltrasi (NF) untuk aplikasi air, dengan menganalisis 100 publikasi NF-ML selama 10 tahun. Membahas tiga domain: optimasi fabrikasi, prediksi kinerja (flux, rejection, permeability), dan diagnosis/mitigasi fouling. Menyoroti tantangan kelangkaan dan heterogenitas data, kurangnya validasi eksternal, dan prospek reinforcement learning untuk kontrol adaptif real-time serta kerangka hybrid ML-mekanistik.</t>
+        </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.2166/wst.2026.234</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>Review penerapan machine learning (ML)/AI pada membran nanofiltrasi (NF) untuk aplikasi air, dengan menganalisis 100 publikasi NF-ML selama 10 tahun. Membahas tiga domain: optimasi fabrikasi, prediksi kinerja (flux, rejection, permeability), dan diagnosis/mitigasi fouling. Menyoroti tantangan kelangkaan dan heterogenitas data, kurangnya validasi eksternal, dan prospek reinforcement learning untuk kontrol adaptif real-time serta kerangka hybrid ML-mekanistik.</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
         <is>
           <t>Memetakan algoritma ML yang berlaku untuk membran (NF/RO): RF, XGBoost, CNN, LSTM, RL, ANFIS, GP; serta menegaskan kelangkaan data, transferabilitas, dan kuantifikasi ketidakpastian sebagai celah riset. Relevan bagi tesis yang menerapkan ML pada RUL membran dan menghadapi small-data.</t>
         </is>
@@ -4125,23 +3610,15 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>Inti-Domain</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.3390/eng7030106</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>Studi membandingkan MLR, ANN, dan SVR untuk memprediksi transmembrane pressure (TMP, indikator fouling) di pabrik desalinasi air laut Boujdour dari lima parameter input (temperatur, turbiditas, pH, konduktivitas, laju alir umpan). Dataset asli 195 pengamatan harian; karena tidak ada stempel waktu, masalah dibingkai sebagai state-to-TMP (bukan peramalan kronologis). SMOGN menambah data latih menjadi ~1961 sampel dengan set uji 39 observasi nyata yang bebas kebocoran; SVR memberi akurasi terbaik (R2 test=0,435) namun dengan interval bootstrap 95 % yang lebar.</t>
+        </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/eng7030106</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>Studi membandingkan MLR, ANN, dan SVR untuk memprediksi transmembrane pressure (TMP, indikator fouling) di pabrik desalinasi air laut Boujdour dari lima parameter input (temperatur, turbiditas, pH, konduktivitas, laju alir umpan). Dataset asli 195 pengamatan harian; karena tidak ada stempel waktu, masalah dibingkai sebagai state-to-TMP (bukan peramalan kronologis). SMOGN menambah data latih menjadi ~1961 sampel dengan set uji 39 observasi nyata yang bebas kebocoran; SVR memberi akurasi terbaik (R2 test=0,435) namun dengan interval bootstrap 95 % yang lebar.</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
         <is>
           <t>Menegaskan bahwa prediksi fouling/tekanan membran di domain RO masih terbatas oleh ukuran data dan tidak adanya indeks waktu, dan menyoroti pentingnya kuantifikasi ketidakpastian serta kontrol kebocoran data; tidak memakai survival/pencensoringan maupun RUL.</t>
         </is>
@@ -4181,23 +3658,15 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.36001/ijphm.2025.v16i2.4260</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>Artikel mengadaptasi arsitektur Transformer DAST dan LSTM menjadi ordinal regression (OR) agar mampu menangani data tersensor kanan (right-censored) pada prediksi RUL. OR mengodekan RUL menjadi vektor status masa depan (0/1/-) dan loss BCE dimask pada koordinat tersensor, memungkinkan pemanfaatan unit yang diganti sebelum gagal. Dievaluasi pada C-MAPSS dan N-CMAPSS dengan tingkat pencensoringan artifisial 0-90%, metode ini setara SOTA pada data tanpa sensor dan lebih unggul pada pencensoringan tinggi pada dataset besar; conformal prediction dipakai untuk interval kepercayaan.</t>
+        </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.36001/ijphm.2025.v16i2.4260</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>Artikel mengadaptasi arsitektur Transformer DAST dan LSTM menjadi ordinal regression (OR) agar mampu menangani data tersensor kanan (right-censored) pada prediksi RUL. OR mengodekan RUL menjadi vektor status masa depan (0/1/-) dan loss BCE dimask pada koordinat tersensor, memungkinkan pemanfaatan unit yang diganti sebelum gagal. Dievaluasi pada C-MAPSS dan N-CMAPSS dengan tingkat pencensoringan artifisial 0-90%, metode ini setara SOTA pada data tanpa sensor dan lebih unggul pada pencensoringan tinggi pada dataset besar; conformal prediction dipakai untuk interval kepercayaan.</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
         <is>
           <t>Menunjukkan cara menggabungkan arsitektur deep-learning RUL modern (LSTM/Transformer) dengan penanganan data tersensor eksplisit dan interval prediksi conformal - dua komponen inti metode tesis, meski domainnya bukan membran.</t>
         </is>
@@ -4237,23 +3706,15 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>Inti-Domain</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.3390/machines13090789</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>Paper mengusulkan DMFR (Deep Multimodal Fine-tuning Regression), framework RUL yang menggabungkan multimodal (deret waktu + citra recurrence plot) dengan transfer learning dua tahap (pre-training terawasi + fine-tuning). Dievaluasi pada dataset NASA C-MAPSS turbofan dengan 12 tugas transfer lintas operating condition/fault mode; model melaporkan RMSE/MAE/R2/Score terbaik antar baseline (CNN, DNN, GRU, LSTM, RNN, TCN) dan menyajikan interval kepercayaan 95%.</t>
+        </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/machines13090789</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>Paper mengusulkan DMFR (Deep Multimodal Fine-tuning Regression), framework RUL yang menggabungkan multimodal (deret waktu + citra recurrence plot) dengan transfer learning dua tahap (pre-training terawasi + fine-tuning). Dievaluasi pada dataset NASA C-MAPSS turbofan dengan 12 tugas transfer lintas operating condition/fault mode; model melaporkan RMSE/MAE/R2/Score terbaik antar baseline (CNN, DNN, GRU, LSTM, RNN, TCN) dan menyajikan interval kepercayaan 95%.</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
         <is>
           <t>Menunjukkan bagaimana transfer learning dan fusi multimodal menangani skenario small-sample dan cross-condition pada RUL; relevan bagi tesis RUL membran yang menghadapi kelangkaan data dan pergeseran kondisi operasi (cocok untuk strategi small-data/transfer).</t>
         </is>
@@ -4293,23 +3754,15 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>Inti-Domain</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.3390/pr13082352</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>Studi membangun kerangka prediksi fouling membran pada membrane bioreactor (MBR) skala penuh dengan menggabungkan feature engineering berbasis AI dan explainable AI (XAI). Target prediksi diubah menjadi specific flux (flux/TMP) sebagai indikator permeabilitas, ditambah COD removal efficiency sebagai indikator kinerja biologis, dan moving average untuk menangkap dinamika fouling temporal. Dari 194 catatan harian, CatBoost paling akurat (R2 = 0,8374), dan SHAP mengidentifikasi rasio F/M dan MLSS sebagai variabel paling berpengaruh.</t>
+        </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/pr13082352</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>Studi membangun kerangka prediksi fouling membran pada membrane bioreactor (MBR) skala penuh dengan menggabungkan feature engineering berbasis AI dan explainable AI (XAI). Target prediksi diubah menjadi specific flux (flux/TMP) sebagai indikator permeabilitas, ditambah COD removal efficiency sebagai indikator kinerja biologis, dan moving average untuk menangkap dinamika fouling temporal. Dari 194 catatan harian, CatBoost paling akurat (R2 = 0,8374), dan SHAP mengidentifikasi rasio F/M dan MLSS sebagai variabel paling berpengaruh.</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
         <is>
           <t>Memberi bukti bahwa prediksi degradasi membran (specific flux) yang interpretable dapat dilakukan pada data lapangan skala penuh yang kecil dan bising, relevan dengan sumbu domain tesis (membran/fouling dan small-data), namun tidak memakai RUL eksplisit, survival analysis, maupun pencensoringan.</t>
         </is>
@@ -4349,23 +3802,15 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.1007/s42979-025-04291-9</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>Artikel ini menyajikan kerangka predictive maintenance modular berbasis survival analysis untuk mengestimasi RUL komponen industri, digabung algoritma optimasi penjadwalan Simulated Annealing. Empat model survival dievaluasi (Cox PH, Random Survival Forest, Gradient Boosting Survival Analysis, Survival SVM), dengan GBSA paling robust karena tahan overfitting dan mampu menangkap degradasi nonlinier. Kerangka divalidasi pada data degradasi elektroda las (nyata) dan dataset sintetis Microsoft Azure, menurunkan downtime 25% dibanding metode tak teroptimasi.</t>
+        </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1007/s42979-025-04291-9</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>Artikel ini menyajikan kerangka predictive maintenance modular berbasis survival analysis untuk mengestimasi RUL komponen industri, digabung algoritma optimasi penjadwalan Simulated Annealing. Empat model survival dievaluasi (Cox PH, Random Survival Forest, Gradient Boosting Survival Analysis, Survival SVM), dengan GBSA paling robust karena tahan overfitting dan mampu menangkap degradasi nonlinier. Kerangka divalidasi pada data degradasi elektroda las (nyata) dan dataset sintetis Microsoft Azure, menurunkan downtime 25% dibanding metode tak teroptimasi.</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
         <is>
           <t>Langkah paling dekat dengan tesis: secara eksplisit mengintegrasikan data tersensor ke dalam model survival (Cox PH/RSF/GBSA/Survival SVM) untuk RUL, lalu menghubungkannya ke keputusan penjadwalan pemeliharaan. Relevan sebagai preseden Inti-Metode; celah yang tersisa adalah belum diterapkan pada membran/RO dan belum memakai deep learning survival (mis. DeepHit/DeepSurv) pada data membran.</t>
         </is>
@@ -4405,23 +3850,15 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.3390/fractalfract8080485</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan model degradation-threshold-shock (DTS) untuk memprediksi RUL komponen penyimpanan daya (baterai LiFePO4 dan superkapasitor). Proses steady degradation dimodelkan dengan fractional Weibull process (fWp) yang memiliki long-range dependence dan heavy tail, sedangkan guncangan acak (shock) dimodelkan dengan non-homogeneous compound Poisson process (NHCP) berintensitas naik; koefisien drift dan diffusion diperbarui secara acak untuk menangkap gangguan lingkungan. RUL dihitung via Monte Carlo sebagai waktu first-passage melewati failure threshold (FT), dan model mengalahkan CNN, EMD-GRU, DTS-BM, serta adaptive FBM pada protokol DST dan UDDS.</t>
+        </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/fractalfract8080485</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan model degradation-threshold-shock (DTS) untuk memprediksi RUL komponen penyimpanan daya (baterai LiFePO4 dan superkapasitor). Proses steady degradation dimodelkan dengan fractional Weibull process (fWp) yang memiliki long-range dependence dan heavy tail, sedangkan guncangan acak (shock) dimodelkan dengan non-homogeneous compound Poisson process (NHCP) berintensitas naik; koefisien drift dan diffusion diperbarui secara acak untuk menangkap gangguan lingkungan. RUL dihitung via Monte Carlo sebagai waktu first-passage melewati failure threshold (FT), dan model mengalahkan CNN, EMD-GRU, DTS-BM, serta adaptive FBM pada protokol DST dan UDDS.</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
         <is>
           <t>Memberi preseden model degradasi stokastik berbasis Weibull + ambang kegagalan (first-passage) untuk RUL sebagai alternatif dari deep learning - relevan dengan pilar A (analisis failure-time) pada tesis, tetapi tidak memodelkan data tersensor dan domainnya komponen penyimpanan daya, bukan membran.</t>
         </is>
@@ -4461,23 +3898,15 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="n">
-        <v>6</v>
+          <t>https://doi.org/10.3390/batteries10030106</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>Penelitian ini memprediksi Remaining Useful Life (RUL) baterai lithium-ion menggunakan dua arsitektur deep learning hybrid: CLDNN (CNN+LSTM+DNN) dan Temporal Transformer (Transformer+LSTM). Memakai dataset Toyota Research Institute berisi 124 sel LFP/graphite yang disiklus hingga gagal, model dioptimasi dengan Bayesian hyperparameter tuning dan menghasilkan MAE 84,012 (CLDNN) serta 85,134 (TT), mengalahkan beberapa pendekatan mapan dengan perbaikan MAPE 4,01-7,12%.</t>
+        </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/batteries10030106</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>Penelitian ini memprediksi Remaining Useful Life (RUL) baterai lithium-ion menggunakan dua arsitektur deep learning hybrid: CLDNN (CNN+LSTM+DNN) dan Temporal Transformer (Transformer+LSTM). Memakai dataset Toyota Research Institute berisi 124 sel LFP/graphite yang disiklus hingga gagal, model dioptimasi dengan Bayesian hyperparameter tuning dan menghasilkan MAE 84,012 (CLDNN) serta 85,134 (TT), mengalahkan beberapa pendekatan mapan dengan perbaikan MAPE 4,01-7,12%.</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
         <is>
           <t>Mendemonstrasikan bahwa arsitektur hybrid CNN-LSTM dan Transformer-LSTM yang dioptimasi Bayesian dapat memprediksi RUL baterai (dalam jumlah siklus) secara akurat dan efisien untuk BMS; menjadi baseline deep learning RUL non-censored yang relevan sebagai pembanding bagi tesis yang menambahkan lapisan survival analysis.</t>
         </is>
@@ -4517,23 +3946,15 @@
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.1007/s44196-024-00639-w</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>Penelitian ini mengusulkan metode prediksi Remaining Useful Life (RUL) mesin pesawat berbasis deep learning yang menggabungkan CNN untuk ekstraksi fitur lokal dari data sensor multivariabel, LSTM untuk pemodelan dependensi temporal, dan mekanisme self-attention agar LSTM lebih fokus pada fitur penting hasil rekonstruksi CNN. Model dilatih dan diuji pada empat subset dataset NASA C-MAPSS (FD001-FD004) dengan target RUL piecewise linear berambang 100 dan sliding window 40, lalu divalidasi melalui studi ablasi dan perbandingan model. Hasil terbaik diperoleh model usulan dengan RMSE 15.977 (FD001), 14.452 (FD002), 13.907 (FD003), dan 16.637 (FD004), mengungguli CNN, LSTM, CNN-LSTM, BP, GRU, CNN-GRU, DCNN, dan TCNN.</t>
+        </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1007/s44196-024-00639-w</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>Penelitian ini mengusulkan metode prediksi Remaining Useful Life (RUL) mesin pesawat berbasis deep learning yang menggabungkan CNN untuk ekstraksi fitur lokal dari data sensor multivariabel, LSTM untuk pemodelan dependensi temporal, dan mekanisme self-attention agar LSTM lebih fokus pada fitur penting hasil rekonstruksi CNN. Model dilatih dan diuji pada empat subset dataset NASA C-MAPSS (FD001-FD004) dengan target RUL piecewise linear berambang 100 dan sliding window 40, lalu divalidasi melalui studi ablasi dan perbandingan model. Hasil terbaik diperoleh model usulan dengan RMSE 15.977 (FD001), 14.452 (FD002), 13.907 (FD003), dan 16.637 (FD004), mengungguli CNN, LSTM, CNN-LSTM, BP, GRU, CNN-GRU, DCNN, dan TCNN.</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr">
         <is>
           <t>Menunjukkan bahwa penambahan mekanisme self-attention pada arsitektur CNN-LSTM meningkatkan akurasi point-prediction RUL pada benchmark C-MAPSS, namun tanpa pemodelan data tersensor, kuantifikasi ketidakpastian, maupun keputusan pemeliharaan. Paper ini memperkuat argumen tesis bahwa integrasi survival analysis (censoring/hazard) dengan deep learning masih merupakan celah terbuka; domainnya aero-engine, bukan membran/RO.</t>
         </is>
@@ -4573,23 +3994,15 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>Konteks</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="n">
-        <v>4</v>
+          <t>https://doi.org/10.1016/j.clwat.2024.100041</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengevaluasi fouling dan efisiensi separasi tiga membran berbasis MXene pada keramik (MX-CM, PDMX-CM, SPDMX-CM) untuk emulsi minyak-dalam-air. Pendekatan menggabungkan uji reliabilitas/kenormalan/stationeritas (ADF, PP, Jarque-Bera, ACF/PACF) dengan machine learning yang dijelaskan memakai SHAP untuk menafsirkan kontribusi fitur (Cycle, PDMX-CM, MX-CM). SPDMX-CM paling stabil dan tahan fouling, tetapi studi tidak memprediksi RUL maupun waktu kegagalan.</t>
+        </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.clwat.2024.100041</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengevaluasi fouling dan efisiensi separasi tiga membran berbasis MXene pada keramik (MX-CM, PDMX-CM, SPDMX-CM) untuk emulsi minyak-dalam-air. Pendekatan menggabungkan uji reliabilitas/kenormalan/stationeritas (ADF, PP, Jarque-Bera, ACF/PACF) dengan machine learning yang dijelaskan memakai SHAP untuk menafsirkan kontribusi fitur (Cycle, PDMX-CM, MX-CM). SPDMX-CM paling stabil dan tahan fouling, tetapi studi tidak memprediksi RUL maupun waktu kegagalan.</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
         <is>
           <t>Memberi konteks domain membran/desalinasi dan fouling sekaligus contoh penanganan small-data (15 observasi) dengan uji reliabilitas/stationeritas dan explainability SHAP - berguna bagi tesis untuk justifikasi praproses dan interpretabilitas, tetapi tanpa RUL/survival/pencensoringan sehingga tidak menyumbang kerangka inti.</t>
         </is>
@@ -4629,23 +4042,15 @@
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>Konteks</t>
-        </is>
-      </c>
-      <c r="I74" s="2" t="n">
-        <v>6</v>
+          <t>https://doi.org/10.5829/ije.2023.36.04a.09</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>Studi eksperimental material fabrikasi membran komposit graphene oxide-silika (GO/SiO2-Psf) dengan metode phase inversion untuk desalinasi air laut dan pengolahan air limbah zat warna. Variasi konsentrasi TEOS (0,6; 0,8; 1,0; 1,2 ml) diteliti terhadap sifat hidrofilik (contact angle), morfologi (SEM), kristalinitas (XRD), gugus fungsi (FTIR), antibakteri (E. coli &amp; S. aureus), salt-rejection NaCl, dan filtrasi metilen biru. Membran TEOS 0,8 ml paling optimal: salt-rejection 67,22% dan adsorpsi metilen biru terbaik.</t>
+        </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.5829/ije.2023.36.04a.09</t>
-        </is>
-      </c>
-      <c r="K74" s="2" t="inlineStr">
-        <is>
-          <t>Studi eksperimental material fabrikasi membran komposit graphene oxide-silika (GO/SiO2-Psf) dengan metode phase inversion untuk desalinasi air laut dan pengolahan air limbah zat warna. Variasi konsentrasi TEOS (0,6; 0,8; 1,0; 1,2 ml) diteliti terhadap sifat hidrofilik (contact angle), morfologi (SEM), kristalinitas (XRD), gugus fungsi (FTIR), antibakteri (E. coli &amp; S. aureus), salt-rejection NaCl, dan filtrasi metilen biru. Membran TEOS 0,8 ml paling optimal: salt-rejection 67,22% dan adsorpsi metilen biru terbaik.</t>
-        </is>
-      </c>
-      <c r="L74" s="2" t="inlineStr">
         <is>
           <t>Memberi konteks domain tentang jenis, fabrikasi, dan karakteristik kinerja membran (GO/SiO2-Psf) untuk desalinasi/zat warna - sebagai latar belakang material membran pada tesis, tetapi sama sekali tidak menyentuh RUL, prognostik, survival analysis, atau pencensoringan.</t>
         </is>
@@ -4685,23 +4090,15 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>Konteks</t>
-        </is>
-      </c>
-      <c r="I75" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.3390/environments10070127</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>Review kritis penerapan machine learning pada sistem membrane bioreactor (MBR) untuk pengolahan air limbah lanjut. Membahas algoritma ML (ANN, SVM, RF, RL, PLSR, ANFIS, DL), aplikasinya untuk prediksi fouling membran (TMP/flux), kontrol dan optimasi, serta deteksi dini kegagalan, sekaligus mengidentifikasi tantangan data quality, interpretabilitas, dan transferabilitas. Menutup dengan rekomendasi integrasi big data/IoT dan model hybrid.</t>
+        </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/environments10070127</t>
-        </is>
-      </c>
-      <c r="K75" s="2" t="inlineStr">
-        <is>
-          <t>Review kritis penerapan machine learning pada sistem membrane bioreactor (MBR) untuk pengolahan air limbah lanjut. Membahas algoritma ML (ANN, SVM, RF, RL, PLSR, ANFIS, DL), aplikasinya untuk prediksi fouling membran (TMP/flux), kontrol dan optimasi, serta deteksi dini kegagalan, sekaligus mengidentifikasi tantangan data quality, interpretabilitas, dan transferabilitas. Menutup dengan rekomendasi integrasi big data/IoT dan model hybrid.</t>
-        </is>
-      </c>
-      <c r="L75" s="2" t="inlineStr">
         <is>
           <t>Memetakan lanskap penerapan ML pada domain membran/desalinasi (fouling, TMP, kontrol) dan secara eksplisit menandai transferabilitas, keterbatasan data berlabel, dan interpretabilitas sebagai celah riset - ketiganya concern langsung tesis pada RUL membran.</t>
         </is>
@@ -4741,23 +4138,15 @@
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>Inti-Domain</t>
-        </is>
-      </c>
-      <c r="I76" s="2" t="n">
-        <v>6</v>
+          <t>https://doi.org/10.3390/sym14061111</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>Artikel mengusulkan skema prediksi RUL pompa roda gigi (gear pump) hidraulik yang menggabungkan deep convolutional autoencoder (DCAE) dan multi-layer Bi-LSTM. Tahap pertama membangun health indicator (HI) secara tanpa supervisi: DCAE 1D simetris mengekstraksi fitur sinyal getaran, SOM mereduksi vektor fitur C6 (100 dimensi), dan HI dihitung sebagai minimum quantization error (MQE). Tahap kedua memakai nilai HI sebagai label otomatis (self-labeling) pada data getaran mentah untuk melatih Bi-LSTM end-to-end yang keluarannya adalah nilai RUL. Validasi memakai data siklus hidup penuh dari uji hidup dipercepat 4 pompa roda gigi; HI yang dibangun unggul pada monotonicity/korelasi dan prediksi RUL lebih akurat dibanding dua metode pelabelan pembanding.</t>
+        </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/sym14061111</t>
-        </is>
-      </c>
-      <c r="K76" s="2" t="inlineStr">
-        <is>
-          <t>Artikel mengusulkan skema prediksi RUL pompa roda gigi (gear pump) hidraulik yang menggabungkan deep convolutional autoencoder (DCAE) dan multi-layer Bi-LSTM. Tahap pertama membangun health indicator (HI) secara tanpa supervisi: DCAE 1D simetris mengekstraksi fitur sinyal getaran, SOM mereduksi vektor fitur C6 (100 dimensi), dan HI dihitung sebagai minimum quantization error (MQE). Tahap kedua memakai nilai HI sebagai label otomatis (self-labeling) pada data getaran mentah untuk melatih Bi-LSTM end-to-end yang keluarannya adalah nilai RUL. Validasi memakai data siklus hidup penuh dari uji hidup dipercepat 4 pompa roda gigi; HI yang dibangun unggul pada monotonicity/korelasi dan prediksi RUL lebih akurat dibanding dua metode pelabelan pembanding.</t>
-        </is>
-      </c>
-      <c r="L76" s="2" t="inlineStr">
         <is>
           <t>Memberi contoh pipeline DL end-to-end untuk RUL (autoencoder konvolusional + SOM untuk HI self-labeled + Bi-LSTM) pada peralatan dengan dataset siklus hidup yang langka melalui uji hidup dipercepat, relevan sebagai pembanding metode DL RUL dan strategi small-data pada tesis. Namun tidak memodelkan data tersensor/survival, tidak mengkuantifikasi ketidakpastian, dan domainnya bukan membran/RO, sehingga tidak menutup celah integrasi survival analysis + DL tersensor pada membran desalinasi.</t>
         </is>
@@ -4797,23 +4186,15 @@
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.36001/ijphm.2022.v13i1.3072</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengevaluasi tiga metodologi prognostik probabilistik data-driven untuk estimasi Remaining Useful Life (dalam satuan remaining flights) sistem rem pesawat komersial yang dipantau ketebalannya secara kontinu: Bayesian Linear Regression (BLR), Non-Homogeneous Hidden Semi Markov Model (NHHSMM), dan Bootstrapped Artificial Neural Network (BNN). Dataset riil (blind) dari armada wide-body sebuah maskapai Eropa berisi 27 riwayat degradasi lengkap, dan model diuji via skema leave-two-out termasuk tiga brake outlier. BNN paling unggul (MAPE &lt;10%, CI tersempit, Prognostic Horizon 0,75) dan bahkan model paling sederhana pun membutuhkan kuantifikasi ketidakpastian untuk menangani stochasticity dan outlier.</t>
+        </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.36001/ijphm.2022.v13i1.3072</t>
-        </is>
-      </c>
-      <c r="K77" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengevaluasi tiga metodologi prognostik probabilistik data-driven untuk estimasi Remaining Useful Life (dalam satuan remaining flights) sistem rem pesawat komersial yang dipantau ketebalannya secara kontinu: Bayesian Linear Regression (BLR), Non-Homogeneous Hidden Semi Markov Model (NHHSMM), dan Bootstrapped Artificial Neural Network (BNN). Dataset riil (blind) dari armada wide-body sebuah maskapai Eropa berisi 27 riwayat degradasi lengkap, dan model diuji via skema leave-two-out termasuk tiga brake outlier. BNN paling unggul (MAPE &lt;10%, CI tersempit, Prognostic Horizon 0,75) dan bahkan model paling sederhana pun membutuhkan kuantifikasi ketidakpastian untuk menangani stochasticity dan outlier.</t>
-        </is>
-      </c>
-      <c r="L77" s="2" t="inlineStr">
         <is>
           <t>Menunjukkan pentingnya kuantifikasi ketidakpastian (interval kepercayaan) dalam prognostik RUL pada dataset riil kecil, dan bahwa model reliabilitas semi-Markov (NHHSMM) maupun Bayesian (BLR) dapat dibandingkan secara langsung - relevan bagi pilar C (Bayesian &amp; Uncertainty) pada tesis; namun tidak memodelkan data tersensor (riwayat tidak lengkap justru dibuang) dan domainnya rem pesawat, bukan membran.</t>
         </is>
@@ -4853,23 +4234,15 @@
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>Konteks</t>
-        </is>
-      </c>
-      <c r="I78" s="2" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.1016/j.rineng.2022.100611</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>Paper mengembangkan membran forward osmosis (FO) berbasis selulosa asetat yang disintesis dari limbah tandan buah kosong kelapa sawit (POEFB) untuk desalinasi air payau, sebagai alternatif pasokan air darurat. Membran difabrikasi dengan metode phase inversion, dikarakterisasi (FTIR, SEM, porositas, swelling, sudut kontak, sifat mekanik), dan diuji pada modul FO dengan draw solution sukrosa. Membran menghasilkan fluks air 2,22 L/m2h (1 M) hingga 4,2 L/m2h (2 M) dengan rejeksi garam 96% dan kualitas air memenuhi baku mutu air minum.</t>
+        </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.rineng.2022.100611</t>
-        </is>
-      </c>
-      <c r="K78" s="2" t="inlineStr">
-        <is>
-          <t>Paper mengembangkan membran forward osmosis (FO) berbasis selulosa asetat yang disintesis dari limbah tandan buah kosong kelapa sawit (POEFB) untuk desalinasi air payau, sebagai alternatif pasokan air darurat. Membran difabrikasi dengan metode phase inversion, dikarakterisasi (FTIR, SEM, porositas, swelling, sudut kontak, sifat mekanik), dan diuji pada modul FO dengan draw solution sukrosa. Membran menghasilkan fluks air 2,22 L/m2h (1 M) hingga 4,2 L/m2h (2 M) dengan rejeksi garam 96% dan kualitas air memenuhi baku mutu air minum.</t>
-        </is>
-      </c>
-      <c r="L78" s="2" t="inlineStr">
         <is>
           <t>Memberi konteks domain membran/desalinasi (bahan dan kinerja membran) tanpa menyentuh RUL, censoring, atau prediksi. Relevan hanya sebagai latar domain tesis: menunjukkan objek membran dan tantangan fouling/kinerja yang menjadi sasaran prediksi RUL, tetapi tidak memberi kontribusi metode.</t>
         </is>
@@ -4909,23 +4282,15 @@
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I79" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.3390/electronics10030285</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan model prediksi RUL turbofan engine dengan menggabungkan RNN (prediksi jangka pendek) dan LSTM (jangka panjang) yang bobot gabungannya dioptimasi NSGA-II. Fitur diekstraksi dengan dekomposisi dua tahap CEEMD-WPT dan enam fitur statistik (Shannon entropy, kurtosis, skewness, peak-to-peak, standar deviasi, mean). Pada dataset benchmark C-MAPSS-TD (FD001-FD004), model mencapai RMSE rata-rata 17,2 dengan validasi 10-fold cross-validation, mengalahkan RNN/LSTM tunggal dan 10 karya pembanding.</t>
+        </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/electronics10030285</t>
-        </is>
-      </c>
-      <c r="K79" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan model prediksi RUL turbofan engine dengan menggabungkan RNN (prediksi jangka pendek) dan LSTM (jangka panjang) yang bobot gabungannya dioptimasi NSGA-II. Fitur diekstraksi dengan dekomposisi dua tahap CEEMD-WPT dan enam fitur statistik (Shannon entropy, kurtosis, skewness, peak-to-peak, standar deviasi, mean). Pada dataset benchmark C-MAPSS-TD (FD001-FD004), model mencapai RMSE rata-rata 17,2 dengan validasi 10-fold cross-validation, mengalahkan RNN/LSTM tunggal dan 10 karya pembanding.</t>
-        </is>
-      </c>
-      <c r="L79" s="2" t="inlineStr">
         <is>
           <t>Preseden metode RUL berbasis deep learning yang kuat dan tervalidasi silang, namun domainnya turbofan engine dan tidak memodelkan penyensoran/survival, sehingga bagi tesis hanya berperan sebagai pembanding metode (Pendukung), bukan irisan metode+domain.</t>
         </is>
@@ -4965,23 +4330,15 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
-        </is>
-      </c>
-      <c r="I80" s="2" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.1155/2020/8814658</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan model deep survival terintegrasi yang menggabungkan 1D temporal convolution dan LSTM untuk mengekstraksi pola tersembunyi dari data sensor deret waktu, lalu memakai regresi (MSE) dan analisis survival berbasis distribusi Weibull diskrit untuk mengestimasi RUL sekaligus probabilitas kegagalan. Dievaluasi pada dataset simulasi degradasi turbofan NASA CMAPSS (FD001-FD004). Model menghasilkan kurva survival Kaplan-Meier dengan interval kepercayaan dan mengklaim performa unggul pada kondisi operasi kompleks (FD002 dan FD004).</t>
+        </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1155/2020/8814658</t>
-        </is>
-      </c>
-      <c r="K80" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan model deep survival terintegrasi yang menggabungkan 1D temporal convolution dan LSTM untuk mengekstraksi pola tersembunyi dari data sensor deret waktu, lalu memakai regresi (MSE) dan analisis survival berbasis distribusi Weibull diskrit untuk mengestimasi RUL sekaligus probabilitas kegagalan. Dievaluasi pada dataset simulasi degradasi turbofan NASA CMAPSS (FD001-FD004). Model menghasilkan kurva survival Kaplan-Meier dengan interval kepercayaan dan mengklaim performa unggul pada kondisi operasi kompleks (FD002 dan FD004).</t>
-        </is>
-      </c>
-      <c r="L80" s="2" t="inlineStr">
         <is>
           <t>Preseden langsung integrasi deep learning (CNN+LSTM) dengan distibusi Weibull diskrit dan log-likelihood tersensor untuk RUL: menunjukkan cara lulusan jaringan menghasilkan parameter alpha/beta Weibull dan kurva survival ber-CI, sangat dekat dengan kebutuhan tesis; namun domainnya turbofan dan bukan membran/RO.</t>
         </is>
@@ -5021,23 +4378,15 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="n">
-        <v>6</v>
+          <t>https://doi.org/10.36001/ijphm.2015.v6i4.2319</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>Artikel ulasan ini memaparkan berbagai aspek kuantifikasi dan manajemen ketidakpastian pada prognostik dan systems health management. Penulis membedakan interpretasi ketidakpastian pada testing-based dan condition-based health management, menunjukkan bahwa prediksi RUL lebih bermakna pada condition-based monitoring dan harus diperlakukan sebagai masalah propagasi ketidakpastian. Empat aktivitas diuraikan: representasi/interpretasi, kuantifikasi, propagasi, dan manajemen ketidakpastian, dilengkapi contoh numerik dan analisis sensitivitas global.</t>
+        </is>
       </c>
       <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.36001/ijphm.2015.v6i4.2319</t>
-        </is>
-      </c>
-      <c r="K81" s="2" t="inlineStr">
-        <is>
-          <t>Artikel ulasan ini memaparkan berbagai aspek kuantifikasi dan manajemen ketidakpastian pada prognostik dan systems health management. Penulis membedakan interpretasi ketidakpastian pada testing-based dan condition-based health management, menunjukkan bahwa prediksi RUL lebih bermakna pada condition-based monitoring dan harus diperlakukan sebagai masalah propagasi ketidakpastian. Empat aktivitas diuraikan: representasi/interpretasi, kuantifikasi, propagasi, dan manajemen ketidakpastian, dilengkapi contoh numerik dan analisis sensitivitas global.</t>
-        </is>
-      </c>
-      <c r="L81" s="2" t="inlineStr">
         <is>
           <t>Kerangka konseptual untuk menginterpretasi, mengkuantifikasi, dan mempropagasi ketidakpastian dalam RUL - relevan sebagai landasan pilar C dan justifikasi mengapa distribusi RUL tidak boleh diasumsikan (mis. Gaussian). Tidak memodelkan data tersensor dan bukan studi empiris domain.</t>
         </is>
@@ -5077,23 +4426,15 @@
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.36001/ijphm.2019.v10i4.2612</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>Paper mengusulkan LSTM-OR, pendekatan ordinal regression berbasis deep LSTM untuk estimasi RUL yang secara alami dapat memanfaatkan instan operasional tersensor (censored) saat melatih, plus kuantifikasi ketidakpastian prediktif lewat ensemble LSTM-OR. Dievaluasi pada benchmark turbofan C-MAPSS FD001 dan FD004 dengan skenario pc = 0/50/70/90%. Ordinal regression dengan censored (ORC) mengalahkan metric regression (MR) saat jumlah instan gagal sedikit, contoh 15,1% (FD001) dan 3,6% (FD004) perbaikan RMSE pada pc=90%.</t>
+        </is>
       </c>
       <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.36001/ijphm.2019.v10i4.2612</t>
-        </is>
-      </c>
-      <c r="K82" s="2" t="inlineStr">
-        <is>
-          <t>Paper mengusulkan LSTM-OR, pendekatan ordinal regression berbasis deep LSTM untuk estimasi RUL yang secara alami dapat memanfaatkan instan operasional tersensor (censored) saat melatih, plus kuantifikasi ketidakpastian prediktif lewat ensemble LSTM-OR. Dievaluasi pada benchmark turbofan C-MAPSS FD001 dan FD004 dengan skenario pc = 0/50/70/90%. Ordinal regression dengan censored (ORC) mengalahkan metric regression (MR) saat jumlah instan gagal sedikit, contoh 15,1% (FD001) dan 3,6% (FD004) perbaikan RMSE pada pc=90%.</t>
-        </is>
-      </c>
-      <c r="L82" s="2" t="inlineStr">
         <is>
           <t>Menunjukkan cara menggabungkan data tersensor ke pelatihan model deep learning RUL lewat label masking pada ordinal regression — inti tesis karena tesis membutuhkan penanganan data tersensor. Juga menyediakan kuantifikasi ketidakpastian ensemble (ESD) yang terbukti berkorelasi dengan error, relevan untuk keputusan maintenance berbasis risiko.</t>
         </is>
@@ -5133,23 +4474,15 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.3390/app8122416</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>Makalah mengusulkan algoritma transfer learning berbasis jaringan BLSTM (bi-directional LSTM) untuk estimasi RUL, guna mengatasi kelangkaan data kegagalan pada prognostik berbasis data. Model dilatih pada dataset sumber yang besar namun terkait, lalu di-fine-tune dengan dataset target yang kecil (parameter-transfer). Eksperimen ekstensif (360 kali) pada benchmark C-MAPSS menunjukkan transfer learning umumnya meningkatkan akurasi, kecuali transfer dari kondisi operasi majemuk (6 kondisi) ke tunggal (1 kondisi) yang menyebabkan negative transfer.</t>
+        </is>
       </c>
       <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/app8122416</t>
-        </is>
-      </c>
-      <c r="K83" s="2" t="inlineStr">
-        <is>
-          <t>Makalah mengusulkan algoritma transfer learning berbasis jaringan BLSTM (bi-directional LSTM) untuk estimasi RUL, guna mengatasi kelangkaan data kegagalan pada prognostik berbasis data. Model dilatih pada dataset sumber yang besar namun terkait, lalu di-fine-tune dengan dataset target yang kecil (parameter-transfer). Eksperimen ekstensif (360 kali) pada benchmark C-MAPSS menunjukkan transfer learning umumnya meningkatkan akurasi, kecuali transfer dari kondisi operasi majemuk (6 kondisi) ke tunggal (1 kondisi) yang menyebabkan negative transfer.</t>
-        </is>
-      </c>
-      <c r="L83" s="2" t="inlineStr">
         <is>
           <t>Memberikan bukti kuat bahwa transfer learning menangani masalah small-data pada RUL - sangat relevan dengan tantangan kecilnya data kegagalan membran; namun tidak memodelkan pencensoringan dan domainnya mesin turbofan.</t>
         </is>
@@ -5189,23 +4522,15 @@
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="n">
-        <v>6</v>
+          <t>https://doi.org/10.3390/batteries3040032</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengestimasi keandalan baterai lithium-ion melalui model degradasi sigmoidal multifase dengan parameter efek acak (nonlinear mixed effect model, NLMEM) dan fungsi distribusi Weibull. Parameter diestimasi dengan MLE dan algoritma Stochastic Approximation Expectation Maximization (SAEM), lalu RUL dan State-of-Health (SOH) diprediksi pada ambang 70% End-of-Life (EOL). Prediksi kapasitas menyimpang &lt;2% dari data eksperimen NASA dan menghasilkan SOH dengan R^2 0,9846-0,9852.</t>
+        </is>
       </c>
       <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/batteries3040032</t>
-        </is>
-      </c>
-      <c r="K84" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengestimasi keandalan baterai lithium-ion melalui model degradasi sigmoidal multifase dengan parameter efek acak (nonlinear mixed effect model, NLMEM) dan fungsi distribusi Weibull. Parameter diestimasi dengan MLE dan algoritma Stochastic Approximation Expectation Maximization (SAEM), lalu RUL dan State-of-Health (SOH) diprediksi pada ambang 70% End-of-Life (EOL). Prediksi kapasitas menyimpang &lt;2% dari data eksperimen NASA dan menghasilkan SOH dengan R^2 0,9846-0,9852.</t>
-        </is>
-      </c>
-      <c r="L84" s="2" t="inlineStr">
         <is>
           <t>Preseden kuat poros survival/Weibull di tesis: pemodelan distribusi waktu-ke-gagal dengan Weibull pada ambang kegagalan, plus penggunaan model efek acak (hierarchical) untuk menangani ketidakpastian lintas-unit. Tidak ada machine learning dan domainnya baterai, bukan membran.</t>
         </is>
@@ -5245,23 +4570,15 @@
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="n">
-        <v>6</v>
+          <t>https://doi.org/10.1155/2014/807693</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>Studi memprediksi umur lelah sambungan solder Sn-3.0Ag-0.5Cu (SAC305) BGA dan FBGA dari uji thermal cycling dipercepat. Data waktu-ke-gagal diproses sebagai data tersensor interval Tipe-I dengan estimasi maksimum likelihood (MLE) dua-parameter Weibull; hasilnya dibandingkan dengan model Engelmaier yang dimodifikasi dan perangkat lunak Minitab/Matlab. Metode data tersensor Tipe-I memberi umur paling tinggi dan akurat (Nf BGA 3104,5; FBGA 3185 siklus) serta panduan pemeliharaan/penggantian.</t>
+        </is>
       </c>
       <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1155/2014/807693</t>
-        </is>
-      </c>
-      <c r="K85" s="2" t="inlineStr">
-        <is>
-          <t>Studi memprediksi umur lelah sambungan solder Sn-3.0Ag-0.5Cu (SAC305) BGA dan FBGA dari uji thermal cycling dipercepat. Data waktu-ke-gagal diproses sebagai data tersensor interval Tipe-I dengan estimasi maksimum likelihood (MLE) dua-parameter Weibull; hasilnya dibandingkan dengan model Engelmaier yang dimodifikasi dan perangkat lunak Minitab/Matlab. Metode data tersensor Tipe-I memberi umur paling tinggi dan akurat (Nf BGA 3104,5; FBGA 3185 siklus) serta panduan pemeliharaan/penggantian.</t>
-        </is>
-      </c>
-      <c r="L85" s="2" t="inlineStr">
         <is>
           <t>Memberi contoh lengkap formulasi likelihood untuk data tersensor Tipe-I (indikator delta_i) dengan Weibull pada uji life-test dipercepat - inti metodologis pilar A tesis. Namun tidak ada machine learning, tidak ada RUL probabilistik, dan domainnya elektronik (bukan membran/RO).</t>
         </is>
@@ -5301,23 +4618,15 @@
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.48084/etasr.15186</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>Paper mengusulkan kerangka hybrid yang menggabungkan machine learning terawasi dengan analisis survival Weibull untuk RUL, dengan premis bahwa parameter skala Weibull (lambda, characteristic life) bukan statis melainkan fungsi dinamis dari kovariat operasional/lingkungan. Berbagai model ML (LightGBM, XGBoost, RF, SVR, LR) dilatih memprediksi lambda sebagai fungsi kovariat dan dibandingkan dengan baseline AFT-OLS. Pada C-MAPSS FD001, LightGBM terbaik (MAE 25,44 siklus; RMSE 34,21) dan mengalahkan AFT klasik.</t>
+        </is>
       </c>
       <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.48084/etasr.15186</t>
-        </is>
-      </c>
-      <c r="K86" s="2" t="inlineStr">
-        <is>
-          <t>Paper mengusulkan kerangka hybrid yang menggabungkan machine learning terawasi dengan analisis survival Weibull untuk RUL, dengan premis bahwa parameter skala Weibull (lambda, characteristic life) bukan statis melainkan fungsi dinamis dari kovariat operasional/lingkungan. Berbagai model ML (LightGBM, XGBoost, RF, SVR, LR) dilatih memprediksi lambda sebagai fungsi kovariat dan dibandingkan dengan baseline AFT-OLS. Pada C-MAPSS FD001, LightGBM terbaik (MAE 25,44 siklus; RMSE 34,21) dan mengalahkan AFT klasik.</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="inlineStr">
         <is>
           <t>Sangat selaras dengan sumbu metode tesis: memakai survival analysis Weibull, memodelkan lambda sebagai fungsi kovariat (relevan untuk covariate membran), dan menawarkan kuantifikasi ketidakpastian dengan menempelkan prediksi ML ke kerangka probabilistic Weibull. Memberi preseden penting untuk menggabungkan ML + survival, meski domainnya turbofan dan bukan penanganan censoring eksplisit.</t>
         </is>
@@ -5357,23 +4666,15 @@
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.46604/peti.2025.15348</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan KCNN-LSTM, model deep learning untuk prediksi RUL bantalan gelinding yang menggabungkan arsitektur CNN-LSTM dengan fungsi loss berbasis Weibull (knowledge-informed) dan health index (HI) eksponensial. Loss gabungan MSE + lambda*Weibull CDF memaksa prediksi mengikuti karakteristik degradasi fisik (accelerated wear). Dievaluasi pada PHM2012 dan XJTU-SY; model mengungguli CNN-LSTM, LSTM, Bi-LSTM, dan FNN berloss Weibull, mencapai RMSE 0,071 dan Score 0,821 (PHM2012) serta RMSE 0,054 (XJTU-SY).</t>
+        </is>
       </c>
       <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.46604/peti.2025.15348</t>
-        </is>
-      </c>
-      <c r="K87" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan KCNN-LSTM, model deep learning untuk prediksi RUL bantalan gelinding yang menggabungkan arsitektur CNN-LSTM dengan fungsi loss berbasis Weibull (knowledge-informed) dan health index (HI) eksponensial. Loss gabungan MSE + lambda*Weibull CDF memaksa prediksi mengikuti karakteristik degradasi fisik (accelerated wear). Dievaluasi pada PHM2012 dan XJTU-SY; model mengungguli CNN-LSTM, LSTM, Bi-LSTM, dan FNN berloss Weibull, mencapai RMSE 0,071 dan Score 0,821 (PHM2012) serta RMSE 0,054 (XJTU-SY).</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr">
         <is>
           <t>Menunjukkan integrasi pengetahuan fisik (distribusi Weibull) ke dalam loss deep learning RUL - pola 'knowledge-informed' yang relevan untuk tesis; namun domain bantalan (bukan membran) dan tidak menangani data tersensor.</t>
         </is>
@@ -5413,23 +4714,15 @@
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.56294/dm20251102</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>Studi komparatif dua teknik analisis survival - Cox Proportional Hazards (semi-parametrik) dan model Weibull (parametrik) - untuk prediksi RUL komponen industri pada dataset AI4I 2020 Predictive Maintenance. Memakai Kaplan-Meier, uji log-rank, dan validasi C-index/AIC; Cox PH unggul (C-index 0,9148 vs 0,639; AIC 4184,44 vs 5915,87) dan menangani kovariat berganda serta data tersensor (right-censored) secara efektif.</t>
+        </is>
       </c>
       <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.56294/dm20251102</t>
-        </is>
-      </c>
-      <c r="K88" s="2" t="inlineStr">
-        <is>
-          <t>Studi komparatif dua teknik analisis survival - Cox Proportional Hazards (semi-parametrik) dan model Weibull (parametrik) - untuk prediksi RUL komponen industri pada dataset AI4I 2020 Predictive Maintenance. Memakai Kaplan-Meier, uji log-rank, dan validasi C-index/AIC; Cox PH unggul (C-index 0,9148 vs 0,639; AIC 4184,44 vs 5915,87) dan menangani kovariat berganda serta data tersensor (right-censored) secara efektif.</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="inlineStr">
         <is>
           <t>Menyediakan justifikasi metodologis langsung untuk tesis: Cox PH lebih tepat daripada Weibull murni ketika terdapat banyak kovariat sensor dan data tersensor, dan menghasilkan RUL yang terindividualisasi per unit. Menjadi kerangka survival analysis acuan yang dapat dikombinasikan dengan machine learning.</t>
         </is>
@@ -5469,23 +4762,15 @@
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
-        </is>
-      </c>
-      <c r="I89" s="2" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.1299/jamdsm.2025jamdsm0044</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>Paper mengusulkan kerangka hybrid PhyMix-UQ-RUL untuk prediksi RUL dan kuantifikasi ketidakpastian, dengan memperluas WTTE-RNN (Weibull Time-To-Event RNN) memakai multi-scale dilated CNN (MsDCNN), LSTM, dan gated degradation stage regularization (GDSR). GDSR membatasi parameter bentuk Weibull (beta) sesuai teori bathtub curve dan loss dual-regularization menjaga kesesuaian fisik. Divalidasi pada C-MAPSS (FD001-FD004) dan N-CMAPSS DS02, model memberi prediksi kompetitif sekaligus prediksi interval dan kurva survival.</t>
+        </is>
       </c>
       <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1299/jamdsm.2025jamdsm0044</t>
-        </is>
-      </c>
-      <c r="K89" s="2" t="inlineStr">
-        <is>
-          <t>Paper mengusulkan kerangka hybrid PhyMix-UQ-RUL untuk prediksi RUL dan kuantifikasi ketidakpastian, dengan memperluas WTTE-RNN (Weibull Time-To-Event RNN) memakai multi-scale dilated CNN (MsDCNN), LSTM, dan gated degradation stage regularization (GDSR). GDSR membatasi parameter bentuk Weibull (beta) sesuai teori bathtub curve dan loss dual-regularization menjaga kesesuaian fisik. Divalidasi pada C-MAPSS (FD001-FD004) dan N-CMAPSS DS02, model memberi prediksi kompetitif sekaligus prediksi interval dan kurva survival.</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="inlineStr">
         <is>
           <t>Sangat dekat dengan inti tesis: memakai WTTE-RNN berbasis survival/Weibull dengan loss log-likelihood yang menangani status kegagalan (censoring), sekaligus mengkuantifikasi ketidakpastian (PI, PDF, kurva survival). Memberi blueprint metodologis untuk menggabungkan deep learning + survival + uncertainty, meski domainnya turbofan, bukan membran.</t>
         </is>
@@ -5525,23 +4810,15 @@
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>Inti-Domain</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.1016/j.dwt.2025.101386</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>Studi membangun empat model machine learning (Tree Regression, Ensemble Learning/Random Forest, Neural Network, Gaussian Process Regression) untuk memprediksi laju alir dan resistansi membran pada sistem ultrafiltrasi (UF) yang berperan sebagai pretreatment pabrik desalinasi air laut, memakai 426 hari data operasional (3,7 x 10^6 sampel pada 1 Hz). ENS dan TR mencapai akurasi tertinggi (R2=0,99; RMSE 3,08 dan 3,27 L/min), dan kendali backwash adaptif yang dipandu prediksi menurunkan ekskursi TMP 18 %, menurunkan frekuensi backwash dari 6 jam ke 8 jam, serta memangkas biaya pemeliharaan sekitar 12 %.</t>
+        </is>
       </c>
       <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.dwt.2025.101386</t>
-        </is>
-      </c>
-      <c r="K90" s="2" t="inlineStr">
-        <is>
-          <t>Studi membangun empat model machine learning (Tree Regression, Ensemble Learning/Random Forest, Neural Network, Gaussian Process Regression) untuk memprediksi laju alir dan resistansi membran pada sistem ultrafiltrasi (UF) yang berperan sebagai pretreatment pabrik desalinasi air laut, memakai 426 hari data operasional (3,7 x 10^6 sampel pada 1 Hz). ENS dan TR mencapai akurasi tertinggi (R2=0,99; RMSE 3,08 dan 3,27 L/min), dan kendali backwash adaptif yang dipandu prediksi menurunkan ekskursi TMP 18 %, menurunkan frekuensi backwash dari 6 jam ke 8 jam, serta memangkas biaya pemeliharaan sekitar 12 %.</t>
-        </is>
-      </c>
-      <c r="L90" s="2" t="inlineStr">
         <is>
           <t>Menunjukkan prediksi fouling real-time + keputusan pemeliharaan (penjadwalan backwash dan biaya) di domain membran/desalinasi, sangat relevan bagi sisi domain tesis; namun tidak memodelkan RUL, survival, maupun data tersensor, sehingga hanya menyumbang dimensi domain dan pemeliharaan.</t>
         </is>
@@ -5581,23 +4858,15 @@
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>Inti-Domain</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.1016/j.dwt.2025.101238</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>Studi memprediksi transmembrane pressure (TMP) sebagai proksi pemicu fouling membran pada MBR skala bench yang mengolah air limbah tekstil sintetik. Tiga model regresi (Random Forest, Support Vector Regression, dan Lasso) dilatih dengan lima parameter lumpur (B_Car, MLSS, SOUR, DSVI, PSD) dari 58 observasi harian pada tiga siklus membran 19-21 hari, memakai pembagian data kronologis untuk menghindari kebocoran informasi. Random Forest terbaik dengan R2 0,95/0,83 dan RMSE 1,75/3,3 kPa (train/test); B_Car (EPS karbohidrat terikat) adalah prediktor paling penting, dan model dilengkapi interval prediksi 80%.</t>
+        </is>
       </c>
       <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.dwt.2025.101238</t>
-        </is>
-      </c>
-      <c r="K91" s="2" t="inlineStr">
-        <is>
-          <t>Studi memprediksi transmembrane pressure (TMP) sebagai proksi pemicu fouling membran pada MBR skala bench yang mengolah air limbah tekstil sintetik. Tiga model regresi (Random Forest, Support Vector Regression, dan Lasso) dilatih dengan lima parameter lumpur (B_Car, MLSS, SOUR, DSVI, PSD) dari 58 observasi harian pada tiga siklus membran 19-21 hari, memakai pembagian data kronologis untuk menghindari kebocoran informasi. Random Forest terbaik dengan R2 0,95/0,83 dan RMSE 1,75/3,3 kPa (train/test); B_Car (EPS karbohidrat terikat) adalah prediktor paling penting, dan model dilengkapi interval prediksi 80%.</t>
-        </is>
-      </c>
-      <c r="L91" s="2" t="inlineStr">
         <is>
           <t>Menunjukkan bahwa regresi ML dengan data kecil (n=58) dapat memetakan TMP membran MBR dan memberi peringkat parameter lumpur, sebagai jembatan domain (membran/fouling) tanpa memodelkan RUL atau penyensoran. Relevan bagi tesis sebagai baseline domain bahwa proksi degradasi (TMP) dapat diprediksi, namun belum ada formalisasi waktu-ke-gagal/penyensoran.</t>
         </is>
@@ -5637,23 +4906,15 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.14456/scitechasia.2025.79</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengembangkan kerangka machine learning untuk memprediksi Water Quality Index (WQI) dan mengklasifikasikan kategori kualitas air (WQC: Excellent/Good/Poor/Unsuitable) pada air permukaan payau yang menjadi umpan pabrik demineralisasi RO (MAROC CENTRAL, Maroko). Dari 10.000 sampel dan 11 parameter fisikokimia, MLP terbaik untuk regresi WQI (R2=98,19 %; MAE=0,0182) dan XGBoost terbaik untuk klasifikasi WQC (akurasi 99,84 %). WQC dikaitkan dengan indikator kinerja RO (feed rate, tekanan, dP, permeate flow, energi).</t>
+        </is>
       </c>
       <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.14456/scitechasia.2025.79</t>
-        </is>
-      </c>
-      <c r="K92" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengembangkan kerangka machine learning untuk memprediksi Water Quality Index (WQI) dan mengklasifikasikan kategori kualitas air (WQC: Excellent/Good/Poor/Unsuitable) pada air permukaan payau yang menjadi umpan pabrik demineralisasi RO (MAROC CENTRAL, Maroko). Dari 10.000 sampel dan 11 parameter fisikokimia, MLP terbaik untuk regresi WQI (R2=98,19 %; MAE=0,0182) dan XGBoost terbaik untuk klasifikasi WQC (akurasi 99,84 %). WQC dikaitkan dengan indikator kinerja RO (feed rate, tekanan, dP, permeate flow, energi).</t>
-        </is>
-      </c>
-      <c r="L92" s="2" t="inlineStr">
         <is>
           <t>Menyumbang konteks domain RO/desalinasi berupa pemantauan kualitas air umpan berbasis ML yang mendukung operasi dan pemeliharaan; target prediksi adalah kualitas air (bukan degradasi/RUL membran), sehingga hanya bersifat pendukung.</t>
         </is>
@@ -5693,23 +4954,15 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>Pendukung</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.1177/16878132241239802</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>Penelitian ini mengusulkan deep Bayesian Neural Network (BNN) dengan Monte Carlo (MC) dropout untuk memprediksi RUL sistem ber-sensor sekaligus mengkuantifikasi ketidakpastian. Model dilatih dan diuji pada dataset NASA C-MAPSS FD001 (100 unit turbofan run-to-failure, 21 sensor). Hasil menunjukkan prediksi mean RUL beserta credible interval 95% yang menangkap ketidakpastian aleatorik dan epistemik, dengan rata-rata CI sekitar 38,78 siklus.</t>
+        </is>
       </c>
       <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1177/16878132241239802</t>
-        </is>
-      </c>
-      <c r="K93" s="2" t="inlineStr">
-        <is>
-          <t>Penelitian ini mengusulkan deep Bayesian Neural Network (BNN) dengan Monte Carlo (MC) dropout untuk memprediksi RUL sistem ber-sensor sekaligus mengkuantifikasi ketidakpastian. Model dilatih dan diuji pada dataset NASA C-MAPSS FD001 (100 unit turbofan run-to-failure, 21 sensor). Hasil menunjukkan prediksi mean RUL beserta credible interval 95% yang menangkap ketidakpastian aleatorik dan epistemik, dengan rata-rata CI sekitar 38,78 siklus.</t>
-        </is>
-      </c>
-      <c r="L93" s="2" t="inlineStr">
         <is>
           <t>Menyediakan kerangka RUL probabilistik (bukan point estimate) yang secara eksplisit mengkuantifikasi ketidakpastian aleatorik dan epistemik melalui MC dropout, sehingga memberi informasi kuantitatif (mean + credible interval) untuk perencanaan maintenance. Relevan ke tesis sebagai contoh deep learning yang menghasilkan distribusi prediksi, namun belum menangani data tersensor secara survival.</t>
         </is>
@@ -5745,23 +4998,15 @@
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>Konteks</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="n">
-        <v>6</v>
+          <t>https://doi.org/10.33263/briac142.029</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>Studi material eksperimental yang mensintesis membran mesoporous CA/PEG (cellulose acetate/polyethylene glycol) dimodifikasi nanopartikel TiO2 (TiO2-NPs) melalui dua metode, yaitu surface coating (SC) dan blending (B), lalu menguji kinerja desalinasi air laut Pantai Kolaka (Sulawesi Tenggara) dengan perangkat RO sederhana 3 tabung (feed + pretreatment pasir/arang/kerikil/serat + membran ber-UV). Karakterisasi XRD, FTIR, dan SEM menunjukkan struktur semikristalin dan keberadaan TiO2 dalam matriks membran. Membran metode B unggul dengan fluks 161,18 L/m2.jam dan rejeksi garam 84%, menurunkan salinitas permeat menjadi 4‰ (kategori air tawar). Artikel tidak mengandung pemodelan RUL, survival analysis/censoring, sensor time-series, machine learning, analisis ketidakpastian, maupun keputusan pemeliharaan.</t>
+        </is>
       </c>
       <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.33263/briac142.029</t>
-        </is>
-      </c>
-      <c r="K94" s="2" t="inlineStr">
-        <is>
-          <t>Studi material eksperimental yang mensintesis membran mesoporous CA/PEG (cellulose acetate/polyethylene glycol) dimodifikasi nanopartikel TiO2 (TiO2-NPs) melalui dua metode, yaitu surface coating (SC) dan blending (B), lalu menguji kinerja desalinasi air laut Pantai Kolaka (Sulawesi Tenggara) dengan perangkat RO sederhana 3 tabung (feed + pretreatment pasir/arang/kerikil/serat + membran ber-UV). Karakterisasi XRD, FTIR, dan SEM menunjukkan struktur semikristalin dan keberadaan TiO2 dalam matriks membran. Membran metode B unggul dengan fluks 161,18 L/m2.jam dan rejeksi garam 84%, menurunkan salinitas permeat menjadi 4‰ (kategori air tawar). Artikel tidak mengandung pemodelan RUL, survival analysis/censoring, sensor time-series, machine learning, analisis ketidakpastian, maupun keputusan pemeliharaan.</t>
-        </is>
-      </c>
-      <c r="L94" s="2" t="inlineStr">
         <is>
           <t>Membandingkan dua rute modifikasi TiO2-NPs (SC vs B) pada membran CA/PEG untuk desalinasi air laut; menunjukkan metode blending menyisipkan TiO2 ke kisi pori membran sehingga porositas dan kinerja pemisahan garam meningkat; merancang perangkat RO sederhana 3 kompartemen (pretreatment + membran + lampu UV) yang murah untuk masyarakat pesisir dan pulau kecil Indonesia.</t>
         </is>
@@ -5801,23 +5046,15 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>Konteks</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.3390/separations10020134</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan kerangka pemodelan multiskala yang menggabungkan model 3D multi-fisika (dinding permeabel dan dinding impermeabel) pada skala sub-milimeter dengan model sistem pada skala meter untuk desalinasi SWRO. Analisis kuantitatif menunjukkan galat rata-rata koefisien gesek dan bilangan Sherwood memakai model dinding impermeabel &lt; 2 % (gesek) dan &lt; 9 % (Sherwood) dibanding model dinding permeabel, sementara model dinding impermeabel 3x lebih efisien komputasi (25,3 jam vs 77,8 jam).</t>
+        </is>
       </c>
       <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/separations10020134</t>
-        </is>
-      </c>
-      <c r="K95" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan kerangka pemodelan multiskala yang menggabungkan model 3D multi-fisika (dinding permeabel dan dinding impermeabel) pada skala sub-milimeter dengan model sistem pada skala meter untuk desalinasi SWRO. Analisis kuantitatif menunjukkan galat rata-rata koefisien gesek dan bilangan Sherwood memakai model dinding impermeabel &lt; 2 % (gesek) dan &lt; 9 % (Sherwood) dibanding model dinding permeabel, sementara model dinding impermeabel 3x lebih efisien komputasi (25,3 jam vs 77,8 jam).</t>
-        </is>
-      </c>
-      <c r="L95" s="2" t="inlineStr">
         <is>
           <t>Menyediakan latar fisik domain (desain feed spacer, mitigasi fouling, concentration polarization) yang menjelaskan mekanisme degradasi membran SWRO; tidak melakukan prediksi berbasis data, RUL, atau survival, sehingga hanya bersifat konteks.</t>
         </is>
@@ -5857,23 +5094,15 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.1155/2020/8829823</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>Studi membangun model general log-linear Weibull (GLL-Weibull) multivariat yang menggabungkan fitur getaran (RRMS) dan suhu relatif sebagai kovariat internal untuk memprediksi RUL bantalan gelinding. Kedua sinyal difuzzifikasi (operator 'excessive vibrations' dan 'overheated bearing') lalu parameter model diestimasi dengan maximum likelihood estimation (MLE) yang secara eksplisit memasukkan sampel tersuspensi (sensor) ke fungsi likelihood. Validasi pada PRONOSTIA dan bantalan HSS turbin angin nyata menunjukkan akurasi superior (MAPE rata-rata 10,76% vs SVM 26,73% dan CNN 11,68%).</t>
+        </is>
       </c>
       <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1155/2020/8829823</t>
-        </is>
-      </c>
-      <c r="K96" s="2" t="inlineStr">
-        <is>
-          <t>Studi membangun model general log-linear Weibull (GLL-Weibull) multivariat yang menggabungkan fitur getaran (RRMS) dan suhu relatif sebagai kovariat internal untuk memprediksi RUL bantalan gelinding. Kedua sinyal difuzzifikasi (operator 'excessive vibrations' dan 'overheated bearing') lalu parameter model diestimasi dengan maximum likelihood estimation (MLE) yang secara eksplisit memasukkan sampel tersuspensi (sensor) ke fungsi likelihood. Validasi pada PRONOSTIA dan bantalan HSS turbin angin nyata menunjukkan akurasi superior (MAPE rata-rata 10,76% vs SVM 26,73% dan CNN 11,68%).</t>
-        </is>
-      </c>
-      <c r="L96" s="2" t="inlineStr">
         <is>
           <t>Buku teks inti untuk tesis: menunjukkan secara konkret bagaimana model survival (Weibull dengan kovariat) dan data tersuspensi diintegrasikan untuk RUL, termasuk estimasi parameter MLE dan PDF RUL. Menjadi acuan langsung untuk memadukan informasi getaran+suhu (analog multi-sensor) dalam hazard model.</t>
         </is>
@@ -5913,23 +5142,15 @@
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>Konteks</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="n">
-        <v>5</v>
+          <t>https://doi.org/10.15294/jpii.v9i3.23310</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>Studi eksperimental memakai membran nanofiltrasi NF270 (cross-flow) untuk mengolah air asam tambang batubara PT Bukit Asam menjadi air minum sesuai Permenkes 492/2010. Kinerja dinilai dari pengaruh tekanan (4, 5, 6 bar) terhadap fluks dan laju rejeksi COD, TSS, TDS, dan Fe pada larutan tunggal, campuran, dan sampel nyata. Tekanan optimum 6 bar; fluks turun tajam pada 15 menit pertama akibat fouling dan polarisasi konsentrasi yang dikonfirmasi SEM.</t>
+        </is>
       </c>
       <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.15294/jpii.v9i3.23310</t>
-        </is>
-      </c>
-      <c r="K97" s="2" t="inlineStr">
-        <is>
-          <t>Studi eksperimental memakai membran nanofiltrasi NF270 (cross-flow) untuk mengolah air asam tambang batubara PT Bukit Asam menjadi air minum sesuai Permenkes 492/2010. Kinerja dinilai dari pengaruh tekanan (4, 5, 6 bar) terhadap fluks dan laju rejeksi COD, TSS, TDS, dan Fe pada larutan tunggal, campuran, dan sampel nyata. Tekanan optimum 6 bar; fluks turun tajam pada 15 menit pertama akibat fouling dan polarisasi konsentrasi yang dikonfirmasi SEM.</t>
-        </is>
-      </c>
-      <c r="L97" s="2" t="inlineStr">
         <is>
           <t>Memberikan bukti domain bahwa degradasi kinerja membran (penurunan fluks karena fouling) adalah proses yang terukur terhadap waktu dan kualitas permeat, namun tidak memodelkan RUL, penyensoran, maupun prediksi sisa umur, sehingga hanya berperan sebagai konteks domain membran/desalinasi bagi tesis.</t>
         </is>
@@ -5969,23 +5190,15 @@
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>Inti-Domain</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="n">
-        <v>8</v>
+          <t>https://doi.org/10.5004/dwt.2019.23444</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengembangkan model prediksi fouling membran SWRO dengan pendekatan machine learning hibrida: Kalman filter (KF) dirangkai seri dengan ANN atau SVM untuk memprediksi resistansi membran (indikator fouling), dilatih dan diuji pada data operasional pabrik Fujairah selama 18 bulan (522 catatan harian). Model hibrida secara konsisten mengungguli model tunggal; KF-SVM memberi akurasi terbaik (R2 uji 0,82; NSE uji 0,72) dan hasilnya diusulkan untuk menyesuaikan jadwal pembersihan/penggantian membran serta sistem peringatan dini fouling.</t>
+        </is>
       </c>
       <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.5004/dwt.2019.23444</t>
-        </is>
-      </c>
-      <c r="K98" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengembangkan model prediksi fouling membran SWRO dengan pendekatan machine learning hibrida: Kalman filter (KF) dirangkai seri dengan ANN atau SVM untuk memprediksi resistansi membran (indikator fouling), dilatih dan diuji pada data operasional pabrik Fujairah selama 18 bulan (522 catatan harian). Model hibrida secara konsisten mengungguli model tunggal; KF-SVM memberi akurasi terbaik (R2 uji 0,82; NSE uji 0,72) dan hasilnya diusulkan untuk menyesuaikan jadwal pembersihan/penggantian membran serta sistem peringatan dini fouling.</t>
-        </is>
-      </c>
-      <c r="L98" s="2" t="inlineStr">
         <is>
           <t>Menunjukkan prediksi degradasi membran (resistansi/fouling) dan kaitannya dengan penyesuaian jadwal pembersihan/penggantian di domain SWRO; sangat relevan bagi domain dan dimensi keputusan pemeliharaan tesis, meski tanpa RUL formal, survival, atau pencensoringan.</t>
         </is>
@@ -6025,23 +5238,15 @@
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.1155/2017/8927937</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>Paper mengembangkan metode hybrid untuk prediksi RUL bearing yang menggabungkan generalized Weibull failure rate function (WFRF) dengan radial basis function (RBF) neural network. Sebuah indikator baru, power value pada sensitive frequency band (SFB), diusulkan untuk melacak degradasi; deret indikator difit dengan generalized WFRF untuk meredam noise, lalu RBF memprediksi life percentage dan RUL. Divalidasi pada dataset bearing IMS dengan akurasi hingga 99,42%.</t>
+        </is>
       </c>
       <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1155/2017/8927937</t>
-        </is>
-      </c>
-      <c r="K99" s="2" t="inlineStr">
-        <is>
-          <t>Paper mengembangkan metode hybrid untuk prediksi RUL bearing yang menggabungkan generalized Weibull failure rate function (WFRF) dengan radial basis function (RBF) neural network. Sebuah indikator baru, power value pada sensitive frequency band (SFB), diusulkan untuk melacak degradasi; deret indikator difit dengan generalized WFRF untuk meredam noise, lalu RBF memprediksi life percentage dan RUL. Divalidasi pada dataset bearing IMS dengan akurasi hingga 99,42%.</t>
-        </is>
-      </c>
-      <c r="L99" s="2" t="inlineStr">
         <is>
           <t>Memberi preseden penggunaan fungsi hazard keluarga Weibull sebagai model degradasi untuk RUL (sumbu metode survival), relevan dengan tesis yang memakai survival analysis. Namun tidak menangani data tersensor secara eksplisit dan tidak mengkuantifikasi ketidakpastian, sehingga gap utama tetap terbuka.</t>
         </is>
@@ -6081,23 +5286,15 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>Inti-Domain</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="n">
-        <v>9</v>
+          <t>https://doi.org/10.3390/machines11020163</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>Paper ini mengembangkan metodologi dan algoritma prognostik explainable untuk memprediksi Remaining Useful Life (RUL) mesin pesawat memakai dataset terbaru NASA CMAPSS (N-CMAPSS) 2021 (DS02 dan DS03). Alur enam fase meliputi seleksi fitur metrik hibrida (robustness, monotonicity, prognosability), estimasi Health Index via regresi logistik (GLM), dan pembaruan model prognostik secara rekursif dengan Unscented Kalman Filter (UKF) untuk mengekstrapolasi EoL/RUL beserta kuantifikasi ketidakpastian (1000 lintasan, confidence interval 90%). Hasilnya memberi RMSE 34,5-55,6% lebih baik dibanding teknik black-box pada dataset yang sama, dengan transparansi dan UQ sebagai pembeda utama.</t>
+        </is>
       </c>
       <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/machines11020163</t>
-        </is>
-      </c>
-      <c r="K100" s="2" t="inlineStr">
-        <is>
-          <t>Paper ini mengembangkan metodologi dan algoritma prognostik explainable untuk memprediksi Remaining Useful Life (RUL) mesin pesawat memakai dataset terbaru NASA CMAPSS (N-CMAPSS) 2021 (DS02 dan DS03). Alur enam fase meliputi seleksi fitur metrik hibrida (robustness, monotonicity, prognosability), estimasi Health Index via regresi logistik (GLM), dan pembaruan model prognostik secara rekursif dengan Unscented Kalman Filter (UKF) untuk mengekstrapolasi EoL/RUL beserta kuantifikasi ketidakpastian (1000 lintasan, confidence interval 90%). Hasilnya memberi RMSE 34,5-55,6% lebih baik dibanding teknik black-box pada dataset yang sama, dengan transparansi dan UQ sebagai pembeda utama.</t>
-        </is>
-      </c>
-      <c r="L100" s="2" t="inlineStr">
         <is>
           <t>Menyediakan alternatif prognostik yang transparan dan terkalibrasi ketidakpastiannya (90% CI) untuk data run-to-failure yang terbatas, mengisi celah antara metode deep learning black-box dan kebutuhan industri safety-critical. Meski domain aplikasinya kedirgantaraan (bukan membran), pendekatan hybrid filtering + UQ dapat ditransfer ke RUL membran RO, namun paper ini tidak memodelkan data tersensor (censoring) maupun survival/Weibull secara aktual.</t>
         </is>
@@ -6137,23 +5334,15 @@
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>Konteks</t>
-        </is>
-      </c>
-      <c r="I101" s="2" t="n">
-        <v>7</v>
+          <t>https://doi.org/10.3390/membranes11010054</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>Studi kasus ini merancang dan memodelkan modul membran flat sheet ultrafiltrasi (UF) kompak untuk pengolahan air minum terdesentralisasi menggunakan simulasi Computational Fluid Dynamics (CFD) 3D (ANSYS 19.2). Tujuan utamanya adalah mengkarakterisasi geometri dan memprediksi aliran fluida di dalam modul melalui analisis sensitivitas parametrik (spacer curviness/thickness, panjang &amp; diameter inlet-outlet, permeabilitas, ketebalan, dan luas membran) untuk memperoleh distribusi aliran seragam di atas permukaan membran. Hasil menunjukkan permeate flux sedikit menurun dari 2,81 L/m2h (curviness 0%) ke 2,73 L/m2h (curviness 100%), dan inlet pressure, permeabilitas, ketebalan serta luas membran berpengaruh signifikan terhadap flux.</t>
+        </is>
       </c>
       <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/membranes11010054</t>
-        </is>
-      </c>
-      <c r="K101" s="2" t="inlineStr">
-        <is>
-          <t>Studi kasus ini merancang dan memodelkan modul membran flat sheet ultrafiltrasi (UF) kompak untuk pengolahan air minum terdesentralisasi menggunakan simulasi Computational Fluid Dynamics (CFD) 3D (ANSYS 19.2). Tujuan utamanya adalah mengkarakterisasi geometri dan memprediksi aliran fluida di dalam modul melalui analisis sensitivitas parametrik (spacer curviness/thickness, panjang &amp; diameter inlet-outlet, permeabilitas, ketebalan, dan luas membran) untuk memperoleh distribusi aliran seragam di atas permukaan membran. Hasil menunjukkan permeate flux sedikit menurun dari 2,81 L/m2h (curviness 0%) ke 2,73 L/m2h (curviness 100%), dan inlet pressure, permeabilitas, ketebalan serta luas membran berpengaruh signifikan terhadap flux.</t>
-        </is>
-      </c>
-      <c r="L101" s="2" t="inlineStr">
         <is>
           <t>Memberikan bukti bahwa pemodelan numerik (CFD) dapat memandu desain modul membran UF lokal tanpa ketergantungan pada modul komersial, menurunkan biaya dan kebutuhan eksperimen pada optimasi. Namun paper ini murni desain hidrodinamika steady-state: tidak ada RUL, prognostik, data tersensor, maupun analisis keputusan pemeliharaan - sehingga hanya relevan sebagai konteks domain (membran/UF) bagi tesis.</t>
         </is>
@@ -6193,23 +5382,15 @@
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="n">
-        <v>4</v>
+          <t>https://doi.org/10.3390/e20120944</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>Paper ini mengusulkan metode data-driven untuk memprediksi RUL bearing berbasis klasifikasi Naive Bayes (NB) dengan pembentukan fitur degradasi memakai distribusi Weibull yang diperluas (Universal Failure Rate Function, UFRF). Enam belas fitur statistik time-domain diekstraksi dari sinyal vibrasi, lalu diseleksi berdasarkan korelasi terhadap RMS (threshold 0,9 menjadi 6 fitur) dan difit oleh UFRF pada tiga tahap degradasi sebagai input pelatihan NB. Klasifikasi lima kelas (health states + empat tahap degradasi) dihaluskan dengan exponential smoothing untuk menghasilkan prediksi RUL; hasilnya lebih akurat dibanding referensi pada data run-to-failure IMS/Cincinnati. Meski memakai distribusi Weibull dan fungsi hazard (UFRF), metode ini tidak menangani data tersensor (censoring).</t>
+        </is>
       </c>
       <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/e20120944</t>
-        </is>
-      </c>
-      <c r="K102" s="2" t="inlineStr">
-        <is>
-          <t>Paper ini mengusulkan metode data-driven untuk memprediksi RUL bearing berbasis klasifikasi Naive Bayes (NB) dengan pembentukan fitur degradasi memakai distribusi Weibull yang diperluas (Universal Failure Rate Function, UFRF). Enam belas fitur statistik time-domain diekstraksi dari sinyal vibrasi, lalu diseleksi berdasarkan korelasi terhadap RMS (threshold 0,9 menjadi 6 fitur) dan difit oleh UFRF pada tiga tahap degradasi sebagai input pelatihan NB. Klasifikasi lima kelas (health states + empat tahap degradasi) dihaluskan dengan exponential smoothing untuk menghasilkan prediksi RUL; hasilnya lebih akurat dibanding referensi pada data run-to-failure IMS/Cincinnati. Meski memakai distribusi Weibull dan fungsi hazard (UFRF), metode ini tidak menangani data tersensor (censoring).</t>
-        </is>
-      </c>
-      <c r="L102" s="2" t="inlineStr">
         <is>
           <t>Menunjukkan penggunaan Weibull/fungsi hazard (UFRF) untuk memuluskan fitur degradasi sebelum klasifikasi NB guna prediksi RUL. Kaitannya dengan tesis: paper ini satu-satunya dari tiga yang menyentuh 'bahasa' survival analysis (Weibull/hazard), namun tidak memodelkan censoring maupun survival regression, sehingga tetap meninggalkan celah untuk survival analysis dengan data tersensor pada RUL membran.</t>
         </is>
@@ -6245,27 +5426,6 @@
       <c r="A107" t="inlineStr">
         <is>
           <t>Klasifikasi kuartil: SCImago 'SJR Best Quartile' (turunan Scopus).</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Relevansi (Opsi C): Inti-Metode / Inti-Domain / Inti-Metode+Domain / Pendukung / Konteks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Kualitas: skor 0-10 (rubrik Q1-Q8) dari pembacaan full-text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Inti-Metode+Domain = irisan gap (paling inti).</t>
         </is>
       </c>
     </row>
@@ -6302,7 +5462,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50+ jurnal internasional (Scopus) + rujukan pendukung nasional</t>
+          <t>101 artikel; 52 Inti; 20 core paper</t>
         </is>
       </c>
     </row>
@@ -10659,4 +9819,4326 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K106"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="7" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="9" customWidth="1" min="10" max="10"/>
+    <col width="26" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Judul</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Penulis</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Tahun</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Tier</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Core</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Skor RQ</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Skor Metode</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Skor Kualitas</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Skor Total</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Peran</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>A Neural Network-Based Survival Analysis Model Considering Censored Data for Failure Prediction</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>Gao et al.</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>YA</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J2" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>LSTM and Transformers based methods for Remaining Useful Life Prediction considering Censored Data</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Noot et al.</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>YA</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Survival Models for Predictive Maintenance and Remaining Useful Life in Sensor-Enabled Smart Energy Networks: A Review</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Shadi et al.</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>YA</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J4" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Data-driven Prognostics with Predictive Uncertainty Estimation using Ensemble of Deep Ordinal Regression Models</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Tv et al.</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>YA</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>64</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>General Log-Linear Weibull Model Combining Vibration and Temperature Characteristics for Remaining Useful Life Prediction of Rolling Element Bearings</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Lv et al.</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>YA</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Remaining useful life estimation in heterogeneous fleets working under variable operating conditions</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Al‐Dahidi et al.</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>2016</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>YA</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J7" s="2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>A Multisensor Cross-Modal Attention Framework for Weibull-Driven RUL Estimation for Liner Using Real-World Industrial Data</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Reddy et al.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>YA</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Weibull recurrent neural networks for failure prognosis using histogram data</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Dhada et al.</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>YA</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Survival-analysis-guided machine learning for failure and remaining-useful-life prediction in railway compressor</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Abdelhafid et al.</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>YA</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>29</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Physics-informed machine learning for cross-study prediction of oil–water membrane fouling</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Alves et al.</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Domain</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>YA</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Domain Adaptive Remaining Useful Life Prediction With Transformer</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Li et al.</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Domain</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>YA</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Reliable prediction of industrial components Remaining Useful Life using Cox and Weibull models: A Comparative Study</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Abdelhafid et al.</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>YA</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>75</v>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Forecasting remaining useful life: Interpretable deep learning approach via variational Bayesian inferences</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Kraus et al.</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>YA</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>A physical knowledge-guided and data-driven framework for remaining useful life prediction (The case of turbofan engines)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Zheng et al.</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>YA</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>A physics-informed neural network-based method for predicting degradation trajectories and remaining useful life of supercapacitors</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>E et al.</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Domain</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>YA</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Weibull Variational Autoencoder for Remaining Useful Life Prediction</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>Yu et al.</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>YA</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Developing Deep Survival Model for Remaining Useful Life Estimation Based on Convolutional and Long Short-Term Memory Neural Networks</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>Chu et al.</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>YA</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>99</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Explainable Data-Driven Method Combined with Bayesian Filtering for Remaining Useful Lifetime Prediction of Aircraft Engines Using NASA CMAPSS Datasets</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Faisal Maulana, Andrew Starr, Agusmian Partogi Ompusunggu</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Domain</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>YA</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="n">
+        <v>68</v>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Multisensor Time Series Forecasting-Based Augmentation Framework for Remaining Useful Life Prediction of Aero Engines</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Chen et al.</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode+Domain</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>YA</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>metode+domain (kandidat gap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="n">
+        <v>81</v>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Probabilistic Modeling of Li-Ion Battery Remaining Useful Life</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Chiodo et al.</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode+Domain</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>YA</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>metode+domain (kandidat gap)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>A comprehensive framework from real‐time prognostics to maintenance decisions</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Jain et al.</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr"/>
+      <c r="G22" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Prediction of Reverse Osmosis Membrane Fouling Using Machine Learning: MLR, ANN, and SVM at a Seawater Desalination Plant</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Kherraf et al.</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Domain</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr"/>
+      <c r="G23" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Prognostic modeling of predictive maintenance with survival analysis for mobile work equipment</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Yang et al.</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Survival Analysis-Based System for Predictive Maintenance Optimization</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Coutinho et al.</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Remaining Useful Life Prediction of Turbine Engines Using Multimodal Transfer Learning</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Li et al.</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Domain</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Integrating Survival Analysis with Bayesian Statistics to Forecast the Remaining Useful Life of a Centrifugal Pump Conditional to Multiple Fault Types</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Kapuria &amp; Cole</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Harnessing machine learning for transmembrane pressure prediction in MBR systems during textile wastewater treatment</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Zahoor et al.</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Domain</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="n">
+        <v>77</v>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Machine Learning for Covariate-Driven Changes in Weibull Scale Parameter</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Ramadhan et al.</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr"/>
+      <c r="G29" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>An insight into real-time monitoring and predictive modelling of ultrafiltration pretreatment for flow rate and fouling mitigation in seawater desalination</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Katibi et al.</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Domain</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr"/>
+      <c r="G30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Remaining Useful Life Prediction of Bearing with Vibration Signals Based on a Novel Indicator</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Wu et al.</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr"/>
+      <c r="G31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Statistical Characterization of the State-of-Health of Lithium-Ion Batteries with Weibull Distribution Function, A Consideration of Random Effect Model in Charge Capacity Decay Estimation</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Ossai et al.</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="n">
+        <v>97</v>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Prediction of remaining useful life (RUL) of Komatsu excavator under reliability analysis in the Weibull-frailty model</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Ghomghaleh et al.</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Improved CNN-LSTM Bearing Remaining Useful Life Prediction Based on the Weibull Loss Function</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Zhang et al.</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>A Bayesian Optimization AdaBN-DCNN Method With Self-Optimized Structure and Hyperparameters for Domain Adaptation Remaining Useful Life Prediction</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Li et al.</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Domain</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Data-Efficient Estimation of Remaining Useful Life for Machinery With a Limited Number of Run-to-Failure Training Sequences</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Sternharz et al.</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Domain</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="n">
+        <v>70</v>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Remaining Useful Life Prognosis of Aircraft Brakes</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Λούτας et al.</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Predicting Remaining Useful Life of Rolling Bearings Based on Deep Feature Representation and Transfer Learning</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Mao et al.</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Domain</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Predictive Framework for Membrane Fouling in Full-Scale Membrane Bioreactors (MBRs): Integrating AI-Driven Feature Engineering and Explainable AI (XAI)</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Liang et al.</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Domain</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>A two-stage framework for cost-sensitive predictive maintenance using deep learning, GANs, and risk-aware clustering</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Hakami</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Domain</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Remaining useful life prediction of rolling bearing under limited data based on adaptive time-series feature window and multi-step ahead strategy</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Kong et al.</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Domain</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>A Neural Network-Based Joint Prognostic Model for Data Fusion and Remaining Useful Life Prediction</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Gao et al.</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Thermal Cycling Life Prediction of Sn-3.0Ag-0.5Cu Solder Joint Using Type-I Censored Data</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Mi et al.</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>2014</v>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>A hybrid signal-dynamics health index fusion framework for prognostics of small-scale wind turbine blades</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>Mobasheri et al.</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>AI-based remaining useful life prediction of seawater desalination membranes</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Alshraideh et al.</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Domain</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Enhancing accuracy of membrane fouling prediction using hybrid machine learning models</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Lim et al.</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Domain</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Remaining Useful Life Prediction of Lithium-Ion Batteries Using Neural Networks with Adaptive Bayesian Learning</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Pugalenthi et al.</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="n">
+        <v>63</v>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Remaining useful life prediction for lithium-ion batteries using particle filter and artificial neural network</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Qin et al.</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="n">
+        <v>69</v>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Remaining Useful Life Prediction for Power Storage Electronic Components Based on Fractional Weibull Process and Shock Poisson Model</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Song et al.</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="n">
+        <v>73</v>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Multiform Informed Machine Learning Based on Piecewise and Weibull for Engine Remaining Useful Life Prediction</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Zhou et al.</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>A Framework for Predicting Remaining Useful Life Curve of Rolling Bearings Under Defect Progression Based on Neural Network and Bayesian Method</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Kitai et al.</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="n">
+        <v>95</v>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Nonlinear degradation modeling and remaining useful life prediction for electric drive system with multiple failure modes</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>Wang et al.</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Transfer Learning with Deep Recurrent Neural Networks for Remaining Useful Life Estimation</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Zhang et al.</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr"/>
+      <c r="G53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>A Bayesian Mixture Neural Network for Remaining Useful Life Prediction of Lithium-Ion Batteries</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>Zhang et al.</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr"/>
+      <c r="G54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Remaining Useful Life Prognosis Based on Ensemble Long Short-Term Memory Neural Network</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Cheng et al.</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr"/>
+      <c r="G55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="n">
+        <v>62</v>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Counterfactual explanations for remaining useful life estimation within a Bayesian framework</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>Andringa et al.</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Utilizing uncertainty information in remaining useful life estimation via Bayesian neural networks and Hamiltonian Monte Carlo</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Benker et al.</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr"/>
+      <c r="G57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="n">
+        <v>72</v>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Bayesian Convolutional Neural Networks for Remaining Useful Life Prognostics of Solenoid Valves With Uncertainty Estimations</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Mazaev et al.</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr"/>
+      <c r="G58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Modeling dependent degradation data considering inherent causal relationships for reliability analysis and remaining useful life prediction</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Chen et al.</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Machine performance degradation assessment and remaining useful life prediction using proportional hazard model and support vector machine</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Tran et al.</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>2012</v>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr"/>
+      <c r="G60" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>A Semi-Supervised Deep Transfer Learning Approach for Rolling-Element Bearing Remaining Useful Life Prediction</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>Berghout et al.</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Domain</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="n">
+        <v>83</v>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Research on Prediction Method of Gear Pump Remaining Useful Life Based on DCAE and Bi-LSTM</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>Wang et al.</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Domain</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr"/>
+      <c r="G62" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>A Data-Driven Auto-CNN-LSTM Prediction Model for Lithium-Ion Battery Remaining Useful Life</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>Ren et al.</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Domain</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr"/>
+      <c r="G63" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>domain</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Bayesian neural networks for uncertainty quantification in remaining useful life prediction of systems with sensor monitoring</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Ochella et al.</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr"/>
+      <c r="G64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="n">
+        <v>49</v>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Remaining Useful Life Prediction of Turbofan Engines Using CNN-LSTM-SAM Approach</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Li et al.</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr"/>
+      <c r="G65" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Attention-Based LSTM Network for Rotatory Machine Remaining Useful Life Prediction</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Zhang et al.</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr"/>
+      <c r="G66" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Remaining Useful Life Prediction Based on the Bayesian Regularized Radial Basis Function Neural Network for an External Gear Pump</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Guo et al.</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Interval Prediction of Remaining Useful Life Based on Uncertainty Quantification with Bayesian Convolutional Neural Networks Featuring Dual-Output Units</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Qu et al.</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr"/>
+      <c r="G68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>Predictive Modeling of Brackish Surface Water Quality for Reverse Osmosis Desalination Plants Using Advanced Machine Learning Techniques</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>Lahlou</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr"/>
+      <c r="G69" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J69" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>A Genetic Algorithm Optimized RNN-LSTM Model for Remaining Useful Life Prediction of Turbofan Engine</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>Chui et al.</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr"/>
+      <c r="G70" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="n">
+        <v>43</v>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>A Novel Cap-LSTM Model for Remaining Useful Life Prediction</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Zhao et al.</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr"/>
+      <c r="G71" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Bi-LSTM-Based Two-Stream Network for Machine Remaining Useful Life Prediction</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Jin et al.</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="n">
+        <v>52</v>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>Machine Learning Implementation in Membrane Bioreactor Systems: Progress, Challenges, and Future Perspectives: A Review</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>Frontistis et al.</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>Konteks</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr"/>
+      <c r="G73" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J73" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>konteks</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>Applying machine learning and AI for nanofiltration membranes water applications: a review</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Abuhabib et al.</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Konteks</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr"/>
+      <c r="G74" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J74" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>konteks</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="n">
+        <v>80</v>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>Prediction of Remaining Useful Life of Aero-engines Based on CNN-LSTM-Attention</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Deng et al.</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr"/>
+      <c r="G75" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J75" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>Hybrid models, digital twins, and digital shadows for sustainable membrane technologies: A critical review</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>Ghasemzadeh et al.</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>Konteks</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr"/>
+      <c r="G76" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J76" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>konteks</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>Bearing Remaining Useful Life Prediction Based on Naive Bayes and Weibull Distributions</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>Nannan Zhang, Lifeng Wu, Zhonghua Wang, Yong Guan</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>Inti-Metode</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr"/>
+      <c r="G77" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>metode</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>Remaining Useful Life Prediction Method for Bearings Based on LSTM with Uncertainty Quantification</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>Yang et al.</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr"/>
+      <c r="G78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J78" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>A Directed Acyclic Graph Network Combined With CNN and LSTM for Remaining Useful Life Prediction</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>Li et al.</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>2019</v>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr"/>
+      <c r="G79" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J79" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>Deep-Convolution-Based LSTM Network for Remaining Useful Life Prediction</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>Ma et al.</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr"/>
+      <c r="G80" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J80" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="n">
+        <v>61</v>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>Remaining Useful Life Prediction of Wind Turbine Main-Bearing Based on LSTM Optimized Network</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>Li et al.</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr"/>
+      <c r="G81" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J81" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="n">
+        <v>74</v>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Degradation-Aware Remaining Useful Life Prediction With LSTM Autoencoder</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Wu et al.</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr"/>
+      <c r="G82" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J82" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>Remaining Useful Life Prediction of Rolling Bearings Based on CBAM-CNN-LSTM</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Sun et al.</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr"/>
+      <c r="G83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J83" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Mechanism-aligned machine learning for membrane fouling prediction and process control in pressure-driven water treatment membranes: A review</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>Yang et al.</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>Konteks</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr"/>
+      <c r="G84" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J84" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>konteks</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>Intelligent framework for coagulant dosing optimization in an industrial-scale seawater reverse osmosis desalination plant</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>Ridwan et al.</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>Konteks</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr"/>
+      <c r="G85" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J85" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>konteks</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Applications of artificial intelligence for membrane separation: A review</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>Jafari et al.</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>Konteks</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr"/>
+      <c r="G86" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J86" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>konteks</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>Uncertainty in Prognostics and Systems Health Management</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>Sankararaman et al.</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr"/>
+      <c r="G87" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J87" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>A Deep Learning-Based Remaining Useful Life Prediction Approach for Bearings</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Cheng et al.</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr"/>
+      <c r="G88" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J88" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="n">
+        <v>50</v>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>Hybrid Neural Networks for Enhanced Predictions of Remaining Useful Life in Lithium-Ion Batteries</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Rastegarpanah et al.</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr"/>
+      <c r="G89" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J89" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="n">
+        <v>55</v>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Graph neural network-based remaining useful life prediction of milling tools using multi-sensor data</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Kumar et al.</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr"/>
+      <c r="G90" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J90" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="n">
+        <v>67</v>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>Prediction of Remaining Useful Life of Lithium Batteries Based on WOA-VMD and LSTM</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Ouyang et al.</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>Pendukung</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr"/>
+      <c r="G91" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J91" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>pendukung</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Design and development of reverse osmosis (RO) plant status monitoring system for early fault prediction and predictive maintenance</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Srivastava et al.</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>2018</v>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>Konteks</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr"/>
+      <c r="G92" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J92" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>konteks</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>Cellulose acetate from palm oil bunch waste for forward osmosis membrane in desalination of brackish water</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Saiful et al.</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>Konteks</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr"/>
+      <c r="G93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J93" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>konteks</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Predictive Maintenance Scheduling for Aircraft Engines Based on Remaining Useful Life Prediction</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Wang et al.</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>Konteks</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr"/>
+      <c r="G94" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J94" s="2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>konteks</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>Multiscale Analysis of Permeable and Impermeable Wall Models for Seawater Reverse Osmosis Desalination</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Yang et al.</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>Konteks</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr"/>
+      <c r="G95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J95" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>konteks</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="n">
+        <v>82</v>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Optimizing silt density index prediction in water treatment systems using pressure-based gradient boosting hybridized with Salp Swarm Algorithm</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Ouadi et al.</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>Konteks</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr"/>
+      <c r="G96" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J96" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>konteks</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence Applications in Water Treatment and Desalination: A Comprehensive Review</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Alenezi et al.</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>Konteks</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr"/>
+      <c r="G97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J97" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>konteks</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="n">
+        <v>100</v>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Numerical Modelling Assisted Design of a Compact Ultrafiltration (UF) Flat Sheet Membrane Module</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Mokgadi F Bopape, Tim Van Geel, Abhishek Dutta, Bart Van Der Bruggen, Maurice Stephen Onyango</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>Konteks</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr"/>
+      <c r="G98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J98" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>konteks</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>Graphene Based Membrane Modified Silica Nanoparticles for Seawater Desalination and Wastewater Treatment: Salt Rejection and Dyes</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Munasir et al.</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>Konteks</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr"/>
+      <c r="G99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J99" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>konteks</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Mesoporous CA/PEG Membrane-Modified TiO2 Nanoparticles with Improved Desalination Performance</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr"/>
+      <c r="D100" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>Konteks</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr"/>
+      <c r="G100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="J100" s="2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>konteks</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Bio-inspired MXene membranes for enhanced separation and anti-fouling in oil-in-water emulsions: SHAP explainability ML</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Baig et al.</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>Konteks</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr"/>
+      <c r="G101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>konteks</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>Treatment of Coal Mine Acid Water Using Nf270 Membrane as Environmentally Friendly Technology</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Kiswanto et al.</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>Konteks</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr"/>
+      <c r="G102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J102" s="2" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>konteks</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="inlineStr">
+        <is>
+          <t>ATURAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Skor total = RQ (0-2) + kedekatan metode D3/D4/D5/D8 (0-2) + kualitas (0-2); maksimum 6.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Core = skor total &gt;= 5.5 ATAU tier Inti-Metode+Domain.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/docs/SLR_Korpus.xlsx
+++ b/docs/SLR_Korpus.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J107"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -894,17 +894,17 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>E. Membrane/RO/Desalination</t>
+          <t>F. DSS &amp; Predictive Maintenance (IS)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Hybrid models, digital twins, and digital shadows for sustainable membrane technologies: A critical review</t>
+          <t>A two-stage framework for cost-sensitive predictive maintenance using deep learning, GANs, and risk-aware clustering</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Ghasemzadeh et al.</t>
+          <t>Hakami</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -912,75 +912,75 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Advanced Membranes</t>
+          <t>Scientific Reports</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>Scopus Q1 (SCImago SJR 2024)</t>
+          <t>Scopus Q1 (SCImago SJR Best Quartile)</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.advmem.2026.100219</t>
+          <t>https://doi.org/10.1038/s41598-026-42910-4</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Tinjauan kritis yang membedakan dan mengintegrasikan tiga tingkat digitalisasi untuk membran: model hibrida (fisika + ML), digital shadow (DS, aliran data satu arah), dan digital twin (DT, loop tertutup dua arah). Review menyintesis aplikasi pada desalinasi/pengolahan air, MBR, separasi gas (CO2/H2/O2/N2), catalytic membrane reactor, dan PEMFC; menyoroti peran CFD untuk menghasilkan data sintetis, kuantifikasi ketidakpastian (mis. Stochastic Greybox Modeling and Control), serta DSS pemeliharaan prediktif membran (mis. optimasi strategi restorasi elemen RO dengan pengurangan penggantian 50-80 %).</t>
+          <t>Studi mengusulkan kerangka predictive maintenance dua tahap yang berorientasi keputusan biaya, menghubungkan prediksi RUL per komponen dengan optimasi jadwal perawatan. Tahap pertama memakai LSTM untuk memprediksi RUL tiap komponen dan WGAN-GP untuk membangkitkan data run-to-failure sintetis guna mengatasi kelangkaan data kegagalan; tahap kedua mengelompokkan komponen dengan degradasi mirip memakai DBSCAN, lalu memilih ambang waktu perawatan optimal per klaster lewat grid search atas fungsi biaya (preventif, korektif, downtime) dengan proxy risiko berbasis CDF. Validasi pada sistem pabrik air minum kemasan (16 komponen, 3.319 jam operasi) menunjukkan jadwal berbasis klaster menurunkan kegagalan korektif dan biaya dibanding strategi random dan fixed-percentile.</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>Memberikan kerangka konseptual domain untuk keputusan pemeliharaan/penggantian membran berbasis digital twin dan DSS, serta menempatkan kuantifikasi ketidakpastian sebagai prioritas; tidak memakai survival/pencensoringan maupun membangun model RUL survivals.</t>
+          <t>Menunjukkan jalur lengkap dari prediksi RUL sampai keputusan perawatan yang sadar-biaya dan sadar-risiko, plus penanganan data kecil via GAN; sangat relevan sebagai cetak biru DSS, tetapi tidak memakai survival/pencensoringan nyata (penulis sendiri menyebutnya sebagai future work) dan domainnya bukan membran.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="n">
+      <c r="A10" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>E. Membrane/RO/Desalination</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Mechanism-aligned machine learning for membrane fouling prediction and process control in pressure-driven water treatment membranes: A review</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Yang et al.</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Journal of Water Process Engineering</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>A. Survival Analysis &amp; Censored Data</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>A Neural Network-Based Survival Analysis Model Considering Censored Data for Failure Prediction</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>Gao et al.</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>IEEE Transactions on Automation Science and Engineering</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>Scopus Q1 (SCImago SJR Best Quartile)</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.jwpe.2026.110543</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Tinjauan kritis yang mengembangkan kerangka machine learning selaras-mekanisme (mechanism-aligned) untuk prediksi fouling dan kontrol proses pada membran UF, NF, dan RO. Kerangka menghubungkan mekanisme fouling dominan dengan struktur data, arsitektur model, dan aksi kontrol: GRU untuk sinyal hidraulik frekuensi tinggi UF (regulasi fluks, backwash), XGBoost terregularisasi untuk variabel kualitas air multikolinear NF (dosis koagulan, pH), dan CNN-GRU-SHAP untuk biofouling/scaling RO yang heterogen spasial (antiscalant, pH, pembersihan tertarget, biocide). Tinjauan juga membahas benchmarking, noise SCADA, kelangkaan data, fallback control, edge deployment, dan interpretabilitas operator.</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>Menghubungkan prediksi fouling (termasuk target seperti 'probability of crossing a cleaning threshold' dan 'expected time to CIP') dengan aksi kontrol/pemeliharaan pada membran RO - sangat relevan untuk konteks domain tesis; namun tidak memakai survival analysis/censoring dan tidak memprediksi RUL secara eksplisit.</t>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1109/tase.2025.3640217</t>
+        </is>
+      </c>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Studi mengusulkan Bayesian LSTM-SURV, metode yang mengintegrasikan survival analysis (SA) dengan jaringan saraf untuk memodelkan hubungan non-linear antara sinyal degradasi multi-sensor dan RUL dengan adanya data tersensor. Alih-alih memprediksi nilai RUL langsung, model mengasumsikan masa pakai mengikuti distribusi Weibull dan memakai fungsi loss yang diturunkan dari likelihood SA agar memanfaatkan data lengkap dan tersensor; prosedur Bayesian mentransfer informasi dari unit latih ke unit uji. Diuji pada data simulasi dan dataset gas turbine C-MAPSS, model mengungguli TSNN dan DeepSurv (RMSE terbaik 4,420) serta mengkuantifikasi ketidakpastian via interval 90%.</t>
+        </is>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Menyediakan kerangka inti-metode tesis: analisis survival + jaringan saraf (LSTM) yang menangani data tersensor sekaligus mengkuantifikasi ketidakpastian prediksi RUL - kombinasi yang persis dibutuhkan tesis untuk membran RO dengan data lapangan tersensor.</t>
         </is>
       </c>
     </row>
@@ -990,21 +990,21 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>E. Membrane/RO/Desalination</t>
+          <t>A. Survival Analysis &amp; Censored Data</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Physics-informed machine learning for cross-study prediction of oil–water membrane fouling</t>
+          <t>Nonlinear degradation modeling and remaining useful life prediction for electric drive system with multiple failure modes</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Alves et al.</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
@@ -1018,17 +1018,17 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41598-026-54120-z</t>
+          <t>https://doi.org/10.1038/s41598-025-22866-7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>Studi menggabungkan model finite-element reduced-order (ROM) transport dan resistansi fouling dengan kerangka data-driven yang memetakan metadata eksperimen ke perilaku penurunan fluks lintas data. Dari 112 dataset (berbagai membran, minyak, kondisi operasi), ROM mereproduksi trajektori fluks dengan R2 rata-rata ~0,95; prediksi tersegmentasi (early/mid/late) memberi MAE 0,079-0,14 pada grouped cross-validation. Validasi publikasi-level (holdout studi tak terlihat) menunjukkan MAE meningkat ~2x, mengungkap 'cross-study generalization penalty': keterbatasan prediksi lebih disebabkan kelengkapan metadata dan variabilitas antar-studi, bukan kapasitas model. Diusulkan checklist metadata minimal untuk model fouling yang reproducible.</t>
+          <t>Studi membangun kerangka prediksi RUL untuk electric drive system (EDS) dengan banyak mode kegagalan. Composite health indicator dibentuk dari fusi kontribusi kerusakan tiap komponen memakai entropy weight method, lalu lintasan degradasi dimodelkan secara nonlinier eksponensial dan dikoreksi dengan acceleration factor antara spektrum uji dipercepat dan spektrum pengguna. Parameter diestimasi dengan EM dan diperbarui secara Bayesian untuk memprediksi RUL beserta kuantifikasi ketidakpastian (distribusi RUL, interval 95%).</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>Sangat relevan pada sumbu domain (fouling membran) dan sumbu transfer lintas-studi (small-data/domain shift) tesis, serta menegaskan pentingnya keterwakilan data; tidak memakai survival/pencensoringan dan berfokus pada MF/UF oil-water, bukan RO.</t>
+          <t>Contoh mutakhir pemodelan degradasi nonlinier + estimasi EM + pembaruan Bayesian yang menghasilkan distribusi RUL dan interval kepercayaan (CIC) per pengguna - pola kuantifikasi ketidakpastian yang berguna bagi tesis; namun tidak memodelkan data tersensor/survival (Weibull/hazard) dan domainnya sistem penggerak listrik, bukan membran.</t>
         </is>
       </c>
     </row>
@@ -1038,93 +1038,93 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>F. DSS &amp; Predictive Maintenance (IS)</t>
+          <t>B. Deep Learning RUL</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>A two-stage framework for cost-sensitive predictive maintenance using deep learning, GANs, and risk-aware clustering</t>
+          <t>A physics-informed neural network-based method for predicting degradation trajectories and remaining useful life of supercapacitors</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Hakami</t>
+          <t>E et al.</t>
         </is>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Scientific Reports</t>
+          <t>Green Energy and Intelligent Transportation</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
+          <t>Scopus Q1 (SCImago SJR 2024)</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.1016/j.geits.2025.100291</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Studi mengembangkan Physics-Informed Neural Network (PINN) berbasis LSTM untuk memprediksi trajektori degradasi dan RUL supercapacitor, dengan menyisipkan persamaan penuaan empiris (SOH = A·ln(cycle) + B) ke dalam fungsi loss. Bobot penyeimbang antara loss data dan loss fisika (lambda) dioptimasi secara adaptif menggunakan Bayesian optimization.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Menunjukkan integrasi pengetahuan fisika dan deep learning dapat memangkas kebutuhan data training secara drastis (hanya 1-5% siklus hidup) sehingga relevan untuk tesis RUL membran yang berhadapan dengan kelangkaan data degradasi; namun belum menangani kelayakan/handling data tersensor maupun ketidakpastian prediksi RUL.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>B. Deep Learning RUL</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Remaining Useful Life Prediction of Rolling Bearings Based on CBAM-CNN-LSTM</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Sun et al.</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Sensors</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>Scopus Q1 (SCImago SJR Best Quartile)</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1038/s41598-026-42910-4</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan kerangka predictive maintenance dua tahap yang berorientasi keputusan biaya, menghubungkan prediksi RUL per komponen dengan optimasi jadwal perawatan. Tahap pertama memakai LSTM untuk memprediksi RUL tiap komponen dan WGAN-GP untuk membangkitkan data run-to-failure sintetis guna mengatasi kelangkaan data kegagalan; tahap kedua mengelompokkan komponen dengan degradasi mirip memakai DBSCAN, lalu memilih ambang waktu perawatan optimal per klaster lewat grid search atas fungsi biaya (preventif, korektif, downtime) dengan proxy risiko berbasis CDF. Validasi pada sistem pabrik air minum kemasan (16 komponen, 3.319 jam operasi) menunjukkan jadwal berbasis klaster menurunkan kegagalan korektif dan biaya dibanding strategi random dan fixed-percentile.</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>Menunjukkan jalur lengkap dari prediksi RUL sampai keputusan perawatan yang sadar-biaya dan sadar-risiko, plus penanganan data kecil via GAN; sangat relevan sebagai cetak biru DSS, tetapi tidak memakai survival/pencensoringan nyata (penulis sendiri menyebutnya sebagai future work) dan domainnya bukan membran.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>A. Survival Analysis &amp; Censored Data</t>
-        </is>
-      </c>
-      <c r="C13" s="3" t="inlineStr">
-        <is>
-          <t>A Neural Network-Based Survival Analysis Model Considering Censored Data for Failure Prediction</t>
-        </is>
-      </c>
-      <c r="D13" s="3" t="inlineStr">
-        <is>
-          <t>Gao et al.</t>
-        </is>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F13" s="3" t="inlineStr">
-        <is>
-          <t>IEEE Transactions on Automation Science and Engineering</t>
-        </is>
-      </c>
-      <c r="G13" s="3" t="inlineStr">
-        <is>
-          <t>Scopus Q1 (SCImago SJR Best Quartile)</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1109/tase.2025.3640217</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan Bayesian LSTM-SURV, metode yang mengintegrasikan survival analysis (SA) dengan jaringan saraf untuk memodelkan hubungan non-linear antara sinyal degradasi multi-sensor dan RUL dengan adanya data tersensor. Alih-alih memprediksi nilai RUL langsung, model mengasumsikan masa pakai mengikuti distribusi Weibull dan memakai fungsi loss yang diturunkan dari likelihood SA agar memanfaatkan data lengkap dan tersensor; prosedur Bayesian mentransfer informasi dari unit latih ke unit uji. Diuji pada data simulasi dan dataset gas turbine C-MAPSS, model mengungguli TSNN dan DeepSurv (RMSE terbaik 4,420) serta mengkuantifikasi ketidakpastian via interval 90%.</t>
-        </is>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>Menyediakan kerangka inti-metode tesis: analisis survival + jaringan saraf (LSTM) yang menangani data tersensor sekaligus mengkuantifikasi ketidakpastian prediksi RUL - kombinasi yang persis dibutuhkan tesis untuk membran RO dengan data lapangan tersensor.</t>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>https://doi.org/10.3390/s25020554</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Studi ini mengusulkan metode prediksi RUL bantalan gelinding berbasis CBAM-CNN-LSTM: sinyal vibrasi diproses FFT ke domain frekuensi, fitur diekstraksi CNN, dibobot oleh CBAM (channel attention lalu spatial attention secara seri), dan dependensi temporalnya dipelajari LSTM secara end-to-end dengan label RUL dinormalisasi ke rentang (0,1). Model diuji pada dataset publik PHM2012 dengan enam bantalan uji (1-3, 1-4, 1-5, 1-7, 2-3, 2-6) dan mengungguli CNN-LSTM, ECA-CNN-LSTM, serta dua metode literatur. Klaim utama: penurunan MSE 53%, MAE 16,87% (abstrak) / 9,75% (kesimpulan), dan RMSE 31,68% dibanding metode pembanding.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>Bagi tesis, paper ini menjadi bukti bahwa arsitektur CNN + atensi hibrida (channel+spatial) + LSTM adalah baseline kuat untuk point-prediction RUL di domain mekanikal, namun sama sekali tidak menangani data tersensor maupun survival analysis. Ini memperkuat gap tesis: integrasi survival analysis (censoring/Weibull/hazard) dengan deep learning masih terbuka, terlebih untuk objek membran/RO.</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>A. Survival Analysis &amp; Censored Data</t>
+          <t>C. Bayesian &amp; Uncertainty</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Nonlinear degradation modeling and remaining useful life prediction for electric drive system with multiple failure modes</t>
+          <t>Counterfactual explanations for remaining useful life estimation within a Bayesian framework</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>Andringa et al.</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Scientific Reports</t>
+          <t>Information Fusion</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1162,17 +1162,17 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41598-025-22866-7</t>
+          <t>https://doi.org/10.1016/j.inffus.2025.102972</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>Studi membangun kerangka prediksi RUL untuk electric drive system (EDS) dengan banyak mode kegagalan. Composite health indicator dibentuk dari fusi kontribusi kerusakan tiap komponen memakai entropy weight method, lalu lintasan degradasi dimodelkan secara nonlinier eksponensial dan dikoreksi dengan acceleration factor antara spektrum uji dipercepat dan spektrum pengguna. Parameter diestimasi dengan EM dan diperbarui secara Bayesian untuk memprediksi RUL beserta kuantifikasi ketidakpastian (distribusi RUL, interval 95%).</t>
+          <t>Studi menggabungkan Bayesian LSTM (B-LSTM) dengan counterfactual explanations (CFE) dari DiCE untuk (1) meningkatkan interpretabilitas estimasi RUL dan (2) meningkatkan akurasi melalui augmentasi data. Dua jenis CFE dihasilkan: RUL CFE (skenario yang menaikkan/menurunkan RUL) dan Uncertainty CFE (skenario yang menurunkan ketidakpastian prediksi). Pada dataset C-MAPSS FD001, model yang diaugmentasi dengan Uncertainty CFE terbaik (RMSE 8,47 vs baseline 9,56; akurasi alpha=0,2 79% vs 74%).</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Contoh mutakhir pemodelan degradasi nonlinier + estimasi EM + pembaruan Bayesian yang menghasilkan distribusi RUL dan interval kepercayaan (CIC) per pengguna - pola kuantifikasi ketidakpastian yang berguna bagi tesis; namun tidak memodelkan data tersensor/survival (Weibull/hazard) dan domainnya sistem penggerak listrik, bukan membran.</t>
+          <t>Menyediakan kerangka kuantifikasi ketidakpastian (posterior Bayesian) sekaligus menjelaskan keterkaitan aksi pemeliharaan dengan perubahan RUL secara kausal-kontrafaktual, inti bagi DSS tesis. Namun tidak memakai survival/penyensoran eksplisit dan tidak menyentuh domain membran.</t>
         </is>
       </c>
     </row>
@@ -1187,40 +1187,40 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>A physics-informed neural network-based method for predicting degradation trajectories and remaining useful life of supercapacitors</t>
+          <t>Remaining Useful Life Prediction of Wind Turbine Main-Bearing Based on LSTM Optimized Network</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>E et al.</t>
+          <t>Li et al.</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Green Energy and Intelligent Transportation</t>
+          <t>IEEE Sensors Journal</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Scopus Q1 (SCImago SJR 2024)</t>
+          <t>Scopus Q1 (SCImago SJR Best Quartile)</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.geits.2025.100291</t>
+          <t>https://doi.org/10.1109/jsen.2024.3402660</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>Studi mengembangkan Physics-Informed Neural Network (PINN) berbasis LSTM untuk memprediksi trajektori degradasi dan RUL supercapacitor, dengan menyisipkan persamaan penuaan empiris (SOH = A·ln(cycle) + B) ke dalam fungsi loss. Bobot penyeimbang antara loss data dan loss fisika (lambda) dioptimasi secara adaptif menggunakan Bayesian optimization.</t>
+          <t>Studi memprediksi RUL bantalan utama (main bearing) turbin angin lepas pantai menggunakan data getaran historis nyata. Indeks kondisi diekstraksi dari prinsip sideband energy ratio (SER) di sekitar frekuensi meshing gearbox, lalu LSTM yang dioptimalkan tree-seed algorithm (TSA-LSTM) memodelkan tren degradasi; RUL diperoleh dari pencocokan eksponensial indeks OM/IM terhadap first prognostic time (FPT). Model mencapai MAPE &lt; 0,228 dan RMSE &lt; 0,014 dan mengungguli LSTM dasar, PSO-LSTM, dan Random Forest.</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Menunjukkan integrasi pengetahuan fisika dan deep learning dapat memangkas kebutuhan data training secara drastis (hanya 1-5% siklus hidup) sehingga relevan untuk tesis RUL membran yang berhadapan dengan kelangkaan data degradasi; namun belum menangani kelayakan/handling data tersensor maupun ketidakpastian prediksi RUL.</t>
+          <t>Memberi contoh konkret pipeline RUL berbasis deep learning pada data getaran nyata dengan ekstraksi fitur fisik (SER) dan optimasi metaheuristik, serta ambang alarm berjenjang. Relevan bagi tesis sebagai pembanding metode RUL DL, namun tanpa sumbu survival/penyensoran maupun domain membran.</t>
         </is>
       </c>
     </row>
@@ -1230,25 +1230,25 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>B. Deep Learning RUL</t>
+          <t>F. DSS &amp; Predictive Maintenance (IS)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Remaining Useful Life Prediction of Rolling Bearings Based on CBAM-CNN-LSTM</t>
+          <t>Predictive Maintenance Scheduling for Aircraft Engines Based on Remaining Useful Life Prediction</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Sun et al.</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Sensors</t>
+          <t>IEEE Internet of Things Journal</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1258,17 +1258,17 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/s25020554</t>
+          <t>https://doi.org/10.1109/jiot.2024.3376715</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>Studi ini mengusulkan metode prediksi RUL bantalan gelinding berbasis CBAM-CNN-LSTM: sinyal vibrasi diproses FFT ke domain frekuensi, fitur diekstraksi CNN, dibobot oleh CBAM (channel attention lalu spatial attention secara seri), dan dependensi temporalnya dipelajari LSTM secara end-to-end dengan label RUL dinormalisasi ke rentang (0,1). Model diuji pada dataset publik PHM2012 dengan enam bantalan uji (1-3, 1-4, 1-5, 1-7, 2-3, 2-6) dan mengungguli CNN-LSTM, ECA-CNN-LSTM, serta dua metode literatur. Klaim utama: penurunan MSE 53%, MAE 16,87% (abstrak) / 9,75% (kesimpulan), dan RMSE 31,68% dibanding metode pembanding.</t>
+          <t>Artikel ini membangun kerangka penjadwalan pemeliharaan prediktif berbasis prediksi RUL untuk mesin pesawat. Prediksi RUL dilakukan oleh model ensemble 1-D CNN dan Bi-LSTM dengan attention (BO-CNN-Bi-LSTM-AM) yang hyperparameter-nya dioptimasi Bayesian optimization; ketika RUL melampaui ambang alarm, tugas penjadwalan dipicu. Penjadwalan banyak mesin ke beberapa pusat perawatan diformulasikan sebagai MILP untuk meminimalkan waktu penyelesaian pemeliharaan maksimum.</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Bagi tesis, paper ini menjadi bukti bahwa arsitektur CNN + atensi hibrida (channel+spatial) + LSTM adalah baseline kuat untuk point-prediction RUL di domain mekanikal, namun sama sekali tidak menangani data tersensor maupun survival analysis. Ini memperkuat gap tesis: integrasi survival analysis (censoring/Weibull/hazard) dengan deep learning masih terbuka, terlebih untuk objek membran/RO.</t>
+          <t>Menghubungkan prediksi RUL dengan keputusan operasional konkret (penjadwalan pemeliharaan banyak-unit) melalui MILP, memberi contoh operasionalisasi keputusan dari RUL. Relevan ke tesis sebagai rujukan lapisan keputusan (d6), namun tidak memodelkan penyensoran/survival maupun domain membran, sehingga menegaskan celah integrasi survival + keputusan pada membran RO.</t>
         </is>
       </c>
     </row>
@@ -1278,25 +1278,25 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>C. Bayesian &amp; Uncertainty</t>
+          <t>A. Survival Analysis &amp; Censored Data</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Counterfactual explanations for remaining useful life estimation within a Bayesian framework</t>
+          <t>Integrating Survival Analysis with Bayesian Statistics to Forecast the Remaining Useful Life of a Centrifugal Pump Conditional to Multiple Fault Types</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Andringa et al.</t>
+          <t>Kapuria &amp; Cole</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Information Fusion</t>
+          <t>Energies</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1306,17 +1306,17 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.inffus.2025.102972</t>
+          <t>https://doi.org/10.3390/en16093707</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>Studi menggabungkan Bayesian LSTM (B-LSTM) dengan counterfactual explanations (CFE) dari DiCE untuk (1) meningkatkan interpretabilitas estimasi RUL dan (2) meningkatkan akurasi melalui augmentasi data. Dua jenis CFE dihasilkan: RUL CFE (skenario yang menaikkan/menurunkan RUL) dan Uncertainty CFE (skenario yang menurunkan ketidakpastian prediksi). Pada dataset C-MAPSS FD001, model yang diaugmentasi dengan Uncertainty CFE terbaik (RMSE 8,47 vs baseline 9,56; akurasi alpha=0,2 79% vs 74%).</t>
+          <t>Paper mengintegrasikan analisis survival dengan Bayesian network untuk memperkirakan RUL pompa sentrifugal secara probabilistik dan terkondisi pada tipe kegagalan (operasi normal, kavitasi, poros bengkok). Data getaran diubah menjadi fitur (crest factor, skewness, kurtosis) yang menjadi evidence Bayesian network; fungsi survival Kaplan-Meier dan model Weibull per-tipe-fault dipakai untuk memprediksi RUL. Studi kasus menunjukkan diagnosis 95,8% kavitasi dan RUL yang mengikuti kurva kavitasi dengan deviasi akibat ketidakpastian.</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Menyediakan kerangka kuantifikasi ketidakpastian (posterior Bayesian) sekaligus menjelaskan keterkaitan aksi pemeliharaan dengan perubahan RUL secara kausal-kontrafaktual, inti bagi DSS tesis. Namun tidak memakai survival/penyensoran eksplisit dan tidak menyentuh domain membran.</t>
+          <t>Menunjukkan cara mengondisikan RUL pada tipe fault via Bayesian network + survival analysis, sehingga RUL menjadi probabilistik dan dapat dipakai dalam kerangka keputusan maintenance. Ini pola yang dapat diadopsi tesis untuk mengondisikan RUL membran pada mode fouling yang berbeda.</t>
         </is>
       </c>
     </row>
@@ -1326,25 +1326,25 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>E. Membrane/RO/Desalination</t>
+          <t>B. Deep Learning RUL</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Applications in Water Treatment and Desalination: A Comprehensive Review</t>
+          <t>Multiform Informed Machine Learning Based on Piecewise and Weibull for Engine Remaining Useful Life Prediction</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Alenezi et al.</t>
+          <t>Zhou et al.</t>
         </is>
       </c>
       <c r="E18" s="2" t="n">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1354,17 +1354,17 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/w17081169</t>
+          <t>https://doi.org/10.3390/s23125669</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>Artikel ini adalah tinjauan komprehensif penerapan kecerdasan buatan (AI) pada pengolahan air dan desalinasi, mencakup machine learning, neural network, dan genetic algorithm untuk prediksi, optimasi proses, serta deteksi kesalahan dan pemeliharaan prediktif. Studi melaporkan AI menurunkan konsumsi energi hingga ~50% (klaim abstrak) dan mendukung pemeliharaan prediktif untuk meminimalkan downtime, dengan studi kasus pada sistem RO, MSF, dan ADD yang ditenagai energi terbarukan. Penulis mengidentifikasi tantangan data, daya komputasi, dan interpretabilitas model.</t>
+          <t>Studi mengusulkan informed machine learning (IML) multiform untuk prediksi RUL aero-engine dengan mengintegrasikan dua bentuk pengetahuan domain dari rekayasa keandalan: (1) Piecewise RUL yang dipakai untuk menetapkan label data latih, dan (2) fungsi distribusi kumulatif Weibull yang diintegrasikan ke loss function (Weibull-combined loss). Model LSTM sederhana dilatih pada C-MAPSS; integrasi kedua pengetahuan menurunkan RMSE paling besar (ablation) dan model Weibull-RMSLE-Comb paling stabil, mengalahkan metode SOTA (MSTformer) pada kondisi operasi kompleks FD002/FD004.</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Memberi peta lanskap penerapan AI di desalinasi/RO dan menegaskan bahwa pemeliharaan prediktif serta prediksi umur/penyumbatan membran adalah area kunci, sekaligus menyoroti kelangkaan data, transparansi pelaporan, dan ketiadaan studi jangka panjang. Relevan ke tesis sebagai justifikasi domain dan celah: prediksi RUL membran berbasis survival dengan data tersensor belum tercakup dalam tinjauan ini.</t>
+          <t>Menunjukkan cara menyuntikkan pengetahuan keandalan (Weibull CDF sebagai loss, label Piecewise) ke dalam pipeline DL untuk RUL - relevan bagi tesis karena memakai distribusi Weibull/reliability sebagai pengetahuan domain dan mengklaim membantu keterbatasan data; tetapi tidak memodelkan data tersensor dan domainnya bukan membran.</t>
         </is>
       </c>
     </row>
@@ -1379,7 +1379,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Remaining Useful Life Prediction of Wind Turbine Main-Bearing Based on LSTM Optimized Network</t>
+          <t>Remaining Useful Life Prediction of Turbofan Engines Using CNN-LSTM-SAM Approach</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="E19" s="2" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
@@ -1402,17 +1402,17 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/jsen.2024.3402660</t>
+          <t>https://doi.org/10.1109/jsen.2023.3261874</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>Studi memprediksi RUL bantalan utama (main bearing) turbin angin lepas pantai menggunakan data getaran historis nyata. Indeks kondisi diekstraksi dari prinsip sideband energy ratio (SER) di sekitar frekuensi meshing gearbox, lalu LSTM yang dioptimalkan tree-seed algorithm (TSA-LSTM) memodelkan tren degradasi; RUL diperoleh dari pencocokan eksponensial indeks OM/IM terhadap first prognostic time (FPT). Model mencapai MAPE &lt; 0,228 dan RMSE &lt; 0,014 dan mengungguli LSTM dasar, PSO-LSTM, dan Random Forest.</t>
+          <t>Paper mengusulkan algoritma fusi deep learning CNN-LSTM dengan self-attention mechanism (SAM/CLS) untuk memprediksi RUL turbofan engine, khususnya pada mode multi-operating point (MOP) yang sangat non-linear. CNN mengekstrak fitur spasial, LSTM mengekstrak fitur temporal, dan SAM memberi bobot adaptif pada unit hidden untuk mengatasi kehilangan informasi LSTM. Dievaluasi pada C-MAPSS FD001-FD004, model mencapai RMSE 12,56/15,25/13,77/18,63 dan mengalahkan metode pembanding pada mode MOP.</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Memberi contoh konkret pipeline RUL berbasis deep learning pada data getaran nyata dengan ekstraksi fitur fisik (SER) dan optimasi metaheuristik, serta ambang alarm berjenjang. Relevan bagi tesis sebagai pembanding metode RUL DL, namun tanpa sumbu survival/penyensoran maupun domain membran.</t>
+          <t>Menjadi contoh state-of-the-art arsitektur deep learning (CNN+LSTM+attention) untuk regresi RUL point-estimate pada data multi-sensor non-stasioner. Relevan ke tesis sebagai baseline model deep learning, tetapi tidak menangani data tersensor maupun kuantifikasi ketidakpastian — justru menunjukkan celah yang coba diisi tesis.</t>
         </is>
       </c>
     </row>
@@ -1422,25 +1422,25 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>E. Membrane/RO/Desalination</t>
+          <t>A. Survival Analysis &amp; Censored Data</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Applications of artificial intelligence for membrane separation: A review</t>
+          <t>Prognostic modeling of predictive maintenance with survival analysis for mobile work equipment</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Jafari et al.</t>
+          <t>Yang et al.</t>
         </is>
       </c>
       <c r="E20" s="2" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Journal of Water Process Engineering</t>
+          <t>Scientific Reports</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1450,17 +1450,17 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.jwpe.2024.106532</t>
+          <t>https://doi.org/10.1038/s41598-022-12572-z</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>Tinjauan bibliometrik (PRISMA, Scopus/Web of Science, 2013-2023) atas penerapan AI pada proses separasi membran, mencakup MF, UF, NF, RO, FO, MBR, dan MD. Review memetakan algoritma (ANN dominan &gt;150 penggunaan; RF dan SVM paling banyak di ML), rata-rata akurasi R2 per algoritma (mis. CNN ~0,98; ANN ~0,94; LR/MLR ~0,58), serta membahas fouling, optimasi proses, kendali real-time, dan tantangan keterbatasan data serta interpretabilitas.</t>
+          <t>Studi menyusun kerangka survival analysis untuk prognostik pemeliharaan prediktif komponen alat kerja bergerak (mobile work equipment). Dari catatan pemeliharaan nyata (7.896 event, 658 mesin, 12 komponen), penulis mengidentifikasi campuran jenis pencensoringan (kiri, interval, kanan) dan menyaring hanya data tersensor-kanan; lalu mengestimasi fungsi survival Kaplan-Meier, hazard non-parametrik (kernel/Nelson-Aalen), serta lima model parametrik (Exponential, Weibull, Log-logistic, Log-normal, Generalized-gamma). Hazard bersifat kompleks; non-parametrik umumnya terbaik, dengan Generalized-gamma sebagai parametrik unggulan.</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Memetakan lanskap AI untuk membran (termasuk RO dan prediksi fouling), berguna sebagai konteks pemilihan metode; tidak memakai survival/pencensoringan, tidak membangun model RUL, dan tidak membangun keputusan pemeliharaan.</t>
+          <t>Preseden metodologis kuat untuk pemodelan data tersensor (survival/hazard/Weibull) yang menjadi inti metode tesis, termasuk penanganan tiga jenis pencensoringan dan pemilihan parametrik vs non-parametrik; namun domainnya alat berat (bukan membran) dan tanpa kovariat/sensor.</t>
         </is>
       </c>
     </row>
@@ -1470,25 +1470,25 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>E. Membrane/RO/Desalination</t>
+          <t>A. Survival Analysis &amp; Censored Data</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Optimizing silt density index prediction in water treatment systems using pressure-based gradient boosting hybridized with Salp Swarm Algorithm</t>
+          <t>Weibull recurrent neural networks for failure prognosis using histogram data</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Ouadi et al.</t>
+          <t>Dhada et al.</t>
         </is>
       </c>
       <c r="E21" s="2" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Journal of Water Process Engineering</t>
+          <t>Neural Computing and Applications</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -1498,17 +1498,17 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.jwpe.2024.106479</t>
+          <t>https://doi.org/10.1007/s00521-022-07667-7</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Studi memprediksi Silt Density Index (SDI) - indikator potensi fouling partikulat pada pra-perlakuan air laut untuk reverse osmosis (RO) - memakai Gradient Boosting (GB) yang hyperparameternya dioptimasi dengan Salp Swarm Algorithm (GBSSA). Fitur input tunggal adalah tekanan harian (bar) tahap pra-perlakuan; targetnya SDI harian. Data diambil dari dua plant desalinasi di Aljazair barat (Benisaf dan El Mactaa) selama satu bulan (30 hari, Tabel 3). Tiga varian dibandingkan: GB standar, GB+PSO (GBPSO), dan GB+SSA (GBSSA). Preprocessing: interpolasi linear untuk data hilang, robust Z-score (buang &gt;3 SD), normalisasi [0,1], split acak 70/30 latih-uji. GBSSA terbaik pada kedua plant; tidak ada pemodelan RUL, survival analysis, censoring, maupun kuantifikasi ketidakpastian.</t>
+          <t>Studi menyajikan use case industri pertama WTTE-RNN (Weibull time-to-event recurrent neural network) untuk prognosis kegagalan turbocharger pada armada truk Scania. WTTE-RNN mengoptimalkan parameter distribusi Weibull waktu-ke-kegagalan via RNN menggunakan loss log-likelihood yang memanfaatkan data tersensor (truk yang tidak gagal). Data kondisi berupa histogram yang jarang ter-sampling (10-30 snapshot/truk); dimensi direduksi via relative entropy antar-histogram. Hasil: WTTE-RNN memberi rentang galat yang memadai untuk perencanaan pemeliharaan; menggabungkan data tersensor memperbaiki prediksi, tetapi rasio tersensor:tak-tersensor yang terlalu timpang merusak performa; clustering sub-armada hanya bermanfaat bila dataset cukup besar.</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Mengusulkan hibrida baru GBSSA (Gradient Boosting + Salp Swarm Algorithm) untuk prediksi SDI pada sistem desalinasi; melakukan tuning hyperparameter GB (learning rate, jumlah pohon, kedalaman) dengan SSA berobjektif MAE; membandingkan secara sistematis GB vs GBPSO vs GBSSA pada dua plant desalinasi nyata; menunjukkan bahwa sensor tekanan yang murah/sederhana (tanpa sensor kompleks dan intervensi manual berlebih) cukup untuk memprediksi SDI; menghubungkan akurasi prediksi SDI dengan keputusan operasional dan jadwal pembersihan membran (manajemen fouling).</t>
+          <t>Mendemonstrasikan secara industri bahwa WTTE-RNN (survival Weibull + RNN) yang memanfaatkan data tersensor dapat langsung mendukung keputusan pemeliharaan berbasis risiko - inti metode tesis, meski domainnya armada truk (bukan membran).</t>
         </is>
       </c>
     </row>
@@ -1518,25 +1518,25 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>F. DSS &amp; Predictive Maintenance (IS)</t>
+          <t>B. Deep Learning RUL</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Predictive Maintenance Scheduling for Aircraft Engines Based on Remaining Useful Life Prediction</t>
+          <t>Bi-LSTM-Based Two-Stream Network for Machine Remaining Useful Life Prediction</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>Jin et al.</t>
         </is>
       </c>
       <c r="E22" s="2" t="n">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>IEEE Internet of Things Journal</t>
+          <t>IEEE Transactions on Instrumentation and Measurement</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1546,17 +1546,17 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/jiot.2024.3376715</t>
+          <t>https://doi.org/10.1109/tim.2022.3167778</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Artikel ini membangun kerangka penjadwalan pemeliharaan prediktif berbasis prediksi RUL untuk mesin pesawat. Prediksi RUL dilakukan oleh model ensemble 1-D CNN dan Bi-LSTM dengan attention (BO-CNN-Bi-LSTM-AM) yang hyperparameter-nya dioptimasi Bayesian optimization; ketika RUL melampaui ambang alarm, tugas penjadwalan dipicu. Penjadwalan banyak mesin ke beberapa pusat perawatan diformulasikan sebagai MILP untuk meminimalkan waktu penyelesaian pemeliharaan maksimum.</t>
+          <t>Studi mengusulkan handcrafted feature flows (HFFs) untuk menekan noise pada sinyal mentah dan jaringan dua-stream berbasis Bi-LSTM yang menggabungkan stream sinyal mentah dengan stream HFF. Tiga metode fusi diuji (late, concatenation, addition); fusi addition terbaik. Pada dataset C-MAPSS (FD001-FD004), model mencapai RMSE 11,96/14,48/13,41/15,11 dan mengungguli 8 metode SOTA termasuk CNN-BiLSTM.</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Menghubungkan prediksi RUL dengan keputusan operasional konkret (penjadwalan pemeliharaan banyak-unit) melalui MILP, memberi contoh operasionalisasi keputusan dari RUL. Relevan ke tesis sebagai rujukan lapisan keputusan (d6), namun tidak memodelkan penyensoran/survival maupun domain membran, sehingga menegaskan celah integrasi survival + keputusan pada membran RO.</t>
+          <t>Preseden metode RUL deep learning dengan rekayasa fitur (HFF) dan arsitektur multi-stream/fusi, berguna sebagai pembanding metode bagi tesis; namun tanpa survival/penyensoran dan bukan domain membran, sehingga Pendukung.</t>
         </is>
       </c>
     </row>
@@ -1566,21 +1566,21 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>A. Survival Analysis &amp; Censored Data</t>
+          <t>B. Deep Learning RUL</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Integrating Survival Analysis with Bayesian Statistics to Forecast the Remaining Useful Life of a Centrifugal Pump Conditional to Multiple Fault Types</t>
+          <t>Prediction of Remaining Useful Life of Lithium Batteries Based on WOA-VMD and LSTM</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Kapuria &amp; Cole</t>
+          <t>Ouyang et al.</t>
         </is>
       </c>
       <c r="E23" s="2" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/en16093707</t>
+          <t>https://doi.org/10.3390/en15238918</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>Paper mengintegrasikan analisis survival dengan Bayesian network untuk memperkirakan RUL pompa sentrifugal secara probabilistik dan terkondisi pada tipe kegagalan (operasi normal, kavitasi, poros bengkok). Data getaran diubah menjadi fitur (crest factor, skewness, kurtosis) yang menjadi evidence Bayesian network; fungsi survival Kaplan-Meier dan model Weibull per-tipe-fault dipakai untuk memprediksi RUL. Studi kasus menunjukkan diagnosis 95,8% kavitasi dan RUL yang mengikuti kurva kavitasi dengan deviasi akibat ketidakpastian.</t>
+          <t>Studi mengusulkan model hibrida WOA-VMD-LSTM untuk prediksi RUL baterai lithium-ion. Whale Optimization Algorithm (WOA) mengoptimalkan parameter VMD (K dan alpha) agar sinyal kapasitas terdekomposisi menjadi komponen ganda tren atenuasi global dan komponen fluaktuasi pemulihan kapasitas; masing-masing komponen diprediksi LSTM lalu direkonstruksi menjadi RUL. Hasil pada dataset NASA menunjukkan AE maksimum 2 siklus, RMSE rata-rata &lt; 0,69%, dan MAPE rata-rata &lt; 0,43%, mengungguli LSTM, EMD-LSTM, VMD-LSTM, dan ELM.</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>Menunjukkan cara mengondisikan RUL pada tipe fault via Bayesian network + survival analysis, sehingga RUL menjadi probabilistik dan dapat dipakai dalam kerangka keputusan maintenance. Ini pola yang dapat diadopsi tesis untuk mengondisikan RUL membran pada mode fouling yang berbeda.</t>
+          <t>Menunjukkan pipeline deep learning RUL dengan pra-pemrosesan dekomposisi sinyal (mengatasi fenomena pemulihan kapasitas), relevan sebagai pembanding arsitektur DL RUL. Namun tidak memakai survival/penyensoran dan bukan domain membran.</t>
         </is>
       </c>
     </row>
@@ -1619,16 +1619,16 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Multiform Informed Machine Learning Based on Piecewise and Weibull for Engine Remaining Useful Life Prediction</t>
+          <t>Remaining Useful Life Prediction Method for Bearings Based on LSTM with Uncertainty Quantification</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Zhou et al.</t>
+          <t>Yang et al.</t>
         </is>
       </c>
       <c r="E24" s="2" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
@@ -1642,17 +1642,17 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/s23125669</t>
+          <t>https://doi.org/10.3390/s22124549</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>Studi mengusulkan informed machine learning (IML) multiform untuk prediksi RUL aero-engine dengan mengintegrasikan dua bentuk pengetahuan domain dari rekayasa keandalan: (1) Piecewise RUL yang dipakai untuk menetapkan label data latih, dan (2) fungsi distribusi kumulatif Weibull yang diintegrasikan ke loss function (Weibull-combined loss). Model LSTM sederhana dilatih pada C-MAPSS; integrasi kedua pengetahuan menurunkan RMSE paling besar (ablation) dan model Weibull-RMSLE-Comb paling stabil, mengalahkan metode SOTA (MSTformer) pada kondisi operasi kompleks FD002/FD004.</t>
+          <t>Makalah mengusulkan metode prediksi RUL bearing berbasis LSTM dengan kuantifikasi ketidakpastian. Fitur degradasi disaring memakai indeks evaluasi komprehensif (korelasi, monotonisitas, robustness), lalu dropout diterapkan pada LSTM untuk memperoleh aproksimasi Bayesian (epistemic uncertainty), dan estimasi kernel density nonparametrik menghasilkan distribusi RUL. Hasil pada PHM2012 menunjukkan RMSE 0,0567 dan MAE 0,0385, lebih baik daripada LSTM fitur acak, CNN, dan adaptive Kalman filter.</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>Menunjukkan cara menyuntikkan pengetahuan keandalan (Weibull CDF sebagai loss, label Piecewise) ke dalam pipeline DL untuk RUL - relevan bagi tesis karena memakai distribusi Weibull/reliability sebagai pengetahuan domain dan mengklaim membantu keterbatasan data; tetapi tidak memodelkan data tersensor dan domainnya bukan membran.</t>
+          <t>Menunjukkan kuantifikasi ketidakpastian (dropout + kernel density) dalam prediksi RUL berbasis LSTM - relevan bagi komponen deep learning + ketidakpastian tesis, tetapi tidak memodelkan data tersensor dan domainnya bearing, bukan membran.</t>
         </is>
       </c>
     </row>
@@ -1662,25 +1662,25 @@
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>B. Deep Learning RUL</t>
+          <t>C. Bayesian &amp; Uncertainty</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Remaining Useful Life Prediction of Turbofan Engines Using CNN-LSTM-SAM Approach</t>
+          <t>A Bayesian Mixture Neural Network for Remaining Useful Life Prediction of Lithium-Ion Batteries</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Li et al.</t>
+          <t>Zhang et al.</t>
         </is>
       </c>
       <c r="E25" s="2" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>IEEE Sensors Journal</t>
+          <t>IEEE Transactions on Transportation Electrification</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1690,17 +1690,17 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/jsen.2023.3261874</t>
+          <t>https://doi.org/10.1109/tte.2022.3161140</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>Paper mengusulkan algoritma fusi deep learning CNN-LSTM dengan self-attention mechanism (SAM/CLS) untuk memprediksi RUL turbofan engine, khususnya pada mode multi-operating point (MOP) yang sangat non-linear. CNN mengekstrak fitur spasial, LSTM mengekstrak fitur temporal, dan SAM memberi bobot adaptif pada unit hidden untuk mengatasi kehilangan informasi LSTM. Dievaluasi pada C-MAPSS FD001-FD004, model mencapai RMSE 12,56/15,25/13,77/18,63 dan mengalahkan metode pembanding pada mode MOP.</t>
+          <t>Artikel ini mengusulkan Bayesian Mixture Neural Network (BMNN) probabilistik untuk prediksi RUL baterai lithium-ion: Bayesian CNN mengekstraksi fitur dari citra temporal hasil transformasi quasi-Gramian Angular Field (Q-GAF), Bayesian LSTM mempelajari korelasi antara kapasitas retensi dan inducemen degradasi, dan variational Bayesian neural network mengeluarkan distribusi hasil prediksi. Metode divalidasi pada empat dataset baterai (NASA, CALCE, MIT, Cavendish) dan memberi estimasi ketidakpastian berupa confidence interval.</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>Menjadi contoh state-of-the-art arsitektur deep learning (CNN+LSTM+attention) untuk regresi RUL point-estimate pada data multi-sensor non-stasioner. Relevan ke tesis sebagai baseline model deep learning, tetapi tidak menangani data tersensor maupun kuantifikasi ketidakpastian — justru menunjukkan celah yang coba diisi tesis.</t>
+          <t>Memberi contoh kuantifikasi ketidakpastian prediktif penuh melalui Bayesian deep learning (posterior predictive distribution + CI), serta teknik representasi ulang time-series menjadi citra (Q-GAF). Relevan ke tesis pada sumbu ketidakpastian (d5) dan model probabilistik, tetapi tanpa pemodelan penyensoran/survival dan bukan domain membran—memperjelas celah integrasi model hazard tersensor dengan deep learning probabilistik pada membran RO.</t>
         </is>
       </c>
     </row>
@@ -1710,25 +1710,25 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>E. Membrane/RO/Desalination</t>
+          <t>C. Bayesian &amp; Uncertainty</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Intelligent framework for coagulant dosing optimization in an industrial-scale seawater reverse osmosis desalination plant</t>
+          <t>Probabilistic Modeling of Li-Ion Battery Remaining Useful Life</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Ridwan et al.</t>
+          <t>Chiodo et al.</t>
         </is>
       </c>
       <c r="E26" s="2" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning with Applications</t>
+          <t>IEEE Transactions on Industry Applications</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1738,17 +1738,17 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.mlwa.2023.100475</t>
+          <t>https://doi.org/10.1109/tia.2022.3170525</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>Studi mengembangkan kerangka inteligent berbasis Artificial Neural Network (ANN) untuk mengoptimalkan dosis koagulan (FeCl3) pada plant SWRO skala industri (216.000 m3/hari, Arab Saudi). Model memprediksi Silt Density Index (SDI) air terfiltrasi setelah dosing kimia dari parameter operasional (pH, turbidity, SDI, laju dosing FeCl3/polimer) yang diperkaya via feature engineering (lag/diff). ANN (10-256-128-64-64-1) mencapai akurasi 95% dan mengalahkan decision tree, random forest, dan linear regression. Setelah diterapkan selama satu tahun, konsumsi koagulan turun 11,7% (penghematan 325.000 SAR), terutama pada musim dingin.</t>
+          <t>Artikel mengusulkan karakterisasi probabilistik RUL baterai Li-ion dengan distribusi inverse Burr (IB) dan dua campurannya: IB-inverse Gaussian (M-IB-IG) dan IB-inverse Weibull (M-IB-IW). Sampel RUL dibangkitkan secara sintetis melalui prosedur elektrokimia dua tahap: solusi analitik PDE difusi (model Rakhmatov) yang memetakan profil arus ke RUL, dan proses Poisson-Monte Carlo yang membangkitkan M profil arus acak. Parameter distribusi diestimasi dengan MLE, dan algoritma EM dikembangkan khusus untuk distribusi campuran, lalu dievaluasi dengan empat uji GOF (ADC, Anderson-Darling, chi-square, Q-Q plot) pada 13 skenario, termasuk skenario data kecil (M=50) dan suhu operasi 25/40/55 derajat C. Distribusi berbasis IB mengungguli benchmark IG, IW, dan Gumbel; fokus paper adalah kecocokan distribusi untuk karakterisasi ketidakpastian RUL, bukan prediksi real-time.</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>Memberi contoh pengendalian fouling/pra-perlakuan membran RO yang terhubung langsung ke penghematan biaya operasional nyata - konteks kuat domain desalinasi untuk tesis; namun bukan prediksi RUL, tanpa survival analysis, dan tanpa data tersensor.</t>
+          <t>1) Perumusan distribusi campuran berbasis IB (M-IB-IG dan M-IB-IW) untuk karakterisasi probabilistik RUL baterai, memperluas hasil konferensi [32]. 2) Pengembangan algoritma EM khusus untuk estimasi parameter campuran (langkah ekspektasi dengan solusi analitik untuk bobot omega, langkah maksimisasi numerik untuk parameter lain). 3) Evaluasi GOF komprehensif dengan uji baru atas 13 skenario operasi (arus pengisian/pengosongan variabel, C-rate tinggi, profil simetris/asimetris, suhu 25/40/55 derajat C) dibandingkan distribusi IG, IW, dan Gumbel sebagai benchmark.</t>
         </is>
       </c>
     </row>
@@ -1758,17 +1758,17 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>A. Survival Analysis &amp; Censored Data</t>
+          <t>C. Bayesian &amp; Uncertainty</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Prognostic modeling of predictive maintenance with survival analysis for mobile work equipment</t>
+          <t>Remaining Useful Life Prediction of Lithium-Ion Batteries Using Neural Networks with Adaptive Bayesian Learning</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Yang et al.</t>
+          <t>Pugalenthi et al.</t>
         </is>
       </c>
       <c r="E27" s="2" t="n">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Scientific Reports</t>
+          <t>Sensors</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -1786,17 +1786,17 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1038/s41598-022-12572-z</t>
+          <t>https://doi.org/10.3390/s22103803</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>Studi menyusun kerangka survival analysis untuk prognostik pemeliharaan prediktif komponen alat kerja bergerak (mobile work equipment). Dari catatan pemeliharaan nyata (7.896 event, 658 mesin, 12 komponen), penulis mengidentifikasi campuran jenis pencensoringan (kiri, interval, kanan) dan menyaring hanya data tersensor-kanan; lalu mengestimasi fungsi survival Kaplan-Meier, hazard non-parametrik (kernel/Nelson-Aalen), serta lima model parametrik (Exponential, Weibull, Log-logistic, Log-normal, Generalized-gamma). Hazard bersifat kompleks; non-parametrik umumnya terbaik, dengan Generalized-gamma sebagai parametrik unggulan.</t>
+          <t>Studi mengusulkan framework prognostik dua tahap: pelatihan adaptive Bayesian (particle filter) untuk mengestimasi parameter (bobot dan bias) MLP, lalu prognosis RUL memakai MLP terkonfigurasi. Kontribusi utamanya adalah weight regularization lewat particle roughening (menambahkan Gaussian jitter kecil pada partikel yang terdegradasi) untuk mengatasi particle degeneracy/impoverishment. Diuji pada data degradasi kapasitas baterai lithium-ion CALCE dan NASA; particle roughening memberi RMSE 0,04 (CALCE) dan 0,24 (NASA) dengan tingkat iterasi sukses 98%.</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>Preseden metodologis kuat untuk pemodelan data tersensor (survival/hazard/Weibull) yang menjadi inti metode tesis, termasuk penanganan tiga jenis pencensoringan dan pemilihan parametrik vs non-parametrik; namun domainnya alat berat (bukan membran) dan tanpa kovariat/sensor.</t>
+          <t>Menunjukkan estimasi RUL probabilistik (distribusi posterior parameter dan RUL) dengan Bayesian/particle filter pada data deret waktu degradasi, relevan sebagai preseden kuantifikasi ketidakpastian (d5) bagi tesis; namun tidak memodelkan penyensoran/survival dan domainnya baterai, sehingga bersifat Pendukung.</t>
         </is>
       </c>
     </row>
@@ -1806,17 +1806,17 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>A. Survival Analysis &amp; Censored Data</t>
+          <t>D. Small-data/Transfer/Hierarchical</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Weibull recurrent neural networks for failure prognosis using histogram data</t>
+          <t>Data-Efficient Estimation of Remaining Useful Life for Machinery With a Limited Number of Run-to-Failure Training Sequences</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Dhada et al.</t>
+          <t>Sternharz et al.</t>
         </is>
       </c>
       <c r="E28" s="2" t="n">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>Neural Computing and Applications</t>
+          <t>IEEE Access</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1834,17 +1834,17 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s00521-022-07667-7</t>
+          <t>https://doi.org/10.1109/access.2022.3226780</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>Studi menyajikan use case industri pertama WTTE-RNN (Weibull time-to-event recurrent neural network) untuk prognosis kegagalan turbocharger pada armada truk Scania. WTTE-RNN mengoptimalkan parameter distribusi Weibull waktu-ke-kegagalan via RNN menggunakan loss log-likelihood yang memanfaatkan data tersensor (truk yang tidak gagal). Data kondisi berupa histogram yang jarang ter-sampling (10-30 snapshot/truk); dimensi direduksi via relative entropy antar-histogram. Hasil: WTTE-RNN memberi rentang galat yang memadai untuk perencanaan pemeliharaan; menggabungkan data tersensor memperbaiki prediksi, tetapi rasio tersensor:tak-tersensor yang terlalu timpang merusak performa; clustering sub-armada hanya bermanfaat bila dataset cukup besar.</t>
+          <t>Studi ini mengusulkan metodologi prediksi RUL yang hemat data: terlebih dahulu memodelkan deviasi kondisi mesin dari keadaan sehat dan rusak memakai Mahalanobis Distance (MD) atau LSTM Autoencoder (AE), lalu menghitung Health Index (HI) dan mendeteksi awal degradasi, sebelum memprediksi RUL dengan SVR, LSTM, atau regresi polinomial kuadratik. Tujuannya mengatasi kelangkaan runtun run-to-failure. Validasi pada dua dataset terbuka (C-MAPSS turbofan dan FEMTO bearing) menunjukkan perbaikan generalisasi pada data latih terbatas.</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>Mendemonstrasikan secara industri bahwa WTTE-RNN (survival Weibull + RNN) yang memanfaatkan data tersensor dapat langsung mendukung keputusan pemeliharaan berbasis risiko - inti metode tesis, meski domainnya armada truk (bukan membran).</t>
+          <t>Mendemonstrasikan strategi RUL yang efisien data lewat representasi ulang fitur menjadi HI dan deteksi awal degradasi (unit-specific), bukan sekadar mengandalkan banyak runtun lengkap. Relevan ke tesis sebagai analogi 'reduksi dimensi + deteksi onset' pada rezim data kecil, tetapi tetap tanpa pemodelan penyensoran, sehingga memperjelas celah bahwa data tersensor + survival belum dieksplorasi untuk HI/RUL membran.</t>
         </is>
       </c>
     </row>
@@ -1854,17 +1854,17 @@
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>B. Deep Learning RUL</t>
+          <t>D. Small-data/Transfer/Hierarchical</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Bi-LSTM-Based Two-Stream Network for Machine Remaining Useful Life Prediction</t>
+          <t>Domain Adaptive Remaining Useful Life Prediction With Transformer</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Jin et al.</t>
+          <t>Li et al.</t>
         </is>
       </c>
       <c r="E29" s="2" t="n">
@@ -1882,17 +1882,17 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/tim.2022.3167778</t>
+          <t>https://doi.org/10.1109/tim.2022.3200667</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>Studi mengusulkan handcrafted feature flows (HFFs) untuk menekan noise pada sinyal mentah dan jaringan dua-stream berbasis Bi-LSTM yang menggabungkan stream sinyal mentah dengan stream HFF. Tiga metode fusi diuji (late, concatenation, addition); fusi addition terbaik. Pada dataset C-MAPSS (FD001-FD004), model mencapai RMSE 11,96/14,48/13,41/15,11 dan mengungguli 8 metode SOTA termasuk CNN-BiLSTM.</t>
+          <t>Artikel ini mengusulkan metode domain adaptation untuk prediksi RUL dengan menyelaraskan distribusi pada level fitur dan level semantik sekaligus, menggunakan Transformer sebagai tulang punggung. Dua diskriminator domain (D_f untuk fitur, D_y untuk keluaran) dilatih secara adversarial dengan Gradient Reversal Layer. Metode diuji pada C-MAPSS dan N-CMAPSS, mencapai hasil state-of-the-art pada tugas RUL source-only dan cross-domain, dilengkapi kuantifikasi ketidakpastian (95% CI) dan uji online.</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>Preseden metode RUL deep learning dengan rekayasa fitur (HFF) dan arsitektur multi-stream/fusi, berguna sebagai pembanding metode bagi tesis; namun tanpa survival/penyensoran dan bukan domain membran, sehingga Pendukung.</t>
+          <t>Mencontohkan transfer learning/domain adaptation untuk RUL lintas kondisi operasi tanpa label target, termasuk kuantifikasi ketidakpastian via Monte Carlo dropout. Relevan ke tesis pada sumbu transfer/small-data (d8) dan ketidakpastian (d5); namun tanpa pemodelan penyensoran/survival dan bukan domain membran—memperjelas celah integrasi survival tersensor dengan backbone Transformer pada membran RO.</t>
         </is>
       </c>
     </row>
@@ -1902,17 +1902,17 @@
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>B. Deep Learning RUL</t>
+          <t>D. Small-data/Transfer/Hierarchical</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Prediction of Remaining Useful Life of Lithium Batteries Based on WOA-VMD and LSTM</t>
+          <t>Remaining useful life prediction of rolling bearing under limited data based on adaptive time-series feature window and multi-step ahead strategy</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Ouyang et al.</t>
+          <t>Kong et al.</t>
         </is>
       </c>
       <c r="E30" s="2" t="n">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>Energies</t>
+          <t>Applied Soft Computing</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1930,17 +1930,17 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/en15238918</t>
+          <t>https://doi.org/10.1016/j.asoc.2022.109630</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>Studi mengusulkan model hibrida WOA-VMD-LSTM untuk prediksi RUL baterai lithium-ion. Whale Optimization Algorithm (WOA) mengoptimalkan parameter VMD (K dan alpha) agar sinyal kapasitas terdekomposisi menjadi komponen ganda tren atenuasi global dan komponen fluaktuasi pemulihan kapasitas; masing-masing komponen diprediksi LSTM lalu direkonstruksi menjadi RUL. Hasil pada dataset NASA menunjukkan AE maksimum 2 siklus, RMSE rata-rata &lt; 0,69%, dan MAPE rata-rata &lt; 0,43%, mengungguli LSTM, EMD-LSTM, VMD-LSTM, dan ELM.</t>
+          <t>Studi mengusulkan metode prediksi RUL bantalan gelinding pada kondisi data terbatas. Tiga komponen utama: identifikasi first prediction time (FPT) berbasis kurtosis dan RMS, jendela fitur deret waktu adaptif yang dikompresi memakai degradation factor, dan jaringan stacked bidirectional LSTM (SBiLSTM) dengan strategi prediksi multi-step ahead bergulir. Pada dataset XJTU-SY, metode mencapai MAPE 6,77%, 18,92%, dan 8,95% untuk tiga bantalan representatif, mengalahkan delapan metode pembanding.</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>Menunjukkan pipeline deep learning RUL dengan pra-pemrosesan dekomposisi sinyal (mengatasi fenomena pemulihan kapasitas), relevan sebagai pembanding arsitektur DL RUL. Namun tidak memakai survival/penyensoran dan bukan domain membran.</t>
+          <t>Menunjukkan strategi RUL yang dirancang khusus untuk data terbatas (small-data) tanpa memerlukan dataset run-to-failure masif, relevan dengan tantangan kelangkaan data kegagalan membran; namun tidak memakai survival/pencensoringan dan domainnya bukan membran.</t>
         </is>
       </c>
     </row>
@@ -1955,20 +1955,20 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Remaining Useful Life Prediction Method for Bearings Based on LSTM with Uncertainty Quantification</t>
+          <t>A Novel Cap-LSTM Model for Remaining Useful Life Prediction</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Yang et al.</t>
+          <t>Zhao et al.</t>
         </is>
       </c>
       <c r="E31" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Sensors</t>
+          <t>IEEE Sensors Journal</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -1978,17 +1978,17 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/s22124549</t>
+          <t>https://doi.org/10.1109/jsen.2021.3109623</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>Makalah mengusulkan metode prediksi RUL bearing berbasis LSTM dengan kuantifikasi ketidakpastian. Fitur degradasi disaring memakai indeks evaluasi komprehensif (korelasi, monotonisitas, robustness), lalu dropout diterapkan pada LSTM untuk memperoleh aproksimasi Bayesian (epistemic uncertainty), dan estimasi kernel density nonparametrik menghasilkan distribusi RUL. Hasil pada PHM2012 menunjukkan RMSE 0,0567 dan MAE 0,0385, lebih baik daripada LSTM fitur acak, CNN, dan adaptive Kalman filter.</t>
+          <t>Studi mengusulkan model hybrid dua kanal Cap-LSTM untuk prediksi RUL, menggabungkan Capsule Neural Network (kanal spasial, menggantikan pooling CNN dengan routing-by-agreement) dan LSTM (kanal temporal untuk dependensi jangka panjang). Data multisensor deret waktu C-MAPSS (14 sensor terseleksi) diproses dengan sliding time window dan label RUL piece-wise linear (knee point 125). Cap-LSTM mencapai RMSE terbaik pada FD001-FD004 (12,27/17,79/12,55/22,05) dibanding CNN, LSTM, BiLSTM, dan CNN+FNN.</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>Menunjukkan kuantifikasi ketidakpastian (dropout + kernel density) dalam prediksi RUL berbasis LSTM - relevan bagi komponen deep learning + ketidakpastian tesis, tetapi tidak memodelkan data tersensor dan domainnya bearing, bukan membran.</t>
+          <t>Preseden arsitektur deep learning RUL (capsule + LSTM) dengan evaluasi ablation dan metrik RMSE/Score pada benchmark publik, relevan sebagai pembanding metode bagi tesis; namun tidak menangani survival/penyensoran dan bukan domain membran, sehingga Pendukung.</t>
         </is>
       </c>
     </row>
@@ -1998,25 +1998,25 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>C. Bayesian &amp; Uncertainty</t>
+          <t>B. Deep Learning RUL</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>A Bayesian Mixture Neural Network for Remaining Useful Life Prediction of Lithium-Ion Batteries</t>
+          <t>Degradation-Aware Remaining Useful Life Prediction With LSTM Autoencoder</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Zhang et al.</t>
+          <t>Wu et al.</t>
         </is>
       </c>
       <c r="E32" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>IEEE Transactions on Transportation Electrification</t>
+          <t>IEEE Transactions on Instrumentation and Measurement</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/tte.2022.3161140</t>
+          <t>https://doi.org/10.1109/tim.2021.3055788</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>Artikel ini mengusulkan Bayesian Mixture Neural Network (BMNN) probabilistik untuk prediksi RUL baterai lithium-ion: Bayesian CNN mengekstraksi fitur dari citra temporal hasil transformasi quasi-Gramian Angular Field (Q-GAF), Bayesian LSTM mempelajari korelasi antara kapasitas retensi dan inducemen degradasi, dan variational Bayesian neural network mengeluarkan distribusi hasil prediksi. Metode divalidasi pada empat dataset baterai (NASA, CALCE, MIT, Cavendish) dan memberi estimasi ketidakpastian berupa confidence interval.</t>
+          <t>Studi mengusulkan DELTA (degradation-aware LSTM autoencoder) untuk prediksi RUL yang sadar tahap degradasi. Tiga modul: (1) identifikasi tahap sehat via Hilbert-Huang transform (HHT) + klasifikasi SVM, (2) estimasi degradation factor dengan LSTM autoencoder (latent variable), dan (3) estimasi RUL via degradation similarity matching berbobot. Diuji pada dataset FEMTO/PRONOSTIA (bearing), DELTA mengalahkan MLP, XGBoost, RFR, CNN, LSTM, SVR, RNN, dan two-stage pada metrik RMSE dan Score.</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>Memberi contoh kuantifikasi ketidakpastian prediktif penuh melalui Bayesian deep learning (posterior predictive distribution + CI), serta teknik representasi ulang time-series menjadi citra (Q-GAF). Relevan ke tesis pada sumbu ketidakpastian (d5) dan model probabilistik, tetapi tanpa pemodelan penyensoran/survival dan bukan domain membran—memperjelas celah integrasi model hazard tersensor dengan deep learning probabilistik pada membran RO.</t>
+          <t>Memberi contoh pipeline DL (LSTM autoencoder + similarity matching) untuk RUL bearing dengan data multisensor - relevan sebagai pembanding metode DL RUL pada tesis, tetapi tidak memodelkan data tersensor, tidak mengkuantifikasi ketidakpastian, dan domainnya bearing.</t>
         </is>
       </c>
     </row>
@@ -2051,20 +2051,20 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Probabilistic Modeling of Li-Ion Battery Remaining Useful Life</t>
+          <t>A Framework for Predicting Remaining Useful Life Curve of Rolling Bearings Under Defect Progression Based on Neural Network and Bayesian Method</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Chiodo et al.</t>
+          <t>Kitai et al.</t>
         </is>
       </c>
       <c r="E33" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>IEEE Transactions on Industry Applications</t>
+          <t>IEEE Access</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -2074,17 +2074,17 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/tia.2022.3170525</t>
+          <t>https://doi.org/10.1109/access.2021.3073945</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>Artikel mengusulkan karakterisasi probabilistik RUL baterai Li-ion dengan distribusi inverse Burr (IB) dan dua campurannya: IB-inverse Gaussian (M-IB-IG) dan IB-inverse Weibull (M-IB-IW). Sampel RUL dibangkitkan secara sintetis melalui prosedur elektrokimia dua tahap: solusi analitik PDE difusi (model Rakhmatov) yang memetakan profil arus ke RUL, dan proses Poisson-Monte Carlo yang membangkitkan M profil arus acak. Parameter distribusi diestimasi dengan MLE, dan algoritma EM dikembangkan khusus untuk distribusi campuran, lalu dievaluasi dengan empat uji GOF (ADC, Anderson-Darling, chi-square, Q-Q plot) pada 13 skenario, termasuk skenario data kecil (M=50) dan suhu operasi 25/40/55 derajat C. Distribusi berbasis IB mengungguli benchmark IG, IW, dan Gumbel; fokus paper adalah kecocokan distribusi untuk karakterisasi ketidakpastian RUL, bukan prediksi real-time.</t>
+          <t>Studi mengusulkan kerangka prediksi kurva RUL bantalan gelinding pada kondisi defek yang terus berkembang, dengan menekankan perbedaan individual antar-bantalan dan fluktuasi fitur vibrasi di tahap defek lanjut. Kerangka ini menggabungkan Feature Fusion Network (FFN) berbasis CNN (memakai spektrogram vibrasi saat ini dan masa lalu serta Degradation Index Vector) dengan Hierarchical Bayesian Regression (HBR) yang menghasilkan kurva RUL monoton beserta distribusi posterior. Dievaluasi lewat leave-one-bearing-out CV pada 33 sampel bantalan, akurasi R2 median meningkat dan variasi antar-sampel menyusut.</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>1) Perumusan distribusi campuran berbasis IB (M-IB-IG dan M-IB-IW) untuk karakterisasi probabilistik RUL baterai, memperluas hasil konferensi [32]. 2) Pengembangan algoritma EM khusus untuk estimasi parameter campuran (langkah ekspektasi dengan solusi analitik untuk bobot omega, langkah maksimisasi numerik untuk parameter lain). 3) Evaluasi GOF komprehensif dengan uji baru atas 13 skenario operasi (arus pengisian/pengosongan variabel, C-rate tinggi, profil simetris/asimetris, suhu 25/40/55 derajat C) dibandingkan distribusi IG, IW, dan Gumbel sebagai benchmark.</t>
+          <t>Menunjukkan bagaimana regresi Bayesian hierarkis dapat menghasilkan kurva RUL monoton beserta interval kredibel per-unit sekaligus menyerap perbedaan individual antar-unit - sebuah pola probabilistic RUL yang relevan bila tesis ingin melaporkan ketidakpastian prediksi; namun tidak memakai survival/Weibull/hazard dan tidak menangani data tersensor.</t>
         </is>
       </c>
     </row>
@@ -2099,20 +2099,20 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Remaining Useful Life Prediction of Lithium-Ion Batteries Using Neural Networks with Adaptive Bayesian Learning</t>
+          <t>Bayesian Convolutional Neural Networks for Remaining Useful Life Prognostics of Solenoid Valves With Uncertainty Estimations</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Pugalenthi et al.</t>
+          <t>Mazaev et al.</t>
         </is>
       </c>
       <c r="E34" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>Sensors</t>
+          <t>IEEE Transactions on Industrial Informatics</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -2122,17 +2122,17 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/s22103803</t>
+          <t>https://doi.org/10.1109/tii.2021.3078193</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>Studi mengusulkan framework prognostik dua tahap: pelatihan adaptive Bayesian (particle filter) untuk mengestimasi parameter (bobot dan bias) MLP, lalu prognosis RUL memakai MLP terkonfigurasi. Kontribusi utamanya adalah weight regularization lewat particle roughening (menambahkan Gaussian jitter kecil pada partikel yang terdegradasi) untuk mengatasi particle degeneracy/impoverishment. Diuji pada data degradasi kapasitas baterai lithium-ion CALCE dan NASA; particle roughening memberi RMSE 0,04 (CALCE) dan 0,24 (NASA) dengan tingkat iterasi sukses 98%.</t>
+          <t>Studi menggunakan Bayesian Convolutional Neural Networks (BCNN) untuk memprediksi RUL solenoid valve (SV) langsung dari representasi citra sinyal arus, diperkaya dua fitur fisik (shading ring force dan Coulomb friction) dari model elektromekanis. Dua arsitektur Bayesian dibandingkan: MC dropout dan mean-field variational inference (MFVI) yang memprediksi mean dan standar deviasi distribusi Gaussian terpangkas secara eksplisit. Hasil pada 48 valve uji dipercepat menunjukkan model BCNN MFVI memberi estimasi ketidakpastian (credible interval 90%) yang terkalibrasi baik, dan menurunkan MAE RUL ~40% dibanding metode deep/feature-based sebelumnya.</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>Menunjukkan estimasi RUL probabilistik (distribusi posterior parameter dan RUL) dengan Bayesian/particle filter pada data deret waktu degradasi, relevan sebagai preseden kuantifikasi ketidakpastian (d5) bagi tesis; namun tidak memodelkan penyensoran/survival dan domainnya baterai, sehingga bersifat Pendukung.</t>
+          <t>Menunjukkan pembangunan kuantifikasi ketidakpastian yang terkalibrasi (credible interval, calibration curve) dalam RUL berbasis DL - relevan bagi pilar C (Bayesian &amp; Uncertainty) pada tesis; namun tidak memodelkan data tersensor dan domainnya solenoid valve, bukan membran.</t>
         </is>
       </c>
     </row>
@@ -2147,20 +2147,20 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Data-Efficient Estimation of Remaining Useful Life for Machinery With a Limited Number of Run-to-Failure Training Sequences</t>
+          <t>A Semi-Supervised Deep Transfer Learning Approach for Rolling-Element Bearing Remaining Useful Life Prediction</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>Sternharz et al.</t>
+          <t>Berghout et al.</t>
         </is>
       </c>
       <c r="E35" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>IEEE Access</t>
+          <t>IEEE Transactions on Energy Conversion</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -2170,17 +2170,17 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/access.2022.3226780</t>
+          <t>https://doi.org/10.1109/tec.2021.3116423</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>Studi ini mengusulkan metodologi prediksi RUL yang hemat data: terlebih dahulu memodelkan deviasi kondisi mesin dari keadaan sehat dan rusak memakai Mahalanobis Distance (MD) atau LSTM Autoencoder (AE), lalu menghitung Health Index (HI) dan mendeteksi awal degradasi, sebelum memprediksi RUL dengan SVR, LSTM, atau regresi polinomial kuadratik. Tujuannya mengatasi kelangkaan runtun run-to-failure. Validasi pada dua dataset terbuka (C-MAPSS turbofan dan FEMTO bearing) menunjukkan perbaikan generalisasi pada data latih terbatas.</t>
+          <t>Studi mengusulkan algoritma deep transfer learning semi-supervised berbasis LSTM untuk memprediksi RUL bantalan gelinding dari data kecil dan tak berlabel. Health index (HI) direkonstruksi sebagai fungsi eksponensial kumulatif dan health stage (HS) dipisahkan dengan Gaussian mixture model (GMM) secara unsupervised; pengetahuan dari siklus hidup bantalan lain ditransfer ke domain target. Transfer learning menurunkan RMSE test rata-rata menjadi 0,1888 (vs 0,3125 DL biasa) dan menaikkan akurasi klasifikasi HS menjadi 0,9044 (vs 0,7558).</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>Mendemonstrasikan strategi RUL yang efisien data lewat representasi ulang fitur menjadi HI dan deteksi awal degradasi (unit-specific), bukan sekadar mengandalkan banyak runtun lengkap. Relevan ke tesis sebagai analogi 'reduksi dimensi + deteksi onset' pada rezim data kecil, tetapi tetap tanpa pemodelan penyensoran, sehingga memperjelas celah bahwa data tersensor + survival belum dieksplorasi untuk HI/RUL membran.</t>
+          <t>Memberikan contoh penanganan data kecil + tak berlabel melalui transfer learning dan pemisahan tahap degradasi (GMM), relevan untuk skenario tesis dengan histori kegagalan membran terbatas. Namun tidak memakai survival/penyensoran eksplisit dan bukan domain membran.</t>
         </is>
       </c>
     </row>
@@ -2190,25 +2190,25 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>D. Small-data/Transfer/Hierarchical</t>
+          <t>F. DSS &amp; Predictive Maintenance (IS)</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Domain Adaptive Remaining Useful Life Prediction With Transformer</t>
+          <t>A comprehensive framework from real‐time prognostics to maintenance decisions</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>Li et al.</t>
+          <t>Jain et al.</t>
         </is>
       </c>
       <c r="E36" s="2" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>IEEE Transactions on Instrumentation and Measurement</t>
+          <t>IET Collaborative Intelligent Manufacturing</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -2218,17 +2218,17 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/tim.2022.3200667</t>
+          <t>https://doi.org/10.1049/cim2.12021</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>Artikel ini mengusulkan metode domain adaptation untuk prediksi RUL dengan menyelaraskan distribusi pada level fitur dan level semantik sekaligus, menggunakan Transformer sebagai tulang punggung. Dua diskriminator domain (D_f untuk fitur, D_y untuk keluaran) dilatih secara adversarial dengan Gradient Reversal Layer. Metode diuji pada C-MAPSS dan N-CMAPSS, mencapai hasil state-of-the-art pada tugas RUL source-only dan cross-domain, dilengkapi kuantifikasi ketidakpastian (95% CI) dan uji online.</t>
+          <t>Studi mengusulkan sistem dukungan pemeliharaan komprehensif yang menggabungkan modul prognostik berbasis survival theory (Weibull time-to-event recurrent neural network, WTTE-RNN) dengan model perencanaan predictive maintenance (PdM) berbasis trade-off biaya corrective maintenance dan waktu/umur yang hilang. Model WTTE-RNN memprediksi parameter distribusi kegagalan Weibull, lalu waktu optimal penggantian prediktif (OPdR) dioptimasi dari parameter biaya operasional dan pemeliharaan. Divalidasi pada studi kasus perencanaan pemeliharaan cutting tool di lingkungan manufaktur dengan analisis sensitivitas sistematis.</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>Mencontohkan transfer learning/domain adaptation untuk RUL lintas kondisi operasi tanpa label target, termasuk kuantifikasi ketidakpastian via Monte Carlo dropout. Relevan ke tesis pada sumbu transfer/small-data (d8) dan ketidakpastian (d5); namun tanpa pemodelan penyensoran/survival dan bukan domain membran—memperjelas celah integrasi survival tersensor dengan backbone Transformer pada membran RO.</t>
+          <t>Sangat relevan ke tesis: menggabungkan survival theory (Weibull/hazard/censoring) dengan deep learning (RNN) untuk RUL, DAN menutup celah sampai keputusan pemeliharaan biaya-optimal. Namun domainnya cutting tool, bukan membran/RO.</t>
         </is>
       </c>
     </row>
@@ -2238,25 +2238,25 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>D. Small-data/Transfer/Hierarchical</t>
+          <t>A. Survival Analysis &amp; Censored Data</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Remaining useful life prediction of rolling bearing under limited data based on adaptive time-series feature window and multi-step ahead strategy</t>
+          <t>Prediction of remaining useful life (RUL) of Komatsu excavator under reliability analysis in the Weibull-frailty model</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Kong et al.</t>
+          <t>Ghomghaleh et al.</t>
         </is>
       </c>
       <c r="E37" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>Applied Soft Computing</t>
+          <t>PLoS ONE</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -2266,17 +2266,17 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.asoc.2022.109630</t>
+          <t>https://doi.org/10.1371/journal.pone.0236128</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>Studi mengusulkan metode prediksi RUL bantalan gelinding pada kondisi data terbatas. Tiga komponen utama: identifikasi first prediction time (FPT) berbasis kurtosis dan RMS, jendela fitur deret waktu adaptif yang dikompresi memakai degradation factor, dan jaringan stacked bidirectional LSTM (SBiLSTM) dengan strategi prediksi multi-step ahead bergulir. Pada dataset XJTU-SY, metode mencapai MAPE 6,77%, 18,92%, dan 8,95% untuk tiga bantalan representatif, mengalahkan delapan metode pembanding.</t>
+          <t>Studi memprediksi RUL excavator Komatsu PC-1250 di tambang tembaga Sungun memakai analisis keandalan dalam model Weibull-frailty. Data time between failures (TBF) dari 80 jam operasional dimodelkan dengan dua pendekatan: model klasik-eksponensial dan model Weibull-frailty yang menyertakan frailty (faktor risiko tak teramati/heterogenitas). Model dipilih lewat uji GOF (AIC/BIC) dan uji heterogenitas likelihood ratio, lalu RUL dihitung dari mean residual life (MRL).</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>Menunjukkan strategi RUL yang dirancang khusus untuk data terbatas (small-data) tanpa memerlukan dataset run-to-failure masif, relevan dengan tantangan kelangkaan data kegagalan membran; namun tidak memakai survival/pencensoringan dan domainnya bukan membran.</t>
+          <t>Preseden langsung penggunaan model survival frailty (Weibull + random effect untuk heterogenitas tak teramati) dalam menghitung RUL, lengkap dengan penanganan data tersensor (suspended data) dan uji GOF/heterogenitas - klop dengan kerangka survival tesis; tetapi tidak memakai deep learning dan domainnya excavator tambang, bukan membran.</t>
         </is>
       </c>
     </row>
@@ -2291,20 +2291,20 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>A Novel Cap-LSTM Model for Remaining Useful Life Prediction</t>
+          <t>A Data-Driven Auto-CNN-LSTM Prediction Model for Lithium-Ion Battery Remaining Useful Life</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Zhao et al.</t>
+          <t>Ren et al.</t>
         </is>
       </c>
       <c r="E38" s="2" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>IEEE Sensors Journal</t>
+          <t>IEEE Transactions on Industrial Informatics</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -2314,17 +2314,17 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/jsen.2021.3109623</t>
+          <t>https://doi.org/10.1109/tii.2020.3008223</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>Studi mengusulkan model hybrid dua kanal Cap-LSTM untuk prediksi RUL, menggabungkan Capsule Neural Network (kanal spasial, menggantikan pooling CNN dengan routing-by-agreement) dan LSTM (kanal temporal untuk dependensi jangka panjang). Data multisensor deret waktu C-MAPSS (14 sensor terseleksi) diproses dengan sliding time window dan label RUL piece-wise linear (knee point 125). Cap-LSTM mencapai RMSE terbaik pada FD001-FD004 (12,27/17,79/12,55/22,05) dibanding CNN, LSTM, BiLSTM, dan CNN+FNN.</t>
+          <t>Studi mengusulkan model Auto-CNN-LSTM untuk memprediksi RUL baterai Li-ion: autoencoder memperbesar dimensi fitur untuk mengatasi keterbatasan data, CNN menambang informasi kedalaman, LSTM mengekstrak informasi temporal, dan DNN 7-lapis menghasilkan prediksi RUL yang dihaluskan dengan filter orde pertama.</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>Preseden arsitektur deep learning RUL (capsule + LSTM) dengan evaluasi ablation dan metrik RMSE/Score pada benchmark publik, relevan sebagai pembanding metode bagi tesis; namun tidak menangani survival/penyensoran dan bukan domain membran, sehingga Pendukung.</t>
+          <t>Memberi contoh strategi augmentasi dimensi berbasis autoencoder untuk data degradasi terbatas dan pipeline hibrida CNN+LSTM — relevan untuk tesis pada sumbu data langka; namun tanpa penanganan censoring/survival, tanpa kuantifikasi ketidakpastian, dan bukan domain membran.</t>
         </is>
       </c>
     </row>
@@ -2339,20 +2339,20 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Degradation-Aware Remaining Useful Life Prediction With LSTM Autoencoder</t>
+          <t>A Deep Learning-Based Remaining Useful Life Prediction Approach for Bearings</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Wu et al.</t>
+          <t>Cheng et al.</t>
         </is>
       </c>
       <c r="E39" s="2" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>IEEE Transactions on Instrumentation and Measurement</t>
+          <t>IEEE/ASME Transactions on Mechatronics</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -2362,17 +2362,17 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/tim.2021.3055788</t>
+          <t>https://doi.org/10.1109/tmech.2020.2971503</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>Studi mengusulkan DELTA (degradation-aware LSTM autoencoder) untuk prediksi RUL yang sadar tahap degradasi. Tiga modul: (1) identifikasi tahap sehat via Hilbert-Huang transform (HHT) + klasifikasi SVM, (2) estimasi degradation factor dengan LSTM autoencoder (latent variable), dan (3) estimasi RUL via degradation similarity matching berbobot. Diuji pada dataset FEMTO/PRONOSTIA (bearing), DELTA mengalahkan MLP, XGBoost, RFR, CNN, LSTM, SVR, RNN, dan two-stage pada metrik RMSE dan Score.</t>
+          <t>Artikel ini mengusulkan kerangka data-driven untuk prediksi RUL rolling element bearing (REB) dengan deep CNN. Getaran mentah diproses memakai Hilbert-Huang Transform untuk menyusun degradation energy indicator (DEI) nonlinier baru sebagai label latih; CNN 6 lapis dilatih untuk memetakan getaran mentah ke DEI, lalu ε-SVR memforecast evolusi DEI hingga melewati failure threshold. Metode divalidasi pada platform PRONOSTIA dan mengungguli delapan metode publikasi.</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>Memberi contoh pipeline DL (LSTM autoencoder + similarity matching) untuk RUL bearing dengan data multisensor - relevan sebagai pembanding metode DL RUL pada tesis, tetapi tidak memodelkan data tersensor, tidak mengkuantifikasi ketidakpastian, dan domainnya bearing.</t>
+          <t>Memperkenalkan indikator degradasi nonlinier (DEI) berbasis frekuensi alami komponen bearing dan framework HHT+CNN+ε-SVR yang menetapkan failure threshold konsisten antar-bearing. Relevan ke tesis sebagai pembanding rekayasa indikator/fitur untuk RUL, namun tanpa survival/penyensoran dan bukan domain membran.</t>
         </is>
       </c>
     </row>
@@ -2382,25 +2382,25 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>C. Bayesian &amp; Uncertainty</t>
+          <t>B. Deep Learning RUL</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>A Framework for Predicting Remaining Useful Life Curve of Rolling Bearings Under Defect Progression Based on Neural Network and Bayesian Method</t>
+          <t>A Neural Network-Based Joint Prognostic Model for Data Fusion and Remaining Useful Life Prediction</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Kitai et al.</t>
+          <t>Gao et al.</t>
         </is>
       </c>
       <c r="E40" s="2" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>IEEE Access</t>
+          <t>IEEE Transactions on Neural Networks and Learning Systems</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -2410,17 +2410,17 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/access.2021.3073945</t>
+          <t>https://doi.org/10.1109/tnnls.2020.2977132</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>Studi mengusulkan kerangka prediksi kurva RUL bantalan gelinding pada kondisi defek yang terus berkembang, dengan menekankan perbedaan individual antar-bantalan dan fluktuasi fitur vibrasi di tahap defek lanjut. Kerangka ini menggabungkan Feature Fusion Network (FFN) berbasis CNN (memakai spektrogram vibrasi saat ini dan masa lalu serta Degradation Index Vector) dengan Hierarchical Bayesian Regression (HBR) yang menghasilkan kurva RUL monoton beserta distribusi posterior. Dievaluasi lewat leave-one-bearing-out CV pada 33 sampel bantalan, akurasi R2 median meningkat dan variasi antar-sampel menyusut.</t>
+          <t>Artikel ini mengusulkan Joint Prognostic Model (JPM) yang menggabungkan model linear Bayesian untuk setiap sinyal sensor (mixed-effects) dengan Artificial Neural Network untuk memetakan hubungan nonlinier antara parameter degradasi multi-sensor dan life percentage. Skema Bayesian updating menghitung distribusi posterior parameter setiap sensor untuk in-service unit, lalu menghasilkan posterior predictive distribution RUL. Metode divalidasi pada C-MAPSS FD001/FD003.</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>Menunjukkan bagaimana regresi Bayesian hierarkis dapat menghasilkan kurva RUL monoton beserta interval kredibel per-unit sekaligus menyerap perbedaan individual antar-unit - sebuah pola probabilistic RUL yang relevan bila tesis ingin melaporkan ketidakpastian prediksi; namun tidak memakai survival/Weibull/hazard dan tidak menangani data tersensor.</t>
+          <t>Menyediakan kerangka Bayesian + NN yang menghasilkan distribusi prediktif RUL (bukan hanya titik) dan menangani heterogenitas antar-unit via mixed-effects. Relevan ke tesis pada sumbu ketidakpastian (d5) dan struktur hierarkis (d8), namun tanpa pemodelan penyensoran/survival—menegaskan celah penggabungan survival tersensor dengan prediksi nonlinier.</t>
         </is>
       </c>
     </row>
@@ -2430,25 +2430,25 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>C. Bayesian &amp; Uncertainty</t>
+          <t>B. Deep Learning RUL</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Bayesian Convolutional Neural Networks for Remaining Useful Life Prognostics of Solenoid Valves With Uncertainty Estimations</t>
+          <t>Attention-Based LSTM Network for Rotatory Machine Remaining Useful Life Prediction</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Mazaev et al.</t>
+          <t>Zhang et al.</t>
         </is>
       </c>
       <c r="E41" s="2" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>IEEE Transactions on Industrial Informatics</t>
+          <t>IEEE Access</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -2458,17 +2458,17 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/tii.2021.3078193</t>
+          <t>https://doi.org/10.1109/access.2020.3010066</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>Studi menggunakan Bayesian Convolutional Neural Networks (BCNN) untuk memprediksi RUL solenoid valve (SV) langsung dari representasi citra sinyal arus, diperkaya dua fitur fisik (shading ring force dan Coulomb friction) dari model elektromekanis. Dua arsitektur Bayesian dibandingkan: MC dropout dan mean-field variational inference (MFVI) yang memprediksi mean dan standar deviasi distribusi Gaussian terpangkas secara eksplisit. Hasil pada 48 valve uji dipercepat menunjukkan model BCNN MFVI memberi estimasi ketidakpastian (credible interval 90%) yang terkalibrasi baik, dan menurunkan MAE RUL ~40% dibanding metode deep/feature-based sebelumnya.</t>
+          <t>Paper mengusulkan kerangka deep learning TLSTM-A (two-layer LSTM dengan attention) yang didahului 1-D CNN untuk memprediksi RUL komponen rotasi (bearing). CNN mengekstrak fitur lokal dari sinyal getaran, dua lapisan LSTM mengekstrak fitur temporal berlapis, dan attention mechanism menyorot informasi kunci serta mengatasi kehilangan informasi pada transmisi jarak jauh LSTM. Dievaluasi pada dataset bearing XJTU-SY, model mencapai RMSE/MAE/Score terbaik di antara pembanding.</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>Menunjukkan pembangunan kuantifikasi ketidakpastian yang terkalibrasi (credible interval, calibration curve) dalam RUL berbasis DL - relevan bagi pilar C (Bayesian &amp; Uncertainty) pada tesis; namun tidak memodelkan data tersensor dan domainnya solenoid valve, bukan membran.</t>
+          <t>Contoh kuat arsitektur deep learning (CNN+LSTM berlapis+attention) point-estimate untuk RUL sinyal getaran, berguna sebagai baseline arsitektur di tesis. Menegaskan celah: tidak ada penanganan data tersensor maupun kuantifikasi ketidakpastian, sehingga tidak menutup gap utama tesis.</t>
         </is>
       </c>
     </row>
@@ -2478,25 +2478,25 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>D. Small-data/Transfer/Hierarchical</t>
+          <t>B. Deep Learning RUL</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>A Semi-Supervised Deep Transfer Learning Approach for Rolling-Element Bearing Remaining Useful Life Prediction</t>
+          <t>Deep-Convolution-Based LSTM Network for Remaining Useful Life Prediction</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Berghout et al.</t>
+          <t>Ma et al.</t>
         </is>
       </c>
       <c r="E42" s="2" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>IEEE Transactions on Energy Conversion</t>
+          <t>IEEE Transactions on Industrial Informatics</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -2506,17 +2506,17 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/tec.2021.3116423</t>
+          <t>https://doi.org/10.1109/tii.2020.2991796</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>Studi mengusulkan algoritma deep transfer learning semi-supervised berbasis LSTM untuk memprediksi RUL bantalan gelinding dari data kecil dan tak berlabel. Health index (HI) direkonstruksi sebagai fungsi eksponensial kumulatif dan health stage (HS) dipisahkan dengan Gaussian mixture model (GMM) secara unsupervised; pengetahuan dari siklus hidup bantalan lain ditransfer ke domain target. Transfer learning menurunkan RMSE test rata-rata menjadi 0,1888 (vs 0,3125 DL biasa) dan menaikkan akurasi klasifikasi HS menjadi 0,9044 (vs 0,7558).</t>
+          <t>Studi mengusulkan jaringan CLSTM (convolution-based LSTM) untuk prediksi RUL bantalan (bearing), dengan operasi konvolusi pada transisi input-to-state dan state-to-state LSTM sehingga menangkap informasi time-frequency dan temporal sekaligus. Input berupa fitur time-frequency (STFT) dari sinyal vibrasi run-to-failure, diproses arsitektur encoding-forecasting berlapis dua CLSTM. Pada dua uji run-to-failure, CLSTM mengalahkan deep CNN dan deep LSTM (RMSE 29,7/10,8 menit vs 47,9/18,2 dan 40,7/15,6).</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>Memberikan contoh penanganan data kecil + tak berlabel melalui transfer learning dan pemisahan tahap degradasi (GMM), relevan untuk skenario tesis dengan histori kegagalan membran terbatas. Namun tidak memakai survival/penyensoran eksplisit dan bukan domain membran.</t>
+          <t>Preseden arsitektur deep learning RUL (convolutional LSTM) dengan data vibrasi run-to-failure nyata dan pembanding deep CNN/LSTM, berguna bagi tesis sebagai rujukan metode prediksi RUL; namun tidak menangani penyensoran/survival dan bukan domain membran, sehingga Pendukung.</t>
         </is>
       </c>
     </row>
@@ -2526,25 +2526,25 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>F. DSS &amp; Predictive Maintenance (IS)</t>
+          <t>B. Deep Learning RUL</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>A comprehensive framework from real‐time prognostics to maintenance decisions</t>
+          <t>Remaining Useful Life Prognosis Based on Ensemble Long Short-Term Memory Neural Network</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Jain et al.</t>
+          <t>Cheng et al.</t>
         </is>
       </c>
       <c r="E43" s="2" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>IET Collaborative Intelligent Manufacturing</t>
+          <t>IEEE Transactions on Instrumentation and Measurement</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -2554,17 +2554,17 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1049/cim2.12021</t>
+          <t>https://doi.org/10.1109/tim.2020.3031113</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>Studi mengusulkan sistem dukungan pemeliharaan komprehensif yang menggabungkan modul prognostik berbasis survival theory (Weibull time-to-event recurrent neural network, WTTE-RNN) dengan model perencanaan predictive maintenance (PdM) berbasis trade-off biaya corrective maintenance dan waktu/umur yang hilang. Model WTTE-RNN memprediksi parameter distribusi kegagalan Weibull, lalu waktu optimal penggantian prediktif (OPdR) dioptimasi dari parameter biaya operasional dan pemeliharaan. Divalidasi pada studi kasus perencanaan pemeliharaan cutting tool di lingkungan manufaktur dengan analisis sensitivitas sistematis.</t>
+          <t>Studi mengusulkan ELSTMNN (Ensemble Long Short-Term Memory Neural Network) untuk prognosis RUL: sejumlah LSTMNN dilatih paralel, masing-masing pada data satu unit peralatan, lalu digabung memakai Bayesian Inference Algorithm (BIA) yang memfit distribusi normal prediksi dan memilih RUL dengan probabilitas tertinggi. Diuji pada C-MAPSS FD001 dan FD003; ELSTMNN mencapai MScore 5,71 (deviasi 0,19) dan RMSE 18,22 (deviasi 1,38) pada FD001, terbaik dibanding ANN, SVR, RVR, DCNN, ELM, EKF, ESKF, DLSTMNN, dan mengalahkan bagging secara signifikan (p=0,0029).</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>Sangat relevan ke tesis: menggabungkan survival theory (Weibull/hazard/censoring) dengan deep learning (RNN) untuk RUL, DAN menutup celah sampai keputusan pemeliharaan biaya-optimal. Namun domainnya cutting tool, bukan membran/RO.</t>
+          <t>Menunjukkan ensemble LSTM + inferensi Bayesian yang memfit distribusi prediksi (prior/posterior) sebagai cara mengkuantifikasi ketidakpastian RUL dan meningkatkan generalisasi lintas-unit, relevan bagi dimensi ketidakpastian tesis; namun tidak memodelkan penyensoran/survival dan bukan domain membran, sehingga Pendukung.</t>
         </is>
       </c>
     </row>
@@ -2574,17 +2574,17 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>A. Survival Analysis &amp; Censored Data</t>
+          <t>C. Bayesian &amp; Uncertainty</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Prediction of remaining useful life (RUL) of Komatsu excavator under reliability analysis in the Weibull-frailty model</t>
+          <t>Remaining Useful Life Prediction Based on the Bayesian Regularized Radial Basis Function Neural Network for an External Gear Pump</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Ghomghaleh et al.</t>
+          <t>Guo et al.</t>
         </is>
       </c>
       <c r="E44" s="2" t="n">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>PLoS ONE</t>
+          <t>IEEE Access</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -2602,17 +2602,17 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1371/journal.pone.0236128</t>
+          <t>https://doi.org/10.1109/access.2020.3001013</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>Studi memprediksi RUL excavator Komatsu PC-1250 di tambang tembaga Sungun memakai analisis keandalan dalam model Weibull-frailty. Data time between failures (TBF) dari 80 jam operasional dimodelkan dengan dua pendekatan: model klasik-eksponensial dan model Weibull-frailty yang menyertakan frailty (faktor risiko tak teramati/heterogenitas). Model dipilih lewat uji GOF (AIC/BIC) dan uji heterogenitas likelihood ratio, lalu RUL dihitung dari mean residual life (MRL).</t>
+          <t>Studi mengusulkan prediksi RUL pompa roda gigi eksternal memakai Bayesian regularized RBF neural network (Trainbr-RBFNN). Sinyal vibrasi dari accelerated life test didenoise dengan VMD-Hilbert (dibandingkan EEMD/MEEMD), lalu fitur time/frequency/time-frequency domain difusikan dengan factor analysis menjadi degradation fusion index; indeks ini diprediksi dengan Holt two-parameter smoothing dan dilatih ke Trainbr-RBFNN untuk menaksir waktu kegagalan. Distribusi Weibull dua parameter dipakai untuk menaksir parameter keandalan dan RUL di bawah tegangan normal.</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>Preseden langsung penggunaan model survival frailty (Weibull + random effect untuk heterogenitas tak teramati) dalam menghitung RUL, lengkap dengan penanganan data tersensor (suspended data) dan uji GOF/heterogenitas - klop dengan kerangka survival tesis; tetapi tidak memakai deep learning dan domainnya excavator tambang, bukan membran.</t>
+          <t>Menunjukkan pemanfaatan Bayesian-regularized neural network untuk RUL plus pemodelan distribusi waktu-kegagalan Weibull dua parameter dengan MLE dan acceleration model - kombinasi jaringan + Weibull yang dekat dengan kerangka tesis, tetapi tanpa pencensoringan eksplisit dan domainnya pompa, bukan membran.</t>
         </is>
       </c>
     </row>
@@ -2622,17 +2622,17 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>B. Deep Learning RUL</t>
+          <t>C. Bayesian &amp; Uncertainty</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>A Data-Driven Auto-CNN-LSTM Prediction Model for Lithium-Ion Battery Remaining Useful Life</t>
+          <t>Utilizing uncertainty information in remaining useful life estimation via Bayesian neural networks and Hamiltonian Monte Carlo</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Ren et al.</t>
+          <t>Benker et al.</t>
         </is>
       </c>
       <c r="E45" s="2" t="n">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>IEEE Transactions on Industrial Informatics</t>
+          <t>Journal of Manufacturing Systems</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -2650,17 +2650,17 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/tii.2020.3008223</t>
+          <t>https://doi.org/10.1016/j.jmsy.2020.11.005</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>Studi mengusulkan model Auto-CNN-LSTM untuk memprediksi RUL baterai Li-ion: autoencoder memperbesar dimensi fitur untuk mengatasi keterbatasan data, CNN menambang informasi kedalaman, LSTM mengekstrak informasi temporal, dan DNN 7-lapis menghasilkan prediksi RUL yang dihaluskan dengan filter orde pertama.</t>
+          <t>Studi menerapkan Bayesian deep learning untuk estimasi RUL mesin turbofan, dengan inference via Hamiltonian Monte Carlo (HMC) dan variational inference (VI), lalu membandingkannya terhadap deep learning non-probabilistik. Kontribusi utamanya adalah memanfaatkan informasi ketidakpastian (varians prediksi) dalam pengambilan keputusan: distribusi RUL digeser sebesar b*sigma untuk meminimalkan fungsi biaya asimetris (score function), sehingga menurunkan total biaya. Model Bayesian mengungguli model non-probabilistik pada semua eksperimen untuk Score1, dan pendekatan pemanfaatan ketidakpastian memperbaiki Score2.</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>Memberi contoh strategi augmentasi dimensi berbasis autoencoder untuk data degradasi terbatas dan pipeline hibrida CNN+LSTM — relevan untuk tesis pada sumbu data langka; namun tanpa penanganan censoring/survival, tanpa kuantifikasi ketidakpastian, dan bukan domain membran.</t>
+          <t>Menunjukkan secara eksplisit bagaimana ketidakpastian RUL diterjemahkan menjadi keputusan biaya (cost-aware decision), pola yang sangat relevan untuk DSS tesis. Tetapi tidak memakai survival/penyensoran dan bukan domain membran.</t>
         </is>
       </c>
     </row>
@@ -2670,17 +2670,17 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>B. Deep Learning RUL</t>
+          <t>D. Small-data/Transfer/Hierarchical</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>A Deep Learning-Based Remaining Useful Life Prediction Approach for Bearings</t>
+          <t>A Bayesian Optimization AdaBN-DCNN Method With Self-Optimized Structure and Hyperparameters for Domain Adaptation Remaining Useful Life Prediction</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Cheng et al.</t>
+          <t>Li et al.</t>
         </is>
       </c>
       <c r="E46" s="2" t="n">
@@ -2688,7 +2688,7 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>IEEE/ASME Transactions on Mechatronics</t>
+          <t>IEEE Access</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -2698,17 +2698,17 @@
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/tmech.2020.2971503</t>
+          <t>https://doi.org/10.1109/access.2020.2976595</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>Artikel ini mengusulkan kerangka data-driven untuk prediksi RUL rolling element bearing (REB) dengan deep CNN. Getaran mentah diproses memakai Hilbert-Huang Transform untuk menyusun degradation energy indicator (DEI) nonlinier baru sebagai label latih; CNN 6 lapis dilatih untuk memetakan getaran mentah ke DEI, lalu ε-SVR memforecast evolusi DEI hingga melewati failure threshold. Metode divalidasi pada platform PRONOSTIA dan mengungguli delapan metode publikasi.</t>
+          <t>Makalah ini mengusulkan metode prediksi RUL berbasis Deep Convolutional Neural Network (DCNN) yang digabung dengan Bayesian optimization dan Adaptive Batch Normalization (AdaBN). Bayesian optimization dipakai untuk memilih struktur jaringan dan hyperparameter secara otomatis, sedangkan AdaBN dipakai untuk adaptasi domain lintas kondisi operasi. Metode divalidasi pada dataset simulasi degradasi mesin turbofan C-MAPSS dan mengalahkan grid search serta random search.</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>Memperkenalkan indikator degradasi nonlinier (DEI) berbasis frekuensi alami komponen bearing dan framework HHT+CNN+ε-SVR yang menetapkan failure threshold konsisten antar-bearing. Relevan ke tesis sebagai pembanding rekayasa indikator/fitur untuk RUL, namun tanpa survival/penyensoran dan bukan domain membran.</t>
+          <t>Memberi contoh strategi transfer/adaptasi domain berbiaya rendah (hanya fine-tuning parameter BN) untuk RUL lintas domain (FD001-FD004). Relevan ke tesis sebagai pembanding bagaimana 'pergeseran domain' ditangani tanpa memodelkan penyensoran, sehingga menegaskan celah bahwa adaptasi domain pada membran RO dengan data tersensor masih terbuka.</t>
         </is>
       </c>
     </row>
@@ -2723,20 +2723,20 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>A Neural Network-Based Joint Prognostic Model for Data Fusion and Remaining Useful Life Prediction</t>
+          <t>A Directed Acyclic Graph Network Combined With CNN and LSTM for Remaining Useful Life Prediction</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Gao et al.</t>
+          <t>Li et al.</t>
         </is>
       </c>
       <c r="E47" s="2" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>IEEE Transactions on Neural Networks and Learning Systems</t>
+          <t>IEEE Access</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -2746,17 +2746,17 @@
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/tnnls.2020.2977132</t>
+          <t>https://doi.org/10.1109/access.2019.2919566</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>Artikel ini mengusulkan Joint Prognostic Model (JPM) yang menggabungkan model linear Bayesian untuk setiap sinyal sensor (mixed-effects) dengan Artificial Neural Network untuk memetakan hubungan nonlinier antara parameter degradasi multi-sensor dan life percentage. Skema Bayesian updating menghitung distribusi posterior parameter setiap sensor untuk in-service unit, lalu menghasilkan posterior predictive distribution RUL. Metode divalidasi pada C-MAPSS FD001/FD003.</t>
+          <t>Artikel ini mengusulkan jaringan Directed Acyclic Graph (DAG) yang menggabungkan CNN dan LSTM secara paralel (bukan serial) untuk prediksi RUL. Dua jalur — jalur LSTM dan jalur CNN — tidak saling terkait tetapi keluarannya dijumlahkan secara element-wise lalu diteruskan ke LSTM kedua dan layer fully connected. Data diproses dengan sliding time window dan target RUL memakai fungsi piecewise-linear; divalidasi pada dataset C-MAPSS.</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>Menyediakan kerangka Bayesian + NN yang menghasilkan distribusi prediktif RUL (bukan hanya titik) dan menangani heterogenitas antar-unit via mixed-effects. Relevan ke tesis pada sumbu ketidakpastian (d5) dan struktur hierarkis (d8), namun tanpa pemodelan penyensoran/survival—menegaskan celah penggabungan survival tersensor dengan prediksi nonlinier.</t>
+          <t>Menunjukkan arsitektur hibrida CNN+LSTM paralel berbasis DAG yang mengoreksi parameter kedua jalur dari galat prediksi secara holistik, dengan penanganan input timestamp lewat sliding time window. Relevan ke tesis sebagai pembanding arsitektur DL RUL, namun tanpa survival/penyensoran dan bukan domain membran.</t>
         </is>
       </c>
     </row>
@@ -2766,25 +2766,25 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>B. Deep Learning RUL</t>
+          <t>C. Bayesian &amp; Uncertainty</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Attention-Based LSTM Network for Rotatory Machine Remaining Useful Life Prediction</t>
+          <t>Remaining useful life prediction for lithium-ion batteries using particle filter and artificial neural network</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Zhang et al.</t>
+          <t>Qin et al.</t>
         </is>
       </c>
       <c r="E48" s="2" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>IEEE Access</t>
+          <t>Industrial Management &amp; Data Systems</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
@@ -2794,17 +2794,17 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/access.2020.3010066</t>
+          <t>https://doi.org/10.1108/imds-03-2019-0195</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>Paper mengusulkan kerangka deep learning TLSTM-A (two-layer LSTM dengan attention) yang didahului 1-D CNN untuk memprediksi RUL komponen rotasi (bearing). CNN mengekstrak fitur lokal dari sinyal getaran, dua lapisan LSTM mengekstrak fitur temporal berlapis, dan attention mechanism menyorot informasi kunci serta mengatasi kehilangan informasi pada transmisi jarak jauh LSTM. Dievaluasi pada dataset bearing XJTU-SY, model mencapai RMSE/MAE/Score terbaik di antara pembanding.</t>
+          <t>Studi mengusulkan model fusi untuk RUL baterai lithium-ion: particle filter (PF) sebagai inti dengan model double-exponential sebagai persamaan keadaan dan artificial neural network (ANN) sebagai persamaan observasi. PF memperbarui distribusi posterior parameter secara online sehingga RUL beserta PDF-nya dapat diestimasi; akurasi meningkat seiring bertambahnya siklus (error 17 siklus pada siklus ke-70 turun menjadi 2 siklus pada siklus ke-90).</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>Contoh kuat arsitektur deep learning (CNN+LSTM berlapis+attention) point-estimate untuk RUL sinyal getaran, berguna sebagai baseline arsitektur di tesis. Menegaskan celah: tidak ada penanganan data tersensor maupun kuantifikasi ketidakpastian, sehingga tidak menutup gap utama tesis.</t>
+          <t>Menunjukkan estimasi RUL berbasis Bayesian state estimation (particle filter) yang memberi ekspresi ketidakpastian (PDF), sekaligus mengatasi data kecil lewat koreksi posterior. Relevan bagi tesis sebagai contoh estimasi RUL probabilistik dengan data terbatas, meski tanpa penyensoran eksplisit dan bukan domain membran.</t>
         </is>
       </c>
     </row>
@@ -2814,25 +2814,25 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>B. Deep Learning RUL</t>
+          <t>D. Small-data/Transfer/Hierarchical</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Deep-Convolution-Based LSTM Network for Remaining Useful Life Prediction</t>
+          <t>Predicting Remaining Useful Life of Rolling Bearings Based on Deep Feature Representation and Transfer Learning</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Ma et al.</t>
+          <t>Mao et al.</t>
         </is>
       </c>
       <c r="E49" s="2" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>IEEE Transactions on Industrial Informatics</t>
+          <t>IEEE Transactions on Instrumentation and Measurement</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -2842,17 +2842,17 @@
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/tii.2020.2991796</t>
+          <t>https://doi.org/10.1109/tim.2019.2917735</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>Studi mengusulkan jaringan CLSTM (convolution-based LSTM) untuk prediksi RUL bantalan (bearing), dengan operasi konvolusi pada transisi input-to-state dan state-to-state LSTM sehingga menangkap informasi time-frequency dan temporal sekaligus. Input berupa fitur time-frequency (STFT) dari sinyal vibrasi run-to-failure, diproses arsitektur encoding-forecasting berlapis dua CLSTM. Pada dua uji run-to-failure, CLSTM mengalahkan deep CNN dan deep LSTM (RMSE 29,7/10,8 menit vs 47,9/18,2 dan 40,7/15,6).</t>
+          <t>Studi mengusulkan kerangka prediksi RUL bearing yang menggabungkan representasi fitur dalam (Contractive Denoising Autoencoder, CDAE) dengan transfer learning (Transfer Component Analysis, TCA). CDAE mengekstrak fitur dari marginal spectrum Hilbert-Huang; korelasi Pearson menilai status kesehatan; TCA menyelaraskan distribusi fitur antar-bearing; LSSVM membangun model regresi RUL.</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>Preseden arsitektur deep learning RUL (convolutional LSTM) dengan data vibrasi run-to-failure nyata dan pembanding deep CNN/LSTM, berguna bagi tesis sebagai rujukan metode prediksi RUL; namun tidak menangani penyensoran/survival dan bukan domain membran, sehingga Pendukung.</t>
+          <t>Menunjukkan transfer learning dapat mengatasi perbedaan distribusi data antar-unit dan data skala kecil — relevan untuk tesis pada sumbu small-data/transfer (mis. antar-modul membran); namun tanpa survival/censoring, tanpa kuantifikasi ketidakpastian penuh, dan bukan domain membran.</t>
         </is>
       </c>
     </row>
@@ -2862,25 +2862,25 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>B. Deep Learning RUL</t>
+          <t>F. DSS &amp; Predictive Maintenance (IS)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Remaining Useful Life Prognosis Based on Ensemble Long Short-Term Memory Neural Network</t>
+          <t>Forecasting remaining useful life: Interpretable deep learning approach via variational Bayesian inferences</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Cheng et al.</t>
+          <t>Kraus et al.</t>
         </is>
       </c>
       <c r="E50" s="2" t="n">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>IEEE Transactions on Instrumentation and Measurement</t>
+          <t>Decision Support Systems</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
@@ -2890,17 +2890,17 @@
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/tim.2020.3031113</t>
+          <t>https://doi.org/10.1016/j.dss.2019.113100</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>Studi mengusulkan ELSTMNN (Ensemble Long Short-Term Memory Neural Network) untuk prognosis RUL: sejumlah LSTMNN dilatih paralel, masing-masing pada data satu unit peralatan, lalu digabung memakai Bayesian Inference Algorithm (BIA) yang memfit distribusi normal prediksi dan memilih RUL dengan probabilitas tertinggi. Diuji pada C-MAPSS FD001 dan FD003; ELSTMNN mencapai MScore 5,71 (deviasi 0,19) dan RMSE 18,22 (deviasi 1,38) pada FD001, terbaik dibanding ANN, SVR, RVR, DCNN, ELM, EKF, ESKF, DLSTMNN, dan mengalahkan bagging secara signifikan (p=0,0029).</t>
+          <t>Studi mengusulkan structured-effect neural network (SENN) untuk memprediksi RUL secara akurat sekaligus interpretable. SENN mendekomposisi prediksi menjadi tiga komponen: (1) baseline non-parametrik berupa probabilitas lifetime (conditional expectation Weibull atau log-normal, E[Z|Z&gt;t] - t), (2) kombinasi linear sensor, dan (3) komponen rekuren (LSTM) untuk menangkap non-linearitas. Parameter diestimasi via variational Bayesian inference (maximisasi ELBO), sehingga diperoleh distribusi posterior dan kuantifikasi ketidakpastian. Pada C-MAPSS, SENN mengalahkan model machine learning tradisional dan mendekati performa LSTM murni dengan interpretabilitas jauh lebih tinggi.</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>Menunjukkan ensemble LSTM + inferensi Bayesian yang memfit distribusi prediksi (prior/posterior) sebagai cara mengkuantifikasi ketidakpastian RUL dan meningkatkan generalisasi lintas-unit, relevan bagi dimensi ketidakpastian tesis; namun tidak memodelkan penyensoran/survival dan bukan domain membran, sehingga Pendukung.</t>
+          <t>Sangat relevan bagi tesis: menggabungkan model kelangsungan hidup (Weibull/log-normal conditional residual life) dengan deep learning (LSTM) dalam satu kerangka interpretable dan Bayesian - tepat pada sumbu survival analysis + DL. Namun tidak memodelkan data tersensor (C-MAPSS run-to-failure) dan domainnya aero-engine, bukan membran.</t>
         </is>
       </c>
     </row>
@@ -2910,25 +2910,25 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>C. Bayesian &amp; Uncertainty</t>
+          <t>F. DSS &amp; Predictive Maintenance (IS)</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Remaining Useful Life Prediction Based on the Bayesian Regularized Radial Basis Function Neural Network for an External Gear Pump</t>
+          <t>Design and development of reverse osmosis (RO) plant status monitoring system for early fault prediction and predictive maintenance</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Guo et al.</t>
+          <t>Srivastava et al.</t>
         </is>
       </c>
       <c r="E51" s="2" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>IEEE Access</t>
+          <t>Applied Water Science</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
@@ -2938,17 +2938,17 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/access.2020.3001013</t>
+          <t>https://doi.org/10.1007/s13201-018-0821-8</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>Studi mengusulkan prediksi RUL pompa roda gigi eksternal memakai Bayesian regularized RBF neural network (Trainbr-RBFNN). Sinyal vibrasi dari accelerated life test didenoise dengan VMD-Hilbert (dibandingkan EEMD/MEEMD), lalu fitur time/frequency/time-frequency domain difusikan dengan factor analysis menjadi degradation fusion index; indeks ini diprediksi dengan Holt two-parameter smoothing dan dilatih ke Trainbr-RBFNN untuk menaksir waktu kegagalan. Distribusi Weibull dua parameter dipakai untuk menaksir parameter keandalan dan RUL di bawah tegangan normal.</t>
+          <t>Penelitian merancang dan membangun unit pemantauan status plant reverse osmosis (RO) berbasis embedded system untuk deteksi dini kerusakan dan pemeliharaan prediktif. Unit memantau parameter real-time (pH, TDS, laju alir feed/produk, tekanan, level tangki, daya) via sensor, menyimpan data ke smartphone/cloud, dan memakai Jaringan Saraf Tiruan (ANN) untuk memprediksi efisiensi membran serta peristiwa fouling/scaling. Sistem menghasilkan peringatan dini dan merekomendasikan tindakan pemeliharaan (chemical wash, water wash, penggantian membran); diuji pada plant 2000 LPH dan 10 desa di Rajasthan.</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>Menunjukkan pemanfaatan Bayesian-regularized neural network untuk RUL plus pemodelan distribusi waktu-kegagalan Weibull dua parameter dengan MLE dan acceleration model - kombinasi jaringan + Weibull yang dekat dengan kerangka tesis, tetapi tanpa pencensoringan eksplisit dan domainnya pompa, bukan membran.</t>
+          <t>Menunjukkan implementasi nyata sistem pemantauan prediktif pada plant RO/desalinasi (domain tesis) dan mengaitkannya ke tindakan pemeliharaan membran; namun tidak memprediksi RUL dan tidak memakai survival analysis/censoring, sehingga berperan sebagai konteks domain dan DSS.</t>
         </is>
       </c>
     </row>
@@ -2958,25 +2958,25 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>C. Bayesian &amp; Uncertainty</t>
+          <t>A. Survival Analysis &amp; Censored Data</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Utilizing uncertainty information in remaining useful life estimation via Bayesian neural networks and Hamiltonian Monte Carlo</t>
+          <t>Remaining useful life estimation in heterogeneous fleets working under variable operating conditions</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Benker et al.</t>
+          <t>Al‐Dahidi et al.</t>
         </is>
       </c>
       <c r="E52" s="2" t="n">
-        <v>2020</v>
+        <v>2016</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>Journal of Manufacturing Systems</t>
+          <t>Reliability Engineering &amp; System Safety</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.jmsy.2020.11.005</t>
+          <t>https://doi.org/10.1016/j.ress.2016.07.019</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>Studi menerapkan Bayesian deep learning untuk estimasi RUL mesin turbofan, dengan inference via Hamiltonian Monte Carlo (HMC) dan variational inference (VI), lalu membandingkannya terhadap deep learning non-probabilistik. Kontribusi utamanya adalah memanfaatkan informasi ketidakpastian (varians prediksi) dalam pengambilan keputusan: distribusi RUL digeser sebesar b*sigma untuk meminimalkan fungsi biaya asimetris (score function), sehingga menurunkan total biaya. Model Bayesian mengungguli model non-probabilistik pada semua eksperimen untuk Score1, dan pendekatan pemanfaatan ketidakpastian memperbaiki Score2.</t>
+          <t>Studi mengusulkan pendekatan prognostik data-driven untuk estimasi RUL peralatan dalam fleet heterogen yang bekerja pada kondisi operasi bervariasi. Tiga fase: (1) identifikasi level degradasi (state) via unsupervised ensemble clustering; (2) estimasi parameter distribusi Weibull diskrit transisi antar-state dengan MLE dan kuantifikasi ketidakpastiannya via Fisher Information Matrix (FIM); (3) estimasi RUL peralatan baru via simulasi Monte Carlo langsung. Dianalisis pada dua studi kasus (kapasitor elektrolit aluminium dan mesin turbofan) dan terbukti lebih baik daripada pendekatan fuzzy similarity.</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>Menunjukkan secara eksplisit bagaimana ketidakpastian RUL diterjemahkan menjadi keputusan biaya (cost-aware decision), pola yang sangat relevan untuk DSS tesis. Tetapi tidak memakai survival/penyensoran dan bukan domain membran.</t>
+          <t>Sangat relevan ke poros survival/Weibull tesis: pemodelan transisi state dengan distribusi Weibull diskrit dan penanganan eksplisit data right-censored (trajektori run-to-failure tak lengkap) di dalam likelihood, plus kuantifikasi ketidakpastian dan strategi fleet/hierarchical. Namun tanpa deep learning dan domainnya bukan membran.</t>
         </is>
       </c>
     </row>
@@ -3006,25 +3006,25 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>D. Small-data/Transfer/Hierarchical</t>
+          <t>A. Survival Analysis &amp; Censored Data</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>A Bayesian Optimization AdaBN-DCNN Method With Self-Optimized Structure and Hyperparameters for Domain Adaptation Remaining Useful Life Prediction</t>
+          <t>Machine performance degradation assessment and remaining useful life prediction using proportional hazard model and support vector machine</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Li et al.</t>
+          <t>Tran et al.</t>
         </is>
       </c>
       <c r="E53" s="2" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>IEEE Access</t>
+          <t>Mechanical Systems and Signal Processing</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
@@ -3034,17 +3034,17 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/access.2020.2976595</t>
+          <t>https://doi.org/10.1016/j.ymssp.2012.02.015</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>Makalah ini mengusulkan metode prediksi RUL berbasis Deep Convolutional Neural Network (DCNN) yang digabung dengan Bayesian optimization dan Adaptive Batch Normalization (AdaBN). Bayesian optimization dipakai untuk memilih struktur jaringan dan hyperparameter secara otomatis, sedangkan AdaBN dipakai untuk adaptasi domain lintas kondisi operasi. Metode divalidasi pada dataset simulasi degradasi mesin turbofan C-MAPSS dan mengalahkan grid search serta random search.</t>
+          <t>Studi mengusulkan metode tiga tahap untuk menilai degradasi kinerja mesin dan memprediksi RUL hanya dari data kondisi operasi normal. Tahap pertama membangun model identifikasi ARMA dan indeks degradasi dari RMS residual; tahap kedua membangun Cox proportional hazard model (PHM) untuk mengestimasi fungsi survival; tahap ketiga memakai support vector regression dengan prediksi multi-langkah untuk meramalkan RUL. Metode divalidasi pada data pemantauan kompresor low methane dan mencapai akurasi RUL 87,5% (RMSE survival 0,33674).</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr">
         <is>
-          <t>Memberi contoh strategi transfer/adaptasi domain berbiaya rendah (hanya fine-tuning parameter BN) untuk RUL lintas domain (FD001-FD004). Relevan ke tesis sebagai pembanding bagaimana 'pergeseran domain' ditangani tanpa memodelkan penyensoran, sehingga menegaskan celah bahwa adaptasi domain pada membran RO dengan data tersensor masih terbuka.</t>
+          <t>Preseden metodologis paling langsung untuk kombinasi survival analysis + machine learning pada RUL: Cox PHM yang secara eksplisit memodelkan data tersensor (seri biner 0/1 dari ambang batas) dipadukan dengan SVM. Relevan bagi poros 'survival analysis' tesis, tetapi domainnya mesin kompresor (bukan membran/RO) sehingga tidak menyentuh poros domain.</t>
         </is>
       </c>
     </row>
@@ -3054,45 +3054,45 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>B. Deep Learning RUL</t>
+          <t>A. Survival Analysis &amp; Censored Data</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>A Directed Acyclic Graph Network Combined With CNN and LSTM for Remaining Useful Life Prediction</t>
+          <t>A Multisensor Cross-Modal Attention Framework for Weibull-Driven RUL Estimation for Liner Using Real-World Industrial Data</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Li et al.</t>
+          <t>Reddy et al.</t>
         </is>
       </c>
       <c r="E54" s="2" t="n">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>IEEE Access</t>
+          <t>IEEE Sensors Letters</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>Scopus Q1 (SCImago SJR Best Quartile)</t>
+          <t>Scopus Q2 (SCImago SJR Best Quartile)</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/access.2019.2919566</t>
+          <t>https://doi.org/10.1109/lsens.2026.3673123</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>Artikel ini mengusulkan jaringan Directed Acyclic Graph (DAG) yang menggabungkan CNN dan LSTM secara paralel (bukan serial) untuk prediksi RUL. Dua jalur — jalur LSTM dan jalur CNN — tidak saling terkait tetapi keluarannya dijumlahkan secara element-wise lalu diteruskan ke LSTM kedua dan layer fully connected. Data diproses dengan sliding time window dan target RUL memakai fungsi piecewise-linear; divalidasi pada dataset C-MAPSS.</t>
+          <t>Studi mengusulkan CMA-WFT (cross-modal attention-Weibull fusion transformer), arsitektur untuk estimasi RUL pada liner press industri dengan menggabungkan encoder temporal per-modalitas, cross-modal attention, dan head survival Weibull parametrik. Setiap modalitas (vibrasi, temperatur, gap/displacement) dikodekan terpisah lalu digabung via cross-modal attention; head Weibull memprediksi parameter shape (k) dan scale (lambda) sehingga menghasilkan estimasi RUL titik sekaligus kurva reliabilitas, dan menangani pengamatan tersensor kanan secara alami. Validasi pada data sintetis, data industri nyata (gear-press), dan benchmark ATE (turbofan); CMA-WFT mengalahkan RF, SVM, RNN-Weibull, dan LSTM-Weibull (akurasi RT 84% vs 72%).</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr">
         <is>
-          <t>Menunjukkan arsitektur hibrida CNN+LSTM paralel berbasis DAG yang mengoreksi parameter kedua jalur dari galat prediksi secara holistik, dengan penanganan input timestamp lewat sliding time window. Relevan ke tesis sebagai pembanding arsitektur DL RUL, namun tanpa survival/penyensoran dan bukan domain membran.</t>
+          <t>Memberi contoh integrasi multisensor + transformer + survival Weibull yang menangani data tersensor kanan sekaligus mengkuantifikasi ketidakpastian (kurva reliabilitas) - sangat dekat dengan kebutuhan metode tesis, meski domainnya liner press/turbofan (bukan membran).</t>
         </is>
       </c>
     </row>
@@ -3102,45 +3102,45 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>C. Bayesian &amp; Uncertainty</t>
+          <t>B. Deep Learning RUL</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Remaining useful life prediction for lithium-ion batteries using particle filter and artificial neural network</t>
+          <t>Graph neural network-based remaining useful life prediction of milling tools using multi-sensor data</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Qin et al.</t>
+          <t>Kumar et al.</t>
         </is>
       </c>
       <c r="E55" s="2" t="n">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>Industrial Management &amp; Data Systems</t>
+          <t>Discover Applied Sciences</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>Scopus Q1 (SCImago SJR Best Quartile)</t>
+          <t>Scopus Q2 (SCImago SJR 2024)</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1108/imds-03-2019-0195</t>
+          <t>https://doi.org/10.1007/s42452-026-08390-x</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>Studi mengusulkan model fusi untuk RUL baterai lithium-ion: particle filter (PF) sebagai inti dengan model double-exponential sebagai persamaan keadaan dan artificial neural network (ANN) sebagai persamaan observasi. PF memperbarui distribusi posterior parameter secara online sehingga RUL beserta PDF-nya dapat diestimasi; akurasi meningkat seiring bertambahnya siklus (error 17 siklus pada siklus ke-70 turun menjadi 2 siklus pada siklus ke-90).</t>
+          <t>Paper mengusulkan pipeline deep learning berbasis graph untuk prediksi RUL/keausan pahat milling CNC memakai sinyal getaran, beban spindel, dan gaya potong. Fitur time-domain dan frequency-domain diubah menjadi graph dengan sisi korelasi dan temporal, lalu tiga arsitektur GNN (GCN, GRN, GAT) dilatih dengan Random Forest Regressor dan hyperparameter tuning Optuna/Bayesian Optimization pada 120 run pemesinan.</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr">
         <is>
-          <t>Menunjukkan estimasi RUL berbasis Bayesian state estimation (particle filter) yang memberi ekspresi ketidakpastian (PDF), sekaligus mengatasi data kecil lewat koreksi posterior. Relevan bagi tesis sebagai contoh estimasi RUL probabilistik dengan data terbatas, meski tanpa penyensoran eksplisit dan bukan domain membran.</t>
+          <t>Menyediakan kerangka evaluasi terpadu GNN (GCN/GRN/GAT) untuk RUL pahat milling dengan konstruksi graph korelasi-temporal yang lebih sparse dan interpretable; relevan bagi tesis sebagai contoh model representasi struktur/temporal dan sebagai pembanding non-survival.</t>
         </is>
       </c>
     </row>
@@ -3150,45 +3150,45 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>D. Small-data/Transfer/Hierarchical</t>
+          <t>C. Bayesian &amp; Uncertainty</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Predicting Remaining Useful Life of Rolling Bearings Based on Deep Feature Representation and Transfer Learning</t>
+          <t>Weibull Variational Autoencoder for Remaining Useful Life Prediction</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Mao et al.</t>
+          <t>Yu et al.</t>
         </is>
       </c>
       <c r="E56" s="2" t="n">
-        <v>2019</v>
+        <v>2026</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>IEEE Transactions on Instrumentation and Measurement</t>
+          <t>Quality and Reliability Engineering International</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Scopus Q1 (SCImago SJR Best Quartile)</t>
+          <t>Scopus Q2 (SCImago SJR Best Quartile)</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/tim.2019.2917735</t>
+          <t>https://doi.org/10.1002/qre.70386</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>Studi mengusulkan kerangka prediksi RUL bearing yang menggabungkan representasi fitur dalam (Contractive Denoising Autoencoder, CDAE) dengan transfer learning (Transfer Component Analysis, TCA). CDAE mengekstrak fitur dari marginal spectrum Hilbert-Huang; korelasi Pearson menilai status kesehatan; TCA menyelaraskan distribusi fitur antar-bearing; LSSVM membangun model regresi RUL.</t>
+          <t>Studi mengusulkan Weibull Variational Autoencoder (WVAE) untuk prediksi RUL, yaitu VAE yang latent space-nya mengikuti distribusi Weibull sehingga bisa mempelajari bentuk dan skala distribusi kegagalan langsung dari riwayat kegagalan. Fungsi loss gabungan MSE ditambah negative log-likelihood Weibull menjaga akurasi titik sekaligus kesetiaan distribusi, sementara Monte Carlo Dropout memberi interval kepercayaan 95%. Validasi pada data simulasi (tiga tipe kegagalan: infant mortality, random, wear-out, dengan tiga tingkat noise) dan dataset lapangan Backblaze hard drive menunjukkan WVAE konsisten dengan distribusi kegagalan historis dan mengalahkan baseline pada CRPS.</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr">
         <is>
-          <t>Menunjukkan transfer learning dapat mengatasi perbedaan distribusi data antar-unit dan data skala kecil — relevan untuk tesis pada sumbu small-data/transfer (mis. antar-modul membran); namun tanpa survival/censoring, tanpa kuantifikasi ketidakpastian penuh, dan bukan domain membran.</t>
+          <t>Menyatukan model berbasis distribusi Weibull dengan arsitektur deep generative untuk RUL, tepat pada sumbu metode tesis (survival/Weibull + kuantifikasi ketidakpastian), namun sengaja mengabaikan observasi tersensor (right-censored) dan domainnya bukan membran.</t>
         </is>
       </c>
     </row>
@@ -3198,45 +3198,45 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>F. DSS &amp; Predictive Maintenance (IS)</t>
+          <t>A. Survival Analysis &amp; Censored Data</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Forecasting remaining useful life: Interpretable deep learning approach via variational Bayesian inferences</t>
+          <t>LSTM and Transformers based methods for Remaining Useful Life Prediction considering Censored Data</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Kraus et al.</t>
+          <t>Noot et al.</t>
         </is>
       </c>
       <c r="E57" s="2" t="n">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>Decision Support Systems</t>
+          <t>International Journal of Prognostics and Health Management</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>Scopus Q1 (SCImago SJR Best Quartile)</t>
+          <t>Scopus Q2 (SCImago SJR Best Quartile)</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.dss.2019.113100</t>
+          <t>https://doi.org/10.36001/ijphm.2025.v16i2.4260</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>Studi mengusulkan structured-effect neural network (SENN) untuk memprediksi RUL secara akurat sekaligus interpretable. SENN mendekomposisi prediksi menjadi tiga komponen: (1) baseline non-parametrik berupa probabilitas lifetime (conditional expectation Weibull atau log-normal, E[Z|Z&gt;t] - t), (2) kombinasi linear sensor, dan (3) komponen rekuren (LSTM) untuk menangkap non-linearitas. Parameter diestimasi via variational Bayesian inference (maximisasi ELBO), sehingga diperoleh distribusi posterior dan kuantifikasi ketidakpastian. Pada C-MAPSS, SENN mengalahkan model machine learning tradisional dan mendekati performa LSTM murni dengan interpretabilitas jauh lebih tinggi.</t>
+          <t>Artikel mengadaptasi arsitektur Transformer DAST dan LSTM menjadi ordinal regression (OR) agar mampu menangani data tersensor kanan (right-censored) pada prediksi RUL. OR mengodekan RUL menjadi vektor status masa depan (0/1/-) dan loss BCE dimask pada koordinat tersensor, memungkinkan pemanfaatan unit yang diganti sebelum gagal. Dievaluasi pada C-MAPSS dan N-CMAPSS dengan tingkat pencensoringan artifisial 0-90%, metode ini setara SOTA pada data tanpa sensor dan lebih unggul pada pencensoringan tinggi pada dataset besar; conformal prediction dipakai untuk interval kepercayaan.</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr">
         <is>
-          <t>Sangat relevan bagi tesis: menggabungkan model kelangsungan hidup (Weibull/log-normal conditional residual life) dengan deep learning (LSTM) dalam satu kerangka interpretable dan Bayesian - tepat pada sumbu survival analysis + DL. Namun tidak memodelkan data tersensor (C-MAPSS run-to-failure) dan domainnya aero-engine, bukan membran.</t>
+          <t>Menunjukkan cara menggabungkan arsitektur deep-learning RUL modern (LSTM/Transformer) dengan penanganan data tersensor eksplisit dan interval prediksi conformal - dua komponen inti metode tesis, meski domainnya bukan membran.</t>
         </is>
       </c>
     </row>
@@ -3246,45 +3246,45 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>F. DSS &amp; Predictive Maintenance (IS)</t>
+          <t>D. Small-data/Transfer/Hierarchical</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Design and development of reverse osmosis (RO) plant status monitoring system for early fault prediction and predictive maintenance</t>
+          <t>Remaining Useful Life Prediction of Turbine Engines Using Multimodal Transfer Learning</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Srivastava et al.</t>
+          <t>Li et al.</t>
         </is>
       </c>
       <c r="E58" s="2" t="n">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>Applied Water Science</t>
+          <t>Machines</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>Scopus Q1 (SCImago SJR Best Quartile)</t>
+          <t>Scopus Q2 (SCImago SJR Best Quartile)</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s13201-018-0821-8</t>
+          <t>https://doi.org/10.3390/machines13090789</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>Penelitian merancang dan membangun unit pemantauan status plant reverse osmosis (RO) berbasis embedded system untuk deteksi dini kerusakan dan pemeliharaan prediktif. Unit memantau parameter real-time (pH, TDS, laju alir feed/produk, tekanan, level tangki, daya) via sensor, menyimpan data ke smartphone/cloud, dan memakai Jaringan Saraf Tiruan (ANN) untuk memprediksi efisiensi membran serta peristiwa fouling/scaling. Sistem menghasilkan peringatan dini dan merekomendasikan tindakan pemeliharaan (chemical wash, water wash, penggantian membran); diuji pada plant 2000 LPH dan 10 desa di Rajasthan.</t>
+          <t>Paper mengusulkan DMFR (Deep Multimodal Fine-tuning Regression), framework RUL yang menggabungkan multimodal (deret waktu + citra recurrence plot) dengan transfer learning dua tahap (pre-training terawasi + fine-tuning). Dievaluasi pada dataset NASA C-MAPSS turbofan dengan 12 tugas transfer lintas operating condition/fault mode; model melaporkan RMSE/MAE/R2/Score terbaik antar baseline (CNN, DNN, GRU, LSTM, RNN, TCN) dan menyajikan interval kepercayaan 95%.</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr">
         <is>
-          <t>Menunjukkan implementasi nyata sistem pemantauan prediktif pada plant RO/desalinasi (domain tesis) dan mengaitkannya ke tindakan pemeliharaan membran; namun tidak memprediksi RUL dan tidak memakai survival analysis/censoring, sehingga berperan sebagai konteks domain dan DSS.</t>
+          <t>Menunjukkan bagaimana transfer learning dan fusi multimodal menangani skenario small-sample dan cross-condition pada RUL; relevan bagi tesis RUL membran yang menghadapi kelangkaan data dan pergeseran kondisi operasi (cocok untuk strategi small-data/transfer).</t>
         </is>
       </c>
     </row>
@@ -3294,45 +3294,45 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>A. Survival Analysis &amp; Censored Data</t>
+          <t>F. DSS &amp; Predictive Maintenance (IS)</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Remaining useful life estimation in heterogeneous fleets working under variable operating conditions</t>
+          <t>Survival Analysis-Based System for Predictive Maintenance Optimization</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Al‐Dahidi et al.</t>
+          <t>Coutinho et al.</t>
         </is>
       </c>
       <c r="E59" s="2" t="n">
-        <v>2016</v>
+        <v>2025</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Reliability Engineering &amp; System Safety</t>
+          <t>SN Computer Science</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>Scopus Q1 (SCImago SJR Best Quartile)</t>
+          <t>Scopus Q2 (SCImago SJR Best Quartile)</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.ress.2016.07.019</t>
+          <t>https://doi.org/10.1007/s42979-025-04291-9</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>Studi mengusulkan pendekatan prognostik data-driven untuk estimasi RUL peralatan dalam fleet heterogen yang bekerja pada kondisi operasi bervariasi. Tiga fase: (1) identifikasi level degradasi (state) via unsupervised ensemble clustering; (2) estimasi parameter distribusi Weibull diskrit transisi antar-state dengan MLE dan kuantifikasi ketidakpastiannya via Fisher Information Matrix (FIM); (3) estimasi RUL peralatan baru via simulasi Monte Carlo langsung. Dianalisis pada dua studi kasus (kapasitor elektrolit aluminium dan mesin turbofan) dan terbukti lebih baik daripada pendekatan fuzzy similarity.</t>
+          <t>Artikel ini menyajikan kerangka predictive maintenance modular berbasis survival analysis untuk mengestimasi RUL komponen industri, digabung algoritma optimasi penjadwalan Simulated Annealing. Empat model survival dievaluasi (Cox PH, Random Survival Forest, Gradient Boosting Survival Analysis, Survival SVM), dengan GBSA paling robust karena tahan overfitting dan mampu menangkap degradasi nonlinier. Kerangka divalidasi pada data degradasi elektroda las (nyata) dan dataset sintetis Microsoft Azure, menurunkan downtime 25% dibanding metode tak teroptimasi.</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr">
         <is>
-          <t>Sangat relevan ke poros survival/Weibull tesis: pemodelan transisi state dengan distribusi Weibull diskrit dan penanganan eksplisit data right-censored (trajektori run-to-failure tak lengkap) di dalam likelihood, plus kuantifikasi ketidakpastian dan strategi fleet/hierarchical. Namun tanpa deep learning dan domainnya bukan membran.</t>
+          <t>Langkah paling dekat dengan tesis: secara eksplisit mengintegrasikan data tersensor ke dalam model survival (Cox PH/RSF/GBSA/Survival SVM) untuk RUL, lalu menghubungkannya ke keputusan penjadwalan pemeliharaan. Relevan sebagai preseden Inti-Metode; celah yang tersisa adalah belum diterapkan pada membran/RO dan belum memakai deep learning survival (mis. DeepHit/DeepSurv) pada data membran.</t>
         </is>
       </c>
     </row>
@@ -3347,40 +3347,40 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Machine performance degradation assessment and remaining useful life prediction using proportional hazard model and support vector machine</t>
+          <t>Remaining Useful Life Prediction for Power Storage Electronic Components Based on Fractional Weibull Process and Shock Poisson Model</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Tran et al.</t>
+          <t>Song et al.</t>
         </is>
       </c>
       <c r="E60" s="2" t="n">
-        <v>2012</v>
+        <v>2024</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>Mechanical Systems and Signal Processing</t>
+          <t>Fractal and Fractional</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>Scopus Q1 (SCImago SJR Best Quartile)</t>
+          <t>Scopus Q2 (SCImago SJR Best Quartile)</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.ymssp.2012.02.015</t>
+          <t>https://doi.org/10.3390/fractalfract8080485</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>Studi mengusulkan metode tiga tahap untuk menilai degradasi kinerja mesin dan memprediksi RUL hanya dari data kondisi operasi normal. Tahap pertama membangun model identifikasi ARMA dan indeks degradasi dari RMS residual; tahap kedua membangun Cox proportional hazard model (PHM) untuk mengestimasi fungsi survival; tahap ketiga memakai support vector regression dengan prediksi multi-langkah untuk meramalkan RUL. Metode divalidasi pada data pemantauan kompresor low methane dan mencapai akurasi RUL 87,5% (RMSE survival 0,33674).</t>
+          <t>Studi mengusulkan model degradation-threshold-shock (DTS) untuk memprediksi RUL komponen penyimpanan daya (baterai LiFePO4 dan superkapasitor). Proses steady degradation dimodelkan dengan fractional Weibull process (fWp) yang memiliki long-range dependence dan heavy tail, sedangkan guncangan acak (shock) dimodelkan dengan non-homogeneous compound Poisson process (NHCP) berintensitas naik; koefisien drift dan diffusion diperbarui secara acak untuk menangkap gangguan lingkungan. RUL dihitung via Monte Carlo sebagai waktu first-passage melewati failure threshold (FT), dan model mengalahkan CNN, EMD-GRU, DTS-BM, serta adaptive FBM pada protokol DST dan UDDS.</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr">
         <is>
-          <t>Preseden metodologis paling langsung untuk kombinasi survival analysis + machine learning pada RUL: Cox PHM yang secara eksplisit memodelkan data tersensor (seri biner 0/1 dari ambang batas) dipadukan dengan SVM. Relevan bagi poros 'survival analysis' tesis, tetapi domainnya mesin kompresor (bukan membran/RO) sehingga tidak menyentuh poros domain.</t>
+          <t>Memberi preseden model degradasi stokastik berbasis Weibull + ambang kegagalan (first-passage) untuk RUL sebagai alternatif dari deep learning - relevan dengan pilar A (analisis failure-time) pada tesis, tetapi tidak memodelkan data tersensor dan domainnya komponen penyimpanan daya, bukan membran.</t>
         </is>
       </c>
     </row>
@@ -3390,25 +3390,25 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>A. Survival Analysis &amp; Censored Data</t>
+          <t>B. Deep Learning RUL</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>A Multisensor Cross-Modal Attention Framework for Weibull-Driven RUL Estimation for Liner Using Real-World Industrial Data</t>
+          <t>Hybrid Neural Networks for Enhanced Predictions of Remaining Useful Life in Lithium-Ion Batteries</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Reddy et al.</t>
+          <t>Rastegarpanah et al.</t>
         </is>
       </c>
       <c r="E61" s="2" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>IEEE Sensors Letters</t>
+          <t>Batteries</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -3418,17 +3418,17 @@
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1109/lsens.2026.3673123</t>
+          <t>https://doi.org/10.3390/batteries10030106</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>Studi mengusulkan CMA-WFT (cross-modal attention-Weibull fusion transformer), arsitektur untuk estimasi RUL pada liner press industri dengan menggabungkan encoder temporal per-modalitas, cross-modal attention, dan head survival Weibull parametrik. Setiap modalitas (vibrasi, temperatur, gap/displacement) dikodekan terpisah lalu digabung via cross-modal attention; head Weibull memprediksi parameter shape (k) dan scale (lambda) sehingga menghasilkan estimasi RUL titik sekaligus kurva reliabilitas, dan menangani pengamatan tersensor kanan secara alami. Validasi pada data sintetis, data industri nyata (gear-press), dan benchmark ATE (turbofan); CMA-WFT mengalahkan RF, SVM, RNN-Weibull, dan LSTM-Weibull (akurasi RT 84% vs 72%).</t>
+          <t>Penelitian ini memprediksi Remaining Useful Life (RUL) baterai lithium-ion menggunakan dua arsitektur deep learning hybrid: CLDNN (CNN+LSTM+DNN) dan Temporal Transformer (Transformer+LSTM). Memakai dataset Toyota Research Institute berisi 124 sel LFP/graphite yang disiklus hingga gagal, model dioptimasi dengan Bayesian hyperparameter tuning dan menghasilkan MAE 84,012 (CLDNN) serta 85,134 (TT), mengalahkan beberapa pendekatan mapan dengan perbaikan MAPE 4,01-7,12%.</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
         <is>
-          <t>Memberi contoh integrasi multisensor + transformer + survival Weibull yang menangani data tersensor kanan sekaligus mengkuantifikasi ketidakpastian (kurva reliabilitas) - sangat dekat dengan kebutuhan metode tesis, meski domainnya liner press/turbofan (bukan membran).</t>
+          <t>Mendemonstrasikan bahwa arsitektur hybrid CNN-LSTM dan Transformer-LSTM yang dioptimasi Bayesian dapat memprediksi RUL baterai (dalam jumlah siklus) secara akurat dan efisien untuk BMS; menjadi baseline deep learning RUL non-censored yang relevan sebagai pembanding bagi tesis yang menambahkan lapisan survival analysis.</t>
         </is>
       </c>
     </row>
@@ -3443,40 +3443,40 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Graph neural network-based remaining useful life prediction of milling tools using multi-sensor data</t>
+          <t>Prediction of Remaining Useful Life of Aero-engines Based on CNN-LSTM-Attention</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Kumar et al.</t>
+          <t>Deng et al.</t>
         </is>
       </c>
       <c r="E62" s="2" t="n">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Discover Applied Sciences</t>
+          <t>International Journal of Computational Intelligence Systems</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>Scopus Q2 (SCImago SJR 2024)</t>
+          <t>Scopus Q2 (SCImago SJR Best Quartile)</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s42452-026-08390-x</t>
+          <t>https://doi.org/10.1007/s44196-024-00639-w</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>Paper mengusulkan pipeline deep learning berbasis graph untuk prediksi RUL/keausan pahat milling CNC memakai sinyal getaran, beban spindel, dan gaya potong. Fitur time-domain dan frequency-domain diubah menjadi graph dengan sisi korelasi dan temporal, lalu tiga arsitektur GNN (GCN, GRN, GAT) dilatih dengan Random Forest Regressor dan hyperparameter tuning Optuna/Bayesian Optimization pada 120 run pemesinan.</t>
+          <t>Penelitian ini mengusulkan metode prediksi Remaining Useful Life (RUL) mesin pesawat berbasis deep learning yang menggabungkan CNN untuk ekstraksi fitur lokal dari data sensor multivariabel, LSTM untuk pemodelan dependensi temporal, dan mekanisme self-attention agar LSTM lebih fokus pada fitur penting hasil rekonstruksi CNN. Model dilatih dan diuji pada empat subset dataset NASA C-MAPSS (FD001-FD004) dengan target RUL piecewise linear berambang 100 dan sliding window 40, lalu divalidasi melalui studi ablasi dan perbandingan model. Hasil terbaik diperoleh model usulan dengan RMSE 15.977 (FD001), 14.452 (FD002), 13.907 (FD003), dan 16.637 (FD004), mengungguli CNN, LSTM, CNN-LSTM, BP, GRU, CNN-GRU, DCNN, dan TCNN.</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr">
         <is>
-          <t>Menyediakan kerangka evaluasi terpadu GNN (GCN/GRN/GAT) untuk RUL pahat milling dengan konstruksi graph korelasi-temporal yang lebih sparse dan interpretable; relevan bagi tesis sebagai contoh model representasi struktur/temporal dan sebagai pembanding non-survival.</t>
+          <t>Menunjukkan bahwa penambahan mekanisme self-attention pada arsitektur CNN-LSTM meningkatkan akurasi point-prediction RUL pada benchmark C-MAPSS, namun tanpa pemodelan data tersensor, kuantifikasi ketidakpastian, maupun keputusan pemeliharaan. Paper ini memperkuat argumen tesis bahwa integrasi survival analysis (censoring/hazard) dengan deep learning masih merupakan celah terbuka; domainnya aero-engine, bukan membran/RO.</t>
         </is>
       </c>
     </row>
@@ -3486,25 +3486,25 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>C. Bayesian &amp; Uncertainty</t>
+          <t>B. Deep Learning RUL</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Weibull Variational Autoencoder for Remaining Useful Life Prediction</t>
+          <t>Research on Prediction Method of Gear Pump Remaining Useful Life Based on DCAE and Bi-LSTM</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Yu et al.</t>
+          <t>Wang et al.</t>
         </is>
       </c>
       <c r="E63" s="2" t="n">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>Quality and Reliability Engineering International</t>
+          <t>Symmetry</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
@@ -3514,17 +3514,17 @@
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1002/qre.70386</t>
+          <t>https://doi.org/10.3390/sym14061111</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>Studi mengusulkan Weibull Variational Autoencoder (WVAE) untuk prediksi RUL, yaitu VAE yang latent space-nya mengikuti distribusi Weibull sehingga bisa mempelajari bentuk dan skala distribusi kegagalan langsung dari riwayat kegagalan. Fungsi loss gabungan MSE ditambah negative log-likelihood Weibull menjaga akurasi titik sekaligus kesetiaan distribusi, sementara Monte Carlo Dropout memberi interval kepercayaan 95%. Validasi pada data simulasi (tiga tipe kegagalan: infant mortality, random, wear-out, dengan tiga tingkat noise) dan dataset lapangan Backblaze hard drive menunjukkan WVAE konsisten dengan distribusi kegagalan historis dan mengalahkan baseline pada CRPS.</t>
+          <t>Artikel mengusulkan skema prediksi RUL pompa roda gigi (gear pump) hidraulik yang menggabungkan deep convolutional autoencoder (DCAE) dan multi-layer Bi-LSTM. Tahap pertama membangun health indicator (HI) secara tanpa supervisi: DCAE 1D simetris mengekstraksi fitur sinyal getaran, SOM mereduksi vektor fitur C6 (100 dimensi), dan HI dihitung sebagai minimum quantization error (MQE). Tahap kedua memakai nilai HI sebagai label otomatis (self-labeling) pada data getaran mentah untuk melatih Bi-LSTM end-to-end yang keluarannya adalah nilai RUL. Validasi memakai data siklus hidup penuh dari uji hidup dipercepat 4 pompa roda gigi; HI yang dibangun unggul pada monotonicity/korelasi dan prediksi RUL lebih akurat dibanding dua metode pelabelan pembanding.</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr">
         <is>
-          <t>Menyatukan model berbasis distribusi Weibull dengan arsitektur deep generative untuk RUL, tepat pada sumbu metode tesis (survival/Weibull + kuantifikasi ketidakpastian), namun sengaja mengabaikan observasi tersensor (right-censored) dan domainnya bukan membran.</t>
+          <t>Memberi contoh pipeline DL end-to-end untuk RUL (autoencoder konvolusional + SOM untuk HI self-labeled + Bi-LSTM) pada peralatan dengan dataset siklus hidup yang langka melalui uji hidup dipercepat, relevan sebagai pembanding metode DL RUL dan strategi small-data pada tesis. Namun tidak memodelkan data tersensor/survival, tidak mengkuantifikasi ketidakpastian, dan domainnya bukan membran/RO, sehingga tidak menutup celah integrasi survival analysis + DL tersensor pada membran desalinasi.</t>
         </is>
       </c>
     </row>
@@ -3534,25 +3534,25 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>E. Membrane/RO/Desalination</t>
+          <t>C. Bayesian &amp; Uncertainty</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Applying machine learning and AI for nanofiltration membranes water applications: a review</t>
+          <t>Remaining Useful Life Prognosis of Aircraft Brakes</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Abuhabib et al.</t>
+          <t>Λούτας et al.</t>
         </is>
       </c>
       <c r="E64" s="2" t="n">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>Water Science &amp; Technology</t>
+          <t>International Journal of Prognostics and Health Management</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
@@ -3562,17 +3562,17 @@
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.2166/wst.2026.234</t>
+          <t>https://doi.org/10.36001/ijphm.2022.v13i1.3072</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>Review penerapan machine learning (ML)/AI pada membran nanofiltrasi (NF) untuk aplikasi air, dengan menganalisis 100 publikasi NF-ML selama 10 tahun. Membahas tiga domain: optimasi fabrikasi, prediksi kinerja (flux, rejection, permeability), dan diagnosis/mitigasi fouling. Menyoroti tantangan kelangkaan dan heterogenitas data, kurangnya validasi eksternal, dan prospek reinforcement learning untuk kontrol adaptif real-time serta kerangka hybrid ML-mekanistik.</t>
+          <t>Studi mengevaluasi tiga metodologi prognostik probabilistik data-driven untuk estimasi Remaining Useful Life (dalam satuan remaining flights) sistem rem pesawat komersial yang dipantau ketebalannya secara kontinu: Bayesian Linear Regression (BLR), Non-Homogeneous Hidden Semi Markov Model (NHHSMM), dan Bootstrapped Artificial Neural Network (BNN). Dataset riil (blind) dari armada wide-body sebuah maskapai Eropa berisi 27 riwayat degradasi lengkap, dan model diuji via skema leave-two-out termasuk tiga brake outlier. BNN paling unggul (MAPE &lt;10%, CI tersempit, Prognostic Horizon 0,75) dan bahkan model paling sederhana pun membutuhkan kuantifikasi ketidakpastian untuk menangani stochasticity dan outlier.</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr">
         <is>
-          <t>Memetakan algoritma ML yang berlaku untuk membran (NF/RO): RF, XGBoost, CNN, LSTM, RL, ANFIS, GP; serta menegaskan kelangkaan data, transferabilitas, dan kuantifikasi ketidakpastian sebagai celah riset. Relevan bagi tesis yang menerapkan ML pada RUL membran dan menghadapi small-data.</t>
+          <t>Menunjukkan pentingnya kuantifikasi ketidakpastian (interval kepercayaan) dalam prognostik RUL pada dataset riil kecil, dan bahwa model reliabilitas semi-Markov (NHHSMM) maupun Bayesian (BLR) dapat dibandingkan secara langsung - relevan bagi pilar C (Bayesian &amp; Uncertainty) pada tesis; namun tidak memodelkan data tersensor (riwayat tidak lengkap justru dibuang) dan domainnya rem pesawat, bukan membran.</t>
         </is>
       </c>
     </row>
@@ -3582,45 +3582,45 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>E. Membrane/RO/Desalination</t>
+          <t>B. Deep Learning RUL</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Prediction of Reverse Osmosis Membrane Fouling Using Machine Learning: MLR, ANN, and SVM at a Seawater Desalination Plant</t>
+          <t>A Genetic Algorithm Optimized RNN-LSTM Model for Remaining Useful Life Prediction of Turbofan Engine</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Kherraf et al.</t>
+          <t>Chui et al.</t>
         </is>
       </c>
       <c r="E65" s="2" t="n">
-        <v>2026</v>
+        <v>2021</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>Eng, Advances in Engineering</t>
+          <t>Electronics</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>Scopus Q2 (SCImago SJR 2024)</t>
+          <t>Scopus Q2 (SCImago SJR Best Quartile)</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/eng7030106</t>
+          <t>https://doi.org/10.3390/electronics10030285</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>Studi membandingkan MLR, ANN, dan SVR untuk memprediksi transmembrane pressure (TMP, indikator fouling) di pabrik desalinasi air laut Boujdour dari lima parameter input (temperatur, turbiditas, pH, konduktivitas, laju alir umpan). Dataset asli 195 pengamatan harian; karena tidak ada stempel waktu, masalah dibingkai sebagai state-to-TMP (bukan peramalan kronologis). SMOGN menambah data latih menjadi ~1961 sampel dengan set uji 39 observasi nyata yang bebas kebocoran; SVR memberi akurasi terbaik (R2 test=0,435) namun dengan interval bootstrap 95 % yang lebar.</t>
+          <t>Studi mengusulkan model prediksi RUL turbofan engine dengan menggabungkan RNN (prediksi jangka pendek) dan LSTM (jangka panjang) yang bobot gabungannya dioptimasi NSGA-II. Fitur diekstraksi dengan dekomposisi dua tahap CEEMD-WPT dan enam fitur statistik (Shannon entropy, kurtosis, skewness, peak-to-peak, standar deviasi, mean). Pada dataset benchmark C-MAPSS-TD (FD001-FD004), model mencapai RMSE rata-rata 17,2 dengan validasi 10-fold cross-validation, mengalahkan RNN/LSTM tunggal dan 10 karya pembanding.</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr">
         <is>
-          <t>Menegaskan bahwa prediksi fouling/tekanan membran di domain RO masih terbatas oleh ukuran data dan tidak adanya indeks waktu, dan menyoroti pentingnya kuantifikasi ketidakpastian serta kontrol kebocoran data; tidak memakai survival/pencensoringan maupun RUL.</t>
+          <t>Preseden metode RUL berbasis deep learning yang kuat dan tervalidasi silang, namun domainnya turbofan engine dan tidak memodelkan penyensoran/survival, sehingga bagi tesis hanya berperan sebagai pembanding metode (Pendukung), bukan irisan metode+domain.</t>
         </is>
       </c>
     </row>
@@ -3635,20 +3635,20 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>LSTM and Transformers based methods for Remaining Useful Life Prediction considering Censored Data</t>
+          <t>Developing Deep Survival Model for Remaining Useful Life Estimation Based on Convolutional and Long Short-Term Memory Neural Networks</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Noot et al.</t>
+          <t>Chu et al.</t>
         </is>
       </c>
       <c r="E66" s="2" t="n">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>International Journal of Prognostics and Health Management</t>
+          <t>Wireless Communications and Mobile Computing</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
@@ -3658,17 +3658,17 @@
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.36001/ijphm.2025.v16i2.4260</t>
+          <t>https://doi.org/10.1155/2020/8814658</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>Artikel mengadaptasi arsitektur Transformer DAST dan LSTM menjadi ordinal regression (OR) agar mampu menangani data tersensor kanan (right-censored) pada prediksi RUL. OR mengodekan RUL menjadi vektor status masa depan (0/1/-) dan loss BCE dimask pada koordinat tersensor, memungkinkan pemanfaatan unit yang diganti sebelum gagal. Dievaluasi pada C-MAPSS dan N-CMAPSS dengan tingkat pencensoringan artifisial 0-90%, metode ini setara SOTA pada data tanpa sensor dan lebih unggul pada pencensoringan tinggi pada dataset besar; conformal prediction dipakai untuk interval kepercayaan.</t>
+          <t>Studi mengusulkan model deep survival terintegrasi yang menggabungkan 1D temporal convolution dan LSTM untuk mengekstraksi pola tersembunyi dari data sensor deret waktu, lalu memakai regresi (MSE) dan analisis survival berbasis distribusi Weibull diskrit untuk mengestimasi RUL sekaligus probabilitas kegagalan. Dievaluasi pada dataset simulasi degradasi turbofan NASA CMAPSS (FD001-FD004). Model menghasilkan kurva survival Kaplan-Meier dengan interval kepercayaan dan mengklaim performa unggul pada kondisi operasi kompleks (FD002 dan FD004).</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr">
         <is>
-          <t>Menunjukkan cara menggabungkan arsitektur deep-learning RUL modern (LSTM/Transformer) dengan penanganan data tersensor eksplisit dan interval prediksi conformal - dua komponen inti metode tesis, meski domainnya bukan membran.</t>
+          <t>Preseden langsung integrasi deep learning (CNN+LSTM) dengan distibusi Weibull diskrit dan log-likelihood tersensor untuk RUL: menunjukkan cara lulusan jaringan menghasilkan parameter alpha/beta Weibull dan kurva survival ber-CI, sangat dekat dengan kebutuhan tesis; namun domainnya turbofan dan bukan membran/RO.</t>
         </is>
       </c>
     </row>
@@ -3678,25 +3678,25 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>D. Small-data/Transfer/Hierarchical</t>
+          <t>C. Bayesian &amp; Uncertainty</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Remaining Useful Life Prediction of Turbine Engines Using Multimodal Transfer Learning</t>
+          <t>Uncertainty in Prognostics and Systems Health Management</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Li et al.</t>
+          <t>Sankararaman et al.</t>
         </is>
       </c>
       <c r="E67" s="2" t="n">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>Machines</t>
+          <t>International Journal of Prognostics and Health Management</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
@@ -3706,17 +3706,17 @@
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/machines13090789</t>
+          <t>https://doi.org/10.36001/ijphm.2015.v6i4.2319</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>Paper mengusulkan DMFR (Deep Multimodal Fine-tuning Regression), framework RUL yang menggabungkan multimodal (deret waktu + citra recurrence plot) dengan transfer learning dua tahap (pre-training terawasi + fine-tuning). Dievaluasi pada dataset NASA C-MAPSS turbofan dengan 12 tugas transfer lintas operating condition/fault mode; model melaporkan RMSE/MAE/R2/Score terbaik antar baseline (CNN, DNN, GRU, LSTM, RNN, TCN) dan menyajikan interval kepercayaan 95%.</t>
+          <t>Artikel ulasan ini memaparkan berbagai aspek kuantifikasi dan manajemen ketidakpastian pada prognostik dan systems health management. Penulis membedakan interpretasi ketidakpastian pada testing-based dan condition-based health management, menunjukkan bahwa prediksi RUL lebih bermakna pada condition-based monitoring dan harus diperlakukan sebagai masalah propagasi ketidakpastian. Empat aktivitas diuraikan: representasi/interpretasi, kuantifikasi, propagasi, dan manajemen ketidakpastian, dilengkapi contoh numerik dan analisis sensitivitas global.</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr">
         <is>
-          <t>Menunjukkan bagaimana transfer learning dan fusi multimodal menangani skenario small-sample dan cross-condition pada RUL; relevan bagi tesis RUL membran yang menghadapi kelangkaan data dan pergeseran kondisi operasi (cocok untuk strategi small-data/transfer).</t>
+          <t>Kerangka konseptual untuk menginterpretasi, mengkuantifikasi, dan mempropagasi ketidakpastian dalam RUL - relevan sebagai landasan pilar C dan justifikasi mengapa distribusi RUL tidak boleh diasumsikan (mis. Gaussian). Tidak memodelkan data tersensor dan bukan studi empiris domain.</t>
         </is>
       </c>
     </row>
@@ -3726,25 +3726,25 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>E. Membrane/RO/Desalination</t>
+          <t>A. Survival Analysis &amp; Censored Data</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Predictive Framework for Membrane Fouling in Full-Scale Membrane Bioreactors (MBRs): Integrating AI-Driven Feature Engineering and Explainable AI (XAI)</t>
+          <t>Data-driven Prognostics with Predictive Uncertainty Estimation using Ensemble of Deep Ordinal Regression Models</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Liang et al.</t>
+          <t>Tv et al.</t>
         </is>
       </c>
       <c r="E68" s="2" t="n">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Processes</t>
+          <t>International Journal of Prognostics and Health Management</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
@@ -3754,17 +3754,17 @@
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/pr13082352</t>
+          <t>https://doi.org/10.36001/ijphm.2019.v10i4.2612</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>Studi membangun kerangka prediksi fouling membran pada membrane bioreactor (MBR) skala penuh dengan menggabungkan feature engineering berbasis AI dan explainable AI (XAI). Target prediksi diubah menjadi specific flux (flux/TMP) sebagai indikator permeabilitas, ditambah COD removal efficiency sebagai indikator kinerja biologis, dan moving average untuk menangkap dinamika fouling temporal. Dari 194 catatan harian, CatBoost paling akurat (R2 = 0,8374), dan SHAP mengidentifikasi rasio F/M dan MLSS sebagai variabel paling berpengaruh.</t>
+          <t>Paper mengusulkan LSTM-OR, pendekatan ordinal regression berbasis deep LSTM untuk estimasi RUL yang secara alami dapat memanfaatkan instan operasional tersensor (censored) saat melatih, plus kuantifikasi ketidakpastian prediktif lewat ensemble LSTM-OR. Dievaluasi pada benchmark turbofan C-MAPSS FD001 dan FD004 dengan skenario pc = 0/50/70/90%. Ordinal regression dengan censored (ORC) mengalahkan metric regression (MR) saat jumlah instan gagal sedikit, contoh 15,1% (FD001) dan 3,6% (FD004) perbaikan RMSE pada pc=90%.</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr">
         <is>
-          <t>Memberi bukti bahwa prediksi degradasi membran (specific flux) yang interpretable dapat dilakukan pada data lapangan skala penuh yang kecil dan bising, relevan dengan sumbu domain tesis (membran/fouling dan small-data), namun tidak memakai RUL eksplisit, survival analysis, maupun pencensoringan.</t>
+          <t>Menunjukkan cara menggabungkan data tersensor ke pelatihan model deep learning RUL lewat label masking pada ordinal regression — inti tesis karena tesis membutuhkan penanganan data tersensor. Juga menyediakan kuantifikasi ketidakpastian ensemble (ESD) yang terbukti berkorelasi dengan error, relevan untuk keputusan maintenance berbasis risiko.</t>
         </is>
       </c>
     </row>
@@ -3774,25 +3774,25 @@
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>F. DSS &amp; Predictive Maintenance (IS)</t>
+          <t>D. Small-data/Transfer/Hierarchical</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Survival Analysis-Based System for Predictive Maintenance Optimization</t>
+          <t>Transfer Learning with Deep Recurrent Neural Networks for Remaining Useful Life Estimation</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Coutinho et al.</t>
+          <t>Zhang et al.</t>
         </is>
       </c>
       <c r="E69" s="2" t="n">
-        <v>2025</v>
+        <v>2018</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>SN Computer Science</t>
+          <t>Applied Sciences</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
@@ -3802,17 +3802,17 @@
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s42979-025-04291-9</t>
+          <t>https://doi.org/10.3390/app8122416</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>Artikel ini menyajikan kerangka predictive maintenance modular berbasis survival analysis untuk mengestimasi RUL komponen industri, digabung algoritma optimasi penjadwalan Simulated Annealing. Empat model survival dievaluasi (Cox PH, Random Survival Forest, Gradient Boosting Survival Analysis, Survival SVM), dengan GBSA paling robust karena tahan overfitting dan mampu menangkap degradasi nonlinier. Kerangka divalidasi pada data degradasi elektroda las (nyata) dan dataset sintetis Microsoft Azure, menurunkan downtime 25% dibanding metode tak teroptimasi.</t>
+          <t>Makalah mengusulkan algoritma transfer learning berbasis jaringan BLSTM (bi-directional LSTM) untuk estimasi RUL, guna mengatasi kelangkaan data kegagalan pada prognostik berbasis data. Model dilatih pada dataset sumber yang besar namun terkait, lalu di-fine-tune dengan dataset target yang kecil (parameter-transfer). Eksperimen ekstensif (360 kali) pada benchmark C-MAPSS menunjukkan transfer learning umumnya meningkatkan akurasi, kecuali transfer dari kondisi operasi majemuk (6 kondisi) ke tunggal (1 kondisi) yang menyebabkan negative transfer.</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr">
         <is>
-          <t>Langkah paling dekat dengan tesis: secara eksplisit mengintegrasikan data tersensor ke dalam model survival (Cox PH/RSF/GBSA/Survival SVM) untuk RUL, lalu menghubungkannya ke keputusan penjadwalan pemeliharaan. Relevan sebagai preseden Inti-Metode; celah yang tersisa adalah belum diterapkan pada membran/RO dan belum memakai deep learning survival (mis. DeepHit/DeepSurv) pada data membran.</t>
+          <t>Memberikan bukti kuat bahwa transfer learning menangani masalah small-data pada RUL - sangat relevan dengan tantangan kecilnya data kegagalan membran; namun tidak memodelkan pencensoringan dan domainnya mesin turbofan.</t>
         </is>
       </c>
     </row>
@@ -3827,20 +3827,20 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Remaining Useful Life Prediction for Power Storage Electronic Components Based on Fractional Weibull Process and Shock Poisson Model</t>
+          <t>Statistical Characterization of the State-of-Health of Lithium-Ion Batteries with Weibull Distribution Function, A Consideration of Random Effect Model in Charge Capacity Decay Estimation</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Song et al.</t>
+          <t>Ossai et al.</t>
         </is>
       </c>
       <c r="E70" s="2" t="n">
-        <v>2024</v>
+        <v>2017</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>Fractal and Fractional</t>
+          <t>Batteries</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
@@ -3850,17 +3850,17 @@
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/fractalfract8080485</t>
+          <t>https://doi.org/10.3390/batteries3040032</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>Studi mengusulkan model degradation-threshold-shock (DTS) untuk memprediksi RUL komponen penyimpanan daya (baterai LiFePO4 dan superkapasitor). Proses steady degradation dimodelkan dengan fractional Weibull process (fWp) yang memiliki long-range dependence dan heavy tail, sedangkan guncangan acak (shock) dimodelkan dengan non-homogeneous compound Poisson process (NHCP) berintensitas naik; koefisien drift dan diffusion diperbarui secara acak untuk menangkap gangguan lingkungan. RUL dihitung via Monte Carlo sebagai waktu first-passage melewati failure threshold (FT), dan model mengalahkan CNN, EMD-GRU, DTS-BM, serta adaptive FBM pada protokol DST dan UDDS.</t>
+          <t>Studi mengestimasi keandalan baterai lithium-ion melalui model degradasi sigmoidal multifase dengan parameter efek acak (nonlinear mixed effect model, NLMEM) dan fungsi distribusi Weibull. Parameter diestimasi dengan MLE dan algoritma Stochastic Approximation Expectation Maximization (SAEM), lalu RUL dan State-of-Health (SOH) diprediksi pada ambang 70% End-of-Life (EOL). Prediksi kapasitas menyimpang &lt;2% dari data eksperimen NASA dan menghasilkan SOH dengan R^2 0,9846-0,9852.</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr">
         <is>
-          <t>Memberi preseden model degradasi stokastik berbasis Weibull + ambang kegagalan (first-passage) untuk RUL sebagai alternatif dari deep learning - relevan dengan pilar A (analisis failure-time) pada tesis, tetapi tidak memodelkan data tersensor dan domainnya komponen penyimpanan daya, bukan membran.</t>
+          <t>Preseden kuat poros survival/Weibull di tesis: pemodelan distribusi waktu-ke-gagal dengan Weibull pada ambang kegagalan, plus penggunaan model efek acak (hierarchical) untuk menangani ketidakpastian lintas-unit. Tidak ada machine learning dan domainnya baterai, bukan membran.</t>
         </is>
       </c>
     </row>
@@ -3870,25 +3870,25 @@
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>B. Deep Learning RUL</t>
+          <t>A. Survival Analysis &amp; Censored Data</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Hybrid Neural Networks for Enhanced Predictions of Remaining Useful Life in Lithium-Ion Batteries</t>
+          <t>Thermal Cycling Life Prediction of Sn-3.0Ag-0.5Cu Solder Joint Using Type-I Censored Data</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Rastegarpanah et al.</t>
+          <t>Mi et al.</t>
         </is>
       </c>
       <c r="E71" s="2" t="n">
-        <v>2024</v>
+        <v>2014</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>Batteries</t>
+          <t>The Scientific World JOURNAL</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
@@ -3898,17 +3898,17 @@
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/batteries10030106</t>
+          <t>https://doi.org/10.1155/2014/807693</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>Penelitian ini memprediksi Remaining Useful Life (RUL) baterai lithium-ion menggunakan dua arsitektur deep learning hybrid: CLDNN (CNN+LSTM+DNN) dan Temporal Transformer (Transformer+LSTM). Memakai dataset Toyota Research Institute berisi 124 sel LFP/graphite yang disiklus hingga gagal, model dioptimasi dengan Bayesian hyperparameter tuning dan menghasilkan MAE 84,012 (CLDNN) serta 85,134 (TT), mengalahkan beberapa pendekatan mapan dengan perbaikan MAPE 4,01-7,12%.</t>
+          <t>Studi memprediksi umur lelah sambungan solder Sn-3.0Ag-0.5Cu (SAC305) BGA dan FBGA dari uji thermal cycling dipercepat. Data waktu-ke-gagal diproses sebagai data tersensor interval Tipe-I dengan estimasi maksimum likelihood (MLE) dua-parameter Weibull; hasilnya dibandingkan dengan model Engelmaier yang dimodifikasi dan perangkat lunak Minitab/Matlab. Metode data tersensor Tipe-I memberi umur paling tinggi dan akurat (Nf BGA 3104,5; FBGA 3185 siklus) serta panduan pemeliharaan/penggantian.</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr">
         <is>
-          <t>Mendemonstrasikan bahwa arsitektur hybrid CNN-LSTM dan Transformer-LSTM yang dioptimasi Bayesian dapat memprediksi RUL baterai (dalam jumlah siklus) secara akurat dan efisien untuk BMS; menjadi baseline deep learning RUL non-censored yang relevan sebagai pembanding bagi tesis yang menambahkan lapisan survival analysis.</t>
+          <t>Memberi contoh lengkap formulasi likelihood untuk data tersensor Tipe-I (indikator delta_i) dengan Weibull pada uji life-test dipercepat - inti metodologis pilar A tesis. Namun tidak ada machine learning, tidak ada RUL probabilistik, dan domainnya elektronik (bukan membran/RO).</t>
         </is>
       </c>
     </row>
@@ -3918,45 +3918,45 @@
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>B. Deep Learning RUL</t>
+          <t>A. Survival Analysis &amp; Censored Data</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Prediction of Remaining Useful Life of Aero-engines Based on CNN-LSTM-Attention</t>
+          <t>Machine Learning for Covariate-Driven Changes in Weibull Scale Parameter</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Deng et al.</t>
+          <t>Ramadhan et al.</t>
         </is>
       </c>
       <c r="E72" s="2" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>International Journal of Computational Intelligence Systems</t>
+          <t>Engineering Technology &amp; Applied Science Research</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>Scopus Q2 (SCImago SJR Best Quartile)</t>
+          <t>Scopus Q3 (SCImago SJR 2024)</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1007/s44196-024-00639-w</t>
+          <t>https://doi.org/10.48084/etasr.15186</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>Penelitian ini mengusulkan metode prediksi Remaining Useful Life (RUL) mesin pesawat berbasis deep learning yang menggabungkan CNN untuk ekstraksi fitur lokal dari data sensor multivariabel, LSTM untuk pemodelan dependensi temporal, dan mekanisme self-attention agar LSTM lebih fokus pada fitur penting hasil rekonstruksi CNN. Model dilatih dan diuji pada empat subset dataset NASA C-MAPSS (FD001-FD004) dengan target RUL piecewise linear berambang 100 dan sliding window 40, lalu divalidasi melalui studi ablasi dan perbandingan model. Hasil terbaik diperoleh model usulan dengan RMSE 15.977 (FD001), 14.452 (FD002), 13.907 (FD003), dan 16.637 (FD004), mengungguli CNN, LSTM, CNN-LSTM, BP, GRU, CNN-GRU, DCNN, dan TCNN.</t>
+          <t>Paper mengusulkan kerangka hybrid yang menggabungkan machine learning terawasi dengan analisis survival Weibull untuk RUL, dengan premis bahwa parameter skala Weibull (lambda, characteristic life) bukan statis melainkan fungsi dinamis dari kovariat operasional/lingkungan. Berbagai model ML (LightGBM, XGBoost, RF, SVR, LR) dilatih memprediksi lambda sebagai fungsi kovariat dan dibandingkan dengan baseline AFT-OLS. Pada C-MAPSS FD001, LightGBM terbaik (MAE 25,44 siklus; RMSE 34,21) dan mengalahkan AFT klasik.</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr">
         <is>
-          <t>Menunjukkan bahwa penambahan mekanisme self-attention pada arsitektur CNN-LSTM meningkatkan akurasi point-prediction RUL pada benchmark C-MAPSS, namun tanpa pemodelan data tersensor, kuantifikasi ketidakpastian, maupun keputusan pemeliharaan. Paper ini memperkuat argumen tesis bahwa integrasi survival analysis (censoring/hazard) dengan deep learning masih merupakan celah terbuka; domainnya aero-engine, bukan membran/RO.</t>
+          <t>Sangat selaras dengan sumbu metode tesis: memakai survival analysis Weibull, memodelkan lambda sebagai fungsi kovariat (relevan untuk covariate membran), dan menawarkan kuantifikasi ketidakpastian dengan menempelkan prediksi ML ke kerangka probabilistic Weibull. Memberi preseden penting untuk menggabungkan ML + survival, meski domainnya turbofan dan bukan penanganan censoring eksplisit.</t>
         </is>
       </c>
     </row>
@@ -3966,45 +3966,45 @@
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>E. Membrane/RO/Desalination</t>
+          <t>B. Deep Learning RUL</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Bio-inspired MXene membranes for enhanced separation and anti-fouling in oil-in-water emulsions: SHAP explainability ML</t>
+          <t>Improved CNN-LSTM Bearing Remaining Useful Life Prediction Based on the Weibull Loss Function</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>Baig et al.</t>
+          <t>Zhang et al.</t>
         </is>
       </c>
       <c r="E73" s="2" t="n">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>Cleaner Water</t>
+          <t>Proceedings of Engineering and Technology Innovation</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>Scopus Q2 (SCImago SJR Best Quartile)</t>
+          <t>Scopus Q3 (SCImago SJR 2024)</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.clwat.2024.100041</t>
+          <t>https://doi.org/10.46604/peti.2025.15348</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>Studi mengevaluasi fouling dan efisiensi separasi tiga membran berbasis MXene pada keramik (MX-CM, PDMX-CM, SPDMX-CM) untuk emulsi minyak-dalam-air. Pendekatan menggabungkan uji reliabilitas/kenormalan/stationeritas (ADF, PP, Jarque-Bera, ACF/PACF) dengan machine learning yang dijelaskan memakai SHAP untuk menafsirkan kontribusi fitur (Cycle, PDMX-CM, MX-CM). SPDMX-CM paling stabil dan tahan fouling, tetapi studi tidak memprediksi RUL maupun waktu kegagalan.</t>
+          <t>Studi mengusulkan KCNN-LSTM, model deep learning untuk prediksi RUL bantalan gelinding yang menggabungkan arsitektur CNN-LSTM dengan fungsi loss berbasis Weibull (knowledge-informed) dan health index (HI) eksponensial. Loss gabungan MSE + lambda*Weibull CDF memaksa prediksi mengikuti karakteristik degradasi fisik (accelerated wear). Dievaluasi pada PHM2012 dan XJTU-SY; model mengungguli CNN-LSTM, LSTM, Bi-LSTM, dan FNN berloss Weibull, mencapai RMSE 0,071 dan Score 0,821 (PHM2012) serta RMSE 0,054 (XJTU-SY).</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr">
         <is>
-          <t>Memberi konteks domain membran/desalinasi dan fouling sekaligus contoh penanganan small-data (15 observasi) dengan uji reliabilitas/stationeritas dan explainability SHAP - berguna bagi tesis untuk justifikasi praproses dan interpretabilitas, tetapi tanpa RUL/survival/pencensoringan sehingga tidak menyumbang kerangka inti.</t>
+          <t>Menunjukkan integrasi pengetahuan fisik (distribusi Weibull) ke dalam loss deep learning RUL - pola 'knowledge-informed' yang relevan untuk tesis; namun domain bantalan (bukan membran) dan tidak menangani data tersensor.</t>
         </is>
       </c>
     </row>
@@ -4014,45 +4014,45 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>E. Membrane/RO/Desalination</t>
+          <t>A. Survival Analysis &amp; Censored Data</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Graphene Based Membrane Modified Silica Nanoparticles for Seawater Desalination and Wastewater Treatment: Salt Rejection and Dyes</t>
+          <t>Reliable prediction of industrial components Remaining Useful Life using Cox and Weibull models: A Comparative Study</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>Munasir et al.</t>
+          <t>Abdelhafid et al.</t>
         </is>
       </c>
       <c r="E74" s="2" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>International Journal of Engineering</t>
+          <t>Data &amp; Metadata</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>Scopus Q2 (SCImago SJR Best Quartile)</t>
+          <t>Scopus Q3 (SCImago SJR 2024)</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.5829/ije.2023.36.04a.09</t>
+          <t>https://doi.org/10.56294/dm20251102</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>Studi eksperimental material fabrikasi membran komposit graphene oxide-silika (GO/SiO2-Psf) dengan metode phase inversion untuk desalinasi air laut dan pengolahan air limbah zat warna. Variasi konsentrasi TEOS (0,6; 0,8; 1,0; 1,2 ml) diteliti terhadap sifat hidrofilik (contact angle), morfologi (SEM), kristalinitas (XRD), gugus fungsi (FTIR), antibakteri (E. coli &amp; S. aureus), salt-rejection NaCl, dan filtrasi metilen biru. Membran TEOS 0,8 ml paling optimal: salt-rejection 67,22% dan adsorpsi metilen biru terbaik.</t>
+          <t>Studi komparatif dua teknik analisis survival - Cox Proportional Hazards (semi-parametrik) dan model Weibull (parametrik) - untuk prediksi RUL komponen industri pada dataset AI4I 2020 Predictive Maintenance. Memakai Kaplan-Meier, uji log-rank, dan validasi C-index/AIC; Cox PH unggul (C-index 0,9148 vs 0,639; AIC 4184,44 vs 5915,87) dan menangani kovariat berganda serta data tersensor (right-censored) secara efektif.</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr">
         <is>
-          <t>Memberi konteks domain tentang jenis, fabrikasi, dan karakteristik kinerja membran (GO/SiO2-Psf) untuk desalinasi/zat warna - sebagai latar belakang material membran pada tesis, tetapi sama sekali tidak menyentuh RUL, prognostik, survival analysis, atau pencensoringan.</t>
+          <t>Menyediakan justifikasi metodologis langsung untuk tesis: Cox PH lebih tepat daripada Weibull murni ketika terdapat banyak kovariat sensor dan data tersensor, dan menghasilkan RUL yang terindividualisasi per unit. Menjadi kerangka survival analysis acuan yang dapat dikombinasikan dengan machine learning.</t>
         </is>
       </c>
     </row>
@@ -4062,45 +4062,45 @@
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>E. Membrane/RO/Desalination</t>
+          <t>B. Deep Learning RUL</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Machine Learning Implementation in Membrane Bioreactor Systems: Progress, Challenges, and Future Perspectives: A Review</t>
+          <t>A physical knowledge-guided and data-driven framework for remaining useful life prediction (The case of turbofan engines)</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>Frontistis et al.</t>
+          <t>Zheng et al.</t>
         </is>
       </c>
       <c r="E75" s="2" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>Environments</t>
+          <t>Journal of Advanced Mechanical Design Systems and Manufacturing</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>Scopus Q2 (SCImago SJR Best Quartile)</t>
+          <t>Scopus Q3 (SCImago SJR Best Quartile)</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/environments10070127</t>
+          <t>https://doi.org/10.1299/jamdsm.2025jamdsm0044</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>Review kritis penerapan machine learning pada sistem membrane bioreactor (MBR) untuk pengolahan air limbah lanjut. Membahas algoritma ML (ANN, SVM, RF, RL, PLSR, ANFIS, DL), aplikasinya untuk prediksi fouling membran (TMP/flux), kontrol dan optimasi, serta deteksi dini kegagalan, sekaligus mengidentifikasi tantangan data quality, interpretabilitas, dan transferabilitas. Menutup dengan rekomendasi integrasi big data/IoT dan model hybrid.</t>
+          <t>Paper mengusulkan kerangka hybrid PhyMix-UQ-RUL untuk prediksi RUL dan kuantifikasi ketidakpastian, dengan memperluas WTTE-RNN (Weibull Time-To-Event RNN) memakai multi-scale dilated CNN (MsDCNN), LSTM, dan gated degradation stage regularization (GDSR). GDSR membatasi parameter bentuk Weibull (beta) sesuai teori bathtub curve dan loss dual-regularization menjaga kesesuaian fisik. Divalidasi pada C-MAPSS (FD001-FD004) dan N-CMAPSS DS02, model memberi prediksi kompetitif sekaligus prediksi interval dan kurva survival.</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr">
         <is>
-          <t>Memetakan lanskap penerapan ML pada domain membran/desalinasi (fouling, TMP, kontrol) dan secara eksplisit menandai transferabilitas, keterbatasan data berlabel, dan interpretabilitas sebagai celah riset - ketiganya concern langsung tesis pada RUL membran.</t>
+          <t>Sangat dekat dengan inti tesis: memakai WTTE-RNN berbasis survival/Weibull dengan loss log-likelihood yang menangani status kegagalan (censoring), sekaligus mengkuantifikasi ketidakpastian (PI, PDF, kurva survival). Memberi blueprint metodologis untuk menggabungkan deep learning + survival + uncertainty, meski domainnya turbofan, bukan membran.</t>
         </is>
       </c>
     </row>
@@ -4110,45 +4110,45 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>B. Deep Learning RUL</t>
+          <t>C. Bayesian &amp; Uncertainty</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Research on Prediction Method of Gear Pump Remaining Useful Life Based on DCAE and Bi-LSTM</t>
+          <t>Bayesian neural networks for uncertainty quantification in remaining useful life prediction of systems with sensor monitoring</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>Wang et al.</t>
+          <t>Ochella et al.</t>
         </is>
       </c>
       <c r="E76" s="2" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>Symmetry</t>
+          <t>Advances in Mechanical Engineering</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>Scopus Q2 (SCImago SJR Best Quartile)</t>
+          <t>Scopus Q3 (SCImago SJR Best Quartile)</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/sym14061111</t>
+          <t>https://doi.org/10.1177/16878132241239802</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>Artikel mengusulkan skema prediksi RUL pompa roda gigi (gear pump) hidraulik yang menggabungkan deep convolutional autoencoder (DCAE) dan multi-layer Bi-LSTM. Tahap pertama membangun health indicator (HI) secara tanpa supervisi: DCAE 1D simetris mengekstraksi fitur sinyal getaran, SOM mereduksi vektor fitur C6 (100 dimensi), dan HI dihitung sebagai minimum quantization error (MQE). Tahap kedua memakai nilai HI sebagai label otomatis (self-labeling) pada data getaran mentah untuk melatih Bi-LSTM end-to-end yang keluarannya adalah nilai RUL. Validasi memakai data siklus hidup penuh dari uji hidup dipercepat 4 pompa roda gigi; HI yang dibangun unggul pada monotonicity/korelasi dan prediksi RUL lebih akurat dibanding dua metode pelabelan pembanding.</t>
+          <t>Penelitian ini mengusulkan deep Bayesian Neural Network (BNN) dengan Monte Carlo (MC) dropout untuk memprediksi RUL sistem ber-sensor sekaligus mengkuantifikasi ketidakpastian. Model dilatih dan diuji pada dataset NASA C-MAPSS FD001 (100 unit turbofan run-to-failure, 21 sensor). Hasil menunjukkan prediksi mean RUL beserta credible interval 95% yang menangkap ketidakpastian aleatorik dan epistemik, dengan rata-rata CI sekitar 38,78 siklus.</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr">
         <is>
-          <t>Memberi contoh pipeline DL end-to-end untuk RUL (autoencoder konvolusional + SOM untuk HI self-labeled + Bi-LSTM) pada peralatan dengan dataset siklus hidup yang langka melalui uji hidup dipercepat, relevan sebagai pembanding metode DL RUL dan strategi small-data pada tesis. Namun tidak memodelkan data tersensor/survival, tidak mengkuantifikasi ketidakpastian, dan domainnya bukan membran/RO, sehingga tidak menutup celah integrasi survival analysis + DL tersensor pada membran desalinasi.</t>
+          <t>Menyediakan kerangka RUL probabilistik (bukan point estimate) yang secara eksplisit mengkuantifikasi ketidakpastian aleatorik dan epistemik melalui MC dropout, sehingga memberi informasi kuantitatif (mean + credible interval) untuk perencanaan maintenance. Relevan ke tesis sebagai contoh deep learning yang menghasilkan distribusi prediksi, namun belum menangani data tersensor secara survival.</t>
         </is>
       </c>
     </row>
@@ -4158,45 +4158,45 @@
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>C. Bayesian &amp; Uncertainty</t>
+          <t>A. Survival Analysis &amp; Censored Data</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Remaining Useful Life Prognosis of Aircraft Brakes</t>
+          <t>General Log-Linear Weibull Model Combining Vibration and Temperature Characteristics for Remaining Useful Life Prediction of Rolling Element Bearings</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Λούτας et al.</t>
+          <t>Lv et al.</t>
         </is>
       </c>
       <c r="E77" s="2" t="n">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>International Journal of Prognostics and Health Management</t>
+          <t>Shock and Vibration</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>Scopus Q2 (SCImago SJR Best Quartile)</t>
+          <t>Scopus Q3 (SCImago SJR Best Quartile)</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.36001/ijphm.2022.v13i1.3072</t>
+          <t>https://doi.org/10.1155/2020/8829823</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>Studi mengevaluasi tiga metodologi prognostik probabilistik data-driven untuk estimasi Remaining Useful Life (dalam satuan remaining flights) sistem rem pesawat komersial yang dipantau ketebalannya secara kontinu: Bayesian Linear Regression (BLR), Non-Homogeneous Hidden Semi Markov Model (NHHSMM), dan Bootstrapped Artificial Neural Network (BNN). Dataset riil (blind) dari armada wide-body sebuah maskapai Eropa berisi 27 riwayat degradasi lengkap, dan model diuji via skema leave-two-out termasuk tiga brake outlier. BNN paling unggul (MAPE &lt;10%, CI tersempit, Prognostic Horizon 0,75) dan bahkan model paling sederhana pun membutuhkan kuantifikasi ketidakpastian untuk menangani stochasticity dan outlier.</t>
+          <t>Studi membangun model general log-linear Weibull (GLL-Weibull) multivariat yang menggabungkan fitur getaran (RRMS) dan suhu relatif sebagai kovariat internal untuk memprediksi RUL bantalan gelinding. Kedua sinyal difuzzifikasi (operator 'excessive vibrations' dan 'overheated bearing') lalu parameter model diestimasi dengan maximum likelihood estimation (MLE) yang secara eksplisit memasukkan sampel tersuspensi (sensor) ke fungsi likelihood. Validasi pada PRONOSTIA dan bantalan HSS turbin angin nyata menunjukkan akurasi superior (MAPE rata-rata 10,76% vs SVM 26,73% dan CNN 11,68%).</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr">
         <is>
-          <t>Menunjukkan pentingnya kuantifikasi ketidakpastian (interval kepercayaan) dalam prognostik RUL pada dataset riil kecil, dan bahwa model reliabilitas semi-Markov (NHHSMM) maupun Bayesian (BLR) dapat dibandingkan secara langsung - relevan bagi pilar C (Bayesian &amp; Uncertainty) pada tesis; namun tidak memodelkan data tersensor (riwayat tidak lengkap justru dibuang) dan domainnya rem pesawat, bukan membran.</t>
+          <t>Buku teks inti untuk tesis: menunjukkan secara konkret bagaimana model survival (Weibull dengan kovariat) dan data tersuspensi diintegrasikan untuk RUL, termasuk estimasi parameter MLE dan PDF RUL. Menjadi acuan langsung untuk memadukan informasi getaran+suhu (analog multi-sensor) dalam hazard model.</t>
         </is>
       </c>
     </row>
@@ -4206,45 +4206,45 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>E. Membrane/RO/Desalination</t>
+          <t>A. Survival Analysis &amp; Censored Data</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Cellulose acetate from palm oil bunch waste for forward osmosis membrane in desalination of brackish water</t>
+          <t>Remaining Useful Life Prediction of Bearing with Vibration Signals Based on a Novel Indicator</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>Saiful et al.</t>
+          <t>Wu et al.</t>
         </is>
       </c>
       <c r="E78" s="2" t="n">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>Results in Engineering</t>
+          <t>Shock and Vibration</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>Scopus Q2 (SCImago SJR Best Quartile)</t>
+          <t>Scopus Q3 (SCImago SJR Best Quartile)</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1016/j.rineng.2022.100611</t>
+          <t>https://doi.org/10.1155/2017/8927937</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>Paper mengembangkan membran forward osmosis (FO) berbasis selulosa asetat yang disintesis dari limbah tandan buah kosong kelapa sawit (POEFB) untuk desalinasi air payau, sebagai alternatif pasokan air darurat. Membran difabrikasi dengan metode phase inversion, dikarakterisasi (FTIR, SEM, porositas, swelling, sudut kontak, sifat mekanik), dan diuji pada modul FO dengan draw solution sukrosa. Membran menghasilkan fluks air 2,22 L/m2h (1 M) hingga 4,2 L/m2h (2 M) dengan rejeksi garam 96% dan kualitas air memenuhi baku mutu air minum.</t>
+          <t>Paper mengembangkan metode hybrid untuk prediksi RUL bearing yang menggabungkan generalized Weibull failure rate function (WFRF) dengan radial basis function (RBF) neural network. Sebuah indikator baru, power value pada sensitive frequency band (SFB), diusulkan untuk melacak degradasi; deret indikator difit dengan generalized WFRF untuk meredam noise, lalu RBF memprediksi life percentage dan RUL. Divalidasi pada dataset bearing IMS dengan akurasi hingga 99,42%.</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr">
         <is>
-          <t>Memberi konteks domain membran/desalinasi (bahan dan kinerja membran) tanpa menyentuh RUL, censoring, atau prediksi. Relevan hanya sebagai latar domain tesis: menunjukkan objek membran dan tantangan fouling/kinerja yang menjadi sasaran prediksi RUL, tetapi tidak memberi kontribusi metode.</t>
+          <t>Memberi preseden penggunaan fungsi hazard keluarga Weibull sebagai model degradasi untuk RUL (sumbu metode survival), relevan dengan tesis yang memakai survival analysis. Namun tidak menangani data tersensor secara eksplisit dan tidak mengkuantifikasi ketidakpastian, sehingga gap utama tetap terbuka.</t>
         </is>
       </c>
     </row>
@@ -4254,45 +4254,45 @@
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>B. Deep Learning RUL</t>
+          <t>C. Bayesian &amp; Uncertainty</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>A Genetic Algorithm Optimized RNN-LSTM Model for Remaining Useful Life Prediction of Turbofan Engine</t>
+          <t>Explainable Data-Driven Method Combined with Bayesian Filtering for Remaining Useful Lifetime Prediction of Aircraft Engines Using NASA CMAPSS Datasets</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>Chui et al.</t>
+          <t>Faisal Maulana, Andrew Starr, Agusmian Partogi Ompusunggu</t>
         </is>
       </c>
       <c r="E79" s="2" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>Electronics</t>
+          <t>Machines (MDPI), 11(2):163, ISSN 2075-1702</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>Scopus Q2 (SCImago SJR Best Quartile)</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.3390/electronics10030285</t>
+          <t>https://doi.org/10.3390/machines11020163</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>Studi mengusulkan model prediksi RUL turbofan engine dengan menggabungkan RNN (prediksi jangka pendek) dan LSTM (jangka panjang) yang bobot gabungannya dioptimasi NSGA-II. Fitur diekstraksi dengan dekomposisi dua tahap CEEMD-WPT dan enam fitur statistik (Shannon entropy, kurtosis, skewness, peak-to-peak, standar deviasi, mean). Pada dataset benchmark C-MAPSS-TD (FD001-FD004), model mencapai RMSE rata-rata 17,2 dengan validasi 10-fold cross-validation, mengalahkan RNN/LSTM tunggal dan 10 karya pembanding.</t>
+          <t>Paper ini mengembangkan metodologi dan algoritma prognostik explainable untuk memprediksi Remaining Useful Life (RUL) mesin pesawat memakai dataset terbaru NASA CMAPSS (N-CMAPSS) 2021 (DS02 dan DS03). Alur enam fase meliputi seleksi fitur metrik hibrida (robustness, monotonicity, prognosability), estimasi Health Index via regresi logistik (GLM), dan pembaruan model prognostik secara rekursif dengan Unscented Kalman Filter (UKF) untuk mengekstrapolasi EoL/RUL beserta kuantifikasi ketidakpastian (1000 lintasan, confidence interval 90%). Hasilnya memberi RMSE 34,5-55,6% lebih baik dibanding teknik black-box pada dataset yang sama, dengan transparansi dan UQ sebagai pembeda utama.</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr">
         <is>
-          <t>Preseden metode RUL berbasis deep learning yang kuat dan tervalidasi silang, namun domainnya turbofan engine dan tidak memodelkan penyensoran/survival, sehingga bagi tesis hanya berperan sebagai pembanding metode (Pendukung), bukan irisan metode+domain.</t>
+          <t>Menyediakan alternatif prognostik yang transparan dan terkalibrasi ketidakpastiannya (90% CI) untuk data run-to-failure yang terbatas, mengisi celah antara metode deep learning black-box dan kebutuhan industri safety-critical. Meski domain aplikasinya kedirgantaraan (bukan membran), pendekatan hybrid filtering + UQ dapat ditransfer ke RUL membran RO, namun paper ini tidak memodelkan data tersensor (censoring) maupun survival/Weibull secara aktual.</t>
         </is>
       </c>
     </row>
@@ -4307,1123 +4307,71 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Developing Deep Survival Model for Remaining Useful Life Estimation Based on Convolutional and Long Short-Term Memory Neural Networks</t>
+          <t>Bearing Remaining Useful Life Prediction Based on Naive Bayes and Weibull Distributions</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>Chu et al.</t>
+          <t>Nannan Zhang, Lifeng Wu, Zhonghua Wang, Yong Guan</t>
         </is>
       </c>
       <c r="E80" s="2" t="n">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>Wireless Communications and Mobile Computing</t>
+          <t>Entropy (MDPI), 20(12):944, ISSN 1099-4300</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>Scopus Q2 (SCImago SJR Best Quartile)</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>https://doi.org/10.1155/2020/8814658</t>
+          <t>https://doi.org/10.3390/e20120944</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>Studi mengusulkan model deep survival terintegrasi yang menggabungkan 1D temporal convolution dan LSTM untuk mengekstraksi pola tersembunyi dari data sensor deret waktu, lalu memakai regresi (MSE) dan analisis survival berbasis distribusi Weibull diskrit untuk mengestimasi RUL sekaligus probabilitas kegagalan. Dievaluasi pada dataset simulasi degradasi turbofan NASA CMAPSS (FD001-FD004). Model menghasilkan kurva survival Kaplan-Meier dengan interval kepercayaan dan mengklaim performa unggul pada kondisi operasi kompleks (FD002 dan FD004).</t>
+          <t>Paper ini mengusulkan metode data-driven untuk memprediksi RUL bearing berbasis klasifikasi Naive Bayes (NB) dengan pembentukan fitur degradasi memakai distribusi Weibull yang diperluas (Universal Failure Rate Function, UFRF). Enam belas fitur statistik time-domain diekstraksi dari sinyal vibrasi, lalu diseleksi berdasarkan korelasi terhadap RMS (threshold 0,9 menjadi 6 fitur) dan difit oleh UFRF pada tiga tahap degradasi sebagai input pelatihan NB. Klasifikasi lima kelas (health states + empat tahap degradasi) dihaluskan dengan exponential smoothing untuk menghasilkan prediksi RUL; hasilnya lebih akurat dibanding referensi pada data run-to-failure IMS/Cincinnati. Meski memakai distribusi Weibull dan fungsi hazard (UFRF), metode ini tidak menangani data tersensor (censoring).</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr">
         <is>
-          <t>Preseden langsung integrasi deep learning (CNN+LSTM) dengan distibusi Weibull diskrit dan log-likelihood tersensor untuk RUL: menunjukkan cara lulusan jaringan menghasilkan parameter alpha/beta Weibull dan kurva survival ber-CI, sangat dekat dengan kebutuhan tesis; namun domainnya turbofan dan bukan membran/RO.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="2" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>C. Bayesian &amp; Uncertainty</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>Uncertainty in Prognostics and Systems Health Management</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
-        <is>
-          <t>Sankararaman et al.</t>
-        </is>
-      </c>
-      <c r="E81" s="2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="F81" s="2" t="inlineStr">
-        <is>
-          <t>International Journal of Prognostics and Health Management</t>
-        </is>
-      </c>
-      <c r="G81" s="2" t="inlineStr">
-        <is>
-          <t>Scopus Q2 (SCImago SJR Best Quartile)</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.36001/ijphm.2015.v6i4.2319</t>
-        </is>
-      </c>
-      <c r="I81" s="2" t="inlineStr">
-        <is>
-          <t>Artikel ulasan ini memaparkan berbagai aspek kuantifikasi dan manajemen ketidakpastian pada prognostik dan systems health management. Penulis membedakan interpretasi ketidakpastian pada testing-based dan condition-based health management, menunjukkan bahwa prediksi RUL lebih bermakna pada condition-based monitoring dan harus diperlakukan sebagai masalah propagasi ketidakpastian. Empat aktivitas diuraikan: representasi/interpretasi, kuantifikasi, propagasi, dan manajemen ketidakpastian, dilengkapi contoh numerik dan analisis sensitivitas global.</t>
-        </is>
-      </c>
-      <c r="J81" s="2" t="inlineStr">
-        <is>
-          <t>Kerangka konseptual untuk menginterpretasi, mengkuantifikasi, dan mempropagasi ketidakpastian dalam RUL - relevan sebagai landasan pilar C dan justifikasi mengapa distribusi RUL tidak boleh diasumsikan (mis. Gaussian). Tidak memodelkan data tersensor dan bukan studi empiris domain.</t>
+          <t>Menunjukkan penggunaan Weibull/fungsi hazard (UFRF) untuk memuluskan fitur degradasi sebelum klasifikasi NB guna prediksi RUL. Kaitannya dengan tesis: paper ini satu-satunya dari tiga yang menyentuh 'bahasa' survival analysis (Weibull/hazard), namun tidak memodelkan censoring maupun survival regression, sehingga tetap meninggalkan celah untuk survival analysis dengan data tersensor pada RUL membran.</t>
         </is>
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>A. Survival Analysis &amp; Censored Data</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>Data-driven Prognostics with Predictive Uncertainty Estimation using Ensemble of Deep Ordinal Regression Models</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
-        <is>
-          <t>Tv et al.</t>
-        </is>
-      </c>
-      <c r="E82" s="2" t="n">
-        <v>2019</v>
-      </c>
-      <c r="F82" s="2" t="inlineStr">
-        <is>
-          <t>International Journal of Prognostics and Health Management</t>
-        </is>
-      </c>
-      <c r="G82" s="2" t="inlineStr">
-        <is>
-          <t>Scopus Q2 (SCImago SJR Best Quartile)</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.36001/ijphm.2019.v10i4.2612</t>
-        </is>
-      </c>
-      <c r="I82" s="2" t="inlineStr">
-        <is>
-          <t>Paper mengusulkan LSTM-OR, pendekatan ordinal regression berbasis deep LSTM untuk estimasi RUL yang secara alami dapat memanfaatkan instan operasional tersensor (censored) saat melatih, plus kuantifikasi ketidakpastian prediktif lewat ensemble LSTM-OR. Dievaluasi pada benchmark turbofan C-MAPSS FD001 dan FD004 dengan skenario pc = 0/50/70/90%. Ordinal regression dengan censored (ORC) mengalahkan metric regression (MR) saat jumlah instan gagal sedikit, contoh 15,1% (FD001) dan 3,6% (FD004) perbaikan RMSE pada pc=90%.</t>
-        </is>
-      </c>
-      <c r="J82" s="2" t="inlineStr">
-        <is>
-          <t>Menunjukkan cara menggabungkan data tersensor ke pelatihan model deep learning RUL lewat label masking pada ordinal regression — inti tesis karena tesis membutuhkan penanganan data tersensor. Juga menyediakan kuantifikasi ketidakpastian ensemble (ESD) yang terbukti berkorelasi dengan error, relevan untuk keputusan maintenance berbasis risiko.</t>
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>LEGENDA</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>D. Small-data/Transfer/Hierarchical</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>Transfer Learning with Deep Recurrent Neural Networks for Remaining Useful Life Estimation</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
-        <is>
-          <t>Zhang et al.</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="F83" s="2" t="inlineStr">
-        <is>
-          <t>Applied Sciences</t>
-        </is>
-      </c>
-      <c r="G83" s="2" t="inlineStr">
-        <is>
-          <t>Scopus Q2 (SCImago SJR Best Quartile)</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/app8122416</t>
-        </is>
-      </c>
-      <c r="I83" s="2" t="inlineStr">
-        <is>
-          <t>Makalah mengusulkan algoritma transfer learning berbasis jaringan BLSTM (bi-directional LSTM) untuk estimasi RUL, guna mengatasi kelangkaan data kegagalan pada prognostik berbasis data. Model dilatih pada dataset sumber yang besar namun terkait, lalu di-fine-tune dengan dataset target yang kecil (parameter-transfer). Eksperimen ekstensif (360 kali) pada benchmark C-MAPSS menunjukkan transfer learning umumnya meningkatkan akurasi, kecuali transfer dari kondisi operasi majemuk (6 kondisi) ke tunggal (1 kondisi) yang menyebabkan negative transfer.</t>
-        </is>
-      </c>
-      <c r="J83" s="2" t="inlineStr">
-        <is>
-          <t>Memberikan bukti kuat bahwa transfer learning menangani masalah small-data pada RUL - sangat relevan dengan tantangan kecilnya data kegagalan membran; namun tidak memodelkan pencensoringan dan domainnya mesin turbofan.</t>
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>Ungu</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>paper acuan utama (Gao et al., 2025, IEEE TASE)</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>A. Survival Analysis &amp; Censored Data</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>Statistical Characterization of the State-of-Health of Lithium-Ion Batteries with Weibull Distribution Function, A Consideration of Random Effect Model in Charge Capacity Decay Estimation</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
-        <is>
-          <t>Ossai et al.</t>
-        </is>
-      </c>
-      <c r="E84" s="2" t="n">
-        <v>2017</v>
-      </c>
-      <c r="F84" s="2" t="inlineStr">
-        <is>
-          <t>Batteries</t>
-        </is>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t>Scopus Q2 (SCImago SJR Best Quartile)</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/batteries3040032</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengestimasi keandalan baterai lithium-ion melalui model degradasi sigmoidal multifase dengan parameter efek acak (nonlinear mixed effect model, NLMEM) dan fungsi distribusi Weibull. Parameter diestimasi dengan MLE dan algoritma Stochastic Approximation Expectation Maximization (SAEM), lalu RUL dan State-of-Health (SOH) diprediksi pada ambang 70% End-of-Life (EOL). Prediksi kapasitas menyimpang &lt;2% dari data eksperimen NASA dan menghasilkan SOH dengan R^2 0,9846-0,9852.</t>
-        </is>
-      </c>
-      <c r="J84" s="2" t="inlineStr">
-        <is>
-          <t>Preseden kuat poros survival/Weibull di tesis: pemodelan distribusi waktu-ke-gagal dengan Weibull pada ambang kegagalan, plus penggunaan model efek acak (hierarchical) untuk menangani ketidakpastian lintas-unit. Tidak ada machine learning dan domainnya baterai, bukan membran.</t>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Urutan: Q1 &gt; Q2 &gt; Q3; dalam tier sama, tahun terbaru lebih dulu.</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>A. Survival Analysis &amp; Censored Data</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>Thermal Cycling Life Prediction of Sn-3.0Ag-0.5Cu Solder Joint Using Type-I Censored Data</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>Mi et al.</t>
-        </is>
-      </c>
-      <c r="E85" s="2" t="n">
-        <v>2014</v>
-      </c>
-      <c r="F85" s="2" t="inlineStr">
-        <is>
-          <t>The Scientific World JOURNAL</t>
-        </is>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t>Scopus Q2 (SCImago SJR Best Quartile)</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1155/2014/807693</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t>Studi memprediksi umur lelah sambungan solder Sn-3.0Ag-0.5Cu (SAC305) BGA dan FBGA dari uji thermal cycling dipercepat. Data waktu-ke-gagal diproses sebagai data tersensor interval Tipe-I dengan estimasi maksimum likelihood (MLE) dua-parameter Weibull; hasilnya dibandingkan dengan model Engelmaier yang dimodifikasi dan perangkat lunak Minitab/Matlab. Metode data tersensor Tipe-I memberi umur paling tinggi dan akurat (Nf BGA 3104,5; FBGA 3185 siklus) serta panduan pemeliharaan/penggantian.</t>
-        </is>
-      </c>
-      <c r="J85" s="2" t="inlineStr">
-        <is>
-          <t>Memberi contoh lengkap formulasi likelihood untuk data tersensor Tipe-I (indikator delta_i) dengan Weibull pada uji life-test dipercepat - inti metodologis pilar A tesis. Namun tidak ada machine learning, tidak ada RUL probabilistik, dan domainnya elektronik (bukan membran/RO).</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="2" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>A. Survival Analysis &amp; Censored Data</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>Machine Learning for Covariate-Driven Changes in Weibull Scale Parameter</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
-        <is>
-          <t>Ramadhan et al.</t>
-        </is>
-      </c>
-      <c r="E86" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F86" s="2" t="inlineStr">
-        <is>
-          <t>Engineering Technology &amp; Applied Science Research</t>
-        </is>
-      </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t>Scopus Q3 (SCImago SJR 2024)</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.48084/etasr.15186</t>
-        </is>
-      </c>
-      <c r="I86" s="2" t="inlineStr">
-        <is>
-          <t>Paper mengusulkan kerangka hybrid yang menggabungkan machine learning terawasi dengan analisis survival Weibull untuk RUL, dengan premis bahwa parameter skala Weibull (lambda, characteristic life) bukan statis melainkan fungsi dinamis dari kovariat operasional/lingkungan. Berbagai model ML (LightGBM, XGBoost, RF, SVR, LR) dilatih memprediksi lambda sebagai fungsi kovariat dan dibandingkan dengan baseline AFT-OLS. Pada C-MAPSS FD001, LightGBM terbaik (MAE 25,44 siklus; RMSE 34,21) dan mengalahkan AFT klasik.</t>
-        </is>
-      </c>
-      <c r="J86" s="2" t="inlineStr">
-        <is>
-          <t>Sangat selaras dengan sumbu metode tesis: memakai survival analysis Weibull, memodelkan lambda sebagai fungsi kovariat (relevan untuk covariate membran), dan menawarkan kuantifikasi ketidakpastian dengan menempelkan prediksi ML ke kerangka probabilistic Weibull. Memberi preseden penting untuk menggabungkan ML + survival, meski domainnya turbofan dan bukan penanganan censoring eksplisit.</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="2" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>B. Deep Learning RUL</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>Improved CNN-LSTM Bearing Remaining Useful Life Prediction Based on the Weibull Loss Function</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
-        <is>
-          <t>Zhang et al.</t>
-        </is>
-      </c>
-      <c r="E87" s="2" t="n">
-        <v>2026</v>
-      </c>
-      <c r="F87" s="2" t="inlineStr">
-        <is>
-          <t>Proceedings of Engineering and Technology Innovation</t>
-        </is>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t>Scopus Q3 (SCImago SJR 2024)</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.46604/peti.2025.15348</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan KCNN-LSTM, model deep learning untuk prediksi RUL bantalan gelinding yang menggabungkan arsitektur CNN-LSTM dengan fungsi loss berbasis Weibull (knowledge-informed) dan health index (HI) eksponensial. Loss gabungan MSE + lambda*Weibull CDF memaksa prediksi mengikuti karakteristik degradasi fisik (accelerated wear). Dievaluasi pada PHM2012 dan XJTU-SY; model mengungguli CNN-LSTM, LSTM, Bi-LSTM, dan FNN berloss Weibull, mencapai RMSE 0,071 dan Score 0,821 (PHM2012) serta RMSE 0,054 (XJTU-SY).</t>
-        </is>
-      </c>
-      <c r="J87" s="2" t="inlineStr">
-        <is>
-          <t>Menunjukkan integrasi pengetahuan fisik (distribusi Weibull) ke dalam loss deep learning RUL - pola 'knowledge-informed' yang relevan untuk tesis; namun domain bantalan (bukan membran) dan tidak menangani data tersensor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="2" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>A. Survival Analysis &amp; Censored Data</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Reliable prediction of industrial components Remaining Useful Life using Cox and Weibull models: A Comparative Study</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>Abdelhafid et al.</t>
-        </is>
-      </c>
-      <c r="E88" s="2" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>Data &amp; Metadata</t>
-        </is>
-      </c>
-      <c r="G88" s="2" t="inlineStr">
-        <is>
-          <t>Scopus Q3 (SCImago SJR 2024)</t>
-        </is>
-      </c>
-      <c r="H88" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.56294/dm20251102</t>
-        </is>
-      </c>
-      <c r="I88" s="2" t="inlineStr">
-        <is>
-          <t>Studi komparatif dua teknik analisis survival - Cox Proportional Hazards (semi-parametrik) dan model Weibull (parametrik) - untuk prediksi RUL komponen industri pada dataset AI4I 2020 Predictive Maintenance. Memakai Kaplan-Meier, uji log-rank, dan validasi C-index/AIC; Cox PH unggul (C-index 0,9148 vs 0,639; AIC 4184,44 vs 5915,87) dan menangani kovariat berganda serta data tersensor (right-censored) secara efektif.</t>
-        </is>
-      </c>
-      <c r="J88" s="2" t="inlineStr">
-        <is>
-          <t>Menyediakan justifikasi metodologis langsung untuk tesis: Cox PH lebih tepat daripada Weibull murni ketika terdapat banyak kovariat sensor dan data tersensor, dan menghasilkan RUL yang terindividualisasi per unit. Menjadi kerangka survival analysis acuan yang dapat dikombinasikan dengan machine learning.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="2" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>B. Deep Learning RUL</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>A physical knowledge-guided and data-driven framework for remaining useful life prediction (The case of turbofan engines)</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
-        <is>
-          <t>Zheng et al.</t>
-        </is>
-      </c>
-      <c r="E89" s="2" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F89" s="2" t="inlineStr">
-        <is>
-          <t>Journal of Advanced Mechanical Design Systems and Manufacturing</t>
-        </is>
-      </c>
-      <c r="G89" s="2" t="inlineStr">
-        <is>
-          <t>Scopus Q3 (SCImago SJR Best Quartile)</t>
-        </is>
-      </c>
-      <c r="H89" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1299/jamdsm.2025jamdsm0044</t>
-        </is>
-      </c>
-      <c r="I89" s="2" t="inlineStr">
-        <is>
-          <t>Paper mengusulkan kerangka hybrid PhyMix-UQ-RUL untuk prediksi RUL dan kuantifikasi ketidakpastian, dengan memperluas WTTE-RNN (Weibull Time-To-Event RNN) memakai multi-scale dilated CNN (MsDCNN), LSTM, dan gated degradation stage regularization (GDSR). GDSR membatasi parameter bentuk Weibull (beta) sesuai teori bathtub curve dan loss dual-regularization menjaga kesesuaian fisik. Divalidasi pada C-MAPSS (FD001-FD004) dan N-CMAPSS DS02, model memberi prediksi kompetitif sekaligus prediksi interval dan kurva survival.</t>
-        </is>
-      </c>
-      <c r="J89" s="2" t="inlineStr">
-        <is>
-          <t>Sangat dekat dengan inti tesis: memakai WTTE-RNN berbasis survival/Weibull dengan loss log-likelihood yang menangani status kegagalan (censoring), sekaligus mengkuantifikasi ketidakpastian (PI, PDF, kurva survival). Memberi blueprint metodologis untuk menggabungkan deep learning + survival + uncertainty, meski domainnya turbofan, bukan membran.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>E. Membrane/RO/Desalination</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>An insight into real-time monitoring and predictive modelling of ultrafiltration pretreatment for flow rate and fouling mitigation in seawater desalination</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>Katibi et al.</t>
-        </is>
-      </c>
-      <c r="E90" s="2" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>Desalination and Water Treatment</t>
-        </is>
-      </c>
-      <c r="G90" s="2" t="inlineStr">
-        <is>
-          <t>Scopus Q3 (SCImago SJR Best Quartile)</t>
-        </is>
-      </c>
-      <c r="H90" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.dwt.2025.101386</t>
-        </is>
-      </c>
-      <c r="I90" s="2" t="inlineStr">
-        <is>
-          <t>Studi membangun empat model machine learning (Tree Regression, Ensemble Learning/Random Forest, Neural Network, Gaussian Process Regression) untuk memprediksi laju alir dan resistansi membran pada sistem ultrafiltrasi (UF) yang berperan sebagai pretreatment pabrik desalinasi air laut, memakai 426 hari data operasional (3,7 x 10^6 sampel pada 1 Hz). ENS dan TR mencapai akurasi tertinggi (R2=0,99; RMSE 3,08 dan 3,27 L/min), dan kendali backwash adaptif yang dipandu prediksi menurunkan ekskursi TMP 18 %, menurunkan frekuensi backwash dari 6 jam ke 8 jam, serta memangkas biaya pemeliharaan sekitar 12 %.</t>
-        </is>
-      </c>
-      <c r="J90" s="2" t="inlineStr">
-        <is>
-          <t>Menunjukkan prediksi fouling real-time + keputusan pemeliharaan (penjadwalan backwash dan biaya) di domain membran/desalinasi, sangat relevan bagi sisi domain tesis; namun tidak memodelkan RUL, survival, maupun data tersensor, sehingga hanya menyumbang dimensi domain dan pemeliharaan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="2" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>E. Membrane/RO/Desalination</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>Harnessing machine learning for transmembrane pressure prediction in MBR systems during textile wastewater treatment</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
-        <is>
-          <t>Zahoor et al.</t>
-        </is>
-      </c>
-      <c r="E91" s="2" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F91" s="2" t="inlineStr">
-        <is>
-          <t>Desalination and Water Treatment</t>
-        </is>
-      </c>
-      <c r="G91" s="2" t="inlineStr">
-        <is>
-          <t>Scopus Q3 (SCImago SJR Best Quartile)</t>
-        </is>
-      </c>
-      <c r="H91" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1016/j.dwt.2025.101238</t>
-        </is>
-      </c>
-      <c r="I91" s="2" t="inlineStr">
-        <is>
-          <t>Studi memprediksi transmembrane pressure (TMP) sebagai proksi pemicu fouling membran pada MBR skala bench yang mengolah air limbah tekstil sintetik. Tiga model regresi (Random Forest, Support Vector Regression, dan Lasso) dilatih dengan lima parameter lumpur (B_Car, MLSS, SOUR, DSVI, PSD) dari 58 observasi harian pada tiga siklus membran 19-21 hari, memakai pembagian data kronologis untuk menghindari kebocoran informasi. Random Forest terbaik dengan R2 0,95/0,83 dan RMSE 1,75/3,3 kPa (train/test); B_Car (EPS karbohidrat terikat) adalah prediktor paling penting, dan model dilengkapi interval prediksi 80%.</t>
-        </is>
-      </c>
-      <c r="J91" s="2" t="inlineStr">
-        <is>
-          <t>Menunjukkan bahwa regresi ML dengan data kecil (n=58) dapat memetakan TMP membran MBR dan memberi peringkat parameter lumpur, sebagai jembatan domain (membran/fouling) tanpa memodelkan RUL atau penyensoran. Relevan bagi tesis sebagai baseline domain bahwa proksi degradasi (TMP) dapat diprediksi, namun belum ada formalisasi waktu-ke-gagal/penyensoran.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>E. Membrane/RO/Desalination</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>Predictive Modeling of Brackish Surface Water Quality for Reverse Osmosis Desalination Plants Using Advanced Machine Learning Techniques</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>Lahlou</t>
-        </is>
-      </c>
-      <c r="E92" s="2" t="n">
-        <v>2025</v>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>Science &amp; Technology Asia</t>
-        </is>
-      </c>
-      <c r="G92" s="2" t="inlineStr">
-        <is>
-          <t>Scopus Q3 (SCImago SJR Best Quartile)</t>
-        </is>
-      </c>
-      <c r="H92" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.14456/scitechasia.2025.79</t>
-        </is>
-      </c>
-      <c r="I92" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengembangkan kerangka machine learning untuk memprediksi Water Quality Index (WQI) dan mengklasifikasikan kategori kualitas air (WQC: Excellent/Good/Poor/Unsuitable) pada air permukaan payau yang menjadi umpan pabrik demineralisasi RO (MAROC CENTRAL, Maroko). Dari 10.000 sampel dan 11 parameter fisikokimia, MLP terbaik untuk regresi WQI (R2=98,19 %; MAE=0,0182) dan XGBoost terbaik untuk klasifikasi WQC (akurasi 99,84 %). WQC dikaitkan dengan indikator kinerja RO (feed rate, tekanan, dP, permeate flow, energi).</t>
-        </is>
-      </c>
-      <c r="J92" s="2" t="inlineStr">
-        <is>
-          <t>Menyumbang konteks domain RO/desalinasi berupa pemantauan kualitas air umpan berbasis ML yang mendukung operasi dan pemeliharaan; target prediksi adalah kualitas air (bukan degradasi/RUL membran), sehingga hanya bersifat pendukung.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="2" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>C. Bayesian &amp; Uncertainty</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>Bayesian neural networks for uncertainty quantification in remaining useful life prediction of systems with sensor monitoring</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
-        <is>
-          <t>Ochella et al.</t>
-        </is>
-      </c>
-      <c r="E93" s="2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F93" s="2" t="inlineStr">
-        <is>
-          <t>Advances in Mechanical Engineering</t>
-        </is>
-      </c>
-      <c r="G93" s="2" t="inlineStr">
-        <is>
-          <t>Scopus Q3 (SCImago SJR Best Quartile)</t>
-        </is>
-      </c>
-      <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1177/16878132241239802</t>
-        </is>
-      </c>
-      <c r="I93" s="2" t="inlineStr">
-        <is>
-          <t>Penelitian ini mengusulkan deep Bayesian Neural Network (BNN) dengan Monte Carlo (MC) dropout untuk memprediksi RUL sistem ber-sensor sekaligus mengkuantifikasi ketidakpastian. Model dilatih dan diuji pada dataset NASA C-MAPSS FD001 (100 unit turbofan run-to-failure, 21 sensor). Hasil menunjukkan prediksi mean RUL beserta credible interval 95% yang menangkap ketidakpastian aleatorik dan epistemik, dengan rata-rata CI sekitar 38,78 siklus.</t>
-        </is>
-      </c>
-      <c r="J93" s="2" t="inlineStr">
-        <is>
-          <t>Menyediakan kerangka RUL probabilistik (bukan point estimate) yang secara eksplisit mengkuantifikasi ketidakpastian aleatorik dan epistemik melalui MC dropout, sehingga memberi informasi kuantitatif (mean + credible interval) untuk perencanaan maintenance. Relevan ke tesis sebagai contoh deep learning yang menghasilkan distribusi prediksi, namun belum menangani data tersensor secara survival.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>E. Membrane/RO/Desalination</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>Mesoporous CA/PEG Membrane-Modified TiO2 Nanoparticles with Improved Desalination Performance</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr"/>
-      <c r="E94" s="2" t="n">
-        <v>2024</v>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>Biointerface Research in Applied Chemistry</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr">
-        <is>
-          <t>Scopus Q3 (SCImago SJR Best Quartile)</t>
-        </is>
-      </c>
-      <c r="H94" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.33263/briac142.029</t>
-        </is>
-      </c>
-      <c r="I94" s="2" t="inlineStr">
-        <is>
-          <t>Studi material eksperimental yang mensintesis membran mesoporous CA/PEG (cellulose acetate/polyethylene glycol) dimodifikasi nanopartikel TiO2 (TiO2-NPs) melalui dua metode, yaitu surface coating (SC) dan blending (B), lalu menguji kinerja desalinasi air laut Pantai Kolaka (Sulawesi Tenggara) dengan perangkat RO sederhana 3 tabung (feed + pretreatment pasir/arang/kerikil/serat + membran ber-UV). Karakterisasi XRD, FTIR, dan SEM menunjukkan struktur semikristalin dan keberadaan TiO2 dalam matriks membran. Membran metode B unggul dengan fluks 161,18 L/m2.jam dan rejeksi garam 84%, menurunkan salinitas permeat menjadi 4‰ (kategori air tawar). Artikel tidak mengandung pemodelan RUL, survival analysis/censoring, sensor time-series, machine learning, analisis ketidakpastian, maupun keputusan pemeliharaan.</t>
-        </is>
-      </c>
-      <c r="J94" s="2" t="inlineStr">
-        <is>
-          <t>Membandingkan dua rute modifikasi TiO2-NPs (SC vs B) pada membran CA/PEG untuk desalinasi air laut; menunjukkan metode blending menyisipkan TiO2 ke kisi pori membran sehingga porositas dan kinerja pemisahan garam meningkat; merancang perangkat RO sederhana 3 kompartemen (pretreatment + membran + lampu UV) yang murah untuk masyarakat pesisir dan pulau kecil Indonesia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="2" t="n">
-        <v>94</v>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>E. Membrane/RO/Desalination</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>Multiscale Analysis of Permeable and Impermeable Wall Models for Seawater Reverse Osmosis Desalination</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
-        <is>
-          <t>Yang et al.</t>
-        </is>
-      </c>
-      <c r="E95" s="2" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F95" s="2" t="inlineStr">
-        <is>
-          <t>Separations</t>
-        </is>
-      </c>
-      <c r="G95" s="2" t="inlineStr">
-        <is>
-          <t>Scopus Q3 (SCImago SJR Best Quartile)</t>
-        </is>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/separations10020134</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengusulkan kerangka pemodelan multiskala yang menggabungkan model 3D multi-fisika (dinding permeabel dan dinding impermeabel) pada skala sub-milimeter dengan model sistem pada skala meter untuk desalinasi SWRO. Analisis kuantitatif menunjukkan galat rata-rata koefisien gesek dan bilangan Sherwood memakai model dinding impermeabel &lt; 2 % (gesek) dan &lt; 9 % (Sherwood) dibanding model dinding permeabel, sementara model dinding impermeabel 3x lebih efisien komputasi (25,3 jam vs 77,8 jam).</t>
-        </is>
-      </c>
-      <c r="J95" s="2" t="inlineStr">
-        <is>
-          <t>Menyediakan latar fisik domain (desain feed spacer, mitigasi fouling, concentration polarization) yang menjelaskan mekanisme degradasi membran SWRO; tidak melakukan prediksi berbasis data, RUL, atau survival, sehingga hanya bersifat konteks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>A. Survival Analysis &amp; Censored Data</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>General Log-Linear Weibull Model Combining Vibration and Temperature Characteristics for Remaining Useful Life Prediction of Rolling Element Bearings</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>Lv et al.</t>
-        </is>
-      </c>
-      <c r="E96" s="2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>Shock and Vibration</t>
-        </is>
-      </c>
-      <c r="G96" s="2" t="inlineStr">
-        <is>
-          <t>Scopus Q3 (SCImago SJR Best Quartile)</t>
-        </is>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1155/2020/8829823</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>Studi membangun model general log-linear Weibull (GLL-Weibull) multivariat yang menggabungkan fitur getaran (RRMS) dan suhu relatif sebagai kovariat internal untuk memprediksi RUL bantalan gelinding. Kedua sinyal difuzzifikasi (operator 'excessive vibrations' dan 'overheated bearing') lalu parameter model diestimasi dengan maximum likelihood estimation (MLE) yang secara eksplisit memasukkan sampel tersuspensi (sensor) ke fungsi likelihood. Validasi pada PRONOSTIA dan bantalan HSS turbin angin nyata menunjukkan akurasi superior (MAPE rata-rata 10,76% vs SVM 26,73% dan CNN 11,68%).</t>
-        </is>
-      </c>
-      <c r="J96" s="2" t="inlineStr">
-        <is>
-          <t>Buku teks inti untuk tesis: menunjukkan secara konkret bagaimana model survival (Weibull dengan kovariat) dan data tersuspensi diintegrasikan untuk RUL, termasuk estimasi parameter MLE dan PDF RUL. Menjadi acuan langsung untuk memadukan informasi getaran+suhu (analog multi-sensor) dalam hazard model.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="2" t="n">
-        <v>96</v>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>G. Konteks Indonesia/Air</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Treatment of Coal Mine Acid Water Using Nf270 Membrane as Environmentally Friendly Technology</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>Kiswanto et al.</t>
-        </is>
-      </c>
-      <c r="E97" s="2" t="n">
-        <v>2020</v>
-      </c>
-      <c r="F97" s="2" t="inlineStr">
-        <is>
-          <t>Jurnal Pendidikan IPA Indonesia</t>
-        </is>
-      </c>
-      <c r="G97" s="2" t="inlineStr">
-        <is>
-          <t>Scopus Q3 (SCImago SJR Best Quartile)</t>
-        </is>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.15294/jpii.v9i3.23310</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>Studi eksperimental memakai membran nanofiltrasi NF270 (cross-flow) untuk mengolah air asam tambang batubara PT Bukit Asam menjadi air minum sesuai Permenkes 492/2010. Kinerja dinilai dari pengaruh tekanan (4, 5, 6 bar) terhadap fluks dan laju rejeksi COD, TSS, TDS, dan Fe pada larutan tunggal, campuran, dan sampel nyata. Tekanan optimum 6 bar; fluks turun tajam pada 15 menit pertama akibat fouling dan polarisasi konsentrasi yang dikonfirmasi SEM.</t>
-        </is>
-      </c>
-      <c r="J97" s="2" t="inlineStr">
-        <is>
-          <t>Memberikan bukti domain bahwa degradasi kinerja membran (penurunan fluks karena fouling) adalah proses yang terukur terhadap waktu dan kualitas permeat, namun tidak memodelkan RUL, penyensoran, maupun prediksi sisa umur, sehingga hanya berperan sebagai konteks domain membran/desalinasi bagi tesis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="n">
-        <v>97</v>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>E. Membrane/RO/Desalination</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Enhancing accuracy of membrane fouling prediction using hybrid machine learning models</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>Lim et al.</t>
-        </is>
-      </c>
-      <c r="E98" s="2" t="n">
-        <v>2019</v>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>Desalination and Water Treatment</t>
-        </is>
-      </c>
-      <c r="G98" s="2" t="inlineStr">
-        <is>
-          <t>Scopus Q3 (SCImago SJR Best Quartile)</t>
-        </is>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.5004/dwt.2019.23444</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>Studi mengembangkan model prediksi fouling membran SWRO dengan pendekatan machine learning hibrida: Kalman filter (KF) dirangkai seri dengan ANN atau SVM untuk memprediksi resistansi membran (indikator fouling), dilatih dan diuji pada data operasional pabrik Fujairah selama 18 bulan (522 catatan harian). Model hibrida secara konsisten mengungguli model tunggal; KF-SVM memberi akurasi terbaik (R2 uji 0,82; NSE uji 0,72) dan hasilnya diusulkan untuk menyesuaikan jadwal pembersihan/penggantian membran serta sistem peringatan dini fouling.</t>
-        </is>
-      </c>
-      <c r="J98" s="2" t="inlineStr">
-        <is>
-          <t>Menunjukkan prediksi degradasi membran (resistansi/fouling) dan kaitannya dengan penyesuaian jadwal pembersihan/penggantian di domain SWRO; sangat relevan bagi domain dan dimensi keputusan pemeliharaan tesis, meski tanpa RUL formal, survival, atau pencensoringan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="n">
-        <v>98</v>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>A. Survival Analysis &amp; Censored Data</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Remaining Useful Life Prediction of Bearing with Vibration Signals Based on a Novel Indicator</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>Wu et al.</t>
-        </is>
-      </c>
-      <c r="E99" s="2" t="n">
-        <v>2017</v>
-      </c>
-      <c r="F99" s="2" t="inlineStr">
-        <is>
-          <t>Shock and Vibration</t>
-        </is>
-      </c>
-      <c r="G99" s="2" t="inlineStr">
-        <is>
-          <t>Scopus Q3 (SCImago SJR Best Quartile)</t>
-        </is>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.1155/2017/8927937</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>Paper mengembangkan metode hybrid untuk prediksi RUL bearing yang menggabungkan generalized Weibull failure rate function (WFRF) dengan radial basis function (RBF) neural network. Sebuah indikator baru, power value pada sensitive frequency band (SFB), diusulkan untuk melacak degradasi; deret indikator difit dengan generalized WFRF untuk meredam noise, lalu RBF memprediksi life percentage dan RUL. Divalidasi pada dataset bearing IMS dengan akurasi hingga 99,42%.</t>
-        </is>
-      </c>
-      <c r="J99" s="2" t="inlineStr">
-        <is>
-          <t>Memberi preseden penggunaan fungsi hazard keluarga Weibull sebagai model degradasi untuk RUL (sumbu metode survival), relevan dengan tesis yang memakai survival analysis. Namun tidak menangani data tersensor secara eksplisit dan tidak mengkuantifikasi ketidakpastian, sehingga gap utama tetap terbuka.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="n">
-        <v>99</v>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>C. Bayesian &amp; Uncertainty</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Explainable Data-Driven Method Combined with Bayesian Filtering for Remaining Useful Lifetime Prediction of Aircraft Engines Using NASA CMAPSS Datasets</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>Faisal Maulana, Andrew Starr, Agusmian Partogi Ompusunggu</t>
-        </is>
-      </c>
-      <c r="E100" s="2" t="n">
-        <v>2023</v>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>Machines (MDPI), 11(2):163, ISSN 2075-1702</t>
-        </is>
-      </c>
-      <c r="G100" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/machines11020163</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>Paper ini mengembangkan metodologi dan algoritma prognostik explainable untuk memprediksi Remaining Useful Life (RUL) mesin pesawat memakai dataset terbaru NASA CMAPSS (N-CMAPSS) 2021 (DS02 dan DS03). Alur enam fase meliputi seleksi fitur metrik hibrida (robustness, monotonicity, prognosability), estimasi Health Index via regresi logistik (GLM), dan pembaruan model prognostik secara rekursif dengan Unscented Kalman Filter (UKF) untuk mengekstrapolasi EoL/RUL beserta kuantifikasi ketidakpastian (1000 lintasan, confidence interval 90%). Hasilnya memberi RMSE 34,5-55,6% lebih baik dibanding teknik black-box pada dataset yang sama, dengan transparansi dan UQ sebagai pembeda utama.</t>
-        </is>
-      </c>
-      <c r="J100" s="2" t="inlineStr">
-        <is>
-          <t>Menyediakan alternatif prognostik yang transparan dan terkalibrasi ketidakpastiannya (90% CI) untuk data run-to-failure yang terbatas, mengisi celah antara metode deep learning black-box dan kebutuhan industri safety-critical. Meski domain aplikasinya kedirgantaraan (bukan membran), pendekatan hybrid filtering + UQ dapat ditransfer ke RUL membran RO, namun paper ini tidak memodelkan data tersensor (censoring) maupun survival/Weibull secara aktual.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="n">
-        <v>100</v>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>E. Membrane/RO/Desalination</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Numerical Modelling Assisted Design of a Compact Ultrafiltration (UF) Flat Sheet Membrane Module</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>Mokgadi F Bopape, Tim Van Geel, Abhishek Dutta, Bart Van Der Bruggen, Maurice Stephen Onyango</t>
-        </is>
-      </c>
-      <c r="E101" s="2" t="n">
-        <v>2021</v>
-      </c>
-      <c r="F101" s="2" t="inlineStr">
-        <is>
-          <t>Membranes (MDPI), 11(1):54, ISSN 2077-0375</t>
-        </is>
-      </c>
-      <c r="G101" s="2" t="inlineStr">
-        <is>
-          <t>Q1</t>
-        </is>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/membranes11010054</t>
-        </is>
-      </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>Studi kasus ini merancang dan memodelkan modul membran flat sheet ultrafiltrasi (UF) kompak untuk pengolahan air minum terdesentralisasi menggunakan simulasi Computational Fluid Dynamics (CFD) 3D (ANSYS 19.2). Tujuan utamanya adalah mengkarakterisasi geometri dan memprediksi aliran fluida di dalam modul melalui analisis sensitivitas parametrik (spacer curviness/thickness, panjang &amp; diameter inlet-outlet, permeabilitas, ketebalan, dan luas membran) untuk memperoleh distribusi aliran seragam di atas permukaan membran. Hasil menunjukkan permeate flux sedikit menurun dari 2,81 L/m2h (curviness 0%) ke 2,73 L/m2h (curviness 100%), dan inlet pressure, permeabilitas, ketebalan serta luas membran berpengaruh signifikan terhadap flux.</t>
-        </is>
-      </c>
-      <c r="J101" s="2" t="inlineStr">
-        <is>
-          <t>Memberikan bukti bahwa pemodelan numerik (CFD) dapat memandu desain modul membran UF lokal tanpa ketergantungan pada modul komersial, menurunkan biaya dan kebutuhan eksperimen pada optimasi. Namun paper ini murni desain hidrodinamika steady-state: tidak ada RUL, prognostik, data tersensor, maupun analisis keputusan pemeliharaan - sehingga hanya relevan sebagai konteks domain (membran/UF) bagi tesis.</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="n">
-        <v>101</v>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>A. Survival Analysis &amp; Censored Data</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Bearing Remaining Useful Life Prediction Based on Naive Bayes and Weibull Distributions</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>Nannan Zhang, Lifeng Wu, Zhonghua Wang, Yong Guan</t>
-        </is>
-      </c>
-      <c r="E102" s="2" t="n">
-        <v>2018</v>
-      </c>
-      <c r="F102" s="2" t="inlineStr">
-        <is>
-          <t>Entropy (MDPI), 20(12):944, ISSN 1099-4300</t>
-        </is>
-      </c>
-      <c r="G102" s="2" t="inlineStr">
-        <is>
-          <t>Q2</t>
-        </is>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>https://doi.org/10.3390/e20120944</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>Paper ini mengusulkan metode data-driven untuk memprediksi RUL bearing berbasis klasifikasi Naive Bayes (NB) dengan pembentukan fitur degradasi memakai distribusi Weibull yang diperluas (Universal Failure Rate Function, UFRF). Enam belas fitur statistik time-domain diekstraksi dari sinyal vibrasi, lalu diseleksi berdasarkan korelasi terhadap RMS (threshold 0,9 menjadi 6 fitur) dan difit oleh UFRF pada tiga tahap degradasi sebagai input pelatihan NB. Klasifikasi lima kelas (health states + empat tahap degradasi) dihaluskan dengan exponential smoothing untuk menghasilkan prediksi RUL; hasilnya lebih akurat dibanding referensi pada data run-to-failure IMS/Cincinnati. Meski memakai distribusi Weibull dan fungsi hazard (UFRF), metode ini tidak menangani data tersensor (censoring).</t>
-        </is>
-      </c>
-      <c r="J102" s="2" t="inlineStr">
-        <is>
-          <t>Menunjukkan penggunaan Weibull/fungsi hazard (UFRF) untuk memuluskan fitur degradasi sebelum klasifikasi NB guna prediksi RUL. Kaitannya dengan tesis: paper ini satu-satunya dari tiga yang menyentuh 'bahasa' survival analysis (Weibull/hazard), namun tidak memodelkan censoring maupun survival regression, sehingga tetap meninggalkan celah untuk survival analysis dengan data tersensor pada RUL membran.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="4" t="inlineStr">
-        <is>
-          <t>LEGENDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="5" t="inlineStr">
-        <is>
-          <t>Ungu</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>paper acuan utama (Gao et al., 2025, IEEE TASE)</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Urutan: Q1 &gt; Q2 &gt; Q3; dalam tier sama, tahun terbaru lebih dulu.</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A85" t="inlineStr">
         <is>
           <t>Klasifikasi kuartil: SCImago 'SJR Best Quartile' (turunan Scopus).</t>
         </is>
@@ -5440,7 +4388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -5462,7 +4410,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>101 artikel; 52 Inti; 20 core paper</t>
+          <t>101 assessed; 79 included; 46 Inti; 19 core paper</t>
         </is>
       </c>
     </row>
@@ -5474,7 +4422,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>101 artikel (semua memiliki abstrak)</t>
+          <t>79 artikel (semua memiliki abstrak)</t>
         </is>
       </c>
     </row>
@@ -5510,7 +4458,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>98/101 jurnal terindeks Scopus (sumber: SCImago 'SJR Best Quartile' + SJR 2024; turunan Scopus)</t>
+          <t>77/79 jurnal terindeks Scopus (sumber: SCImago 'SJR Best Quartile' + SJR 2024; turunan Scopus)</t>
         </is>
       </c>
     </row>
@@ -5522,7 +4470,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Q1=59, Q2=25, Q3=14 (tanpa Q4)</t>
+          <t>Q1=52, Q2=18, Q3=7 (tanpa Q4)</t>
         </is>
       </c>
     </row>
@@ -5592,7 +4540,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -5603,16 +4551,6 @@
       </c>
       <c r="B16" t="n">
         <v>6</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>G. Konteks Indonesia/Air</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5626,7 +4564,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J107"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5965,7 +4903,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Ghasemzadeh et al. (2026)</t>
+          <t>Hakami (2026)</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
@@ -5973,29 +4911,29 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr"/>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E9" s="7" t="inlineStr"/>
       <c r="F9" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G9" s="7" t="inlineStr"/>
       <c r="H9" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J9" s="7" t="inlineStr"/>
+      <c r="I9" s="7" t="inlineStr"/>
+      <c r="J9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -6003,37 +4941,41 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Yang et al. (2026)</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr"/>
-      <c r="F10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G10" s="7" t="inlineStr"/>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J10" s="7" t="inlineStr"/>
+          <t>Gao et al. (2025)</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G10" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr"/>
+      <c r="I10" s="7" t="inlineStr"/>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -6041,7 +4983,7 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Alves et al. (2026)</t>
+          <t>Wang et al. (2025)</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
@@ -6049,7 +4991,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D11" s="7" t="inlineStr"/>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E11" s="7" t="inlineStr"/>
       <c r="F11" s="8" t="inlineStr">
         <is>
@@ -6062,11 +5008,7 @@
         </is>
       </c>
       <c r="H11" s="7" t="inlineStr"/>
-      <c r="I11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I11" s="7" t="inlineStr"/>
       <c r="J11" s="8" t="inlineStr">
         <is>
           <t>✓</t>
@@ -6079,7 +5021,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Hakami (2026)</t>
+          <t>E et al. (2025)</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -6098,12 +5040,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr"/>
-      <c r="H12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr"/>
       <c r="I12" s="7" t="inlineStr"/>
       <c r="J12" s="8" t="inlineStr">
         <is>
@@ -6117,41 +5059,29 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Gao et al. (2025)</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>Sun et al. (2025)</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr"/>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr"/>
       <c r="H13" s="7" t="inlineStr"/>
       <c r="I13" s="7" t="inlineStr"/>
-      <c r="J13" s="9" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -6159,7 +5089,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Wang et al. (2025)</t>
+          <t>Andringa et al. (2025)</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -6183,13 +5113,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H14" s="7" t="inlineStr"/>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I14" s="7" t="inlineStr"/>
-      <c r="J14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -6197,7 +5127,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>E et al. (2025)</t>
+          <t>Li et al. (2024)</t>
         </is>
       </c>
       <c r="C15" s="8" t="inlineStr">
@@ -6216,18 +5146,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H15" s="7" t="inlineStr"/>
+      <c r="G15" s="7" t="inlineStr"/>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I15" s="7" t="inlineStr"/>
-      <c r="J15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -6235,7 +5161,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Sun et al. (2025)</t>
+          <t>Wang et al. (2024)</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -6255,7 +5181,11 @@
         </is>
       </c>
       <c r="G16" s="7" t="inlineStr"/>
-      <c r="H16" s="7" t="inlineStr"/>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I16" s="7" t="inlineStr"/>
       <c r="J16" s="7" t="inlineStr"/>
     </row>
@@ -6265,7 +5195,7 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Andringa et al. (2025)</t>
+          <t>Kapuria &amp; Cole (2023)</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -6278,7 +5208,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E17" s="7" t="inlineStr"/>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
           <t>✓</t>
@@ -6303,24 +5237,28 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>Alenezi et al. (2025)</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr"/>
-      <c r="D18" s="7" t="inlineStr"/>
+          <t>Zhou et al. (2023)</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E18" s="7" t="inlineStr"/>
-      <c r="F18" s="7" t="inlineStr"/>
+      <c r="F18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G18" s="7" t="inlineStr"/>
-      <c r="H18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H18" s="7" t="inlineStr"/>
+      <c r="I18" s="7" t="inlineStr"/>
       <c r="J18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
@@ -6329,7 +5267,7 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>Li et al. (2024)</t>
+          <t>Li et al. (2023)</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
@@ -6349,11 +5287,7 @@
         </is>
       </c>
       <c r="G19" s="7" t="inlineStr"/>
-      <c r="H19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H19" s="7" t="inlineStr"/>
       <c r="I19" s="7" t="inlineStr"/>
       <c r="J19" s="7" t="inlineStr"/>
     </row>
@@ -6363,24 +5297,36 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>Jafari et al. (2024)</t>
+          <t>Yang et al. (2022)</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr"/>
-      <c r="D20" s="7" t="inlineStr"/>
-      <c r="E20" s="7" t="inlineStr"/>
+      <c r="D20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G20" s="7" t="inlineStr"/>
-      <c r="H20" s="7" t="inlineStr"/>
-      <c r="I20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="inlineStr"/>
       <c r="J20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
@@ -6389,7 +5335,7 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>Ouadi et al. (2024)</t>
+          <t>Dhada et al. (2022)</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -6397,25 +5343,37 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr"/>
-      <c r="E21" s="7" t="inlineStr"/>
+      <c r="D21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F21" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G21" s="7" t="inlineStr"/>
+      <c r="G21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr"/>
+      <c r="I21" s="7" t="inlineStr"/>
+      <c r="J21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -6423,7 +5381,7 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Wang et al. (2024)</t>
+          <t>Jin et al. (2022)</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -6443,11 +5401,7 @@
         </is>
       </c>
       <c r="G22" s="7" t="inlineStr"/>
-      <c r="H22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H22" s="7" t="inlineStr"/>
       <c r="I22" s="7" t="inlineStr"/>
       <c r="J22" s="7" t="inlineStr"/>
     </row>
@@ -6457,7 +5411,7 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Kapuria &amp; Cole (2023)</t>
+          <t>Ouyang et al. (2022)</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
@@ -6470,26 +5424,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E23" s="7" t="inlineStr"/>
       <c r="F23" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G23" s="7" t="inlineStr"/>
+      <c r="H23" s="7" t="inlineStr"/>
       <c r="I23" s="7" t="inlineStr"/>
       <c r="J23" s="7" t="inlineStr"/>
     </row>
@@ -6499,7 +5441,7 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>Zhou et al. (2023)</t>
+          <t>Yang et al. (2022)</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -6518,7 +5460,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G24" s="7" t="inlineStr"/>
+      <c r="G24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H24" s="7" t="inlineStr"/>
       <c r="I24" s="7" t="inlineStr"/>
       <c r="J24" s="7" t="inlineStr"/>
@@ -6529,7 +5475,7 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Li et al. (2023)</t>
+          <t>Zhang et al. (2022)</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -6548,7 +5494,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G25" s="7" t="inlineStr"/>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H25" s="7" t="inlineStr"/>
       <c r="I25" s="7" t="inlineStr"/>
       <c r="J25" s="7" t="inlineStr"/>
@@ -6559,33 +5509,29 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Ridwan et al. (2023)</t>
-        </is>
-      </c>
-      <c r="C26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D26" s="7" t="inlineStr"/>
+          <t>Chiodo et al. (2022)</t>
+        </is>
+      </c>
+      <c r="C26" s="7" t="inlineStr"/>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E26" s="7" t="inlineStr"/>
-      <c r="F26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G26" s="7" t="inlineStr"/>
-      <c r="H26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J26" s="7" t="inlineStr"/>
+      <c r="F26" s="7" t="inlineStr"/>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr"/>
+      <c r="I26" s="7" t="inlineStr"/>
+      <c r="J26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="7" t="n">
@@ -6593,20 +5539,20 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Yang et al. (2022)</t>
-        </is>
-      </c>
-      <c r="C27" s="7" t="inlineStr"/>
+          <t>Pugalenthi et al. (2022)</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="D27" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E27" s="7" t="inlineStr"/>
       <c r="F27" s="8" t="inlineStr">
         <is>
           <t>✓</t>
@@ -6617,13 +5563,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H27" s="7" t="inlineStr"/>
       <c r="I27" s="7" t="inlineStr"/>
-      <c r="J27" s="7" t="inlineStr"/>
+      <c r="J27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="7" t="n">
@@ -6631,7 +5577,7 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Dhada et al. (2022)</t>
+          <t>Sternharz et al. (2022)</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -6644,26 +5590,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E28" s="7" t="inlineStr"/>
       <c r="F28" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G28" s="7" t="inlineStr"/>
+      <c r="H28" s="7" t="inlineStr"/>
       <c r="I28" s="7" t="inlineStr"/>
       <c r="J28" s="8" t="inlineStr">
         <is>
@@ -6677,7 +5611,7 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Jin et al. (2022)</t>
+          <t>Li et al. (2022)</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -6696,10 +5630,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G29" s="7" t="inlineStr"/>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H29" s="7" t="inlineStr"/>
       <c r="I29" s="7" t="inlineStr"/>
-      <c r="J29" s="7" t="inlineStr"/>
+      <c r="J29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="7" t="n">
@@ -6707,7 +5649,7 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Ouyang et al. (2022)</t>
+          <t>Kong et al. (2022)</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -6729,7 +5671,11 @@
       <c r="G30" s="7" t="inlineStr"/>
       <c r="H30" s="7" t="inlineStr"/>
       <c r="I30" s="7" t="inlineStr"/>
-      <c r="J30" s="7" t="inlineStr"/>
+      <c r="J30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="7" t="n">
@@ -6737,7 +5683,7 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Yang et al. (2022)</t>
+          <t>Zhao et al. (2021)</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -6756,11 +5702,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G31" s="7" t="inlineStr"/>
       <c r="H31" s="7" t="inlineStr"/>
       <c r="I31" s="7" t="inlineStr"/>
       <c r="J31" s="7" t="inlineStr"/>
@@ -6771,7 +5713,7 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Zhang et al. (2022)</t>
+          <t>Wu et al. (2021)</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -6790,11 +5732,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G32" s="7" t="inlineStr"/>
       <c r="H32" s="7" t="inlineStr"/>
       <c r="I32" s="7" t="inlineStr"/>
       <c r="J32" s="7" t="inlineStr"/>
@@ -6805,17 +5743,25 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Chiodo et al. (2022)</t>
-        </is>
-      </c>
-      <c r="C33" s="7" t="inlineStr"/>
+          <t>Kitai et al. (2021)</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="D33" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr"/>
-      <c r="F33" s="7" t="inlineStr"/>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G33" s="8" t="inlineStr">
         <is>
           <t>✓</t>
@@ -6835,7 +5781,7 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Pugalenthi et al. (2022)</t>
+          <t>Mazaev et al. (2021)</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -6861,11 +5807,7 @@
       </c>
       <c r="H34" s="7" t="inlineStr"/>
       <c r="I34" s="7" t="inlineStr"/>
-      <c r="J34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="7" t="n">
@@ -6873,7 +5815,7 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>Sternharz et al. (2022)</t>
+          <t>Berghout et al. (2021)</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -6907,7 +5849,7 @@
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>Li et al. (2022)</t>
+          <t>Jain et al. (2021)</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -6920,7 +5862,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E36" s="7" t="inlineStr"/>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
           <t>✓</t>
@@ -6931,13 +5877,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H36" s="7" t="inlineStr"/>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I36" s="7" t="inlineStr"/>
-      <c r="J36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="7" t="n">
@@ -6945,26 +5891,26 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Kong et al. (2022)</t>
-        </is>
-      </c>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>Ghomghaleh et al. (2020)</t>
+        </is>
+      </c>
+      <c r="C37" s="7" t="inlineStr"/>
       <c r="D37" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E37" s="7" t="inlineStr"/>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G37" s="7" t="inlineStr"/>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr"/>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H37" s="7" t="inlineStr"/>
       <c r="I37" s="7" t="inlineStr"/>
       <c r="J37" s="8" t="inlineStr">
@@ -6979,7 +5925,7 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Zhao et al. (2021)</t>
+          <t>Ren et al. (2020)</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
@@ -7001,7 +5947,11 @@
       <c r="G38" s="7" t="inlineStr"/>
       <c r="H38" s="7" t="inlineStr"/>
       <c r="I38" s="7" t="inlineStr"/>
-      <c r="J38" s="7" t="inlineStr"/>
+      <c r="J38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="7" t="n">
@@ -7009,7 +5959,7 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>Wu et al. (2021)</t>
+          <t>Cheng et al. (2020)</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
@@ -7039,7 +5989,7 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>Kitai et al. (2021)</t>
+          <t>Gao et al. (2020)</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
@@ -7077,7 +6027,7 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Mazaev et al. (2021)</t>
+          <t>Zhang et al. (2020)</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
@@ -7096,11 +6046,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G41" s="7" t="inlineStr"/>
       <c r="H41" s="7" t="inlineStr"/>
       <c r="I41" s="7" t="inlineStr"/>
       <c r="J41" s="7" t="inlineStr"/>
@@ -7111,7 +6057,7 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Berghout et al. (2021)</t>
+          <t>Ma et al. (2020)</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
@@ -7133,11 +6079,7 @@
       <c r="G42" s="7" t="inlineStr"/>
       <c r="H42" s="7" t="inlineStr"/>
       <c r="I42" s="7" t="inlineStr"/>
-      <c r="J42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J42" s="7" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="7" t="n">
@@ -7145,7 +6087,7 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Jain et al. (2021)</t>
+          <t>Cheng et al. (2020)</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
@@ -7158,11 +6100,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E43" s="7" t="inlineStr"/>
       <c r="F43" s="8" t="inlineStr">
         <is>
           <t>✓</t>
@@ -7173,11 +6111,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H43" s="7" t="inlineStr"/>
       <c r="I43" s="7" t="inlineStr"/>
       <c r="J43" s="7" t="inlineStr"/>
     </row>
@@ -7187,10 +6121,14 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Ghomghaleh et al. (2020)</t>
-        </is>
-      </c>
-      <c r="C44" s="7" t="inlineStr"/>
+          <t>Guo et al. (2020)</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
           <t>✓</t>
@@ -7201,19 +6139,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="F44" s="7" t="inlineStr"/>
-      <c r="G44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="inlineStr"/>
       <c r="H44" s="7" t="inlineStr"/>
       <c r="I44" s="7" t="inlineStr"/>
-      <c r="J44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="7" t="n">
@@ -7221,7 +6155,7 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Ren et al. (2020)</t>
+          <t>Benker et al. (2020)</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
@@ -7240,14 +6174,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G45" s="7" t="inlineStr"/>
-      <c r="H45" s="7" t="inlineStr"/>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I45" s="7" t="inlineStr"/>
-      <c r="J45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J45" s="7" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="7" t="n">
@@ -7255,7 +6193,7 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Cheng et al. (2020)</t>
+          <t>Li et al. (2020)</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
@@ -7277,7 +6215,11 @@
       <c r="G46" s="7" t="inlineStr"/>
       <c r="H46" s="7" t="inlineStr"/>
       <c r="I46" s="7" t="inlineStr"/>
-      <c r="J46" s="7" t="inlineStr"/>
+      <c r="J46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="7" t="n">
@@ -7285,7 +6227,7 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Gao et al. (2020)</t>
+          <t>Li et al. (2019)</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
@@ -7304,18 +6246,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G47" s="7" t="inlineStr"/>
       <c r="H47" s="7" t="inlineStr"/>
       <c r="I47" s="7" t="inlineStr"/>
-      <c r="J47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="7" t="n">
@@ -7323,7 +6257,7 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>Zhang et al. (2020)</t>
+          <t>Qin et al. (2019)</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
@@ -7342,10 +6276,22 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G48" s="7" t="inlineStr"/>
-      <c r="H48" s="7" t="inlineStr"/>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I48" s="7" t="inlineStr"/>
-      <c r="J48" s="7" t="inlineStr"/>
+      <c r="J48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="7" t="n">
@@ -7353,7 +6299,7 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Ma et al. (2020)</t>
+          <t>Mao et al. (2019)</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
@@ -7375,7 +6321,11 @@
       <c r="G49" s="7" t="inlineStr"/>
       <c r="H49" s="7" t="inlineStr"/>
       <c r="I49" s="7" t="inlineStr"/>
-      <c r="J49" s="7" t="inlineStr"/>
+      <c r="J49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="7" t="n">
@@ -7383,7 +6333,7 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Cheng et al. (2020)</t>
+          <t>Kraus et al. (2019)</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
@@ -7396,7 +6346,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E50" s="7" t="inlineStr"/>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
           <t>✓</t>
@@ -7407,7 +6361,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H50" s="7" t="inlineStr"/>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I50" s="7" t="inlineStr"/>
       <c r="J50" s="7" t="inlineStr"/>
     </row>
@@ -7417,7 +6375,7 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Guo et al. (2020)</t>
+          <t>Srivastava et al. (2018)</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
@@ -7430,19 +6388,23 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E51" s="7" t="inlineStr"/>
       <c r="F51" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="G51" s="7" t="inlineStr"/>
-      <c r="H51" s="7" t="inlineStr"/>
-      <c r="I51" s="7" t="inlineStr"/>
+      <c r="H51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="J51" s="7" t="inlineStr"/>
     </row>
     <row r="52">
@@ -7451,7 +6413,7 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Benker et al. (2020)</t>
+          <t>Al‐Dahidi et al. (2016)</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
@@ -7464,7 +6426,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr"/>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
           <t>✓</t>
@@ -7475,13 +6441,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H52" s="7" t="inlineStr"/>
       <c r="I52" s="7" t="inlineStr"/>
-      <c r="J52" s="7" t="inlineStr"/>
+      <c r="J52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="7" t="n">
@@ -7489,7 +6455,7 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Li et al. (2020)</t>
+          <t>Tran et al. (2012)</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
@@ -7502,7 +6468,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr"/>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
           <t>✓</t>
@@ -7511,11 +6481,7 @@
       <c r="G53" s="7" t="inlineStr"/>
       <c r="H53" s="7" t="inlineStr"/>
       <c r="I53" s="7" t="inlineStr"/>
-      <c r="J53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J53" s="7" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="7" t="n">
@@ -7523,7 +6489,7 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Li et al. (2019)</t>
+          <t>Reddy et al. (2026)</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
@@ -7536,16 +6502,28 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr"/>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G54" s="7" t="inlineStr"/>
+      <c r="G54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H54" s="7" t="inlineStr"/>
       <c r="I54" s="7" t="inlineStr"/>
-      <c r="J54" s="7" t="inlineStr"/>
+      <c r="J54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="7" t="n">
@@ -7553,7 +6531,7 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Qin et al. (2019)</t>
+          <t>Kumar et al. (2026)</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
@@ -7572,22 +6550,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G55" s="7" t="inlineStr"/>
+      <c r="H55" s="7" t="inlineStr"/>
       <c r="I55" s="7" t="inlineStr"/>
-      <c r="J55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J55" s="7" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="7" t="n">
@@ -7595,7 +6561,7 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Mao et al. (2019)</t>
+          <t>Yu et al. (2026)</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
@@ -7608,20 +6574,24 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E56" s="7" t="inlineStr"/>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G56" s="7" t="inlineStr"/>
+      <c r="G56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H56" s="7" t="inlineStr"/>
       <c r="I56" s="7" t="inlineStr"/>
-      <c r="J56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J56" s="7" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="7" t="n">
@@ -7629,7 +6599,7 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>Kraus et al. (2019)</t>
+          <t>Noot et al. (2025)</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
@@ -7657,13 +6627,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H57" s="7" t="inlineStr"/>
       <c r="I57" s="7" t="inlineStr"/>
-      <c r="J57" s="7" t="inlineStr"/>
+      <c r="J57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="7" t="n">
@@ -7671,7 +6641,7 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>Srivastava et al. (2018)</t>
+          <t>Li et al. (2025)</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
@@ -7690,18 +6660,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G58" s="7" t="inlineStr"/>
-      <c r="H58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J58" s="7" t="inlineStr"/>
+      <c r="G58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="inlineStr"/>
+      <c r="I58" s="7" t="inlineStr"/>
+      <c r="J58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="7" t="n">
@@ -7709,7 +6679,7 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>Al‐Dahidi et al. (2016)</t>
+          <t>Coutinho et al. (2025)</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
@@ -7737,13 +6707,13 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H59" s="7" t="inlineStr"/>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I59" s="7" t="inlineStr"/>
-      <c r="J59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J59" s="7" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="7" t="n">
@@ -7751,7 +6721,7 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Tran et al. (2012)</t>
+          <t>Song et al. (2024)</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
@@ -7764,18 +6734,18 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E60" s="7" t="inlineStr"/>
       <c r="F60" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="G60" s="7" t="inlineStr"/>
-      <c r="H60" s="7" t="inlineStr"/>
+      <c r="H60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I60" s="7" t="inlineStr"/>
       <c r="J60" s="7" t="inlineStr"/>
     </row>
@@ -7785,7 +6755,7 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>Reddy et al. (2026)</t>
+          <t>Rastegarpanah et al. (2024)</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
@@ -7798,28 +6768,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E61" s="7" t="inlineStr"/>
       <c r="F61" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G61" s="7" t="inlineStr"/>
       <c r="H61" s="7" t="inlineStr"/>
       <c r="I61" s="7" t="inlineStr"/>
-      <c r="J61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J61" s="7" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="7" t="n">
@@ -7827,7 +6785,7 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>Kumar et al. (2026)</t>
+          <t>Deng et al. (2024)</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
@@ -7857,7 +6815,7 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>Yu et al. (2026)</t>
+          <t>Wang et al. (2022)</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
@@ -7870,24 +6828,20 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E63" s="7" t="inlineStr"/>
       <c r="F63" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G63" s="7" t="inlineStr"/>
       <c r="H63" s="7" t="inlineStr"/>
       <c r="I63" s="7" t="inlineStr"/>
-      <c r="J63" s="7" t="inlineStr"/>
+      <c r="J63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="7" t="n">
@@ -7895,7 +6849,7 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>Abuhabib et al. (2026)</t>
+          <t>Λούτας et al. (2022)</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
@@ -7903,7 +6857,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr"/>
+      <c r="D64" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E64" s="7" t="inlineStr"/>
       <c r="F64" s="8" t="inlineStr">
         <is>
@@ -7920,16 +6878,8 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="I64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J64" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I64" s="7" t="inlineStr"/>
+      <c r="J64" s="7" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="7" t="n">
@@ -7937,33 +6887,29 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>Kherraf et al. (2026)</t>
-        </is>
-      </c>
-      <c r="C65" s="7" t="inlineStr"/>
-      <c r="D65" s="7" t="inlineStr"/>
+          <t>Chui et al. (2021)</t>
+        </is>
+      </c>
+      <c r="C65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D65" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="E65" s="7" t="inlineStr"/>
       <c r="F65" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G65" s="7" t="inlineStr"/>
       <c r="H65" s="7" t="inlineStr"/>
-      <c r="I65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J65" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I65" s="7" t="inlineStr"/>
+      <c r="J65" s="7" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="7" t="n">
@@ -7971,7 +6917,7 @@
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>Noot et al. (2025)</t>
+          <t>Chu et al. (2020)</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
@@ -8001,11 +6947,7 @@
       </c>
       <c r="H66" s="7" t="inlineStr"/>
       <c r="I66" s="7" t="inlineStr"/>
-      <c r="J66" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J66" s="7" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="7" t="n">
@@ -8013,25 +6955,17 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>Li et al. (2025)</t>
-        </is>
-      </c>
-      <c r="C67" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>Sankararaman et al. (2020)</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr"/>
       <c r="D67" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr"/>
-      <c r="F67" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="F67" s="7" t="inlineStr"/>
       <c r="G67" s="8" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8039,11 +6973,7 @@
       </c>
       <c r="H67" s="7" t="inlineStr"/>
       <c r="I67" s="7" t="inlineStr"/>
-      <c r="J67" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J67" s="7" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="7" t="n">
@@ -8051,7 +6981,7 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Liang et al. (2025)</t>
+          <t>Tv et al. (2019)</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
@@ -8064,23 +6994,23 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E68" s="7" t="inlineStr"/>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G68" s="7" t="inlineStr"/>
-      <c r="H68" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I68" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G68" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="inlineStr"/>
+      <c r="I68" s="7" t="inlineStr"/>
       <c r="J68" s="8" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8093,7 +7023,7 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Coutinho et al. (2025)</t>
+          <t>Zhang et al. (2018)</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
@@ -8106,28 +7036,20 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E69" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="E69" s="7" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G69" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H69" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G69" s="7" t="inlineStr"/>
+      <c r="H69" s="7" t="inlineStr"/>
       <c r="I69" s="7" t="inlineStr"/>
-      <c r="J69" s="7" t="inlineStr"/>
+      <c r="J69" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="7" t="n">
@@ -8135,33 +7057,37 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Song et al. (2024)</t>
-        </is>
-      </c>
-      <c r="C70" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>Ossai et al. (2017)</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr"/>
       <c r="D70" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E70" s="7" t="inlineStr"/>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G70" s="7" t="inlineStr"/>
-      <c r="H70" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G70" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr"/>
       <c r="I70" s="7" t="inlineStr"/>
-      <c r="J70" s="7" t="inlineStr"/>
+      <c r="J70" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="7" t="n">
@@ -8169,26 +7095,30 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>Rastegarpanah et al. (2024)</t>
-        </is>
-      </c>
-      <c r="C71" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>Mi et al. (2014)</t>
+        </is>
+      </c>
+      <c r="C71" s="7" t="inlineStr"/>
       <c r="D71" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="E71" s="7" t="inlineStr"/>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F71" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G71" s="7" t="inlineStr"/>
+      <c r="G71" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H71" s="7" t="inlineStr"/>
       <c r="I71" s="7" t="inlineStr"/>
       <c r="J71" s="7" t="inlineStr"/>
@@ -8199,7 +7129,7 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>Deng et al. (2024)</t>
+          <t>Ramadhan et al. (2026)</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
@@ -8212,13 +7142,21 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr"/>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F72" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="G72" s="7" t="inlineStr"/>
+      <c r="G72" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H72" s="7" t="inlineStr"/>
       <c r="I72" s="7" t="inlineStr"/>
       <c r="J72" s="7" t="inlineStr"/>
@@ -8229,7 +7167,7 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>Baig et al. (2024)</t>
+          <t>Zhang et al. (2026)</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
@@ -8237,21 +7175,25 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D73" s="7" t="inlineStr"/>
-      <c r="E73" s="7" t="inlineStr"/>
-      <c r="F73" s="7" t="inlineStr"/>
+      <c r="D73" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G73" s="7" t="inlineStr"/>
       <c r="H73" s="7" t="inlineStr"/>
-      <c r="I73" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J73" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I73" s="7" t="inlineStr"/>
+      <c r="J73" s="7" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="7" t="n">
@@ -8259,20 +7201,40 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Munasir et al. (2023)</t>
-        </is>
-      </c>
-      <c r="C74" s="7" t="inlineStr"/>
-      <c r="D74" s="7" t="inlineStr"/>
-      <c r="E74" s="7" t="inlineStr"/>
-      <c r="F74" s="7" t="inlineStr"/>
-      <c r="G74" s="7" t="inlineStr"/>
-      <c r="H74" s="7" t="inlineStr"/>
-      <c r="I74" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+          <t>Abdelhafid et al. (2025)</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F74" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G74" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="I74" s="7" t="inlineStr"/>
       <c r="J74" s="7" t="inlineStr"/>
     </row>
     <row r="75">
@@ -8281,7 +7243,7 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>Frontistis et al. (2023)</t>
+          <t>Zheng et al. (2025)</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
@@ -8289,8 +7251,16 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="D75" s="7" t="inlineStr"/>
-      <c r="E75" s="7" t="inlineStr"/>
+      <c r="D75" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F75" s="8" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8301,21 +7271,9 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="H75" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I75" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J75" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="H75" s="7" t="inlineStr"/>
+      <c r="I75" s="7" t="inlineStr"/>
+      <c r="J75" s="7" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="7" t="n">
@@ -8323,7 +7281,7 @@
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>Wang et al. (2022)</t>
+          <t>Ochella et al. (2024)</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
@@ -8342,14 +7300,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G76" s="7" t="inlineStr"/>
+      <c r="G76" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="H76" s="7" t="inlineStr"/>
       <c r="I76" s="7" t="inlineStr"/>
-      <c r="J76" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="J76" s="7" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="7" t="n">
@@ -8357,7 +7315,7 @@
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>Λούτας et al. (2022)</t>
+          <t>Lv et al. (2020)</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
@@ -8370,7 +7328,11 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="E77" s="7" t="inlineStr"/>
+      <c r="E77" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="F77" s="8" t="inlineStr">
         <is>
           <t>✓</t>
@@ -8387,7 +7349,11 @@
         </is>
       </c>
       <c r="I77" s="7" t="inlineStr"/>
-      <c r="J77" s="7" t="inlineStr"/>
+      <c r="J77" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="7" t="n">
@@ -8395,20 +7361,32 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Saiful et al. (2022)</t>
-        </is>
-      </c>
-      <c r="C78" s="7" t="inlineStr"/>
-      <c r="D78" s="7" t="inlineStr"/>
-      <c r="E78" s="7" t="inlineStr"/>
-      <c r="F78" s="7" t="inlineStr"/>
+          <t>Wu et al. (2017)</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F78" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="G78" s="7" t="inlineStr"/>
       <c r="H78" s="7" t="inlineStr"/>
-      <c r="I78" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="I78" s="7" t="inlineStr"/>
       <c r="J78" s="7" t="inlineStr"/>
     </row>
     <row r="79">
@@ -8417,7 +7395,7 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>Chui et al. (2021)</t>
+          <t>Faisal Maulana, Andrew Starr, Agusmian Partogi Ompusunggu (2023)</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
@@ -8436,10 +7414,22 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G79" s="7" t="inlineStr"/>
-      <c r="H79" s="7" t="inlineStr"/>
+      <c r="G79" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
       <c r="I79" s="7" t="inlineStr"/>
-      <c r="J79" s="7" t="inlineStr"/>
+      <c r="J79" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="7" t="n">
@@ -8447,7 +7437,7 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>Chu et al. (2020)</t>
+          <t>Nannan Zhang, Lifeng Wu, Zhonghua Wang, Yong Guan (2018)</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
@@ -8470,812 +7460,44 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="G80" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
+      <c r="G80" s="7" t="inlineStr"/>
       <c r="H80" s="7" t="inlineStr"/>
       <c r="I80" s="7" t="inlineStr"/>
       <c r="J80" s="7" t="inlineStr"/>
     </row>
-    <row r="81">
-      <c r="A81" s="7" t="n">
-        <v>80</v>
-      </c>
-      <c r="B81" s="7" t="inlineStr">
-        <is>
-          <t>Sankararaman et al. (2020)</t>
-        </is>
-      </c>
-      <c r="C81" s="7" t="inlineStr"/>
-      <c r="D81" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E81" s="7" t="inlineStr"/>
-      <c r="F81" s="7" t="inlineStr"/>
-      <c r="G81" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H81" s="7" t="inlineStr"/>
-      <c r="I81" s="7" t="inlineStr"/>
-      <c r="J81" s="7" t="inlineStr"/>
-    </row>
     <row r="82">
-      <c r="A82" s="7" t="n">
-        <v>81</v>
-      </c>
-      <c r="B82" s="7" t="inlineStr">
-        <is>
-          <t>Tv et al. (2019)</t>
-        </is>
-      </c>
-      <c r="C82" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D82" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E82" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F82" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G82" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H82" s="7" t="inlineStr"/>
-      <c r="I82" s="7" t="inlineStr"/>
-      <c r="J82" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
+      <c r="A82" s="4" t="inlineStr">
+        <is>
+          <t>LEGENDA</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="7" t="n">
-        <v>82</v>
-      </c>
-      <c r="B83" s="7" t="inlineStr">
-        <is>
-          <t>Zhang et al. (2018)</t>
-        </is>
-      </c>
-      <c r="C83" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D83" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E83" s="7" t="inlineStr"/>
-      <c r="F83" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G83" s="7" t="inlineStr"/>
-      <c r="H83" s="7" t="inlineStr"/>
-      <c r="I83" s="7" t="inlineStr"/>
-      <c r="J83" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
+      <c r="A83" s="10" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>dimensi tercakup</t>
         </is>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="7" t="n">
-        <v>83</v>
-      </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>Ossai et al. (2017)</t>
-        </is>
-      </c>
-      <c r="C84" s="7" t="inlineStr"/>
-      <c r="D84" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E84" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F84" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G84" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H84" s="7" t="inlineStr"/>
-      <c r="I84" s="7" t="inlineStr"/>
-      <c r="J84" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
+      <c r="A84" s="11" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>paper acuan utama (Gao et al., 2025) — hanya sel yang dicentang</t>
         </is>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="7" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>Mi et al. (2014)</t>
-        </is>
-      </c>
-      <c r="C85" s="7" t="inlineStr"/>
-      <c r="D85" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E85" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F85" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G85" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H85" s="7" t="inlineStr"/>
-      <c r="I85" s="7" t="inlineStr"/>
-      <c r="J85" s="7" t="inlineStr"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="7" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" s="7" t="inlineStr">
-        <is>
-          <t>Ramadhan et al. (2026)</t>
-        </is>
-      </c>
-      <c r="C86" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D86" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E86" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F86" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G86" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H86" s="7" t="inlineStr"/>
-      <c r="I86" s="7" t="inlineStr"/>
-      <c r="J86" s="7" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="7" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" s="7" t="inlineStr">
-        <is>
-          <t>Zhang et al. (2026)</t>
-        </is>
-      </c>
-      <c r="C87" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D87" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E87" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F87" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G87" s="7" t="inlineStr"/>
-      <c r="H87" s="7" t="inlineStr"/>
-      <c r="I87" s="7" t="inlineStr"/>
-      <c r="J87" s="7" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="7" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" s="7" t="inlineStr">
-        <is>
-          <t>Abdelhafid et al. (2025)</t>
-        </is>
-      </c>
-      <c r="C88" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D88" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E88" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F88" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G88" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H88" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I88" s="7" t="inlineStr"/>
-      <c r="J88" s="7" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" s="7" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" s="7" t="inlineStr">
-        <is>
-          <t>Zheng et al. (2025)</t>
-        </is>
-      </c>
-      <c r="C89" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D89" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E89" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F89" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G89" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H89" s="7" t="inlineStr"/>
-      <c r="I89" s="7" t="inlineStr"/>
-      <c r="J89" s="7" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="7" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" s="7" t="inlineStr">
-        <is>
-          <t>Katibi et al. (2025)</t>
-        </is>
-      </c>
-      <c r="C90" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D90" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E90" s="7" t="inlineStr"/>
-      <c r="F90" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G90" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H90" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I90" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J90" s="7" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" s="7" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" s="7" t="inlineStr">
-        <is>
-          <t>Zahoor et al. (2025)</t>
-        </is>
-      </c>
-      <c r="C91" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D91" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E91" s="7" t="inlineStr"/>
-      <c r="F91" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G91" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H91" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I91" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J91" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="7" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" s="7" t="inlineStr">
-        <is>
-          <t>Lahlou (2025)</t>
-        </is>
-      </c>
-      <c r="C92" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D92" s="7" t="inlineStr"/>
-      <c r="E92" s="7" t="inlineStr"/>
-      <c r="F92" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G92" s="7" t="inlineStr"/>
-      <c r="H92" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I92" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J92" s="7" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" s="7" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" s="7" t="inlineStr">
-        <is>
-          <t>Ochella et al. (2024)</t>
-        </is>
-      </c>
-      <c r="C93" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D93" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E93" s="7" t="inlineStr"/>
-      <c r="F93" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G93" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H93" s="7" t="inlineStr"/>
-      <c r="I93" s="7" t="inlineStr"/>
-      <c r="J93" s="7" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="7" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> (2024)</t>
-        </is>
-      </c>
-      <c r="C94" s="7" t="inlineStr"/>
-      <c r="D94" s="7" t="inlineStr"/>
-      <c r="E94" s="7" t="inlineStr"/>
-      <c r="F94" s="7" t="inlineStr"/>
-      <c r="G94" s="7" t="inlineStr"/>
-      <c r="H94" s="7" t="inlineStr"/>
-      <c r="I94" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J94" s="7" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" s="7" t="n">
-        <v>94</v>
-      </c>
-      <c r="B95" s="7" t="inlineStr">
-        <is>
-          <t>Yang et al. (2023)</t>
-        </is>
-      </c>
-      <c r="C95" s="7" t="inlineStr"/>
-      <c r="D95" s="7" t="inlineStr"/>
-      <c r="E95" s="7" t="inlineStr"/>
-      <c r="F95" s="7" t="inlineStr"/>
-      <c r="G95" s="7" t="inlineStr"/>
-      <c r="H95" s="7" t="inlineStr"/>
-      <c r="I95" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J95" s="7" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" s="7" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" s="7" t="inlineStr">
-        <is>
-          <t>Lv et al. (2020)</t>
-        </is>
-      </c>
-      <c r="C96" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D96" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E96" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F96" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G96" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H96" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I96" s="7" t="inlineStr"/>
-      <c r="J96" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="7" t="n">
-        <v>96</v>
-      </c>
-      <c r="B97" s="7" t="inlineStr">
-        <is>
-          <t>Kiswanto et al. (2020)</t>
-        </is>
-      </c>
-      <c r="C97" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D97" s="7" t="inlineStr"/>
-      <c r="E97" s="7" t="inlineStr"/>
-      <c r="F97" s="7" t="inlineStr"/>
-      <c r="G97" s="7" t="inlineStr"/>
-      <c r="H97" s="7" t="inlineStr"/>
-      <c r="I97" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J97" s="7" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" s="7" t="n">
-        <v>97</v>
-      </c>
-      <c r="B98" s="7" t="inlineStr">
-        <is>
-          <t>Lim et al. (2019)</t>
-        </is>
-      </c>
-      <c r="C98" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D98" s="7" t="inlineStr"/>
-      <c r="E98" s="7" t="inlineStr"/>
-      <c r="F98" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G98" s="7" t="inlineStr"/>
-      <c r="H98" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I98" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J98" s="7" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" s="7" t="n">
-        <v>98</v>
-      </c>
-      <c r="B99" s="7" t="inlineStr">
-        <is>
-          <t>Wu et al. (2017)</t>
-        </is>
-      </c>
-      <c r="C99" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D99" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E99" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F99" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G99" s="7" t="inlineStr"/>
-      <c r="H99" s="7" t="inlineStr"/>
-      <c r="I99" s="7" t="inlineStr"/>
-      <c r="J99" s="7" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" s="7" t="n">
-        <v>99</v>
-      </c>
-      <c r="B100" s="7" t="inlineStr">
-        <is>
-          <t>Faisal Maulana, Andrew Starr, Agusmian Partogi Ompusunggu (2023)</t>
-        </is>
-      </c>
-      <c r="C100" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D100" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E100" s="7" t="inlineStr"/>
-      <c r="F100" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G100" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="H100" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="I100" s="7" t="inlineStr"/>
-      <c r="J100" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="7" t="n">
-        <v>100</v>
-      </c>
-      <c r="B101" s="7" t="inlineStr">
-        <is>
-          <t>Mokgadi F Bopape, Tim Van Geel, Abhishek Dutta, Bart Van Der Bruggen, Maurice Stephen Onyango (2021)</t>
-        </is>
-      </c>
-      <c r="C101" s="7" t="inlineStr"/>
-      <c r="D101" s="7" t="inlineStr"/>
-      <c r="E101" s="7" t="inlineStr"/>
-      <c r="F101" s="7" t="inlineStr"/>
-      <c r="G101" s="7" t="inlineStr"/>
-      <c r="H101" s="7" t="inlineStr"/>
-      <c r="I101" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="J101" s="7" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" s="7" t="n">
-        <v>101</v>
-      </c>
-      <c r="B102" s="7" t="inlineStr">
-        <is>
-          <t>Nannan Zhang, Lifeng Wu, Zhonghua Wang, Yong Guan (2018)</t>
-        </is>
-      </c>
-      <c r="C102" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="D102" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="E102" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="F102" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="G102" s="7" t="inlineStr"/>
-      <c r="H102" s="7" t="inlineStr"/>
-      <c r="I102" s="7" t="inlineStr"/>
-      <c r="J102" s="7" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" s="4" t="inlineStr">
-        <is>
-          <t>LEGENDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="10" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>dimensi tercakup</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="11" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>paper acuan utama (Gao et al., 2025) — hanya sel yang dicentang</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
+      <c r="A85" t="inlineStr">
         <is>
           <t>Kolom D1–D8 = dimensi konsep (lihat sheet 'Sintesis &amp; Gap Final').</t>
         </is>
@@ -9321,7 +7543,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>/ 101</t>
+          <t>/ 79</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -9337,11 +7559,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>/ 101</t>
+          <t>/ 79</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -9357,11 +7579,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>/ 101</t>
+          <t>/ 79</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -9381,7 +7603,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>/ 101</t>
+          <t>/ 79</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -9397,11 +7619,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>90</v>
+        <v>76</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>/ 101</t>
+          <t>/ 79</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -9417,11 +7639,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>/ 101</t>
+          <t>/ 79</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -9437,11 +7659,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>/ 101</t>
+          <t>/ 79</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -9457,11 +7679,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>/ 101</t>
+          <t>/ 79</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -9477,11 +7699,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>/ 101</t>
+          <t>/ 79</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -10307,20 +8529,20 @@
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Physics-informed machine learning for cross-study prediction of oil–water membrane fouling</t>
+          <t>Domain Adaptive Remaining Useful Life Prediction With Transformer</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Alves et al.</t>
+          <t>Li et al.</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
@@ -10352,24 +8574,24 @@
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Domain Adaptive Remaining Useful Life Prediction With Transformer</t>
+          <t>Reliable prediction of industrial components Remaining Useful Life using Cox and Weibull models: A Comparative Study</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Li et al.</t>
+          <t>Abdelhafid et al.</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Inti-Domain</t>
+          <t>Inti-Metode</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -10391,26 +8613,26 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>domain</t>
+          <t>metode</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n">
-        <v>54</v>
+        <v>75</v>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Reliable prediction of industrial components Remaining Useful Life using Cox and Weibull models: A Comparative Study</t>
+          <t>Forecasting remaining useful life: Interpretable deep learning approach via variational Bayesian inferences</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Abdelhafid et al.</t>
+          <t>Kraus et al.</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>2025</v>
+        <v>2019</v>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
@@ -10442,20 +8664,20 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Forecasting remaining useful life: Interpretable deep learning approach via variational Bayesian inferences</t>
+          <t>A physical knowledge-guided and data-driven framework for remaining useful life prediction (The case of turbofan engines)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Kraus et al.</t>
+          <t>Zheng et al.</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>2019</v>
+        <v>2025</v>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
@@ -10487,16 +8709,16 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>A physical knowledge-guided and data-driven framework for remaining useful life prediction (The case of turbofan engines)</t>
+          <t>A physics-informed neural network-based method for predicting degradation trajectories and remaining useful life of supercapacitors</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Zheng et al.</t>
+          <t>E et al.</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
@@ -10504,7 +8726,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
+          <t>Inti-Domain</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -10526,30 +8748,30 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>metode</t>
+          <t>domain</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>A physics-informed neural network-based method for predicting degradation trajectories and remaining useful life of supercapacitors</t>
+          <t>Weibull Variational Autoencoder for Remaining Useful Life Prediction</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>E et al.</t>
+          <t>Yu et al.</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Inti-Domain</t>
+          <t>Inti-Metode</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -10571,26 +8793,26 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>domain</t>
+          <t>metode</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Weibull Variational Autoencoder for Remaining Useful Life Prediction</t>
+          <t>Developing Deep Survival Model for Remaining Useful Life Estimation Based on Convolutional and Long Short-Term Memory Neural Networks</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Yu et al.</t>
+          <t>Chu et al.</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>2026</v>
+        <v>2020</v>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
@@ -10622,24 +8844,24 @@
     </row>
     <row r="18">
       <c r="A18" s="2" t="n">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Developing Deep Survival Model for Remaining Useful Life Estimation Based on Convolutional and Long Short-Term Memory Neural Networks</t>
+          <t>Explainable Data-Driven Method Combined with Bayesian Filtering for Remaining Useful Lifetime Prediction of Aircraft Engines Using NASA CMAPSS Datasets</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Chu et al.</t>
+          <t>Faisal Maulana, Andrew Starr, Agusmian Partogi Ompusunggu</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode</t>
+          <t>Inti-Domain</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -10661,30 +8883,30 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>metode</t>
+          <t>domain</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Explainable Data-Driven Method Combined with Bayesian Filtering for Remaining Useful Lifetime Prediction of Aircraft Engines Using NASA CMAPSS Datasets</t>
+          <t>Multisensor Time Series Forecasting-Based Augmentation Framework for Remaining Useful Life Prediction of Aero Engines</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Faisal Maulana, Andrew Starr, Agusmian Partogi Ompusunggu</t>
+          <t>Chen et al.</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Inti-Domain</t>
+          <t>Inti-Metode+Domain</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -10696,36 +8918,36 @@
         <v>2</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>5.5</v>
+        <v>4.2</v>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>domain</t>
+          <t>metode+domain (gap)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Multisensor Time Series Forecasting-Based Augmentation Framework for Remaining Useful Life Prediction of Aero Engines</t>
+          <t>Probabilistic Modeling of Li-Ion Battery Remaining Useful Life</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Chen et al.</t>
+          <t>Chiodo et al.</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>2026</v>
+        <v>2022</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
@@ -10744,59 +8966,55 @@
         <v>1</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>metode+domain (kandidat gap)</t>
+          <t>metode+domain (gap)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Probabilistic Modeling of Li-Ion Battery Remaining Useful Life</t>
+          <t>Physics-informed machine learning for cross-study prediction of oil–water membrane fouling</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Chiodo et al.</t>
+          <t>Alves et al.</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>2022</v>
+        <v>2026</v>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Inti-Metode+Domain</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>YA</t>
-        </is>
-      </c>
+          <t>Inti-Domain</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="n">
         <v>2</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0.8</v>
+        <v>2</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>3.8</v>
+        <v>5.5</v>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>metode+domain (kandidat gap)</t>
+          <t>domain</t>
         </is>
       </c>
     </row>
